--- a/import/timetable.xlsx
+++ b/import/timetable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michaelstork/Library/CloudStorage/Box-Box/Feel Festival/Marketing/03_Website/2026_timetable/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{22301117-9429-C646-B13A-142F01558545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85781D53-5B34-024D-9F14-FAD1DD4088ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-51200" yWindow="-5160" windowWidth="26540" windowHeight="28300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-51200" yWindow="-5160" windowWidth="42040" windowHeight="28300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3237" uniqueCount="715">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3238" uniqueCount="715">
   <si>
     <t>Timetable 2026</t>
   </si>
@@ -2410,18 +2410,12 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -2469,7 +2463,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2488,24 +2482,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2520,7 +2503,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2530,13 +2512,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -2740,7 +2717,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="6" customWidth="1"/>
+    <col min="2" max="2" width="18.5" customWidth="1"/>
     <col min="3" max="3" width="9" style="6" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
     <col min="5" max="6" width="18" customWidth="1"/>
@@ -2757,7 +2734,7 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="13" t="s">
         <v>679</v>
       </c>
     </row>
@@ -2768,7 +2745,7 @@
       <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="20" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="2" t="s">
@@ -3391,7 +3368,7 @@
       <c r="B22" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C22" s="13">
+      <c r="C22" s="11">
         <v>0.94791666666666663</v>
       </c>
       <c r="D22" s="5" t="s">
@@ -3606,8 +3583,8 @@
       <c r="A29" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B29" s="11">
-        <v>0.94791666666666663</v>
+      <c r="B29" s="14" t="s">
+        <v>233</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>78</v>
@@ -3848,10 +3825,10 @@
       <c r="A37" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B37" s="13">
+      <c r="B37" s="11">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="C37" s="13">
+      <c r="C37" s="11">
         <v>0.10416666666666667</v>
       </c>
       <c r="D37" s="6" t="s">
@@ -4124,7 +4101,7 @@
       <c r="A46" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B46" s="13">
+      <c r="B46" s="11">
         <v>0.10416666666666667</v>
       </c>
       <c r="C46" s="5" t="s">
@@ -4552,30 +4529,30 @@
       </c>
     </row>
     <row r="60" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="14" t="s">
+      <c r="A60" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="B60" s="15" t="s">
+      <c r="B60" s="5" t="s">
         <v>571</v>
       </c>
-      <c r="C60" s="15" t="s">
+      <c r="C60" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="D60" s="15" t="s">
+      <c r="D60" s="5" t="s">
         <v>572</v>
       </c>
-      <c r="E60" s="15"/>
-      <c r="F60" s="15" t="s">
+      <c r="E60" s="5"/>
+      <c r="F60" s="5" t="s">
         <v>573</v>
       </c>
-      <c r="G60" s="15" t="s">
+      <c r="G60" s="5" t="s">
         <v>574</v>
       </c>
-      <c r="H60" s="15"/>
-      <c r="I60" s="15" t="s">
+      <c r="H60" s="5"/>
+      <c r="I60" s="5" t="s">
         <v>575</v>
       </c>
-      <c r="J60" s="15" t="s">
+      <c r="J60" s="5" t="s">
         <v>19</v>
       </c>
       <c r="L60" s="7" t="s">
@@ -4834,7 +4811,7 @@
         <v>148</v>
       </c>
       <c r="H68" s="5"/>
-      <c r="I68" s="12" t="s">
+      <c r="I68" s="10" t="s">
         <v>149</v>
       </c>
       <c r="J68" s="5" t="s">
@@ -4868,7 +4845,7 @@
         <v>151</v>
       </c>
       <c r="H69" s="5"/>
-      <c r="I69" s="12"/>
+      <c r="I69" s="10"/>
       <c r="J69" s="5" t="s">
         <v>19</v>
       </c>
@@ -5229,10 +5206,10 @@
       <c r="A81" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B81" s="19" t="s">
+      <c r="B81" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="C81" s="19" t="s">
+      <c r="C81" s="14" t="s">
         <v>181</v>
       </c>
       <c r="D81" s="5" t="s">
@@ -5625,7 +5602,7 @@
       <c r="B93" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="C93" s="19" t="s">
+      <c r="C93" s="14" t="s">
         <v>21</v>
       </c>
       <c r="D93" s="6" t="s">
@@ -5652,7 +5629,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="94" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:13" s="23" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="5" t="s">
         <v>84</v>
       </c>
@@ -6531,30 +6508,30 @@
       </c>
     </row>
     <row r="122" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="15" t="s">
+      <c r="A122" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B122" s="15" t="s">
+      <c r="B122" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="C122" s="15" t="s">
+      <c r="C122" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="D122" s="16" t="s">
+      <c r="D122" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="E122" s="15"/>
-      <c r="F122" s="16" t="s">
+      <c r="E122" s="5"/>
+      <c r="F122" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="G122" s="15" t="s">
+      <c r="G122" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="H122" s="15"/>
-      <c r="I122" s="24" t="s">
+      <c r="H122" s="5"/>
+      <c r="I122" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="J122" s="15" t="s">
+      <c r="J122" s="5" t="s">
         <v>19</v>
       </c>
       <c r="L122" s="7" t="s">
@@ -6565,30 +6542,30 @@
       </c>
     </row>
     <row r="123" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="15" t="s">
+      <c r="A123" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B123" s="15" t="s">
+      <c r="B123" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C123" s="15" t="s">
+      <c r="C123" s="5" t="s">
         <v>45</v>
       </c>
       <c r="D123" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="E123" s="15"/>
+      <c r="E123" s="5"/>
       <c r="F123" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="G123" s="15" t="s">
+      <c r="G123" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="H123" s="15"/>
-      <c r="I123" s="15" t="s">
+      <c r="H123" s="5"/>
+      <c r="I123" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="J123" s="15" t="s">
+      <c r="J123" s="5" t="s">
         <v>19</v>
       </c>
       <c r="L123" s="7" t="s">
@@ -6702,7 +6679,7 @@
       <c r="B127" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C127" s="25" t="s">
+      <c r="C127" s="19" t="s">
         <v>236</v>
       </c>
       <c r="D127" s="6" t="s">
@@ -6731,7 +6708,7 @@
       <c r="B128" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C128" s="25" t="s">
+      <c r="C128" s="19" t="s">
         <v>236</v>
       </c>
       <c r="D128" s="6" t="s">
@@ -6760,7 +6737,7 @@
       <c r="B129" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C129" s="25" t="s">
+      <c r="C129" s="19" t="s">
         <v>236</v>
       </c>
       <c r="D129" s="6" t="s">
@@ -7012,7 +6989,7 @@
       <c r="B137" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C137" s="25" t="s">
+      <c r="C137" s="19" t="s">
         <v>251</v>
       </c>
       <c r="D137" s="6" t="s">
@@ -7041,7 +7018,7 @@
       <c r="B138" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="C138" s="25" t="s">
+      <c r="C138" s="19" t="s">
         <v>680</v>
       </c>
       <c r="D138" s="6" t="s">
@@ -7070,7 +7047,7 @@
       <c r="B139" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="C139" s="25" t="s">
+      <c r="C139" s="19" t="s">
         <v>681</v>
       </c>
       <c r="D139" s="6" t="s">
@@ -7104,7 +7081,7 @@
       <c r="B140" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="C140" s="25" t="s">
+      <c r="C140" s="19" t="s">
         <v>257</v>
       </c>
       <c r="D140" s="6" t="s">
@@ -7127,13 +7104,13 @@
       </c>
     </row>
     <row r="141" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="20" t="s">
+      <c r="A141" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="B141" s="20" t="s">
+      <c r="B141" s="15" t="s">
         <v>241</v>
       </c>
-      <c r="C141" s="27" t="s">
+      <c r="C141" s="21" t="s">
         <v>257</v>
       </c>
       <c r="D141" s="6" t="s">
@@ -7161,20 +7138,20 @@
       </c>
     </row>
     <row r="142" spans="1:13" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A142" s="14" t="s">
+      <c r="A142" s="12" t="s">
         <v>261</v>
       </c>
-      <c r="B142" s="15" t="s">
+      <c r="B142" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C142" s="15" t="s">
+      <c r="C142" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="D142" s="16" t="s">
+      <c r="D142" s="6" t="s">
         <v>262</v>
       </c>
       <c r="E142" s="9"/>
-      <c r="F142" s="23" t="s">
+      <c r="F142" s="18" t="s">
         <v>262</v>
       </c>
       <c r="G142" s="9" t="s">
@@ -7466,30 +7443,30 @@
       </c>
     </row>
     <row r="152" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A152" s="28" t="s">
+      <c r="A152" s="19" t="s">
         <v>261</v>
       </c>
-      <c r="B152" s="15" t="s">
+      <c r="B152" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C152" s="15" t="s">
+      <c r="C152" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="D152" s="15" t="s">
+      <c r="D152" s="5" t="s">
         <v>616</v>
       </c>
-      <c r="E152" s="15"/>
-      <c r="F152" s="15" t="s">
+      <c r="E152" s="5"/>
+      <c r="F152" s="5" t="s">
         <v>616</v>
       </c>
-      <c r="G152" s="15" t="s">
+      <c r="G152" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="H152" s="15"/>
-      <c r="I152" s="15" t="s">
+      <c r="H152" s="5"/>
+      <c r="I152" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="J152" s="15" t="s">
+      <c r="J152" s="5" t="s">
         <v>19</v>
       </c>
       <c r="L152" s="7" t="s">
@@ -8506,10 +8483,10 @@
       <c r="A185" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="B185" s="19" t="s">
+      <c r="B185" s="14" t="s">
         <v>576</v>
       </c>
-      <c r="C185" s="19" t="s">
+      <c r="C185" s="14" t="s">
         <v>628</v>
       </c>
       <c r="D185" s="5" t="s">
@@ -9649,28 +9626,28 @@
       </c>
     </row>
     <row r="221" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A221" s="15" t="s">
+      <c r="A221" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="B221" s="15" t="s">
+      <c r="B221" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C221" s="15" t="s">
+      <c r="C221" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D221" s="16" t="s">
+      <c r="D221" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="E221" s="15"/>
-      <c r="F221" s="16" t="s">
+      <c r="E221" s="5"/>
+      <c r="F221" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="G221" s="15" t="s">
+      <c r="G221" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H221" s="15"/>
-      <c r="I221" s="15"/>
-      <c r="J221" s="15" t="s">
+      <c r="H221" s="5"/>
+      <c r="I221" s="5"/>
+      <c r="J221" s="5" t="s">
         <v>19</v>
       </c>
       <c r="L221" s="7" t="s">
@@ -10250,28 +10227,28 @@
       </c>
     </row>
     <row r="240" spans="1:13" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A240" s="15" t="s">
+      <c r="A240" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="B240" s="15" t="s">
+      <c r="B240" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C240" s="15" t="s">
+      <c r="C240" s="5" t="s">
         <v>390</v>
       </c>
       <c r="D240" s="6" t="s">
         <v>391</v>
       </c>
-      <c r="E240" s="15"/>
+      <c r="E240" s="5"/>
       <c r="F240" s="6" t="s">
         <v>391</v>
       </c>
-      <c r="G240" s="15" t="s">
+      <c r="G240" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="H240" s="15"/>
+      <c r="H240" s="5"/>
       <c r="I240" s="5"/>
-      <c r="J240" s="15" t="s">
+      <c r="J240" s="5" t="s">
         <v>19</v>
       </c>
       <c r="L240" s="7" t="s">
@@ -10605,7 +10582,7 @@
       <c r="B251" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C251" s="25" t="s">
+      <c r="C251" s="19" t="s">
         <v>408</v>
       </c>
       <c r="D251" s="6" t="s">
@@ -10720,7 +10697,7 @@
       <c r="B255" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C255" s="25" t="s">
+      <c r="C255" s="19" t="s">
         <v>408</v>
       </c>
       <c r="D255" s="6" t="s">
@@ -10812,7 +10789,7 @@
       <c r="B258" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C258" s="25" t="s">
+      <c r="C258" s="19" t="s">
         <v>398</v>
       </c>
       <c r="D258" s="6" t="s">
@@ -10840,19 +10817,19 @@
       </c>
     </row>
     <row r="259" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A259" s="20" t="s">
+      <c r="A259" s="15" t="s">
         <v>261</v>
       </c>
-      <c r="B259" s="20" t="s">
+      <c r="B259" s="15" t="s">
         <v>253</v>
       </c>
-      <c r="C259" s="27" t="s">
+      <c r="C259" s="21" t="s">
         <v>408</v>
       </c>
-      <c r="D259" s="16" t="s">
+      <c r="D259" s="6" t="s">
         <v>423</v>
       </c>
-      <c r="E259" s="20"/>
+      <c r="E259" s="15"/>
       <c r="F259" s="6" t="s">
         <v>423</v>
       </c>
@@ -10866,7 +10843,6 @@
       <c r="J259" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="K259" s="17"/>
       <c r="L259" s="7" t="s">
         <v>68</v>
       </c>
@@ -10875,31 +10851,30 @@
       </c>
     </row>
     <row r="260" spans="1:13" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A260" s="14" t="s">
+      <c r="A260" s="12" t="s">
         <v>425</v>
       </c>
-      <c r="B260" s="15" t="s">
+      <c r="B260" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C260" s="30" t="s">
+      <c r="C260" s="14" t="s">
         <v>86</v>
       </c>
       <c r="D260" s="6" t="s">
         <v>426</v>
       </c>
       <c r="E260" s="9"/>
-      <c r="F260" s="23" t="s">
+      <c r="F260" s="18" t="s">
         <v>426</v>
       </c>
       <c r="G260" s="9" t="s">
         <v>37</v>
       </c>
       <c r="H260" s="9"/>
-      <c r="I260" s="29"/>
+      <c r="I260" s="22"/>
       <c r="J260" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="K260" s="17"/>
       <c r="L260" s="7" t="s">
         <v>20</v>
       </c>
@@ -12126,30 +12101,30 @@
       </c>
     </row>
     <row r="300" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A300" s="15" t="s">
+      <c r="A300" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="B300" s="15" t="s">
+      <c r="B300" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="C300" s="15" t="s">
+      <c r="C300" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="D300" s="15" t="s">
+      <c r="D300" s="5" t="s">
         <v>659</v>
       </c>
-      <c r="E300" s="15"/>
-      <c r="F300" s="15" t="s">
+      <c r="E300" s="5"/>
+      <c r="F300" s="5" t="s">
         <v>660</v>
       </c>
-      <c r="G300" s="15" t="s">
+      <c r="G300" s="5" t="s">
         <v>582</v>
       </c>
-      <c r="H300" s="15"/>
-      <c r="I300" s="15" t="s">
+      <c r="H300" s="5"/>
+      <c r="I300" s="5" t="s">
         <v>661</v>
       </c>
-      <c r="J300" s="15" t="s">
+      <c r="J300" s="5" t="s">
         <v>19</v>
       </c>
       <c r="L300" s="7" t="s">
@@ -12160,30 +12135,30 @@
       </c>
     </row>
     <row r="301" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A301" s="15" t="s">
+      <c r="A301" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="B301" s="15" t="s">
+      <c r="B301" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="C301" s="15" t="s">
+      <c r="C301" s="5" t="s">
         <v>140</v>
       </c>
       <c r="D301" s="6" t="s">
         <v>488</v>
       </c>
-      <c r="E301" s="15"/>
+      <c r="E301" s="5"/>
       <c r="F301" s="6" t="s">
         <v>488</v>
       </c>
-      <c r="G301" s="15" t="s">
+      <c r="G301" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="H301" s="15"/>
-      <c r="I301" s="17" t="s">
+      <c r="H301" s="5"/>
+      <c r="I301" t="s">
         <v>489</v>
       </c>
-      <c r="J301" s="15" t="s">
+      <c r="J301" s="5" t="s">
         <v>19</v>
       </c>
       <c r="L301" s="7" t="s">
@@ -12194,28 +12169,28 @@
       </c>
     </row>
     <row r="302" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A302" s="15" t="s">
+      <c r="A302" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="B302" s="15" t="s">
+      <c r="B302" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="C302" s="15" t="s">
+      <c r="C302" s="5" t="s">
         <v>143</v>
       </c>
       <c r="D302" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E302" s="15"/>
+      <c r="E302" s="5"/>
       <c r="F302" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G302" s="15" t="s">
+      <c r="G302" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H302" s="15"/>
-      <c r="I302" s="15"/>
-      <c r="J302" s="15" t="s">
+      <c r="H302" s="5"/>
+      <c r="I302" s="5"/>
+      <c r="J302" s="5" t="s">
         <v>19</v>
       </c>
       <c r="L302" s="7" t="s">
@@ -12289,10 +12264,10 @@
       <c r="A305" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="B305" s="19" t="s">
+      <c r="B305" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="C305" s="19" t="s">
+      <c r="C305" s="14" t="s">
         <v>146</v>
       </c>
       <c r="D305" s="5" t="s">
@@ -12606,28 +12581,28 @@
       </c>
     </row>
     <row r="315" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A315" s="15" t="s">
+      <c r="A315" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="B315" s="15" t="s">
+      <c r="B315" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="C315" s="15" t="s">
+      <c r="C315" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D315" s="16" t="s">
+      <c r="D315" s="6" t="s">
         <v>500</v>
       </c>
-      <c r="E315" s="15"/>
-      <c r="F315" s="16" t="s">
+      <c r="E315" s="5"/>
+      <c r="F315" s="6" t="s">
         <v>500</v>
       </c>
-      <c r="G315" s="15" t="s">
+      <c r="G315" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="H315" s="15"/>
-      <c r="I315" s="15"/>
-      <c r="J315" s="15" t="s">
+      <c r="H315" s="5"/>
+      <c r="I315" s="5"/>
+      <c r="J315" s="5" t="s">
         <v>19</v>
       </c>
       <c r="L315" s="7" t="s">
@@ -12635,28 +12610,28 @@
       </c>
     </row>
     <row r="316" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A316" s="15" t="s">
+      <c r="A316" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="B316" s="15" t="s">
+      <c r="B316" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C316" s="15" t="s">
+      <c r="C316" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D316" s="16" t="s">
+      <c r="D316" s="6" t="s">
         <v>501</v>
       </c>
-      <c r="E316" s="15"/>
-      <c r="F316" s="16" t="s">
+      <c r="E316" s="5"/>
+      <c r="F316" s="6" t="s">
         <v>501</v>
       </c>
-      <c r="G316" s="15" t="s">
+      <c r="G316" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="H316" s="15"/>
-      <c r="I316" s="15"/>
-      <c r="J316" s="15" t="s">
+      <c r="H316" s="5"/>
+      <c r="I316" s="5"/>
+      <c r="J316" s="5" t="s">
         <v>19</v>
       </c>
       <c r="L316" s="7" t="s">
@@ -12853,30 +12828,30 @@
       </c>
     </row>
     <row r="323" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A323" s="15" t="s">
+      <c r="A323" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="B323" s="15" t="s">
+      <c r="B323" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="C323" s="15" t="s">
+      <c r="C323" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D323" s="16" t="s">
+      <c r="D323" s="6" t="s">
         <v>509</v>
       </c>
-      <c r="E323" s="15"/>
-      <c r="F323" s="16" t="s">
+      <c r="E323" s="5"/>
+      <c r="F323" s="6" t="s">
         <v>509</v>
       </c>
-      <c r="G323" s="15" t="s">
+      <c r="G323" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H323" s="15"/>
-      <c r="I323" s="17" t="s">
+      <c r="H323" s="5"/>
+      <c r="I323" t="s">
         <v>510</v>
       </c>
-      <c r="J323" s="15" t="s">
+      <c r="J323" s="5" t="s">
         <v>19</v>
       </c>
       <c r="L323" s="7" t="s">
@@ -13207,28 +13182,28 @@
       </c>
     </row>
     <row r="334" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A334" s="15" t="s">
+      <c r="A334" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="B334" s="15" t="s">
+      <c r="B334" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C334" s="15" t="s">
+      <c r="C334" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D334" s="16" t="s">
+      <c r="D334" s="6" t="s">
         <v>525</v>
       </c>
-      <c r="E334" s="15"/>
-      <c r="F334" s="16" t="s">
+      <c r="E334" s="5"/>
+      <c r="F334" s="6" t="s">
         <v>525</v>
       </c>
-      <c r="G334" s="15" t="s">
+      <c r="G334" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="H334" s="15"/>
-      <c r="I334" s="15"/>
-      <c r="J334" s="15" t="s">
+      <c r="H334" s="5"/>
+      <c r="I334" s="5"/>
+      <c r="J334" s="5" t="s">
         <v>19</v>
       </c>
       <c r="L334" s="7" t="s">
@@ -13236,30 +13211,30 @@
       </c>
     </row>
     <row r="335" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A335" s="15" t="s">
+      <c r="A335" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="B335" s="15" t="s">
+      <c r="B335" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C335" s="15" t="s">
+      <c r="C335" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D335" s="16" t="s">
+      <c r="D335" s="6" t="s">
         <v>526</v>
       </c>
-      <c r="E335" s="15"/>
-      <c r="F335" s="16" t="s">
+      <c r="E335" s="5"/>
+      <c r="F335" s="6" t="s">
         <v>526</v>
       </c>
-      <c r="G335" s="15" t="s">
+      <c r="G335" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H335" s="15"/>
-      <c r="I335" s="17" t="s">
+      <c r="H335" s="5"/>
+      <c r="I335" t="s">
         <v>527</v>
       </c>
-      <c r="J335" s="15" t="s">
+      <c r="J335" s="5" t="s">
         <v>19</v>
       </c>
       <c r="L335" s="7" t="s">
@@ -13493,28 +13468,28 @@
       </c>
     </row>
     <row r="343" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A343" s="15" t="s">
+      <c r="A343" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="B343" s="15" t="s">
+      <c r="B343" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C343" s="15" t="s">
+      <c r="C343" s="5" t="s">
         <v>532</v>
       </c>
-      <c r="D343" s="16" t="s">
+      <c r="D343" s="6" t="s">
         <v>540</v>
       </c>
-      <c r="E343" s="15"/>
-      <c r="F343" s="16" t="s">
+      <c r="E343" s="5"/>
+      <c r="F343" s="6" t="s">
         <v>540</v>
       </c>
-      <c r="G343" s="15" t="s">
+      <c r="G343" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H343" s="15"/>
-      <c r="I343" s="15"/>
-      <c r="J343" s="15" t="s">
+      <c r="H343" s="5"/>
+      <c r="I343" s="5"/>
+      <c r="J343" s="5" t="s">
         <v>19</v>
       </c>
       <c r="L343" s="7" t="s">
@@ -13614,30 +13589,30 @@
       </c>
     </row>
     <row r="347" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A347" s="20" t="s">
+      <c r="A347" s="15" t="s">
         <v>425</v>
       </c>
-      <c r="B347" s="20" t="s">
+      <c r="B347" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C347" s="20" t="s">
+      <c r="C347" s="15" t="s">
         <v>547</v>
       </c>
-      <c r="D347" s="22" t="s">
+      <c r="D347" s="17" t="s">
         <v>548</v>
       </c>
-      <c r="E347" s="20"/>
-      <c r="F347" s="22" t="s">
+      <c r="E347" s="15"/>
+      <c r="F347" s="17" t="s">
         <v>548</v>
       </c>
-      <c r="G347" s="20" t="s">
+      <c r="G347" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H347" s="20"/>
-      <c r="I347" s="21" t="s">
+      <c r="H347" s="15"/>
+      <c r="I347" s="16" t="s">
         <v>549</v>
       </c>
-      <c r="J347" s="20" t="s">
+      <c r="J347" s="15" t="s">
         <v>19</v>
       </c>
       <c r="L347" s="7" t="s">
@@ -13648,28 +13623,28 @@
       </c>
     </row>
     <row r="348" spans="1:13" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A348" s="14" t="s">
+      <c r="A348" s="12" t="s">
         <v>550</v>
       </c>
-      <c r="B348" s="15" t="s">
+      <c r="B348" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C348" s="15" t="s">
+      <c r="C348" s="5" t="s">
         <v>86</v>
       </c>
       <c r="D348" s="6" t="s">
         <v>551</v>
       </c>
-      <c r="E348" s="15"/>
+      <c r="E348" s="5"/>
       <c r="F348" s="6" t="s">
         <v>551</v>
       </c>
-      <c r="G348" s="15" t="s">
+      <c r="G348" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H348" s="15"/>
-      <c r="I348" s="15"/>
-      <c r="J348" s="15" t="s">
+      <c r="H348" s="5"/>
+      <c r="I348" s="5"/>
+      <c r="J348" s="5" t="s">
         <v>19</v>
       </c>
       <c r="L348" s="7" t="s">
@@ -13827,30 +13802,30 @@
       </c>
     </row>
     <row r="354" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A354" s="15" t="s">
+      <c r="A354" s="5" t="s">
         <v>550</v>
       </c>
-      <c r="B354" s="15" t="s">
+      <c r="B354" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="C354" s="15" t="s">
+      <c r="C354" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="D354" s="16" t="s">
+      <c r="D354" s="6" t="s">
         <v>558</v>
       </c>
-      <c r="E354" s="15"/>
-      <c r="F354" s="16" t="s">
+      <c r="E354" s="5"/>
+      <c r="F354" s="6" t="s">
         <v>558</v>
       </c>
-      <c r="G354" s="15" t="s">
+      <c r="G354" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="H354" s="15"/>
-      <c r="I354" s="17" t="s">
+      <c r="H354" s="5"/>
+      <c r="I354" t="s">
         <v>559</v>
       </c>
-      <c r="J354" s="15" t="s">
+      <c r="J354" s="5" t="s">
         <v>19</v>
       </c>
       <c r="L354" s="7" t="s">
@@ -13861,30 +13836,30 @@
       </c>
     </row>
     <row r="355" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A355" s="15" t="s">
+      <c r="A355" s="5" t="s">
         <v>550</v>
       </c>
-      <c r="B355" s="15" t="s">
+      <c r="B355" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="C355" s="15" t="s">
+      <c r="C355" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D355" s="16" t="s">
+      <c r="D355" s="6" t="s">
         <v>560</v>
       </c>
-      <c r="E355" s="15"/>
-      <c r="F355" s="16" t="s">
+      <c r="E355" s="5"/>
+      <c r="F355" s="6" t="s">
         <v>560</v>
       </c>
-      <c r="G355" s="15" t="s">
+      <c r="G355" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="H355" s="15"/>
-      <c r="I355" s="17" t="s">
+      <c r="H355" s="5"/>
+      <c r="I355" t="s">
         <v>561</v>
       </c>
-      <c r="J355" s="15" t="s">
+      <c r="J355" s="5" t="s">
         <v>19</v>
       </c>
       <c r="L355" s="7" t="s">

--- a/import/timetable.xlsx
+++ b/import/timetable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michaelstork/Library/CloudStorage/Box-Box/Feel Festival/Marketing/03_Website/2026_timetable/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85781D53-5B34-024D-9F14-FAD1DD4088ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3207C9F-3800-A64B-8466-3DC814FFFBBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-51200" yWindow="-5160" windowWidth="42040" windowHeight="28300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3238" uniqueCount="715">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3240" uniqueCount="715">
   <si>
     <t>Timetable 2026</t>
   </si>
@@ -2463,7 +2463,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2513,7 +2513,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -3825,8 +3833,8 @@
       <c r="A37" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B37" s="11">
-        <v>4.1666666666666664E-2</v>
+      <c r="B37" s="23" t="s">
+        <v>96</v>
       </c>
       <c r="C37" s="11">
         <v>0.10416666666666667</v>
@@ -3859,7 +3867,7 @@
       <c r="A38" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="24" t="s">
         <v>96</v>
       </c>
       <c r="C38" s="5" t="s">
@@ -4097,24 +4105,24 @@
         <v>20</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="5" t="s">
+    <row r="46" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="B46" s="11">
-        <v>0.10416666666666667</v>
-      </c>
-      <c r="C46" s="5" t="s">
+      <c r="B46" s="23" t="s">
+        <v>274</v>
+      </c>
+      <c r="C46" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="D46" s="6" t="s">
+      <c r="D46" s="25" t="s">
         <v>103</v>
       </c>
       <c r="E46" s="5"/>
-      <c r="F46" s="6" t="s">
+      <c r="F46" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="G46" s="5" t="s">
+      <c r="G46" s="19" t="s">
         <v>47</v>
       </c>
       <c r="H46" s="5"/>
@@ -5629,7 +5637,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="94" spans="1:13" s="23" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="5" t="s">
         <v>84</v>
       </c>
@@ -5656,7 +5664,6 @@
       <c r="J94" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="K94"/>
       <c r="L94" s="7" t="s">
         <v>161</v>
       </c>

--- a/import/timetable.xlsx
+++ b/import/timetable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michaelstork/Library/CloudStorage/Box-Box/Feel Festival/Marketing/03_Website/2026_timetable/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26678501-1BA7-0E4E-AE0D-CC8648E3689C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D914C116-DF04-1149-8A62-C2D5C1BE1372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2083,9 +2083,6 @@
     <t>Die Sonne glitzert auf dem See, der Bass wummert noch nach, der Körper will sanft landen. Unser Massage-Workshop lädt ein, von Party in Entspannung zu wechseln: niederschwellig, achtsam, von Freundinnen für Freundinnen. Selbst- und Partner*innenmassage für Festival-Hotspots: Nacken, Kopf, Hände, mit Fokus auf Consent und Grenzen. Kommt allein oder als Gruppe. Bitte Handtücher mitbringen :)</t>
   </si>
   <si>
-    <t>Stand: 22.07.2026 10:51</t>
-  </si>
-  <si>
     <t>00:15 
 (25.07.)</t>
   </si>
@@ -2223,6 +2220,9 @@
   </si>
   <si>
     <t>Sova embarked on his musical journey in 215 with the purchase of his first turntables. Since then, he has been organizing events in Dresden—initially with DDAC—where his own series "Pluto" had its inception. Since 219, Sova has been a part of Palais Palett and objekt klein a, where he not only continues the series but also began his residency amidst various other projects.</t>
+  </si>
+  <si>
+    <t>Stand: 22.07.2026 20:42</t>
   </si>
 </sst>
 </file>
@@ -2628,7 +2628,7 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>646</v>
+        <v>679</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -2797,7 +2797,7 @@
         <v>20</v>
       </c>
       <c r="M7" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3385,7 +3385,7 @@
         <v>20</v>
       </c>
       <c r="M25" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -4415,7 +4415,7 @@
         <v>20</v>
       </c>
       <c r="M58" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -5391,7 +5391,7 @@
         <v>20</v>
       </c>
       <c r="M88" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="89" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5459,7 +5459,7 @@
         <v>20</v>
       </c>
       <c r="M90" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="91" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6543,7 +6543,7 @@
         <v>20</v>
       </c>
       <c r="M124" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="125" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.2">
@@ -6772,7 +6772,7 @@
         <v>253</v>
       </c>
       <c r="C132" s="18" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D132" s="5" t="s">
         <v>254</v>
@@ -6802,7 +6802,7 @@
         <v>253</v>
       </c>
       <c r="C133" s="18" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D133" s="5" t="s">
         <v>255</v>
@@ -6983,7 +6983,7 @@
         <v>20</v>
       </c>
       <c r="M138" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="139" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7047,7 +7047,7 @@
         <v>20</v>
       </c>
       <c r="M140" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="141" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7355,7 +7355,7 @@
         <v>20</v>
       </c>
       <c r="M150" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="151" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7423,7 +7423,7 @@
         <v>20</v>
       </c>
       <c r="M152" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="153" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8187,7 +8187,7 @@
         <v>161</v>
       </c>
       <c r="M176" s="5" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="177" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -8281,7 +8281,7 @@
         <v>20</v>
       </c>
       <c r="M179" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="180" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8539,7 +8539,7 @@
         <v>161</v>
       </c>
       <c r="M187" s="5" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="188" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8573,7 +8573,7 @@
         <v>20</v>
       </c>
       <c r="M188" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="189" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -8758,7 +8758,7 @@
         <v>161</v>
       </c>
       <c r="M194" s="4" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="195" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -8826,7 +8826,7 @@
         <v>161</v>
       </c>
       <c r="M196" s="5" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="197" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8960,7 +8960,7 @@
         <v>20</v>
       </c>
       <c r="M200" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="201" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -9344,7 +9344,7 @@
         <v>20</v>
       </c>
       <c r="M212" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="213" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9660,7 +9660,7 @@
         <v>20</v>
       </c>
       <c r="M222" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="223" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9694,7 +9694,7 @@
         <v>20</v>
       </c>
       <c r="M223" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="224" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9886,7 +9886,7 @@
         <v>68</v>
       </c>
       <c r="M229" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="230" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9980,7 +9980,7 @@
         <v>161</v>
       </c>
       <c r="M232" s="4" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="233" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -10014,7 +10014,7 @@
         <v>20</v>
       </c>
       <c r="M233" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="234" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -10078,7 +10078,7 @@
         <v>68</v>
       </c>
       <c r="M235" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="236" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -11018,7 +11018,7 @@
         <v>20</v>
       </c>
       <c r="M265" s="25" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="266" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -11116,7 +11116,7 @@
         <v>20</v>
       </c>
       <c r="M268" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="269" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -11244,7 +11244,7 @@
         <v>20</v>
       </c>
       <c r="M272" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="273" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -12331,7 +12331,7 @@
         <v>20</v>
       </c>
       <c r="M306" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="307" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -12915,7 +12915,7 @@
         <v>20</v>
       </c>
       <c r="M324" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="325" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -13043,7 +13043,7 @@
         <v>20</v>
       </c>
       <c r="M328" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="329" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -13355,7 +13355,7 @@
         <v>20</v>
       </c>
       <c r="M338" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="339" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -13607,7 +13607,6 @@
       <c r="M346"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M346" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A247:M331">
     <sortCondition ref="B247:B331"/>
   </sortState>

--- a/import/timetable.xlsx
+++ b/import/timetable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michaelstork/Library/CloudStorage/Box-Box/Feel Festival/Marketing/03_Website/2026_timetable/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E518979-976F-CC42-93E4-1741F42D8FCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31A959D0-A685-0D40-BD38-7971F661195B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3046" uniqueCount="673">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3046" uniqueCount="672">
   <si>
     <t>Timetable 2026</t>
   </si>
@@ -530,9 +530,6 @@
   </si>
   <si>
     <t>13:30</t>
-  </si>
-  <si>
-    <t>How to Kommunalpolotik</t>
   </si>
   <si>
     <t>How to Kommunalpolitik</t>
@@ -1558,9 +1555,6 @@
     <t>ATTA B2B CHRISTA K</t>
   </si>
   <si>
-    <t>LUCID TRAILS</t>
-  </si>
-  <si>
     <t>Der Sound von Lucid Trails lässt sich als experimentellen dark pop bezeichnen. Das Berliner Duo zeichnet sich durch eine selbstverständliche Offenheit für Genregrenzen aus, getragen von analogen Synths und und poetischen Texten. Von Ambient bis Trance entfalten ihre Lieder emotionale Landschaften voller Brüche, Wandel und Widerstand.</t>
   </si>
   <si>
@@ -2065,9 +2059,6 @@
     <t>EM.ÆVI</t>
   </si>
   <si>
-    <t>JÖRDIIS B2B FREHSAX</t>
-  </si>
-  <si>
     <t>FIRST GRADERS</t>
   </si>
   <si>
@@ -2189,6 +2180,12 @@
   </si>
   <si>
     <t>KID SIMIUS</t>
+  </si>
+  <si>
+    <t>LUCIDTRAILS</t>
+  </si>
+  <si>
+    <t>JÖRDIIS B2B FRESHSAX</t>
   </si>
 </sst>
 </file>
@@ -4610,19 +4607,19 @@
       <c r="C65" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="D65" s="4" t="s">
+      <c r="D65" s="17" t="s">
         <v>161</v>
       </c>
       <c r="E65" s="4"/>
       <c r="F65" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="G65" s="4" t="s">
         <v>162</v>
-      </c>
-      <c r="G65" s="4" t="s">
-        <v>163</v>
       </c>
       <c r="H65" s="4"/>
       <c r="I65" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J65" s="4" t="s">
         <v>20</v>
@@ -4631,7 +4628,7 @@
         <v>149</v>
       </c>
       <c r="M65" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -4645,18 +4642,18 @@
         <v>160</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E66" s="4"/>
       <c r="F66" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G66" s="4" t="s">
         <v>152</v>
       </c>
       <c r="H66" s="4"/>
       <c r="I66" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J66" s="4" t="s">
         <v>20</v>
@@ -4665,7 +4662,7 @@
         <v>149</v>
       </c>
       <c r="M66" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="67" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -4676,14 +4673,14 @@
         <v>154</v>
       </c>
       <c r="C67" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D67" s="5" t="s">
         <v>167</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>168</v>
       </c>
       <c r="E67" s="4"/>
       <c r="F67" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G67" s="4" t="s">
         <v>56</v>
@@ -4706,21 +4703,21 @@
         <v>154</v>
       </c>
       <c r="C68" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D68" s="4" t="s">
         <v>169</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>170</v>
       </c>
       <c r="E68" s="4"/>
       <c r="F68" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="G68" s="4" t="s">
         <v>170</v>
-      </c>
-      <c r="G68" s="4" t="s">
-        <v>171</v>
       </c>
       <c r="H68" s="4"/>
       <c r="I68" s="26" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J68" s="4" t="s">
         <v>20</v>
@@ -4729,7 +4726,7 @@
         <v>149</v>
       </c>
       <c r="M68" s="24" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="69" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -4740,17 +4737,17 @@
         <v>154</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E69" s="4"/>
       <c r="F69" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="G69" s="4" t="s">
         <v>173</v>
-      </c>
-      <c r="G69" s="4" t="s">
-        <v>174</v>
       </c>
       <c r="H69" s="4"/>
       <c r="I69" s="9"/>
@@ -4773,11 +4770,11 @@
         <v>16</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E70" s="4"/>
       <c r="F70" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G70" s="4" t="s">
         <v>39</v>
@@ -4803,11 +4800,11 @@
         <v>16</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E71" s="4"/>
       <c r="F71" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G71" s="4" t="s">
         <v>28</v>
@@ -4833,11 +4830,11 @@
         <v>16</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E72" s="4"/>
       <c r="F72" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G72" s="4" t="s">
         <v>31</v>
@@ -4863,18 +4860,18 @@
         <v>16</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E73" s="4"/>
       <c r="F73" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G73" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H73" s="4"/>
       <c r="I73" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J73" s="4" t="s">
         <v>20</v>
@@ -4883,7 +4880,7 @@
         <v>21</v>
       </c>
       <c r="M73" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="74" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -4897,18 +4894,18 @@
         <v>16</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E74" s="4"/>
       <c r="F74" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H74" s="4"/>
       <c r="I74" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J74" s="4" t="s">
         <v>20</v>
@@ -4917,7 +4914,7 @@
         <v>149</v>
       </c>
       <c r="M74" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="75" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -4928,21 +4925,21 @@
         <v>144</v>
       </c>
       <c r="C75" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D75" s="4" t="s">
         <v>182</v>
-      </c>
-      <c r="D75" s="4" t="s">
-        <v>183</v>
       </c>
       <c r="E75" s="4"/>
       <c r="F75" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G75" s="4" t="s">
         <v>152</v>
       </c>
       <c r="H75" s="4"/>
       <c r="I75" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J75" s="4" t="s">
         <v>20</v>
@@ -4951,7 +4948,7 @@
         <v>149</v>
       </c>
       <c r="M75" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="76" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -4959,24 +4956,24 @@
         <v>88</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>159</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E76" s="4"/>
       <c r="F76" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G76" s="4" t="s">
         <v>147</v>
       </c>
       <c r="H76" s="4"/>
       <c r="I76" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J76" s="4" t="s">
         <v>20</v>
@@ -4985,7 +4982,7 @@
         <v>149</v>
       </c>
       <c r="M76" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="77" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -4993,17 +4990,17 @@
         <v>88</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C77" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D77" s="5" t="s">
         <v>188</v>
-      </c>
-      <c r="D77" s="5" t="s">
-        <v>189</v>
       </c>
       <c r="E77" s="4"/>
       <c r="F77" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G77" s="4" t="s">
         <v>56</v>
@@ -5023,24 +5020,24 @@
         <v>88</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E78" s="4"/>
       <c r="F78" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H78" s="4"/>
       <c r="I78" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J78" s="4" t="s">
         <v>20</v>
@@ -5049,7 +5046,7 @@
         <v>149</v>
       </c>
       <c r="M78" s="24" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="79" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5057,24 +5054,24 @@
         <v>88</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E79" s="4"/>
       <c r="F79" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H79" s="4"/>
       <c r="I79" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J79" s="4" t="s">
         <v>20</v>
@@ -5083,7 +5080,7 @@
         <v>149</v>
       </c>
       <c r="M79" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="80" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5091,20 +5088,20 @@
         <v>88</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E80" s="4"/>
       <c r="F80" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="G80" s="4" t="s">
         <v>194</v>
-      </c>
-      <c r="G80" s="4" t="s">
-        <v>195</v>
       </c>
       <c r="H80" s="4"/>
       <c r="I80" s="4"/>
@@ -5127,11 +5124,11 @@
         <v>22</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E81" s="4"/>
       <c r="F81" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G81" s="4" t="s">
         <v>39</v>
@@ -5157,18 +5154,18 @@
         <v>22</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E82" s="4"/>
       <c r="F82" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G82" s="4" t="s">
         <v>28</v>
       </c>
       <c r="H82" s="4"/>
       <c r="I82" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J82" s="4" t="s">
         <v>20</v>
@@ -5177,7 +5174,7 @@
         <v>21</v>
       </c>
       <c r="M82" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -5191,11 +5188,11 @@
         <v>22</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E83" s="4"/>
       <c r="F83" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G83" s="4" t="s">
         <v>31</v>
@@ -5221,18 +5218,18 @@
         <v>22</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E84" s="4"/>
       <c r="F84" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G84" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H84" s="4"/>
       <c r="I84" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J84" s="4" t="s">
         <v>20</v>
@@ -5241,7 +5238,7 @@
         <v>21</v>
       </c>
       <c r="M84" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -5252,21 +5249,21 @@
         <v>16</v>
       </c>
       <c r="C85" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="D85" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>203</v>
       </c>
       <c r="E85" s="4"/>
       <c r="F85" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G85" s="4" t="s">
         <v>152</v>
       </c>
       <c r="H85" s="4"/>
       <c r="I85" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J85" s="4" t="s">
         <v>20</v>
@@ -5275,7 +5272,7 @@
         <v>149</v>
       </c>
       <c r="M85" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5286,21 +5283,21 @@
         <v>159</v>
       </c>
       <c r="C86" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="D86" s="5" t="s">
         <v>205</v>
-      </c>
-      <c r="D86" s="5" t="s">
-        <v>206</v>
       </c>
       <c r="E86" s="4"/>
       <c r="F86" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H86" s="4"/>
       <c r="I86" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J86" s="4" t="s">
         <v>20</v>
@@ -5309,7 +5306,7 @@
         <v>71</v>
       </c>
       <c r="M86" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="87" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5323,27 +5320,27 @@
         <v>22</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E87" s="4"/>
       <c r="F87" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G87" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H87" s="4"/>
       <c r="I87" t="s">
+        <v>208</v>
+      </c>
+      <c r="J87" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L87" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M87" t="s">
         <v>209</v>
-      </c>
-      <c r="J87" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L87" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M87" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="88" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5354,21 +5351,21 @@
         <v>159</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E88" s="4"/>
       <c r="F88" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H88" s="4"/>
       <c r="I88" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J88" s="4" t="s">
         <v>20</v>
@@ -5377,7 +5374,7 @@
         <v>149</v>
       </c>
       <c r="M88" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="89" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5385,33 +5382,33 @@
         <v>88</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>17</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E89" s="4"/>
       <c r="F89" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G89" s="4" t="s">
         <v>56</v>
       </c>
       <c r="H89" s="4"/>
       <c r="I89" t="s">
+        <v>213</v>
+      </c>
+      <c r="J89" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L89" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M89" t="s">
         <v>214</v>
-      </c>
-      <c r="J89" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L89" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M89" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="90" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5419,24 +5416,24 @@
         <v>88</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C90" s="12" t="s">
         <v>22</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E90" s="4"/>
       <c r="F90" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H90" s="4"/>
       <c r="I90" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J90" s="4" t="s">
         <v>20</v>
@@ -5445,7 +5442,7 @@
         <v>149</v>
       </c>
       <c r="M90" s="24" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="91" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5453,20 +5450,20 @@
         <v>88</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C91" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="D91" s="5" t="s">
         <v>218</v>
-      </c>
-      <c r="D91" s="5" t="s">
-        <v>219</v>
       </c>
       <c r="E91" s="4"/>
       <c r="F91" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H91" s="4"/>
       <c r="I91" s="4"/>
@@ -5486,14 +5483,14 @@
         <v>22</v>
       </c>
       <c r="C92" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="D92" s="5" t="s">
         <v>220</v>
-      </c>
-      <c r="D92" s="5" t="s">
-        <v>221</v>
       </c>
       <c r="E92" s="4"/>
       <c r="F92" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G92" s="4" t="s">
         <v>49</v>
@@ -5519,11 +5516,11 @@
         <v>23</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E93" s="4"/>
       <c r="F93" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G93" s="4" t="s">
         <v>39</v>
@@ -5549,11 +5546,11 @@
         <v>17</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E94" s="4"/>
       <c r="F94" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G94" s="4" t="s">
         <v>25</v>
@@ -5579,18 +5576,18 @@
         <v>23</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E95" s="4"/>
       <c r="F95" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G95" s="4" t="s">
         <v>28</v>
       </c>
       <c r="H95" s="4"/>
       <c r="I95" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J95" s="4" t="s">
         <v>20</v>
@@ -5599,7 +5596,7 @@
         <v>21</v>
       </c>
       <c r="M95" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="96" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5613,11 +5610,11 @@
         <v>23</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E96" s="4"/>
       <c r="F96" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G96" s="4" t="s">
         <v>31</v>
@@ -5643,18 +5640,18 @@
         <v>23</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E97" s="4"/>
       <c r="F97" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G97" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H97" s="4"/>
       <c r="I97" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J97" s="4" t="s">
         <v>20</v>
@@ -5663,7 +5660,7 @@
         <v>21</v>
       </c>
       <c r="M97" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5677,11 +5674,11 @@
         <v>23</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E98" s="4"/>
       <c r="F98" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G98" s="4" t="s">
         <v>19</v>
@@ -5707,18 +5704,18 @@
         <v>17</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E99" s="4"/>
       <c r="F99" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G99" s="4" t="s">
         <v>152</v>
       </c>
       <c r="H99" s="4"/>
       <c r="I99" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="J99" s="4" t="s">
         <v>20</v>
@@ -5727,7 +5724,7 @@
         <v>149</v>
       </c>
       <c r="M99" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="100" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -5735,20 +5732,20 @@
         <v>88</v>
       </c>
       <c r="B100" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="C100" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="C100" s="4" t="s">
+      <c r="D100" s="5" t="s">
         <v>233</v>
-      </c>
-      <c r="D100" s="5" t="s">
-        <v>234</v>
       </c>
       <c r="E100" s="4"/>
       <c r="F100" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H100" s="4"/>
       <c r="I100" s="4"/>
@@ -5768,14 +5765,14 @@
         <v>17</v>
       </c>
       <c r="C101" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="D101" s="5" t="s">
         <v>235</v>
-      </c>
-      <c r="D101" s="5" t="s">
-        <v>236</v>
       </c>
       <c r="E101" s="4"/>
       <c r="F101" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G101" s="4" t="s">
         <v>49</v>
@@ -5801,18 +5798,18 @@
         <v>23</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E102" s="4"/>
       <c r="F102" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G102" s="4" t="s">
         <v>25</v>
       </c>
       <c r="H102" s="4"/>
       <c r="I102" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J102" s="4" t="s">
         <v>20</v>
@@ -5821,7 +5818,7 @@
         <v>21</v>
       </c>
       <c r="M102" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="103" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -5835,11 +5832,11 @@
         <v>23</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E103" s="4"/>
       <c r="F103" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G103" s="4" t="s">
         <v>56</v>
@@ -5865,18 +5862,18 @@
         <v>23</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E104" s="4"/>
       <c r="F104" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H104" s="4"/>
       <c r="I104" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J104" s="4" t="s">
         <v>20</v>
@@ -5885,7 +5882,7 @@
         <v>149</v>
       </c>
       <c r="M104" s="24" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="105" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -5899,18 +5896,18 @@
         <v>23</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E105" s="4"/>
       <c r="F105" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G105" s="4" t="s">
         <v>152</v>
       </c>
       <c r="H105" s="4"/>
       <c r="I105" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J105" s="4" t="s">
         <v>20</v>
@@ -5919,7 +5916,7 @@
         <v>149</v>
       </c>
       <c r="M105" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="106" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -5927,24 +5924,24 @@
         <v>88</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E106" s="4"/>
       <c r="F106" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H106" s="4"/>
       <c r="I106" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J106" s="4" t="s">
         <v>20</v>
@@ -5953,7 +5950,7 @@
         <v>71</v>
       </c>
       <c r="M106" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="107" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -5967,11 +5964,11 @@
         <v>47</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E107" s="4"/>
       <c r="F107" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G107" s="4" t="s">
         <v>39</v>
@@ -5997,11 +5994,11 @@
         <v>47</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E108" s="4"/>
       <c r="F108" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G108" s="4" t="s">
         <v>25</v>
@@ -6027,11 +6024,11 @@
         <v>47</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E109" s="4"/>
       <c r="F109" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G109" s="4" t="s">
         <v>28</v>
@@ -6057,11 +6054,11 @@
         <v>47</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E110" s="4"/>
       <c r="F110" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G110" s="4" t="s">
         <v>31</v>
@@ -6087,18 +6084,18 @@
         <v>47</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E111" s="4"/>
       <c r="F111" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G111" s="4" t="s">
         <v>56</v>
       </c>
       <c r="H111" s="4"/>
       <c r="I111" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="J111" s="4" t="s">
         <v>20</v>
@@ -6107,7 +6104,7 @@
         <v>21</v>
       </c>
       <c r="M111" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="112" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6121,11 +6118,11 @@
         <v>47</v>
       </c>
       <c r="D112" s="31" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E112" s="4"/>
       <c r="F112" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G112" s="4" t="s">
         <v>35</v>
@@ -6151,18 +6148,18 @@
         <v>47</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E113" s="4"/>
       <c r="F113" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G113" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H113" s="4"/>
       <c r="I113" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="J113" s="4" t="s">
         <v>20</v>
@@ -6171,7 +6168,7 @@
         <v>21</v>
       </c>
       <c r="M113" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="114" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -6182,21 +6179,21 @@
         <v>23</v>
       </c>
       <c r="C114" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="D114" s="5" t="s">
         <v>257</v>
-      </c>
-      <c r="D114" s="5" t="s">
-        <v>258</v>
       </c>
       <c r="E114" s="4"/>
       <c r="F114" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="G114" s="4" t="s">
         <v>258</v>
-      </c>
-      <c r="G114" s="4" t="s">
-        <v>259</v>
       </c>
       <c r="H114" s="4"/>
       <c r="I114" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J114" s="4" t="s">
         <v>20</v>
@@ -6205,7 +6202,7 @@
         <v>21</v>
       </c>
       <c r="M114" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="115" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -6219,18 +6216,18 @@
         <v>43</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E115" s="4"/>
       <c r="F115" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H115" s="4"/>
       <c r="I115" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="J115" s="4" t="s">
         <v>20</v>
@@ -6239,7 +6236,7 @@
         <v>149</v>
       </c>
       <c r="M115" s="24" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="116" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -6247,17 +6244,17 @@
         <v>88</v>
       </c>
       <c r="B116" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C116" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="C116" s="4" t="s">
+      <c r="D116" s="5" t="s">
         <v>264</v>
-      </c>
-      <c r="D116" s="5" t="s">
-        <v>265</v>
       </c>
       <c r="E116" s="4"/>
       <c r="F116" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G116" s="4" t="s">
         <v>49</v>
@@ -6277,24 +6274,24 @@
         <v>88</v>
       </c>
       <c r="B117" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="C117" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="C117" s="4" t="s">
+      <c r="D117" s="5" t="s">
         <v>267</v>
-      </c>
-      <c r="D117" s="5" t="s">
-        <v>268</v>
       </c>
       <c r="E117" s="4"/>
       <c r="F117" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H117" s="4"/>
       <c r="I117" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="J117" s="4" t="s">
         <v>20</v>
@@ -6303,7 +6300,7 @@
         <v>71</v>
       </c>
       <c r="M117" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="118" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6317,18 +6314,18 @@
         <v>47</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E118" s="4"/>
       <c r="F118" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H118" s="4"/>
       <c r="I118" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J118" s="4" t="s">
         <v>20</v>
@@ -6337,7 +6334,7 @@
         <v>149</v>
       </c>
       <c r="M118" s="24" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="119" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6345,20 +6342,20 @@
         <v>88</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>54</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E119" s="4"/>
       <c r="F119" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H119" s="4"/>
       <c r="I119" s="4"/>
@@ -6375,24 +6372,24 @@
         <v>88</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>67</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E120" s="4"/>
       <c r="F120" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G120" s="4" t="s">
         <v>49</v>
       </c>
       <c r="H120" s="4"/>
       <c r="I120" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J120" s="4" t="s">
         <v>20</v>
@@ -6401,7 +6398,7 @@
         <v>71</v>
       </c>
       <c r="M120" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="121" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6412,14 +6409,14 @@
         <v>47</v>
       </c>
       <c r="C121" s="17" t="s">
+        <v>275</v>
+      </c>
+      <c r="D121" s="5" t="s">
         <v>276</v>
-      </c>
-      <c r="D121" s="5" t="s">
-        <v>277</v>
       </c>
       <c r="E121" s="4"/>
       <c r="F121" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G121" s="4" t="s">
         <v>39</v>
@@ -6442,14 +6439,14 @@
         <v>47</v>
       </c>
       <c r="C122" s="17" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E122" s="4"/>
       <c r="F122" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G122" s="4" t="s">
         <v>25</v>
@@ -6472,30 +6469,30 @@
         <v>47</v>
       </c>
       <c r="C123" s="17" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E123" s="4"/>
       <c r="F123" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G123" s="4" t="s">
         <v>28</v>
       </c>
       <c r="H123" s="4"/>
       <c r="I123" t="s">
+        <v>279</v>
+      </c>
+      <c r="J123" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L123" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M123" t="s">
         <v>280</v>
-      </c>
-      <c r="J123" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L123" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M123" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="124" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.2">
@@ -6506,14 +6503,14 @@
         <v>47</v>
       </c>
       <c r="C124" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="D124" s="5" t="s">
         <v>282</v>
-      </c>
-      <c r="D124" s="5" t="s">
-        <v>283</v>
       </c>
       <c r="E124" s="4"/>
       <c r="F124" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G124" s="4" t="s">
         <v>31</v>
@@ -6536,21 +6533,21 @@
         <v>47</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E125" s="4"/>
       <c r="F125" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G125" s="4" t="s">
         <v>56</v>
       </c>
       <c r="H125" s="4"/>
       <c r="I125" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J125" s="4" t="s">
         <v>20</v>
@@ -6559,7 +6556,7 @@
         <v>21</v>
       </c>
       <c r="M125" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="126" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6570,14 +6567,14 @@
         <v>47</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E126" s="4"/>
       <c r="F126" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G126" s="4" t="s">
         <v>35</v>
@@ -6603,14 +6600,14 @@
         <v>67</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E127" s="4"/>
       <c r="F127" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H127" s="4"/>
       <c r="I127" s="4"/>
@@ -6630,14 +6627,14 @@
         <v>47</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E128" s="4"/>
       <c r="F128" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G128" s="4" t="s">
         <v>19</v>
@@ -6660,21 +6657,21 @@
         <v>61</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E129" s="4"/>
       <c r="F129" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H129" s="4"/>
       <c r="I129" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J129" s="4" t="s">
         <v>20</v>
@@ -6683,7 +6680,7 @@
         <v>149</v>
       </c>
       <c r="M129" s="24" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="130" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -6694,17 +6691,17 @@
         <v>54</v>
       </c>
       <c r="C130" s="17" t="s">
+        <v>291</v>
+      </c>
+      <c r="D130" s="5" t="s">
         <v>292</v>
-      </c>
-      <c r="D130" s="5" t="s">
-        <v>293</v>
       </c>
       <c r="E130" s="4"/>
       <c r="F130" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H130" s="4"/>
       <c r="I130" s="4"/>
@@ -6721,17 +6718,17 @@
         <v>88</v>
       </c>
       <c r="B131" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="C131" s="17" t="s">
         <v>294</v>
       </c>
-      <c r="C131" s="17" t="s">
+      <c r="D131" s="5" t="s">
         <v>295</v>
-      </c>
-      <c r="D131" s="5" t="s">
-        <v>296</v>
       </c>
       <c r="E131" s="4"/>
       <c r="F131" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G131" s="4" t="s">
         <v>49</v>
@@ -6751,24 +6748,24 @@
         <v>88</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C132" s="17" t="s">
+        <v>296</v>
+      </c>
+      <c r="D132" s="5" t="s">
         <v>297</v>
-      </c>
-      <c r="D132" s="5" t="s">
-        <v>298</v>
       </c>
       <c r="E132" s="4"/>
       <c r="F132" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H132" s="4"/>
       <c r="I132" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J132" s="4" t="s">
         <v>20</v>
@@ -6777,7 +6774,7 @@
         <v>71</v>
       </c>
       <c r="M132" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="133" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6785,17 +6782,17 @@
         <v>88</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C133" s="17" t="s">
+        <v>299</v>
+      </c>
+      <c r="D133" s="5" t="s">
         <v>300</v>
-      </c>
-      <c r="D133" s="5" t="s">
-        <v>301</v>
       </c>
       <c r="E133" s="4"/>
       <c r="F133" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G133" s="4" t="s">
         <v>31</v>
@@ -6815,24 +6812,24 @@
         <v>88</v>
       </c>
       <c r="B134" s="13" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C134" s="19" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E134" s="4"/>
       <c r="F134" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G134" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H134" s="4"/>
       <c r="I134" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J134" s="4" t="s">
         <v>20</v>
@@ -6841,12 +6838,12 @@
         <v>21</v>
       </c>
       <c r="M134" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="135" spans="1:13" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A135" s="10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B135" s="4" t="s">
         <v>89</v>
@@ -6855,11 +6852,11 @@
         <v>90</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E135" s="8"/>
       <c r="F135" s="16" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G135" s="8" t="s">
         <v>39</v>
@@ -6876,7 +6873,7 @@
     </row>
     <row r="136" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B136" s="4" t="s">
         <v>89</v>
@@ -6885,11 +6882,11 @@
         <v>90</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E136" s="4"/>
       <c r="F136" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G136" s="4" t="s">
         <v>25</v>
@@ -6906,7 +6903,7 @@
     </row>
     <row r="137" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B137" s="4" t="s">
         <v>89</v>
@@ -6915,32 +6912,32 @@
         <v>90</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E137" s="4"/>
       <c r="F137" s="5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G137" s="4" t="s">
         <v>28</v>
       </c>
       <c r="H137" s="4"/>
       <c r="I137" t="s">
+        <v>307</v>
+      </c>
+      <c r="J137" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L137" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M137" t="s">
         <v>308</v>
-      </c>
-      <c r="J137" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L137" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M137" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="138" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B138" s="4" t="s">
         <v>89</v>
@@ -6949,11 +6946,11 @@
         <v>90</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E138" s="4"/>
       <c r="F138" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G138" s="4" t="s">
         <v>56</v>
@@ -6970,7 +6967,7 @@
     </row>
     <row r="139" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B139" s="4" t="s">
         <v>89</v>
@@ -6979,45 +6976,45 @@
         <v>90</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E139" s="4"/>
       <c r="F139" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G139" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H139" s="4"/>
       <c r="I139" t="s">
+        <v>311</v>
+      </c>
+      <c r="J139" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L139" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M139" t="s">
         <v>312</v>
-      </c>
-      <c r="J139" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L139" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M139" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="140" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B140" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="C140" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="C140" s="4" t="s">
+      <c r="D140" s="5" t="s">
         <v>315</v>
-      </c>
-      <c r="D140" s="5" t="s">
-        <v>316</v>
       </c>
       <c r="E140" s="4"/>
       <c r="F140" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G140" s="4" t="s">
         <v>49</v>
@@ -7034,23 +7031,23 @@
     </row>
     <row r="141" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C141" s="4" t="s">
         <v>90</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E141" s="4"/>
       <c r="F141" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H141" s="4"/>
       <c r="I141" s="4"/>
@@ -7064,7 +7061,7 @@
     </row>
     <row r="142" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B142" s="4" t="s">
         <v>98</v>
@@ -7073,11 +7070,11 @@
         <v>115</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E142" s="4"/>
       <c r="F142" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G142" s="4" t="s">
         <v>31</v>
@@ -7094,7 +7091,7 @@
     </row>
     <row r="143" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B143" s="4" t="s">
         <v>98</v>
@@ -7103,11 +7100,11 @@
         <v>115</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E143" s="4"/>
       <c r="F143" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G143" s="4" t="s">
         <v>19</v>
@@ -7124,7 +7121,7 @@
     </row>
     <row r="144" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B144" s="4" t="s">
         <v>98</v>
@@ -7133,18 +7130,18 @@
         <v>115</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E144" s="4"/>
       <c r="F144" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H144" s="4"/>
       <c r="I144" s="24" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="J144" s="4" t="s">
         <v>20</v>
@@ -7153,25 +7150,25 @@
         <v>21</v>
       </c>
       <c r="M144" s="24" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="145" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C145" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="D145" s="5" t="s">
         <v>323</v>
-      </c>
-      <c r="D145" s="5" t="s">
-        <v>324</v>
       </c>
       <c r="E145" s="4"/>
       <c r="F145" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G145" s="4" t="s">
         <v>49</v>
@@ -7188,7 +7185,7 @@
     </row>
     <row r="146" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B146" s="4" t="s">
         <v>90</v>
@@ -7197,11 +7194,11 @@
         <v>106</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E146" s="4"/>
       <c r="F146" s="5" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G146" s="4" t="s">
         <v>39</v>
@@ -7218,20 +7215,20 @@
     </row>
     <row r="147" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B147" s="4" t="s">
         <v>90</v>
       </c>
       <c r="C147" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="D147" s="5" t="s">
         <v>326</v>
-      </c>
-      <c r="D147" s="5" t="s">
-        <v>327</v>
       </c>
       <c r="E147" s="4"/>
       <c r="F147" s="5" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G147" s="4" t="s">
         <v>25</v>
@@ -7248,7 +7245,7 @@
     </row>
     <row r="148" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B148" s="4" t="s">
         <v>90</v>
@@ -7257,11 +7254,11 @@
         <v>106</v>
       </c>
       <c r="D148" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E148" s="4"/>
       <c r="F148" s="5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G148" s="4" t="s">
         <v>28</v>
@@ -7278,7 +7275,7 @@
     </row>
     <row r="149" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B149" s="4" t="s">
         <v>90</v>
@@ -7287,32 +7284,32 @@
         <v>106</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E149" s="4"/>
       <c r="F149" s="5" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G149" s="4" t="s">
         <v>56</v>
       </c>
       <c r="H149" s="4"/>
       <c r="I149" t="s">
+        <v>330</v>
+      </c>
+      <c r="J149" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L149" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M149" t="s">
         <v>331</v>
-      </c>
-      <c r="J149" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L149" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M149" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="150" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B150" s="4" t="s">
         <v>90</v>
@@ -7321,18 +7318,18 @@
         <v>106</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E150" s="4"/>
       <c r="F150" s="5" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G150" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H150" s="4"/>
       <c r="I150" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="J150" s="4" t="s">
         <v>20</v>
@@ -7341,12 +7338,12 @@
         <v>21</v>
       </c>
       <c r="M150" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="151" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B151" s="4" t="s">
         <v>115</v>
@@ -7355,32 +7352,32 @@
         <v>106</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E151" s="4"/>
       <c r="F151" s="5" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G151" s="4" t="s">
         <v>31</v>
       </c>
       <c r="H151" s="4"/>
       <c r="I151" t="s">
+        <v>335</v>
+      </c>
+      <c r="J151" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L151" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M151" t="s">
         <v>336</v>
-      </c>
-      <c r="J151" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L151" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M151" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="152" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B152" s="4" t="s">
         <v>115</v>
@@ -7389,11 +7386,11 @@
         <v>106</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E152" s="4"/>
       <c r="F152" s="5" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G152" s="4" t="s">
         <v>19</v>
@@ -7410,7 +7407,7 @@
     </row>
     <row r="153" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B153" s="4" t="s">
         <v>115</v>
@@ -7419,18 +7416,18 @@
         <v>106</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E153" s="4"/>
       <c r="F153" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H153" s="4"/>
       <c r="I153" s="24" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J153" s="4" t="s">
         <v>20</v>
@@ -7439,25 +7436,25 @@
         <v>21</v>
       </c>
       <c r="M153" s="24" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="154" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C154" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="D154" s="5" t="s">
         <v>341</v>
-      </c>
-      <c r="D154" s="5" t="s">
-        <v>342</v>
       </c>
       <c r="E154" s="4"/>
       <c r="F154" s="5" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G154" s="4" t="s">
         <v>49</v>
@@ -7474,20 +7471,20 @@
     </row>
     <row r="155" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C155" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="D155" s="5" t="s">
         <v>343</v>
-      </c>
-      <c r="D155" s="5" t="s">
-        <v>344</v>
       </c>
       <c r="E155" s="4"/>
       <c r="F155" s="5" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G155" s="4" t="s">
         <v>25</v>
@@ -7504,7 +7501,7 @@
     </row>
     <row r="156" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B156" s="4" t="s">
         <v>106</v>
@@ -7513,11 +7510,11 @@
         <v>119</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E156" s="4"/>
       <c r="F156" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G156" s="4" t="s">
         <v>39</v>
@@ -7534,7 +7531,7 @@
     </row>
     <row r="157" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B157" s="4" t="s">
         <v>106</v>
@@ -7543,11 +7540,11 @@
         <v>119</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E157" s="4"/>
       <c r="F157" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G157" s="4" t="s">
         <v>28</v>
@@ -7564,20 +7561,20 @@
     </row>
     <row r="158" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B158" s="4" t="s">
         <v>106</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E158" s="4"/>
       <c r="F158" s="5" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G158" s="4" t="s">
         <v>31</v>
@@ -7594,7 +7591,7 @@
     </row>
     <row r="159" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B159" s="4" t="s">
         <v>106</v>
@@ -7603,18 +7600,18 @@
         <v>119</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E159" s="4"/>
       <c r="F159" s="5" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G159" s="4" t="s">
         <v>56</v>
       </c>
       <c r="H159" s="4"/>
       <c r="I159" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J159" s="4" t="s">
         <v>20</v>
@@ -7623,12 +7620,12 @@
         <v>21</v>
       </c>
       <c r="M159" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="160" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B160" s="4" t="s">
         <v>106</v>
@@ -7637,18 +7634,18 @@
         <v>119</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E160" s="4"/>
       <c r="F160" s="5" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G160" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H160" s="4"/>
       <c r="I160" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="J160" s="4" t="s">
         <v>20</v>
@@ -7657,12 +7654,12 @@
         <v>21</v>
       </c>
       <c r="M160" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="161" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B161" s="4" t="s">
         <v>106</v>
@@ -7671,11 +7668,11 @@
         <v>119</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E161" s="4"/>
       <c r="F161" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G161" s="4" t="s">
         <v>19</v>
@@ -7692,27 +7689,27 @@
     </row>
     <row r="162" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B162" s="4" t="s">
         <v>106</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D162" s="17" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E162" s="4"/>
       <c r="F162" s="17" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H162" s="4"/>
       <c r="I162" s="24" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="J162" s="4" t="s">
         <v>20</v>
@@ -7721,25 +7718,25 @@
         <v>21</v>
       </c>
       <c r="M162" s="24" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="163" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C163" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="D163" s="5" t="s">
         <v>356</v>
-      </c>
-      <c r="D163" s="5" t="s">
-        <v>357</v>
       </c>
       <c r="E163" s="4"/>
       <c r="F163" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G163" s="4" t="s">
         <v>25</v>
@@ -7756,20 +7753,20 @@
     </row>
     <row r="164" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E164" s="4"/>
       <c r="F164" s="5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G164" s="4" t="s">
         <v>31</v>
@@ -7786,7 +7783,7 @@
     </row>
     <row r="165" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B165" s="4" t="s">
         <v>119</v>
@@ -7795,11 +7792,11 @@
         <v>127</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E165" s="4"/>
       <c r="F165" s="5" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G165" s="4" t="s">
         <v>28</v>
@@ -7816,7 +7813,7 @@
     </row>
     <row r="166" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B166" s="4" t="s">
         <v>119</v>
@@ -7825,11 +7822,11 @@
         <v>127</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E166" s="4"/>
       <c r="F166" s="5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G166" s="4" t="s">
         <v>56</v>
@@ -7846,7 +7843,7 @@
     </row>
     <row r="167" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B167" s="4" t="s">
         <v>119</v>
@@ -7855,18 +7852,18 @@
         <v>127</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E167" s="4"/>
       <c r="F167" s="5" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G167" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H167" s="4"/>
       <c r="I167" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J167" s="4" t="s">
         <v>20</v>
@@ -7875,32 +7872,32 @@
         <v>21</v>
       </c>
       <c r="M167" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="168" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C168" s="4" t="s">
         <v>129</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E168" s="4"/>
       <c r="F168" s="5" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G168" s="4" t="s">
         <v>25</v>
       </c>
       <c r="H168" s="4"/>
       <c r="I168" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="J168" s="4" t="s">
         <v>20</v>
@@ -7909,12 +7906,12 @@
         <v>21</v>
       </c>
       <c r="M168" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="169" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B169" s="4" t="s">
         <v>127</v>
@@ -7923,18 +7920,18 @@
         <v>136</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E169" s="4"/>
       <c r="F169" s="5" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G169" s="4" t="s">
         <v>56</v>
       </c>
       <c r="H169" s="4"/>
       <c r="I169" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="J169" s="4" t="s">
         <v>20</v>
@@ -7943,12 +7940,12 @@
         <v>21</v>
       </c>
       <c r="M169" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="170" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B170" s="4" t="s">
         <v>127</v>
@@ -7957,11 +7954,11 @@
         <v>136</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E170" s="4"/>
       <c r="F170" s="5" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G170" s="4" t="s">
         <v>35</v>
@@ -7978,7 +7975,7 @@
     </row>
     <row r="171" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B171" s="4" t="s">
         <v>136</v>
@@ -7987,18 +7984,18 @@
         <v>140</v>
       </c>
       <c r="D171" s="5" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E171" s="4"/>
       <c r="F171" s="5" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G171" s="4" t="s">
         <v>56</v>
       </c>
       <c r="H171" s="4"/>
       <c r="I171" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="J171" s="4" t="s">
         <v>20</v>
@@ -8007,12 +8004,12 @@
         <v>21</v>
       </c>
       <c r="M171" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="172" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B172" s="4" t="s">
         <v>136</v>
@@ -8021,11 +8018,11 @@
         <v>140</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E172" s="4"/>
       <c r="F172" s="5" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G172" s="4" t="s">
         <v>35</v>
@@ -8042,7 +8039,7 @@
     </row>
     <row r="173" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B173" s="4" t="s">
         <v>136</v>
@@ -8051,18 +8048,18 @@
         <v>134</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E173" s="4"/>
       <c r="F173" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G173" s="4" t="s">
         <v>152</v>
       </c>
       <c r="H173" s="4"/>
       <c r="I173" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="J173" s="4" t="s">
         <v>20</v>
@@ -8071,12 +8068,12 @@
         <v>149</v>
       </c>
       <c r="M173" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="174" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B174" s="4" t="s">
         <v>143</v>
@@ -8085,18 +8082,18 @@
         <v>140</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E174" s="4"/>
       <c r="F174" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H174" s="4"/>
       <c r="I174" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="J174" s="4" t="s">
         <v>20</v>
@@ -8105,32 +8102,32 @@
         <v>149</v>
       </c>
       <c r="M174" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="175" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B175" s="12" t="s">
         <v>150</v>
       </c>
       <c r="C175" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="D175" s="4" t="s">
         <v>375</v>
-      </c>
-      <c r="D175" s="4" t="s">
-        <v>376</v>
       </c>
       <c r="E175" s="4"/>
       <c r="F175" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G175" s="4" t="s">
         <v>152</v>
       </c>
       <c r="H175" s="4"/>
       <c r="I175" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J175" s="4" t="s">
         <v>20</v>
@@ -8139,12 +8136,12 @@
         <v>149</v>
       </c>
       <c r="M175" s="5" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="176" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B176" s="4" t="s">
         <v>140</v>
@@ -8153,11 +8150,11 @@
         <v>144</v>
       </c>
       <c r="D176" s="5" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E176" s="4"/>
       <c r="F176" s="5" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="G176" s="4" t="s">
         <v>28</v>
@@ -8174,7 +8171,7 @@
     </row>
     <row r="177" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B177" s="4" t="s">
         <v>140</v>
@@ -8183,11 +8180,11 @@
         <v>144</v>
       </c>
       <c r="D177" s="5" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E177" s="4"/>
       <c r="F177" s="5" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G177" s="4" t="s">
         <v>31</v>
@@ -8204,7 +8201,7 @@
     </row>
     <row r="178" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B178" s="4" t="s">
         <v>140</v>
@@ -8213,32 +8210,32 @@
         <v>144</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E178" s="4"/>
       <c r="F178" s="5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G178" s="4" t="s">
         <v>56</v>
       </c>
       <c r="H178" s="4"/>
       <c r="I178" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="J178" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L178" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M178" t="s">
         <v>382</v>
-      </c>
-      <c r="J178" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L178" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M178" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="179" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B179" s="4" t="s">
         <v>140</v>
@@ -8247,11 +8244,11 @@
         <v>144</v>
       </c>
       <c r="D179" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E179" s="4"/>
       <c r="F179" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G179" s="4" t="s">
         <v>35</v>
@@ -8268,7 +8265,7 @@
     </row>
     <row r="180" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B180" s="4" t="s">
         <v>140</v>
@@ -8298,7 +8295,7 @@
     </row>
     <row r="181" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B181" s="4" t="s">
         <v>140</v>
@@ -8307,18 +8304,18 @@
         <v>160</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E181" s="4"/>
       <c r="F181" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H181" s="4"/>
       <c r="I181" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="J181" s="4" t="s">
         <v>20</v>
@@ -8327,32 +8324,32 @@
         <v>149</v>
       </c>
       <c r="M181" s="24" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="182" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C182" s="4" t="s">
         <v>144</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E182" s="4"/>
       <c r="F182" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H182" s="4"/>
       <c r="I182" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="J182" s="4" t="s">
         <v>20</v>
@@ -8361,26 +8358,26 @@
         <v>149</v>
       </c>
       <c r="M182" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="183" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B183" s="4" t="s">
         <v>154</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E183" s="4"/>
       <c r="F183"/>
       <c r="G183" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H183" s="4"/>
       <c r="I183" s="4"/>
@@ -8394,27 +8391,27 @@
     </row>
     <row r="184" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B184" s="4" t="s">
         <v>154</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E184" s="4"/>
       <c r="F184" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G184" s="4" t="s">
         <v>147</v>
       </c>
       <c r="H184" s="4"/>
       <c r="I184" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="J184" s="4" t="s">
         <v>20</v>
@@ -8423,12 +8420,12 @@
         <v>149</v>
       </c>
       <c r="M184" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="185" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B185" s="4" t="s">
         <v>154</v>
@@ -8437,18 +8434,18 @@
         <v>144</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E185" s="4"/>
       <c r="F185" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G185" s="4" t="s">
         <v>152</v>
       </c>
       <c r="H185" s="4"/>
       <c r="I185" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="J185" s="4" t="s">
         <v>20</v>
@@ -8457,12 +8454,12 @@
         <v>149</v>
       </c>
       <c r="M185" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="186" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B186" s="4" t="s">
         <v>144</v>
@@ -8471,32 +8468,32 @@
         <v>16</v>
       </c>
       <c r="D186" s="31" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E186" s="4"/>
       <c r="F186" s="5" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G186" s="4" t="s">
         <v>39</v>
       </c>
       <c r="H186" s="4"/>
       <c r="I186" t="s">
+        <v>394</v>
+      </c>
+      <c r="J186" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L186" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M186" t="s">
         <v>395</v>
-      </c>
-      <c r="J186" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L186" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M186" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="187" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B187" s="4" t="s">
         <v>144</v>
@@ -8505,11 +8502,11 @@
         <v>16</v>
       </c>
       <c r="D187" s="5" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E187" s="4"/>
       <c r="F187" s="5" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G187" s="4" t="s">
         <v>28</v>
@@ -8526,7 +8523,7 @@
     </row>
     <row r="188" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B188" s="4" t="s">
         <v>144</v>
@@ -8535,18 +8532,18 @@
         <v>16</v>
       </c>
       <c r="D188" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E188" s="4"/>
       <c r="F188" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G188" s="4" t="s">
         <v>31</v>
       </c>
       <c r="H188" s="4"/>
       <c r="I188" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="J188" s="4" t="s">
         <v>20</v>
@@ -8555,12 +8552,12 @@
         <v>21</v>
       </c>
       <c r="M188" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="189" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B189" s="4" t="s">
         <v>144</v>
@@ -8569,11 +8566,11 @@
         <v>16</v>
       </c>
       <c r="D189" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E189" s="4"/>
       <c r="F189" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G189" s="4" t="s">
         <v>56</v>
@@ -8590,7 +8587,7 @@
     </row>
     <row r="190" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B190" s="4" t="s">
         <v>144</v>
@@ -8599,11 +8596,11 @@
         <v>16</v>
       </c>
       <c r="D190" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E190" s="4"/>
       <c r="F190" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G190" s="4" t="s">
         <v>35</v>
@@ -8620,7 +8617,7 @@
     </row>
     <row r="191" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B191" s="4" t="s">
         <v>144</v>
@@ -8629,15 +8626,15 @@
         <v>16</v>
       </c>
       <c r="D191" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E191" s="4"/>
       <c r="G191" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H191" s="4"/>
       <c r="I191" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="J191" s="4" t="s">
         <v>20</v>
@@ -8646,32 +8643,32 @@
         <v>149</v>
       </c>
       <c r="M191" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="192" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C192" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="D192" s="5" t="s">
         <v>405</v>
-      </c>
-      <c r="D192" s="5" t="s">
-        <v>406</v>
       </c>
       <c r="E192" s="4"/>
       <c r="F192" s="5" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G192" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H192" s="4"/>
       <c r="I192" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="J192" s="4" t="s">
         <v>20</v>
@@ -8680,32 +8677,32 @@
         <v>71</v>
       </c>
       <c r="M192" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="193" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C193" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D193" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E193" s="4"/>
       <c r="F193" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="G193" s="4" t="s">
         <v>152</v>
       </c>
       <c r="H193" s="4"/>
       <c r="I193" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="J193" s="4" t="s">
         <v>20</v>
@@ -8714,30 +8711,30 @@
         <v>149</v>
       </c>
       <c r="M193" s="5" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="194" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C194" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D194" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E194" s="4"/>
       <c r="F194" s="4"/>
       <c r="G194" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H194" s="4"/>
       <c r="I194" s="4" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="J194" s="4" t="s">
         <v>20</v>
@@ -8746,32 +8743,32 @@
         <v>149</v>
       </c>
       <c r="M194" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="195" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C195" s="4" t="s">
         <v>159</v>
       </c>
       <c r="D195" s="5" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E195" s="4"/>
       <c r="F195" s="5" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G195" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H195" s="4"/>
       <c r="I195" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="J195" s="4" t="s">
         <v>20</v>
@@ -8780,12 +8777,12 @@
         <v>71</v>
       </c>
       <c r="M195" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="196" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B196" s="4" t="s">
         <v>16</v>
@@ -8794,18 +8791,18 @@
         <v>22</v>
       </c>
       <c r="D196" s="5" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E196" s="4"/>
       <c r="F196" s="5" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G196" s="4" t="s">
         <v>39</v>
       </c>
       <c r="H196" s="4"/>
       <c r="I196" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="J196" s="4" t="s">
         <v>20</v>
@@ -8814,12 +8811,12 @@
         <v>21</v>
       </c>
       <c r="M196" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="197" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B197" s="4" t="s">
         <v>16</v>
@@ -8828,32 +8825,32 @@
         <v>22</v>
       </c>
       <c r="D197" s="5" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E197" s="4"/>
       <c r="F197" s="5" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G197" s="4" t="s">
         <v>28</v>
       </c>
       <c r="H197" s="4"/>
       <c r="I197" t="s">
+        <v>418</v>
+      </c>
+      <c r="J197" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L197" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M197" t="s">
         <v>419</v>
-      </c>
-      <c r="J197" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L197" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M197" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="198" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B198" s="4" t="s">
         <v>16</v>
@@ -8862,11 +8859,11 @@
         <v>22</v>
       </c>
       <c r="D198" s="5" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E198" s="4"/>
       <c r="F198" s="5" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G198" s="4" t="s">
         <v>31</v>
@@ -8883,7 +8880,7 @@
     </row>
     <row r="199" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B199" s="4" t="s">
         <v>16</v>
@@ -8892,11 +8889,11 @@
         <v>22</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E199" s="4"/>
       <c r="F199" s="5" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G199" s="4" t="s">
         <v>56</v>
@@ -8913,7 +8910,7 @@
     </row>
     <row r="200" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B200" s="4" t="s">
         <v>16</v>
@@ -8922,11 +8919,11 @@
         <v>22</v>
       </c>
       <c r="D200" s="5" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E200" s="4"/>
       <c r="F200" s="5" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="G200" s="4" t="s">
         <v>35</v>
@@ -8943,7 +8940,7 @@
     </row>
     <row r="201" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B201" s="4" t="s">
         <v>16</v>
@@ -8952,18 +8949,18 @@
         <v>22</v>
       </c>
       <c r="D201" s="5" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E201" s="4"/>
       <c r="F201" s="5" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="G201" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H201" s="4"/>
       <c r="I201" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="J201" s="4" t="s">
         <v>20</v>
@@ -8972,25 +8969,25 @@
         <v>21</v>
       </c>
       <c r="M201" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="202" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B202" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D202" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E202" s="4"/>
       <c r="F202" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G202" s="4" t="s">
         <v>147</v>
@@ -9007,7 +9004,7 @@
     </row>
     <row r="203" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B203" s="4" t="s">
         <v>159</v>
@@ -9016,18 +9013,18 @@
         <v>22</v>
       </c>
       <c r="D203" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E203" s="4"/>
       <c r="F203" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G203" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H203" s="4"/>
       <c r="I203" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="J203" s="4" t="s">
         <v>20</v>
@@ -9036,32 +9033,32 @@
         <v>149</v>
       </c>
       <c r="M203" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="204" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B204" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="C204" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="D204" s="5" t="s">
         <v>430</v>
-      </c>
-      <c r="C204" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="D204" s="5" t="s">
-        <v>431</v>
       </c>
       <c r="E204" s="4"/>
       <c r="F204" s="5" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G204" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H204" s="4"/>
       <c r="I204" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="J204" s="4" t="s">
         <v>20</v>
@@ -9070,32 +9067,32 @@
         <v>71</v>
       </c>
       <c r="M204" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="205" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C205" s="4" t="s">
         <v>22</v>
       </c>
       <c r="D205" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E205" s="4"/>
       <c r="F205" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="G205" s="4" t="s">
         <v>152</v>
       </c>
       <c r="H205" s="4"/>
       <c r="I205" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="J205" s="4" t="s">
         <v>20</v>
@@ -9104,12 +9101,12 @@
         <v>149</v>
       </c>
       <c r="M205" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="206" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B206" s="4" t="s">
         <v>22</v>
@@ -9118,11 +9115,11 @@
         <v>23</v>
       </c>
       <c r="D206" s="5" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E206" s="4"/>
       <c r="F206" s="5" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="G206" s="4" t="s">
         <v>39</v>
@@ -9139,7 +9136,7 @@
     </row>
     <row r="207" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B207" s="4" t="s">
         <v>22</v>
@@ -9148,11 +9145,11 @@
         <v>37</v>
       </c>
       <c r="D207" s="5" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E207" s="4"/>
       <c r="F207" s="5" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G207" s="4" t="s">
         <v>25</v>
@@ -9169,7 +9166,7 @@
     </row>
     <row r="208" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B208" s="4" t="s">
         <v>22</v>
@@ -9178,18 +9175,18 @@
         <v>23</v>
       </c>
       <c r="D208" s="5" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E208" s="4"/>
       <c r="F208" s="5" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="G208" s="4" t="s">
         <v>28</v>
       </c>
       <c r="H208" s="4"/>
       <c r="I208" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J208" s="4" t="s">
         <v>20</v>
@@ -9198,12 +9195,12 @@
         <v>21</v>
       </c>
       <c r="M208" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="209" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B209" s="4" t="s">
         <v>22</v>
@@ -9212,32 +9209,32 @@
         <v>29</v>
       </c>
       <c r="D209" s="5" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E209" s="4"/>
       <c r="F209" s="5" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="G209" s="4" t="s">
         <v>31</v>
       </c>
       <c r="H209" s="4"/>
       <c r="I209" t="s">
+        <v>440</v>
+      </c>
+      <c r="J209" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L209" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M209" t="s">
         <v>441</v>
-      </c>
-      <c r="J209" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L209" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M209" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="210" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B210" s="4" t="s">
         <v>22</v>
@@ -9246,11 +9243,11 @@
         <v>23</v>
       </c>
       <c r="D210" s="5" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E210" s="4"/>
       <c r="F210" s="5" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G210" s="4" t="s">
         <v>56</v>
@@ -9267,7 +9264,7 @@
     </row>
     <row r="211" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B211" s="4" t="s">
         <v>22</v>
@@ -9276,11 +9273,11 @@
         <v>23</v>
       </c>
       <c r="D211" s="5" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E211" s="4"/>
       <c r="F211" s="5" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="G211" s="4" t="s">
         <v>35</v>
@@ -9297,27 +9294,27 @@
     </row>
     <row r="212" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B212" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C212" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="D212" s="5" t="s">
         <v>445</v>
-      </c>
-      <c r="D212" s="5" t="s">
-        <v>446</v>
       </c>
       <c r="E212" s="4"/>
       <c r="F212" s="5" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G212" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H212" s="4"/>
       <c r="I212" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="J212" s="4" t="s">
         <v>20</v>
@@ -9326,12 +9323,12 @@
         <v>71</v>
       </c>
       <c r="M212" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="213" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B213" s="4" t="s">
         <v>22</v>
@@ -9340,11 +9337,11 @@
         <v>29</v>
       </c>
       <c r="D213" s="5" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E213" s="4"/>
       <c r="F213" s="5" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="G213" s="4" t="s">
         <v>19</v>
@@ -9361,7 +9358,7 @@
     </row>
     <row r="214" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B214" s="4" t="s">
         <v>22</v>
@@ -9370,18 +9367,18 @@
         <v>23</v>
       </c>
       <c r="D214" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E214" s="4"/>
       <c r="F214" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="G214" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H214" s="4"/>
       <c r="I214" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="J214" s="4" t="s">
         <v>20</v>
@@ -9390,12 +9387,12 @@
         <v>149</v>
       </c>
       <c r="M214" s="24" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="215" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B215" s="4" t="s">
         <v>22</v>
@@ -9404,14 +9401,14 @@
         <v>29</v>
       </c>
       <c r="D215" s="23" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E215" s="4"/>
       <c r="F215" s="23" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G215" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H215" s="4"/>
       <c r="I215" s="4"/>
@@ -9425,27 +9422,27 @@
     </row>
     <row r="216" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C216" s="4" t="s">
         <v>29</v>
       </c>
       <c r="D216" s="4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E216" s="4"/>
       <c r="F216" s="4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G216" s="4" t="s">
         <v>152</v>
       </c>
       <c r="H216" s="4"/>
       <c r="I216" s="4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="J216" s="4" t="s">
         <v>20</v>
@@ -9454,25 +9451,25 @@
         <v>149</v>
       </c>
       <c r="M216" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="217" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B217" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C217" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D217" s="5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E217" s="4"/>
       <c r="F217" s="5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G217" s="4" t="s">
         <v>49</v>
@@ -9489,23 +9486,23 @@
     </row>
     <row r="218" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B218" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C218" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="D218" s="5" t="s">
         <v>457</v>
-      </c>
-      <c r="D218" s="5" t="s">
-        <v>458</v>
       </c>
       <c r="E218" s="4"/>
       <c r="F218" s="5" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G218" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H218" s="4"/>
       <c r="I218" s="4"/>
@@ -9519,41 +9516,41 @@
     </row>
     <row r="219" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B219" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C219" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D219" s="5" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E219" s="4"/>
       <c r="F219" s="5" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="G219" s="4" t="s">
         <v>31</v>
       </c>
       <c r="H219" s="4"/>
       <c r="I219" t="s">
+        <v>459</v>
+      </c>
+      <c r="J219" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L219" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M219" t="s">
         <v>460</v>
-      </c>
-      <c r="J219" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L219" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M219" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="220" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B220" s="4" t="s">
         <v>29</v>
@@ -9562,32 +9559,32 @@
         <v>43</v>
       </c>
       <c r="D220" s="5" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E220" s="4"/>
       <c r="F220" s="5" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="G220" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H220" s="4"/>
       <c r="I220" t="s">
+        <v>462</v>
+      </c>
+      <c r="J220" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L220" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M220" t="s">
         <v>463</v>
-      </c>
-      <c r="J220" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L220" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M220" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="221" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B221" s="4" t="s">
         <v>23</v>
@@ -9596,11 +9593,11 @@
         <v>47</v>
       </c>
       <c r="D221" s="5" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E221" s="4"/>
       <c r="F221" s="5" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="G221" s="4" t="s">
         <v>39</v>
@@ -9617,7 +9614,7 @@
     </row>
     <row r="222" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B222" s="4" t="s">
         <v>23</v>
@@ -9626,11 +9623,11 @@
         <v>47</v>
       </c>
       <c r="D222" s="5" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E222" s="4"/>
       <c r="F222" s="5" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G222" s="4" t="s">
         <v>28</v>
@@ -9647,7 +9644,7 @@
     </row>
     <row r="223" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B223" s="4" t="s">
         <v>23</v>
@@ -9655,19 +9652,19 @@
       <c r="C223" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D223" s="5" t="s">
-        <v>467</v>
+      <c r="D223" s="23" t="s">
+        <v>670</v>
       </c>
       <c r="E223" s="4"/>
-      <c r="F223" s="5" t="s">
-        <v>467</v>
+      <c r="F223" s="23" t="s">
+        <v>670</v>
       </c>
       <c r="G223" s="4" t="s">
         <v>56</v>
       </c>
       <c r="H223" s="4"/>
       <c r="I223" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="J223" s="4" t="s">
         <v>20</v>
@@ -9676,12 +9673,12 @@
         <v>71</v>
       </c>
       <c r="M223" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="224" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B224" s="4" t="s">
         <v>23</v>
@@ -9690,18 +9687,18 @@
         <v>47</v>
       </c>
       <c r="D224" s="5" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E224" s="4"/>
       <c r="F224" s="5" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="G224" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H224" s="4"/>
       <c r="I224" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="J224" s="4" t="s">
         <v>20</v>
@@ -9710,28 +9707,28 @@
         <v>21</v>
       </c>
       <c r="M224" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="225" spans="1:13" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B225" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C225" s="4" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D225" s="5" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E225" s="4"/>
       <c r="F225" s="5" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="G225" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H225" s="4"/>
       <c r="I225" s="4"/>
@@ -9745,27 +9742,27 @@
     </row>
     <row r="226" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B226" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="C226" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="D226" s="5" t="s">
         <v>473</v>
-      </c>
-      <c r="C226" s="4" t="s">
-        <v>474</v>
-      </c>
-      <c r="D226" s="5" t="s">
-        <v>475</v>
       </c>
       <c r="E226" s="4"/>
       <c r="F226" s="5" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="G226" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H226" s="4"/>
       <c r="I226" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="J226" s="4" t="s">
         <v>20</v>
@@ -9774,25 +9771,25 @@
         <v>71</v>
       </c>
       <c r="M226" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="227" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C227" s="4" t="s">
         <v>43</v>
       </c>
       <c r="D227" s="5" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E227" s="4"/>
       <c r="F227" s="5" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="G227" s="4" t="s">
         <v>49</v>
@@ -9809,7 +9806,7 @@
     </row>
     <row r="228" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B228" s="4" t="s">
         <v>37</v>
@@ -9818,11 +9815,11 @@
         <v>61</v>
       </c>
       <c r="D228" s="5" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E228" s="4"/>
       <c r="F228" s="5" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G228" s="4" t="s">
         <v>25</v>
@@ -9839,27 +9836,27 @@
     </row>
     <row r="229" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B229" s="4" t="s">
         <v>37</v>
       </c>
       <c r="C229" s="4" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D229" s="4" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E229" s="4"/>
       <c r="F229" s="4" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="G229" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H229" s="4"/>
       <c r="I229" s="4" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="J229" s="4" t="s">
         <v>20</v>
@@ -9868,12 +9865,12 @@
         <v>149</v>
       </c>
       <c r="M229" s="4" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="230" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B230" s="4" t="s">
         <v>43</v>
@@ -9882,18 +9879,18 @@
         <v>61</v>
       </c>
       <c r="D230" s="5" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E230" s="4"/>
       <c r="F230" s="5" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="G230" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H230" s="4"/>
       <c r="I230" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="J230" s="4" t="s">
         <v>20</v>
@@ -9902,25 +9899,25 @@
         <v>21</v>
       </c>
       <c r="M230" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="231" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C231" s="4" t="s">
         <v>54</v>
       </c>
       <c r="D231" s="5" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E231" s="4"/>
       <c r="F231" s="5" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="G231" s="4" t="s">
         <v>31</v>
@@ -9937,27 +9934,27 @@
     </row>
     <row r="232" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C232" s="4" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D232" s="5" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E232" s="4"/>
       <c r="F232" s="5" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="G232" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H232" s="4"/>
       <c r="I232" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="J232" s="4" t="s">
         <v>20</v>
@@ -9966,25 +9963,25 @@
         <v>71</v>
       </c>
       <c r="M232" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="233" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C233" s="4" t="s">
         <v>61</v>
       </c>
       <c r="D233" s="5" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E233" s="4"/>
       <c r="F233" s="5" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="G233" s="4" t="s">
         <v>49</v>
@@ -10001,27 +9998,27 @@
     </row>
     <row r="234" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B234" s="4" t="s">
         <v>47</v>
       </c>
       <c r="C234" s="4" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D234" s="5" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="E234" s="4"/>
       <c r="F234" s="5" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="G234" s="4" t="s">
         <v>39</v>
       </c>
       <c r="H234" s="4"/>
       <c r="I234" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="J234" s="4" t="s">
         <v>20</v>
@@ -10030,25 +10027,25 @@
         <v>21</v>
       </c>
       <c r="M234" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="235" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B235" s="4" t="s">
         <v>47</v>
       </c>
       <c r="C235" s="17" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D235" s="5" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E235" s="4"/>
       <c r="F235" s="5" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="G235" s="4" t="s">
         <v>28</v>
@@ -10065,20 +10062,20 @@
     </row>
     <row r="236" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B236" s="4" t="s">
         <v>47</v>
       </c>
       <c r="C236" s="4" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D236" s="5" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E236" s="4"/>
       <c r="F236" s="5" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="G236" s="4" t="s">
         <v>56</v>
@@ -10095,20 +10092,20 @@
     </row>
     <row r="237" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B237" s="4" t="s">
         <v>47</v>
       </c>
       <c r="C237" s="4" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D237" s="5" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="E237" s="4"/>
       <c r="F237" s="5" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="G237" s="4" t="s">
         <v>35</v>
@@ -10125,23 +10122,23 @@
     </row>
     <row r="238" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B238" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="C238" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="D238" s="5" t="s">
         <v>499</v>
-      </c>
-      <c r="C238" s="4" t="s">
-        <v>500</v>
-      </c>
-      <c r="D238" s="5" t="s">
-        <v>501</v>
       </c>
       <c r="E238" s="4"/>
       <c r="F238" s="5" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="G238" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H238" s="4"/>
       <c r="I238" s="4"/>
@@ -10155,27 +10152,27 @@
     </row>
     <row r="239" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B239" s="4" t="s">
         <v>61</v>
       </c>
       <c r="C239" s="17" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D239" s="5" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="E239" s="4"/>
       <c r="F239" s="5" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="G239" s="4" t="s">
         <v>25</v>
       </c>
       <c r="H239" s="4"/>
       <c r="I239" s="4" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="J239" s="4" t="s">
         <v>20</v>
@@ -10184,25 +10181,25 @@
         <v>71</v>
       </c>
       <c r="M239" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="240" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B240" s="4" t="s">
         <v>61</v>
       </c>
       <c r="C240" s="4" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D240" s="5" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="E240" s="4"/>
       <c r="F240" s="5" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="G240" s="4" t="s">
         <v>19</v>
@@ -10219,20 +10216,20 @@
     </row>
     <row r="241" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B241" s="4" t="s">
         <v>54</v>
       </c>
       <c r="C241" s="4" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D241" s="5" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="E241" s="4"/>
       <c r="F241" s="5" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="G241" s="4" t="s">
         <v>49</v>
@@ -10249,27 +10246,27 @@
     </row>
     <row r="242" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B242" s="4" t="s">
         <v>54</v>
       </c>
       <c r="C242" s="17" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D242" s="5" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="E242" s="4"/>
       <c r="F242" s="5" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="G242" s="4" t="s">
         <v>31</v>
       </c>
       <c r="H242" s="4"/>
       <c r="I242" s="4" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="J242" s="4" t="s">
         <v>20</v>
@@ -10278,32 +10275,32 @@
         <v>21</v>
       </c>
       <c r="M242" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="243" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A243" s="13" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B243" s="13" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C243" s="19" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D243" s="5" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E243" s="13"/>
       <c r="F243" s="5" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="G243" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H243" s="4"/>
       <c r="I243" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="J243" s="4" t="s">
         <v>20</v>
@@ -10312,12 +10309,12 @@
         <v>71</v>
       </c>
       <c r="M243" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="244" spans="1:13" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A244" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B244" s="4" t="s">
         <v>89</v>
@@ -10326,11 +10323,11 @@
         <v>90</v>
       </c>
       <c r="D244" s="5" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E244" s="8"/>
       <c r="F244" s="16" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="G244" s="8" t="s">
         <v>39</v>
@@ -10347,7 +10344,7 @@
     </row>
     <row r="245" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B245" s="4" t="s">
         <v>89</v>
@@ -10356,18 +10353,18 @@
         <v>90</v>
       </c>
       <c r="D245" s="5" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E245" s="4"/>
       <c r="F245" s="5" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="G245" s="4" t="s">
         <v>25</v>
       </c>
       <c r="H245" s="4"/>
       <c r="I245" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="J245" s="4" t="s">
         <v>20</v>
@@ -10376,12 +10373,12 @@
         <v>21</v>
       </c>
       <c r="M245" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B246" s="4" t="s">
         <v>89</v>
@@ -10390,11 +10387,11 @@
         <v>90</v>
       </c>
       <c r="D246" s="5" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E246" s="4"/>
       <c r="F246" s="5" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="G246" s="4" t="s">
         <v>28</v>
@@ -10411,7 +10408,7 @@
     </row>
     <row r="247" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B247" s="4" t="s">
         <v>89</v>
@@ -10420,11 +10417,11 @@
         <v>98</v>
       </c>
       <c r="D247" s="5" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="E247" s="4"/>
       <c r="F247" s="5" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="G247" s="4" t="s">
         <v>56</v>
@@ -10441,7 +10438,7 @@
     </row>
     <row r="248" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B248" s="4" t="s">
         <v>89</v>
@@ -10450,11 +10447,11 @@
         <v>90</v>
       </c>
       <c r="D248" s="5" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E248" s="4"/>
       <c r="F248" s="5" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="G248" s="4" t="s">
         <v>35</v>
@@ -10471,7 +10468,7 @@
     </row>
     <row r="249" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B249" s="4" t="s">
         <v>89</v>
@@ -10480,18 +10477,18 @@
         <v>95</v>
       </c>
       <c r="D249" s="5" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="E249" s="4"/>
       <c r="F249" s="5" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="G249" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H249" s="4"/>
       <c r="I249" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="J249" s="4" t="s">
         <v>20</v>
@@ -10500,25 +10497,25 @@
         <v>21</v>
       </c>
       <c r="M249" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="250" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C250" s="4" t="s">
         <v>95</v>
       </c>
       <c r="D250" s="5" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E250" s="4"/>
       <c r="F250" s="5" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="G250" s="4" t="s">
         <v>49</v>
@@ -10535,20 +10532,20 @@
     </row>
     <row r="251" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C251" s="4" t="s">
         <v>90</v>
       </c>
       <c r="D251" s="5" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="E251" s="4"/>
       <c r="F251" s="5" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="G251" s="4" t="s">
         <v>31</v>
@@ -10565,23 +10562,23 @@
     </row>
     <row r="252" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C252" s="4" t="s">
         <v>95</v>
       </c>
       <c r="D252" s="5" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E252" s="4"/>
       <c r="F252" s="5" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="G252" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H252" s="4"/>
       <c r="I252" s="4"/>
@@ -10595,7 +10592,7 @@
     </row>
     <row r="253" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B253" s="4" t="s">
         <v>98</v>
@@ -10604,11 +10601,11 @@
         <v>104</v>
       </c>
       <c r="D253" s="5" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E253" s="4"/>
       <c r="F253" s="5" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="G253" s="4" t="s">
         <v>56</v>
@@ -10625,7 +10622,7 @@
     </row>
     <row r="254" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B254" s="4" t="s">
         <v>98</v>
@@ -10634,18 +10631,18 @@
         <v>115</v>
       </c>
       <c r="D254" s="4" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="E254" s="4"/>
       <c r="F254" s="4" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="G254" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H254" s="4"/>
       <c r="I254" s="24" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="J254" s="4" t="s">
         <v>20</v>
@@ -10654,12 +10651,12 @@
         <v>21</v>
       </c>
       <c r="M254" s="24" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="255" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B255" s="4" t="s">
         <v>95</v>
@@ -10668,11 +10665,11 @@
         <v>104</v>
       </c>
       <c r="D255" s="5" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="E255" s="4"/>
       <c r="F255" s="5" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="G255" s="4" t="s">
         <v>49</v>
@@ -10689,7 +10686,7 @@
     </row>
     <row r="256" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B256" s="4" t="s">
         <v>95</v>
@@ -10698,11 +10695,11 @@
         <v>104</v>
       </c>
       <c r="D256" s="5" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="E256" s="4"/>
       <c r="F256" s="5" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="G256" s="4" t="s">
         <v>19</v>
@@ -10719,7 +10716,7 @@
     </row>
     <row r="257" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B257" s="4" t="s">
         <v>90</v>
@@ -10728,11 +10725,11 @@
         <v>106</v>
       </c>
       <c r="D257" s="5" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="E257" s="4"/>
       <c r="F257" s="5" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="G257" s="4" t="s">
         <v>39</v>
@@ -10749,7 +10746,7 @@
     </row>
     <row r="258" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B258" s="4" t="s">
         <v>90</v>
@@ -10758,18 +10755,18 @@
         <v>106</v>
       </c>
       <c r="D258" s="5" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E258" s="4"/>
       <c r="F258" s="5" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="G258" s="4" t="s">
         <v>25</v>
       </c>
       <c r="H258" s="4"/>
       <c r="I258" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="J258" s="4" t="s">
         <v>20</v>
@@ -10778,12 +10775,12 @@
         <v>21</v>
       </c>
       <c r="M258" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="259" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B259" s="4" t="s">
         <v>90</v>
@@ -10792,11 +10789,11 @@
         <v>106</v>
       </c>
       <c r="D259" s="5" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="E259" s="4"/>
       <c r="F259" s="5" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="G259" s="4" t="s">
         <v>28</v>
@@ -10813,20 +10810,20 @@
     </row>
     <row r="260" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B260" s="4" t="s">
         <v>90</v>
       </c>
       <c r="C260" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D260" s="5" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E260" s="4"/>
       <c r="F260" s="5" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="G260" s="4" t="s">
         <v>31</v>
@@ -10843,7 +10840,7 @@
     </row>
     <row r="261" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B261" s="4" t="s">
         <v>90</v>
@@ -10852,18 +10849,18 @@
         <v>106</v>
       </c>
       <c r="D261" s="5" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="E261" s="4"/>
       <c r="F261" s="5" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="G261" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H261" s="4"/>
       <c r="I261" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="J261" s="4" t="s">
         <v>20</v>
@@ -10872,12 +10869,12 @@
         <v>21</v>
       </c>
       <c r="M261" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="262" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B262" s="4" t="s">
         <v>115</v>
@@ -10886,18 +10883,18 @@
         <v>106</v>
       </c>
       <c r="D262" s="4" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="E262" s="4"/>
       <c r="F262" s="4" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="G262" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H262" s="4"/>
       <c r="I262" s="24" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="J262" s="4" t="s">
         <v>20</v>
@@ -10906,12 +10903,12 @@
         <v>21</v>
       </c>
       <c r="M262" s="24" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="263" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B263" s="4" t="s">
         <v>104</v>
@@ -10920,11 +10917,11 @@
         <v>117</v>
       </c>
       <c r="D263" s="5" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E263" s="4"/>
       <c r="F263" s="5" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="G263" s="4" t="s">
         <v>49</v>
@@ -10941,7 +10938,7 @@
     </row>
     <row r="264" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B264" s="4" t="s">
         <v>104</v>
@@ -10950,18 +10947,18 @@
         <v>110</v>
       </c>
       <c r="D264" s="5" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="E264" s="4"/>
       <c r="F264" s="5" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="G264" s="4" t="s">
         <v>56</v>
       </c>
       <c r="H264" s="4"/>
       <c r="I264" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="J264" s="4" t="s">
         <v>20</v>
@@ -10970,12 +10967,12 @@
         <v>71</v>
       </c>
       <c r="M264" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="265" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B265" s="4" t="s">
         <v>104</v>
@@ -10984,18 +10981,18 @@
         <v>117</v>
       </c>
       <c r="D265" s="5" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="E265" s="4"/>
       <c r="F265" s="5" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="G265" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H265" s="4"/>
       <c r="I265" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="J265" s="4" t="s">
         <v>20</v>
@@ -11004,25 +11001,25 @@
         <v>21</v>
       </c>
       <c r="M265" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="266" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B266" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C266" s="4" t="s">
         <v>110</v>
       </c>
       <c r="D266" s="5" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="E266" s="4"/>
       <c r="F266" s="5" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="G266" s="4" t="s">
         <v>31</v>
@@ -11039,7 +11036,7 @@
     </row>
     <row r="267" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B267" s="4" t="s">
         <v>106</v>
@@ -11048,11 +11045,11 @@
         <v>119</v>
       </c>
       <c r="D267" s="5" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="E267" s="4"/>
       <c r="F267" s="5" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="G267" s="4" t="s">
         <v>39</v>
@@ -11069,7 +11066,7 @@
     </row>
     <row r="268" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B268" s="4" t="s">
         <v>106</v>
@@ -11078,18 +11075,18 @@
         <v>119</v>
       </c>
       <c r="D268" s="5" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="E268" s="4"/>
       <c r="F268" s="5" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="G268" s="4" t="s">
         <v>25</v>
       </c>
       <c r="H268" s="4"/>
       <c r="I268" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="J268" s="4" t="s">
         <v>20</v>
@@ -11098,12 +11095,12 @@
         <v>21</v>
       </c>
       <c r="M268" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="269" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B269" s="4" t="s">
         <v>106</v>
@@ -11112,18 +11109,18 @@
         <v>119</v>
       </c>
       <c r="D269" s="5" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="E269" s="4"/>
       <c r="F269" s="5" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="G269" s="4" t="s">
         <v>28</v>
       </c>
       <c r="H269" s="4"/>
       <c r="I269" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="J269" s="4" t="s">
         <v>20</v>
@@ -11132,12 +11129,12 @@
         <v>21</v>
       </c>
       <c r="M269" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="270" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B270" s="4" t="s">
         <v>106</v>
@@ -11146,18 +11143,18 @@
         <v>119</v>
       </c>
       <c r="D270" s="5" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="E270" s="4"/>
       <c r="F270" s="5" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="G270" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H270" s="4"/>
       <c r="I270" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="J270" s="4" t="s">
         <v>20</v>
@@ -11166,28 +11163,28 @@
         <v>21</v>
       </c>
       <c r="M270" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="271" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B271" s="4" t="s">
         <v>106</v>
       </c>
       <c r="C271" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D271" s="4" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="E271" s="4"/>
       <c r="F271" s="4" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="G271" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H271" s="4"/>
       <c r="I271" s="4"/>
@@ -11200,7 +11197,7 @@
     </row>
     <row r="272" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B272" s="4" t="s">
         <v>117</v>
@@ -11209,11 +11206,11 @@
         <v>119</v>
       </c>
       <c r="D272" s="5" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E272" s="4"/>
       <c r="F272" s="5" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="G272" s="4" t="s">
         <v>19</v>
@@ -11230,20 +11227,20 @@
     </row>
     <row r="273" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B273" s="4" t="s">
         <v>110</v>
       </c>
       <c r="C273" s="4" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="D273" s="5" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="E273" s="4"/>
       <c r="F273" s="5" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="G273" s="4" t="s">
         <v>31</v>
@@ -11260,7 +11257,7 @@
     </row>
     <row r="274" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B274" s="4" t="s">
         <v>110</v>
@@ -11269,18 +11266,18 @@
         <v>119</v>
       </c>
       <c r="D274" s="5" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E274" s="4"/>
       <c r="F274" s="5" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="G274" s="4" t="s">
         <v>56</v>
       </c>
       <c r="H274" s="4"/>
       <c r="I274" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="J274" s="4" t="s">
         <v>20</v>
@@ -11289,12 +11286,12 @@
         <v>71</v>
       </c>
       <c r="M274" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="275" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B275" s="4" t="s">
         <v>119</v>
@@ -11303,11 +11300,11 @@
         <v>129</v>
       </c>
       <c r="D275" s="5" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="E275" s="4"/>
       <c r="F275" s="5" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="G275" s="4" t="s">
         <v>25</v>
@@ -11324,7 +11321,7 @@
     </row>
     <row r="276" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B276" s="4" t="s">
         <v>119</v>
@@ -11333,18 +11330,18 @@
         <v>127</v>
       </c>
       <c r="D276" s="5" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="E276" s="4"/>
       <c r="F276" s="5" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="G276" s="4" t="s">
         <v>28</v>
       </c>
       <c r="H276" s="4"/>
       <c r="I276" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="J276" s="4" t="s">
         <v>20</v>
@@ -11353,32 +11350,32 @@
         <v>21</v>
       </c>
       <c r="M276" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="277" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B277" s="4" t="s">
         <v>119</v>
       </c>
       <c r="C277" s="4" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="D277" s="5" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="E277" s="4"/>
       <c r="F277" s="5" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="G277" s="4" t="s">
         <v>56</v>
       </c>
       <c r="H277" s="4"/>
       <c r="I277" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="J277" s="4" t="s">
         <v>20</v>
@@ -11387,12 +11384,12 @@
         <v>21</v>
       </c>
       <c r="M277" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="278" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B278" s="4" t="s">
         <v>119</v>
@@ -11401,18 +11398,18 @@
         <v>127</v>
       </c>
       <c r="D278" s="5" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="E278" s="4"/>
       <c r="F278" s="5" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="G278" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H278" s="4"/>
       <c r="I278" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="J278" s="4" t="s">
         <v>20</v>
@@ -11421,25 +11418,25 @@
         <v>21</v>
       </c>
       <c r="M278" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="279" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B279" s="4" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C279" s="4" t="s">
         <v>129</v>
       </c>
       <c r="D279" s="5" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E279" s="4"/>
       <c r="F279" s="5" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="G279" s="4" t="s">
         <v>56</v>
@@ -11456,7 +11453,7 @@
     </row>
     <row r="280" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B280" s="4" t="s">
         <v>127</v>
@@ -11465,18 +11462,18 @@
         <v>136</v>
       </c>
       <c r="D280" s="5" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="E280" s="4"/>
       <c r="F280" s="5" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="G280" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H280" s="4"/>
       <c r="I280" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="J280" s="4" t="s">
         <v>20</v>
@@ -11485,12 +11482,12 @@
         <v>21</v>
       </c>
       <c r="M280" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="281" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B281" s="4" t="s">
         <v>129</v>
@@ -11499,18 +11496,18 @@
         <v>134</v>
       </c>
       <c r="D281" s="5" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E281" s="4"/>
       <c r="F281" s="5" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="G281" s="4" t="s">
         <v>56</v>
       </c>
       <c r="H281" s="4"/>
       <c r="I281" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="J281" s="4" t="s">
         <v>20</v>
@@ -11519,12 +11516,12 @@
         <v>21</v>
       </c>
       <c r="M281" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="282" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B282" s="4" t="s">
         <v>136</v>
@@ -11533,11 +11530,11 @@
         <v>140</v>
       </c>
       <c r="D282" s="5" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E282" s="4"/>
       <c r="F282" s="5" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="G282" s="4" t="s">
         <v>35</v>
@@ -11554,7 +11551,7 @@
     </row>
     <row r="283" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B283" s="4" t="s">
         <v>134</v>
@@ -11563,18 +11560,18 @@
         <v>154</v>
       </c>
       <c r="D283" s="5" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="E283" s="4"/>
       <c r="F283" s="5" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="G283" s="4" t="s">
         <v>56</v>
       </c>
       <c r="H283" s="4"/>
       <c r="I283" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="J283" s="4" t="s">
         <v>20</v>
@@ -11583,12 +11580,12 @@
         <v>21</v>
       </c>
       <c r="M283" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="284" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B284" s="4" t="s">
         <v>134</v>
@@ -11597,18 +11594,18 @@
         <v>140</v>
       </c>
       <c r="D284" s="4" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E284" s="4"/>
       <c r="F284" s="4" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="G284" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H284" s="4"/>
       <c r="I284" s="4" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="J284" s="4" t="s">
         <v>20</v>
@@ -11617,12 +11614,12 @@
         <v>149</v>
       </c>
       <c r="M284" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="285" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B285" s="4" t="s">
         <v>140</v>
@@ -11631,18 +11628,18 @@
         <v>144</v>
       </c>
       <c r="D285" s="5" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E285" s="4"/>
       <c r="F285" s="5" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="G285" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H285" s="4"/>
       <c r="I285" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="J285" s="4" t="s">
         <v>20</v>
@@ -11651,12 +11648,12 @@
         <v>21</v>
       </c>
       <c r="M285" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="286" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B286" s="4" t="s">
         <v>140</v>
@@ -11686,27 +11683,27 @@
     </row>
     <row r="287" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B287" s="4" t="s">
         <v>154</v>
       </c>
       <c r="C287" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D287" s="5" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E287" s="4"/>
       <c r="F287" s="5" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="G287" s="4" t="s">
         <v>56</v>
       </c>
       <c r="H287" s="4"/>
       <c r="I287" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="J287" s="4" t="s">
         <v>20</v>
@@ -11715,28 +11712,28 @@
         <v>21</v>
       </c>
       <c r="M287" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="288" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B288" s="4" t="s">
         <v>154</v>
       </c>
       <c r="C288" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D288" s="5" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="E288" s="4"/>
       <c r="F288" s="5" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="G288" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H288" s="4"/>
       <c r="I288" s="4"/>
@@ -11750,27 +11747,27 @@
     </row>
     <row r="289" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B289" s="12" t="s">
         <v>154</v>
       </c>
       <c r="C289" s="12" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D289" s="4" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E289" s="4"/>
       <c r="F289" s="4" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="G289" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H289" s="4"/>
       <c r="I289" s="4" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="J289" s="4" t="s">
         <v>20</v>
@@ -11779,12 +11776,12 @@
         <v>149</v>
       </c>
       <c r="M289" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="290" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B290" s="4" t="s">
         <v>154</v>
@@ -11793,18 +11790,18 @@
         <v>144</v>
       </c>
       <c r="D290" s="4" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="E290" s="4"/>
       <c r="F290" s="4" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="G290" s="4" t="s">
         <v>152</v>
       </c>
       <c r="H290" s="4"/>
       <c r="I290" s="4" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="J290" s="4" t="s">
         <v>20</v>
@@ -11813,7 +11810,7 @@
         <v>149</v>
       </c>
       <c r="M290" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="291" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -11832,27 +11829,27 @@
     </row>
     <row r="292" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B292" s="4" t="s">
         <v>160</v>
       </c>
       <c r="C292" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D292" s="4" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E292" s="4"/>
       <c r="F292" s="4" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="G292" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H292" s="4"/>
       <c r="I292" s="4" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="J292" s="4" t="s">
         <v>20</v>
@@ -11861,12 +11858,12 @@
         <v>149</v>
       </c>
       <c r="M292" s="24" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="293" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B293" s="4" t="s">
         <v>144</v>
@@ -11875,18 +11872,18 @@
         <v>16</v>
       </c>
       <c r="D293" s="5" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E293" s="4"/>
       <c r="F293" s="5" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="G293" s="4" t="s">
         <v>39</v>
       </c>
       <c r="H293" s="4"/>
       <c r="I293" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="J293" s="4" t="s">
         <v>20</v>
@@ -11895,12 +11892,12 @@
         <v>21</v>
       </c>
       <c r="M293" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="294" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B294" s="4" t="s">
         <v>144</v>
@@ -11909,11 +11906,11 @@
         <v>16</v>
       </c>
       <c r="D294" s="5" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="E294" s="4"/>
       <c r="F294" s="5" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="G294" s="4" t="s">
         <v>28</v>
@@ -11930,7 +11927,7 @@
     </row>
     <row r="295" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B295" s="4" t="s">
         <v>144</v>
@@ -11939,11 +11936,11 @@
         <v>16</v>
       </c>
       <c r="D295" s="5" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="E295" s="4"/>
       <c r="F295" s="5" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G295" s="4" t="s">
         <v>31</v>
@@ -11960,7 +11957,7 @@
     </row>
     <row r="296" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B296" s="4" t="s">
         <v>144</v>
@@ -11969,11 +11966,11 @@
         <v>16</v>
       </c>
       <c r="D296" s="5" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="E296" s="4"/>
       <c r="F296" s="5" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="G296" s="4" t="s">
         <v>35</v>
@@ -11990,27 +11987,27 @@
     </row>
     <row r="297" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B297" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C297" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D297" s="4" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="E297" s="4"/>
       <c r="F297" s="4" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="G297" s="4" t="s">
         <v>152</v>
       </c>
       <c r="H297" s="4"/>
       <c r="I297" s="4" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="J297" s="4" t="s">
         <v>20</v>
@@ -12019,25 +12016,25 @@
         <v>149</v>
       </c>
       <c r="M297" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="298" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B298" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C298" s="4" t="s">
         <v>22</v>
       </c>
       <c r="D298" s="5" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E298" s="4"/>
       <c r="F298" s="5" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="G298" s="4" t="s">
         <v>56</v>
@@ -12054,7 +12051,7 @@
     </row>
     <row r="299" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A299" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B299" s="4" t="s">
         <v>16</v>
@@ -12063,11 +12060,11 @@
         <v>22</v>
       </c>
       <c r="D299" s="5" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="E299" s="4"/>
       <c r="F299" s="5" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="G299" s="4" t="s">
         <v>39</v>
@@ -12084,7 +12081,7 @@
     </row>
     <row r="300" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A300" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B300" s="4" t="s">
         <v>16</v>
@@ -12093,11 +12090,11 @@
         <v>22</v>
       </c>
       <c r="D300" s="5" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E300" s="4"/>
       <c r="F300" s="5" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="G300" s="4" t="s">
         <v>25</v>
@@ -12114,7 +12111,7 @@
     </row>
     <row r="301" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A301" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B301" s="4" t="s">
         <v>16</v>
@@ -12123,11 +12120,11 @@
         <v>22</v>
       </c>
       <c r="D301" s="5" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="E301" s="4"/>
       <c r="F301" s="5" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="G301" s="4" t="s">
         <v>28</v>
@@ -12144,7 +12141,7 @@
     </row>
     <row r="302" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A302" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B302" s="4" t="s">
         <v>16</v>
@@ -12153,11 +12150,11 @@
         <v>22</v>
       </c>
       <c r="D302" s="5" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E302" s="4"/>
       <c r="F302" s="5" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="G302" s="4" t="s">
         <v>31</v>
@@ -12174,7 +12171,7 @@
     </row>
     <row r="303" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B303" s="4" t="s">
         <v>16</v>
@@ -12183,18 +12180,18 @@
         <v>22</v>
       </c>
       <c r="D303" s="5" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E303" s="4"/>
       <c r="F303" s="5" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="G303" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H303" s="4"/>
       <c r="I303" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="J303" s="4" t="s">
         <v>20</v>
@@ -12203,32 +12200,32 @@
         <v>21</v>
       </c>
       <c r="M303" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="304" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B304" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C304" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D304" s="4" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="E304" s="4"/>
       <c r="F304" s="4" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="G304" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H304" s="4"/>
       <c r="I304" s="4" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="J304" s="4" t="s">
         <v>20</v>
@@ -12237,12 +12234,12 @@
         <v>149</v>
       </c>
       <c r="M304" s="24" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="305" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A305" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B305" s="4" t="s">
         <v>159</v>
@@ -12251,18 +12248,18 @@
         <v>22</v>
       </c>
       <c r="D305" s="5" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E305" s="4"/>
       <c r="F305" s="5" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="G305" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H305" s="4"/>
       <c r="I305" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="J305" s="4" t="s">
         <v>20</v>
@@ -12271,12 +12268,12 @@
         <v>21</v>
       </c>
       <c r="M305" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="306" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B306" s="4" t="s">
         <v>22</v>
@@ -12285,18 +12282,18 @@
         <v>23</v>
       </c>
       <c r="D306" s="5" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="E306" s="4"/>
       <c r="F306" s="5" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="G306" s="4" t="s">
         <v>39</v>
       </c>
       <c r="H306" s="4"/>
       <c r="I306" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="J306" s="4" t="s">
         <v>20</v>
@@ -12305,12 +12302,12 @@
         <v>21</v>
       </c>
       <c r="M306" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="307" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A307" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B307" s="4" t="s">
         <v>22</v>
@@ -12319,18 +12316,18 @@
         <v>23</v>
       </c>
       <c r="D307" s="5" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="E307" s="4"/>
       <c r="F307" s="5" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="G307" s="4" t="s">
         <v>25</v>
       </c>
       <c r="H307" s="4"/>
       <c r="I307" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="J307" s="4" t="s">
         <v>20</v>
@@ -12339,12 +12336,12 @@
         <v>21</v>
       </c>
       <c r="M307" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="308" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A308" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B308" s="4" t="s">
         <v>22</v>
@@ -12353,11 +12350,11 @@
         <v>23</v>
       </c>
       <c r="D308" s="5" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="E308" s="4"/>
       <c r="F308" s="5" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="G308" s="4" t="s">
         <v>28</v>
@@ -12374,7 +12371,7 @@
     </row>
     <row r="309" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A309" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B309" s="4" t="s">
         <v>22</v>
@@ -12383,11 +12380,11 @@
         <v>23</v>
       </c>
       <c r="D309" s="5" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="E309" s="4"/>
       <c r="F309" s="5" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="G309" s="4" t="s">
         <v>31</v>
@@ -12404,7 +12401,7 @@
     </row>
     <row r="310" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A310" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B310" s="4" t="s">
         <v>22</v>
@@ -12413,11 +12410,11 @@
         <v>43</v>
       </c>
       <c r="D310" s="5" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="E310" s="4"/>
       <c r="F310" s="5" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="G310" s="4" t="s">
         <v>56</v>
@@ -12434,7 +12431,7 @@
     </row>
     <row r="311" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A311" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B311" s="4" t="s">
         <v>22</v>
@@ -12443,18 +12440,18 @@
         <v>43</v>
       </c>
       <c r="D311" s="5" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="E311" s="4"/>
       <c r="F311" s="5" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="G311" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H311" s="4"/>
       <c r="I311" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="J311" s="4" t="s">
         <v>20</v>
@@ -12463,12 +12460,12 @@
         <v>21</v>
       </c>
       <c r="M311" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="312" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A312" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B312" s="4" t="s">
         <v>22</v>
@@ -12477,18 +12474,18 @@
         <v>29</v>
       </c>
       <c r="D312" s="5" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="E312" s="4"/>
       <c r="F312" s="5" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="G312" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H312" s="4"/>
       <c r="I312" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="J312" s="4" t="s">
         <v>20</v>
@@ -12497,12 +12494,12 @@
         <v>21</v>
       </c>
       <c r="M312" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="313" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A313" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B313" s="4" t="s">
         <v>22</v>
@@ -12511,18 +12508,18 @@
         <v>47</v>
       </c>
       <c r="D313" s="4" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="E313" s="4"/>
       <c r="F313" s="4" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="G313" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H313" s="4"/>
       <c r="I313" s="4" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="J313" s="4" t="s">
         <v>20</v>
@@ -12531,12 +12528,12 @@
         <v>149</v>
       </c>
       <c r="M313" s="24" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="314" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A314" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B314" s="4" t="s">
         <v>29</v>
@@ -12545,11 +12542,11 @@
         <v>43</v>
       </c>
       <c r="D314" s="5" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="E314" s="4"/>
       <c r="F314" s="5" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="G314" s="4" t="s">
         <v>19</v>
@@ -12566,7 +12563,7 @@
     </row>
     <row r="315" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A315" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B315" s="4" t="s">
         <v>23</v>
@@ -12575,11 +12572,11 @@
         <v>47</v>
       </c>
       <c r="D315" s="5" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="E315" s="4"/>
       <c r="F315" s="5" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="G315" s="4" t="s">
         <v>39</v>
@@ -12596,7 +12593,7 @@
     </row>
     <row r="316" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A316" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B316" s="4" t="s">
         <v>23</v>
@@ -12605,18 +12602,18 @@
         <v>54</v>
       </c>
       <c r="D316" s="5" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E316" s="4"/>
       <c r="F316" s="5" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="G316" s="4" t="s">
         <v>25</v>
       </c>
       <c r="H316" s="4"/>
       <c r="I316" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="J316" s="4" t="s">
         <v>20</v>
@@ -12625,12 +12622,12 @@
         <v>21</v>
       </c>
       <c r="M316" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
     </row>
     <row r="317" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A317" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B317" s="4" t="s">
         <v>23</v>
@@ -12639,18 +12636,18 @@
         <v>47</v>
       </c>
       <c r="D317" s="5" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="E317" s="4"/>
       <c r="F317" s="5" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="G317" s="4" t="s">
         <v>28</v>
       </c>
       <c r="H317" s="4"/>
       <c r="I317" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="J317" s="4" t="s">
         <v>20</v>
@@ -12659,32 +12656,32 @@
         <v>21</v>
       </c>
       <c r="M317" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="318" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A318" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B318" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C318" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D318" s="5" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="E318" s="4"/>
       <c r="F318" s="5" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G318" s="4" t="s">
         <v>31</v>
       </c>
       <c r="H318" s="4"/>
       <c r="I318" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="J318" s="4" t="s">
         <v>20</v>
@@ -12693,25 +12690,25 @@
         <v>21</v>
       </c>
       <c r="M318" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="319" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A319" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B319" s="4" t="s">
         <v>43</v>
       </c>
       <c r="C319" s="4" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="D319" s="5" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E319" s="4"/>
       <c r="F319" s="5" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G319" s="4" t="s">
         <v>56</v>
@@ -12728,7 +12725,7 @@
     </row>
     <row r="320" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A320" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B320" s="4" t="s">
         <v>43</v>
@@ -12736,12 +12733,12 @@
       <c r="C320" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D320" s="5" t="s">
-        <v>632</v>
+      <c r="D320" s="23" t="s">
+        <v>671</v>
       </c>
       <c r="E320" s="4"/>
-      <c r="F320" s="5" t="s">
-        <v>632</v>
+      <c r="F320" s="23" t="s">
+        <v>671</v>
       </c>
       <c r="G320" s="4" t="s">
         <v>35</v>
@@ -12758,7 +12755,7 @@
     </row>
     <row r="321" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A321" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B321" s="4" t="s">
         <v>43</v>
@@ -12767,18 +12764,18 @@
         <v>61</v>
       </c>
       <c r="D321" s="5" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="E321" s="4"/>
       <c r="F321" s="5" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="G321" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H321" s="4"/>
       <c r="I321" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="J321" s="4" t="s">
         <v>20</v>
@@ -12787,32 +12784,32 @@
         <v>21</v>
       </c>
       <c r="M321" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
     </row>
     <row r="322" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A322" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C322" s="4" t="s">
         <v>54</v>
       </c>
       <c r="D322" s="5" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="E322" s="4"/>
       <c r="F322" s="5" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="G322" s="4" t="s">
         <v>31</v>
       </c>
       <c r="H322" s="4"/>
       <c r="I322" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="J322" s="4" t="s">
         <v>20</v>
@@ -12821,25 +12818,25 @@
         <v>21</v>
       </c>
       <c r="M322" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
     </row>
     <row r="323" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A323" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B323" s="4" t="s">
         <v>47</v>
       </c>
       <c r="C323" s="4" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="D323" s="5" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="E323" s="4"/>
       <c r="F323" s="5" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="G323" s="4" t="s">
         <v>39</v>
@@ -12856,20 +12853,20 @@
     </row>
     <row r="324" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A324" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B324" s="4" t="s">
         <v>47</v>
       </c>
       <c r="C324" s="4" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="D324" s="5" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="E324" s="4"/>
       <c r="F324" s="5" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="G324" s="4" t="s">
         <v>28</v>
@@ -12886,27 +12883,27 @@
     </row>
     <row r="325" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A325" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B325" s="4" t="s">
         <v>61</v>
       </c>
       <c r="C325" s="4" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="D325" s="5" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="E325" s="4"/>
       <c r="F325" s="5" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="G325" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H325" s="4"/>
       <c r="I325" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="J325" s="4" t="s">
         <v>20</v>
@@ -12915,25 +12912,25 @@
         <v>21</v>
       </c>
       <c r="M325" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="326" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A326" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B326" s="4" t="s">
         <v>54</v>
       </c>
       <c r="C326" s="4" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="D326" s="5" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="E326" s="4"/>
       <c r="F326" s="5" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="G326" s="4" t="s">
         <v>25</v>
@@ -12950,20 +12947,20 @@
     </row>
     <row r="327" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A327" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B327" s="4" t="s">
         <v>54</v>
       </c>
       <c r="C327" s="4" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="D327" s="5" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="E327" s="4"/>
       <c r="F327" s="5" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="G327" s="4" t="s">
         <v>31</v>
@@ -12980,27 +12977,27 @@
     </row>
     <row r="328" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A328" s="13" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B328" s="13" t="s">
         <v>54</v>
       </c>
       <c r="C328" s="13" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="D328" s="32" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="E328" s="13"/>
       <c r="F328" s="15" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="G328" s="13" t="s">
         <v>35</v>
       </c>
       <c r="H328" s="13"/>
       <c r="I328" s="14" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="J328" s="13" t="s">
         <v>20</v>
@@ -13009,12 +13006,12 @@
         <v>21</v>
       </c>
       <c r="M328" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
     </row>
     <row r="329" spans="1:13" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A329" s="10" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B329" s="4" t="s">
         <v>89</v>
@@ -13023,11 +13020,11 @@
         <v>90</v>
       </c>
       <c r="D329" s="5" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="E329" s="4"/>
       <c r="F329" s="5" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="G329" s="4" t="s">
         <v>28</v>
@@ -13044,7 +13041,7 @@
     </row>
     <row r="330" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A330" s="4" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B330" s="4" t="s">
         <v>89</v>
@@ -13053,11 +13050,11 @@
         <v>90</v>
       </c>
       <c r="D330" s="5" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="E330" s="4"/>
       <c r="F330" s="5" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="G330" s="4" t="s">
         <v>56</v>
@@ -13074,27 +13071,27 @@
     </row>
     <row r="331" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A331" s="4" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C331" s="4" t="s">
         <v>90</v>
       </c>
       <c r="D331" s="5" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="E331" s="4"/>
       <c r="F331" s="5" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="G331" s="4" t="s">
         <v>31</v>
       </c>
       <c r="H331" s="4"/>
       <c r="I331" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="J331" s="4" t="s">
         <v>20</v>
@@ -13103,12 +13100,12 @@
         <v>21</v>
       </c>
       <c r="M331" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
     </row>
     <row r="332" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A332" s="4" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B332" s="4" t="s">
         <v>98</v>
@@ -13117,11 +13114,11 @@
         <v>104</v>
       </c>
       <c r="D332" s="5" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="E332" s="4"/>
       <c r="F332" s="5" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="G332" s="4" t="s">
         <v>35</v>
@@ -13138,7 +13135,7 @@
     </row>
     <row r="333" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A333" s="4" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B333" s="4" t="s">
         <v>90</v>
@@ -13147,11 +13144,11 @@
         <v>110</v>
       </c>
       <c r="D333" s="5" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="E333" s="4"/>
       <c r="F333" s="5" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="G333" s="4" t="s">
         <v>25</v>
@@ -13168,7 +13165,7 @@
     </row>
     <row r="334" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A334" s="4" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B334" s="4" t="s">
         <v>90</v>
@@ -13177,11 +13174,11 @@
         <v>106</v>
       </c>
       <c r="D334" s="5" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="E334" s="4"/>
       <c r="F334" s="5" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="G334" s="4" t="s">
         <v>28</v>
@@ -13198,7 +13195,7 @@
     </row>
     <row r="335" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A335" s="4" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B335" s="4" t="s">
         <v>90</v>
@@ -13207,18 +13204,18 @@
         <v>119</v>
       </c>
       <c r="D335" s="5" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="E335" s="4"/>
       <c r="F335" s="5" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="G335" s="4" t="s">
         <v>56</v>
       </c>
       <c r="H335" s="4"/>
       <c r="I335" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="J335" s="4" t="s">
         <v>20</v>
@@ -13227,12 +13224,12 @@
         <v>21</v>
       </c>
       <c r="M335" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
     </row>
     <row r="336" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A336" s="4" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B336" s="4" t="s">
         <v>104</v>
@@ -13241,18 +13238,18 @@
         <v>110</v>
       </c>
       <c r="D336" s="5" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="E336" s="4"/>
       <c r="F336" s="5" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="G336" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H336" s="4"/>
       <c r="I336" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="J336" s="4" t="s">
         <v>20</v>
@@ -13261,12 +13258,12 @@
         <v>21</v>
       </c>
       <c r="M336" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="337" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A337" s="4" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B337" s="4" t="s">
         <v>106</v>
@@ -13275,11 +13272,11 @@
         <v>119</v>
       </c>
       <c r="D337" s="5" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="E337" s="4"/>
       <c r="F337" s="5" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="G337" s="4" t="s">
         <v>28</v>
@@ -13296,20 +13293,20 @@
     </row>
     <row r="338" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A338" s="4" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B338" s="4" t="s">
         <v>110</v>
       </c>
       <c r="C338" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D338" s="5" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="E338" s="4"/>
       <c r="F338" s="5" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="G338" s="4" t="s">
         <v>35</v>
@@ -13326,7 +13323,7 @@
     </row>
     <row r="339" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A339" s="4" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B339" s="4" t="s">
         <v>119</v>
@@ -13335,11 +13332,11 @@
         <v>129</v>
       </c>
       <c r="D339" s="5" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="E339" s="4"/>
       <c r="F339" s="5" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="G339" s="4" t="s">
         <v>28</v>
@@ -13356,27 +13353,27 @@
     </row>
     <row r="340" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A340" s="4" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C340" s="4" t="s">
         <v>129</v>
       </c>
       <c r="D340" s="5" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="E340" s="4"/>
       <c r="F340" s="5" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="G340" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H340" s="4"/>
       <c r="I340" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="J340" s="4" t="s">
         <v>20</v>
@@ -13385,12 +13382,12 @@
         <v>21</v>
       </c>
       <c r="M340" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="341" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A341" s="4" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B341" s="4" t="s">
         <v>129</v>
@@ -13399,11 +13396,11 @@
         <v>134</v>
       </c>
       <c r="D341" s="5" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="E341" s="4"/>
       <c r="F341" s="5" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="G341" s="4" t="s">
         <v>35</v>
@@ -13420,7 +13417,7 @@
     </row>
     <row r="342" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A342" s="4" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B342" s="4" t="s">
         <v>134</v>
@@ -13429,11 +13426,11 @@
         <v>154</v>
       </c>
       <c r="D342" s="5" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="E342" s="4"/>
       <c r="F342" s="5" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="G342" s="4" t="s">
         <v>35</v>
@@ -13450,20 +13447,20 @@
     </row>
     <row r="343" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A343" s="4" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B343" s="4" t="s">
         <v>154</v>
       </c>
       <c r="C343" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D343" s="5" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="E343" s="4"/>
       <c r="F343" s="5" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="G343" s="4" t="s">
         <v>35</v>

--- a/import/timetable.xlsx
+++ b/import/timetable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michaelstork/Library/CloudStorage/Box-Box/Feel Festival/Marketing/03_Website/2026_timetable/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31A959D0-A685-0D40-BD38-7971F661195B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA132741-E5EA-E748-95FF-25676D477CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Worksheet!$A$3:$M$343</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Worksheet!$A$3:$M$342</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3046" uniqueCount="672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3048" uniqueCount="672">
   <si>
     <t>Timetable 2026</t>
   </si>
@@ -2301,7 +2301,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2343,9 +2343,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2372,17 +2369,37 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="20" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2583,7 +2600,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M343"/>
+  <dimension ref="A1:M342"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -2591,13 +2608,13 @@
     <col min="3" max="3" width="9" style="5" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="18" style="24" customWidth="1"/>
+    <col min="6" max="6" width="18" style="23" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="9" max="9" width="20" style="24" customWidth="1"/>
+    <col min="9" max="9" width="20" style="23" customWidth="1"/>
     <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="12" max="12" width="8.5" style="24"/>
-    <col min="13" max="13" width="27.6640625" style="24" customWidth="1"/>
+    <col min="12" max="12" width="8.5" style="23"/>
+    <col min="13" max="13" width="27.6640625" style="23" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.25">
@@ -2626,7 +2643,7 @@
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="25" t="s">
+      <c r="F3" s="24" t="s">
         <v>7</v>
       </c>
       <c r="G3" s="2" t="s">
@@ -2635,7 +2652,7 @@
       <c r="H3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="25" t="s">
+      <c r="I3" s="24" t="s">
         <v>10</v>
       </c>
       <c r="J3" s="2" t="s">
@@ -2644,10 +2661,10 @@
       <c r="K3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="27" t="s">
+      <c r="L3" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="27" t="s">
+      <c r="M3" s="26" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2655,10 +2672,10 @@
       <c r="A4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="21" t="s">
         <v>17</v>
       </c>
       <c r="D4" s="5" t="s">
@@ -2685,10 +2702,10 @@
       <c r="A5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="21" t="s">
         <v>23</v>
       </c>
       <c r="D5" s="5" t="s">
@@ -2719,10 +2736,10 @@
       <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="21" t="s">
         <v>23</v>
       </c>
       <c r="D6" s="5" t="s">
@@ -2749,10 +2766,10 @@
       <c r="A7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="21" t="s">
         <v>29</v>
       </c>
       <c r="D7" s="5" t="s">
@@ -2783,10 +2800,10 @@
       <c r="A8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="21" t="s">
         <v>29</v>
       </c>
       <c r="D8" s="5" t="s">
@@ -2817,10 +2834,10 @@
       <c r="A9" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="21" t="s">
         <v>37</v>
       </c>
       <c r="D9" s="5" t="s">
@@ -2851,10 +2868,10 @@
       <c r="A10" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="21" t="s">
         <v>23</v>
       </c>
       <c r="D10" s="5" t="s">
@@ -2885,10 +2902,10 @@
       <c r="A11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="21" t="s">
         <v>43</v>
       </c>
       <c r="D11" s="5" t="s">
@@ -2915,10 +2932,10 @@
       <c r="A12" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="21" t="s">
         <v>43</v>
       </c>
       <c r="D12" s="5" t="s">
@@ -2949,10 +2966,10 @@
       <c r="A13" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="21" t="s">
         <v>47</v>
       </c>
       <c r="D13" s="5" t="s">
@@ -2979,10 +2996,10 @@
       <c r="A14" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="21" t="s">
         <v>47</v>
       </c>
       <c r="D14" s="5" t="s">
@@ -3013,10 +3030,10 @@
       <c r="A15" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="21" t="s">
         <v>47</v>
       </c>
       <c r="D15" s="5" t="s">
@@ -3047,10 +3064,10 @@
       <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="21" t="s">
         <v>54</v>
       </c>
       <c r="D16" s="5" t="s">
@@ -3081,10 +3098,10 @@
       <c r="A17" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="21" t="s">
         <v>43</v>
       </c>
       <c r="D17" s="5" t="s">
@@ -3111,10 +3128,10 @@
       <c r="A18" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="21" t="s">
         <v>47</v>
       </c>
       <c r="D18" s="5" t="s">
@@ -3145,10 +3162,10 @@
       <c r="A19" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="21" t="s">
         <v>61</v>
       </c>
       <c r="D19" s="5" t="s">
@@ -3179,10 +3196,10 @@
       <c r="A20" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="21" t="s">
         <v>61</v>
       </c>
       <c r="D20" s="5" t="s">
@@ -3213,10 +3230,10 @@
       <c r="A21" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="21" t="s">
         <v>47</v>
       </c>
       <c r="D21" s="5" t="s">
@@ -3243,10 +3260,10 @@
       <c r="A22" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="21" t="s">
+      <c r="C22" s="20" t="s">
         <v>67</v>
       </c>
       <c r="D22" s="17" t="s">
@@ -3266,7 +3283,7 @@
       <c r="J22" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L22" s="29" t="s">
+      <c r="L22" s="28" t="s">
         <v>71</v>
       </c>
       <c r="M22" t="s">
@@ -3277,10 +3294,10 @@
       <c r="A23" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="21" t="s">
         <v>72</v>
       </c>
       <c r="D23" s="5" t="s">
@@ -3307,10 +3324,10 @@
       <c r="A24" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="21" t="s">
         <v>72</v>
       </c>
       <c r="D24" s="5" t="s">
@@ -3337,10 +3354,10 @@
       <c r="A25" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="21" t="s">
         <v>72</v>
       </c>
       <c r="D25" s="5" t="s">
@@ -3371,10 +3388,10 @@
       <c r="A26" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="21" t="s">
         <v>54</v>
       </c>
       <c r="D26" s="5" t="s">
@@ -3401,10 +3418,10 @@
       <c r="A27" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="21" t="s">
         <v>72</v>
       </c>
       <c r="D27" s="5" t="s">
@@ -3424,7 +3441,8 @@
       <c r="J27" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L27" s="6" t="s">
+      <c r="K27" s="34"/>
+      <c r="L27" s="35" t="s">
         <v>71</v>
       </c>
       <c r="M27" t="s">
@@ -3435,10 +3453,10 @@
       <c r="A28" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="21" t="s">
         <v>72</v>
       </c>
       <c r="D28" s="5" t="s">
@@ -3456,7 +3474,8 @@
       <c r="J28" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L28" s="6" t="s">
+      <c r="K28" s="34"/>
+      <c r="L28" s="35" t="s">
         <v>21</v>
       </c>
       <c r="M28"/>
@@ -3468,7 +3487,7 @@
       <c r="B29" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="21" t="s">
         <v>82</v>
       </c>
       <c r="D29" s="5" t="s">
@@ -3486,7 +3505,8 @@
       <c r="J29" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L29" s="29" t="s">
+      <c r="K29" s="34"/>
+      <c r="L29" s="35" t="s">
         <v>21</v>
       </c>
       <c r="M29"/>
@@ -3495,10 +3515,10 @@
       <c r="A30" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="21" t="s">
         <v>84</v>
       </c>
       <c r="D30" s="5" t="s">
@@ -3518,7 +3538,8 @@
       <c r="J30" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L30" s="6" t="s">
+      <c r="K30" s="34"/>
+      <c r="L30" s="35" t="s">
         <v>21</v>
       </c>
       <c r="M30" t="s">
@@ -3529,10 +3550,10 @@
       <c r="A31" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="21" t="s">
         <v>82</v>
       </c>
       <c r="D31" s="5" t="s">
@@ -3550,7 +3571,8 @@
       <c r="J31" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L31" s="6" t="s">
+      <c r="K31" s="34"/>
+      <c r="L31" s="35" t="s">
         <v>21</v>
       </c>
       <c r="M31"/>
@@ -3559,10 +3581,10 @@
       <c r="A32" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" s="37" t="s">
         <v>90</v>
       </c>
       <c r="D32" s="5" t="s">
@@ -3580,7 +3602,8 @@
       <c r="J32" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="L32" s="6" t="s">
+      <c r="K32" s="34"/>
+      <c r="L32" s="35" t="s">
         <v>21</v>
       </c>
       <c r="M32"/>
@@ -3589,10 +3612,10 @@
       <c r="A33" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="21" t="s">
         <v>90</v>
       </c>
       <c r="D33" s="5" t="s">
@@ -3619,13 +3642,13 @@
       <c r="A34" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="D34" s="31" t="s">
         <v>93</v>
       </c>
       <c r="E34" s="4"/>
@@ -3653,13 +3676,13 @@
       <c r="A35" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D35" s="31" t="s">
         <v>96</v>
       </c>
       <c r="E35" s="4"/>
@@ -3683,13 +3706,13 @@
       <c r="A36" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="C36" s="30">
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="D36" s="5" t="s">
+      <c r="C36" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="D36" s="31" t="s">
         <v>97</v>
       </c>
       <c r="E36" s="4"/>
@@ -3713,13 +3736,13 @@
       <c r="A37" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B37" s="21" t="s">
+      <c r="B37" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="C37" s="30">
-        <v>0.10416666666666667</v>
-      </c>
-      <c r="D37" s="5" t="s">
+      <c r="C37" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="D37" s="31" t="s">
         <v>99</v>
       </c>
       <c r="E37" s="4"/>
@@ -3747,10 +3770,10 @@
       <c r="A38" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B38" s="22" t="s">
+      <c r="B38" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="21" t="s">
         <v>90</v>
       </c>
       <c r="D38" s="4" t="s">
@@ -3781,10 +3804,10 @@
       <c r="A39" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="21" t="s">
         <v>104</v>
       </c>
       <c r="D39" s="5" t="s">
@@ -3811,10 +3834,10 @@
       <c r="A40" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="21" t="s">
         <v>106</v>
       </c>
       <c r="D40" s="5" t="s">
@@ -3841,10 +3864,10 @@
       <c r="A41" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" s="21" t="s">
         <v>106</v>
       </c>
       <c r="D41" s="5" t="s">
@@ -3871,10 +3894,10 @@
       <c r="A42" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" s="21" t="s">
         <v>106</v>
       </c>
       <c r="D42" s="5" t="s">
@@ -3901,10 +3924,10 @@
       <c r="A43" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" s="21" t="s">
         <v>110</v>
       </c>
       <c r="D43" s="5" t="s">
@@ -3935,10 +3958,10 @@
       <c r="A44" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="21" t="s">
         <v>106</v>
       </c>
       <c r="D44" s="5" t="s">
@@ -3965,10 +3988,10 @@
       <c r="A45" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C45" s="21" t="s">
         <v>106</v>
       </c>
       <c r="D45" s="5" t="s">
@@ -3995,17 +4018,17 @@
       <c r="A46" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="B46" s="21" t="s">
+      <c r="B46" s="20" t="s">
         <v>115</v>
       </c>
       <c r="C46" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="D46" s="23" t="s">
+      <c r="D46" s="22" t="s">
         <v>116</v>
       </c>
       <c r="E46" s="4"/>
-      <c r="F46" s="23" t="s">
+      <c r="F46" s="22" t="s">
         <v>116</v>
       </c>
       <c r="G46" s="17" t="s">
@@ -4025,10 +4048,10 @@
       <c r="A47" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C47" s="21" t="s">
         <v>117</v>
       </c>
       <c r="D47" s="5" t="s">
@@ -4055,10 +4078,10 @@
       <c r="A48" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C48" s="21" t="s">
         <v>119</v>
       </c>
       <c r="D48" s="5" t="s">
@@ -4085,10 +4108,10 @@
       <c r="A49" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="B49" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="C49" s="4" t="s">
+      <c r="C49" s="21" t="s">
         <v>119</v>
       </c>
       <c r="D49" s="5" t="s">
@@ -4115,10 +4138,10 @@
       <c r="A50" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="B50" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="C50" s="21" t="s">
         <v>119</v>
       </c>
       <c r="D50" s="5" t="s">
@@ -4149,10 +4172,10 @@
       <c r="A51" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B51" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="C51" s="21" t="s">
         <v>119</v>
       </c>
       <c r="D51" s="5" t="s">
@@ -4183,10 +4206,10 @@
       <c r="A52" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B52" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C52" s="21" t="s">
         <v>119</v>
       </c>
       <c r="D52" s="5" t="s">
@@ -4213,10 +4236,10 @@
       <c r="A53" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B53" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="C53" s="21" t="s">
         <v>127</v>
       </c>
       <c r="D53" s="5" t="s">
@@ -4243,10 +4266,10 @@
       <c r="A54" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="C54" s="21" t="s">
         <v>129</v>
       </c>
       <c r="D54" s="5" t="s">
@@ -4273,10 +4296,10 @@
       <c r="A55" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B55" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="C55" s="21" t="s">
         <v>127</v>
       </c>
       <c r="D55" s="5" t="s">
@@ -4303,10 +4326,10 @@
       <c r="A56" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="C56" s="21" t="s">
         <v>127</v>
       </c>
       <c r="D56" s="5" t="s">
@@ -4337,10 +4360,10 @@
       <c r="A57" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="B57" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="C57" s="21" t="s">
         <v>134</v>
       </c>
       <c r="D57" s="5" t="s">
@@ -4367,10 +4390,10 @@
       <c r="A58" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B58" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="C58" s="21" t="s">
         <v>136</v>
       </c>
       <c r="D58" s="5" t="s">
@@ -4401,10 +4424,10 @@
       <c r="A59" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B59" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="C59" s="4" t="s">
+      <c r="C59" s="21" t="s">
         <v>140</v>
       </c>
       <c r="D59" s="5" t="s">
@@ -4435,10 +4458,10 @@
       <c r="A60" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B60" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="C60" s="4" t="s">
+      <c r="C60" s="21" t="s">
         <v>144</v>
       </c>
       <c r="D60" s="4" t="s">
@@ -4469,10 +4492,10 @@
       <c r="A61" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B61" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="C61" s="21" t="s">
         <v>150</v>
       </c>
       <c r="D61" s="4" t="s">
@@ -4503,10 +4526,10 @@
       <c r="A62" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="B62" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="C62" s="4" t="s">
+      <c r="C62" s="21" t="s">
         <v>154</v>
       </c>
       <c r="D62" s="5" t="s">
@@ -4537,10 +4560,10 @@
       <c r="A63" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B63" s="4" t="s">
+      <c r="B63" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="C63" s="4" t="s">
+      <c r="C63" s="21" t="s">
         <v>144</v>
       </c>
       <c r="D63" s="5" t="s">
@@ -4571,10 +4594,10 @@
       <c r="A64" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B64" s="4" t="s">
+      <c r="B64" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="C64" s="4" t="s">
+      <c r="C64" s="21" t="s">
         <v>159</v>
       </c>
       <c r="D64" s="5" t="s">
@@ -4601,10 +4624,10 @@
       <c r="A65" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B65" s="4" t="s">
+      <c r="B65" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="C65" s="4" t="s">
+      <c r="C65" s="21" t="s">
         <v>160</v>
       </c>
       <c r="D65" s="17" t="s">
@@ -4635,10 +4658,10 @@
       <c r="A66" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="B66" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="C66" s="21" t="s">
         <v>160</v>
       </c>
       <c r="D66" s="4" t="s">
@@ -4669,10 +4692,10 @@
       <c r="A67" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B67" s="4" t="s">
+      <c r="B67" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="C67" s="4" t="s">
+      <c r="C67" s="21" t="s">
         <v>166</v>
       </c>
       <c r="D67" s="5" t="s">
@@ -4699,10 +4722,10 @@
       <c r="A68" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B68" s="4" t="s">
+      <c r="B68" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="C68" s="4" t="s">
+      <c r="C68" s="21" t="s">
         <v>168</v>
       </c>
       <c r="D68" s="4" t="s">
@@ -4716,16 +4739,16 @@
         <v>170</v>
       </c>
       <c r="H68" s="4"/>
-      <c r="I68" s="26" t="s">
+      <c r="I68" s="25" t="s">
         <v>171</v>
       </c>
       <c r="J68" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L68" s="33" t="s">
+      <c r="L68" s="30" t="s">
         <v>149</v>
       </c>
-      <c r="M68" s="24" t="s">
+      <c r="M68" s="23" t="s">
         <v>171</v>
       </c>
     </row>
@@ -4733,10 +4756,10 @@
       <c r="A69" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B69" s="4" t="s">
+      <c r="B69" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="C69" s="4" t="s">
+      <c r="C69" s="21" t="s">
         <v>168</v>
       </c>
       <c r="D69" s="5" t="s">
@@ -4763,10 +4786,10 @@
       <c r="A70" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B70" s="4" t="s">
+      <c r="B70" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="C70" s="4" t="s">
+      <c r="C70" s="21" t="s">
         <v>16</v>
       </c>
       <c r="D70" s="5" t="s">
@@ -4793,10 +4816,10 @@
       <c r="A71" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B71" s="4" t="s">
+      <c r="B71" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="C71" s="4" t="s">
+      <c r="C71" s="21" t="s">
         <v>16</v>
       </c>
       <c r="D71" s="5" t="s">
@@ -4823,10 +4846,10 @@
       <c r="A72" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B72" s="4" t="s">
+      <c r="B72" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="C72" s="4" t="s">
+      <c r="C72" s="21" t="s">
         <v>16</v>
       </c>
       <c r="D72" s="5" t="s">
@@ -4844,7 +4867,7 @@
       <c r="J72" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L72" s="29" t="s">
+      <c r="L72" s="28" t="s">
         <v>149</v>
       </c>
       <c r="M72"/>
@@ -4853,10 +4876,10 @@
       <c r="A73" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B73" s="4" t="s">
+      <c r="B73" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="C73" s="4" t="s">
+      <c r="C73" s="21" t="s">
         <v>16</v>
       </c>
       <c r="D73" s="5" t="s">
@@ -4887,10 +4910,10 @@
       <c r="A74" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B74" s="4" t="s">
+      <c r="B74" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="C74" s="4" t="s">
+      <c r="C74" s="21" t="s">
         <v>16</v>
       </c>
       <c r="D74" s="4" t="s">
@@ -4921,10 +4944,10 @@
       <c r="A75" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B75" s="4" t="s">
+      <c r="B75" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="C75" s="4" t="s">
+      <c r="C75" s="21" t="s">
         <v>181</v>
       </c>
       <c r="D75" s="4" t="s">
@@ -4955,10 +4978,10 @@
       <c r="A76" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B76" s="4" t="s">
+      <c r="B76" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="C76" s="4" t="s">
+      <c r="C76" s="21" t="s">
         <v>159</v>
       </c>
       <c r="D76" s="4" t="s">
@@ -4989,10 +5012,10 @@
       <c r="A77" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B77" s="4" t="s">
+      <c r="B77" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="C77" s="4" t="s">
+      <c r="C77" s="21" t="s">
         <v>187</v>
       </c>
       <c r="D77" s="5" t="s">
@@ -5019,10 +5042,10 @@
       <c r="A78" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B78" s="4" t="s">
+      <c r="B78" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="C78" s="4" t="s">
+      <c r="C78" s="21" t="s">
         <v>187</v>
       </c>
       <c r="D78" s="4" t="s">
@@ -5042,10 +5065,10 @@
       <c r="J78" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L78" s="28" t="s">
+      <c r="L78" s="27" t="s">
         <v>149</v>
       </c>
-      <c r="M78" s="24" t="s">
+      <c r="M78" s="23" t="s">
         <v>190</v>
       </c>
     </row>
@@ -5053,10 +5076,10 @@
       <c r="A79" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B79" s="4" t="s">
+      <c r="B79" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="C79" s="4" t="s">
+      <c r="C79" s="21" t="s">
         <v>187</v>
       </c>
       <c r="D79" s="5" t="s">
@@ -5087,10 +5110,10 @@
       <c r="A80" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B80" s="4" t="s">
+      <c r="B80" s="21" t="s">
         <v>181</v>
       </c>
-      <c r="C80" s="4" t="s">
+      <c r="C80" s="21" t="s">
         <v>16</v>
       </c>
       <c r="D80" s="5" t="s">
@@ -5117,10 +5140,10 @@
       <c r="A81" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B81" s="4" t="s">
+      <c r="B81" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C81" s="4" t="s">
+      <c r="C81" s="21" t="s">
         <v>22</v>
       </c>
       <c r="D81" s="5" t="s">
@@ -5147,10 +5170,10 @@
       <c r="A82" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B82" s="4" t="s">
+      <c r="B82" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C82" s="4" t="s">
+      <c r="C82" s="21" t="s">
         <v>22</v>
       </c>
       <c r="D82" s="5" t="s">
@@ -5181,10 +5204,10 @@
       <c r="A83" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B83" s="4" t="s">
+      <c r="B83" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C83" s="4" t="s">
+      <c r="C83" s="21" t="s">
         <v>22</v>
       </c>
       <c r="D83" s="5" t="s">
@@ -5211,10 +5234,10 @@
       <c r="A84" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B84" s="4" t="s">
+      <c r="B84" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C84" s="4" t="s">
+      <c r="C84" s="21" t="s">
         <v>22</v>
       </c>
       <c r="D84" s="5" t="s">
@@ -5245,10 +5268,10 @@
       <c r="A85" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B85" s="4" t="s">
+      <c r="B85" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C85" s="4" t="s">
+      <c r="C85" s="21" t="s">
         <v>201</v>
       </c>
       <c r="D85" s="4" t="s">
@@ -5279,10 +5302,10 @@
       <c r="A86" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B86" s="4" t="s">
+      <c r="B86" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="C86" s="4" t="s">
+      <c r="C86" s="21" t="s">
         <v>204</v>
       </c>
       <c r="D86" s="5" t="s">
@@ -5313,10 +5336,10 @@
       <c r="A87" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B87" s="4" t="s">
+      <c r="B87" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="C87" s="4" t="s">
+      <c r="C87" s="21" t="s">
         <v>22</v>
       </c>
       <c r="D87" s="5" t="s">
@@ -5347,10 +5370,10 @@
       <c r="A88" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B88" s="4" t="s">
+      <c r="B88" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="C88" s="4" t="s">
+      <c r="C88" s="21" t="s">
         <v>201</v>
       </c>
       <c r="D88" s="4" t="s">
@@ -5381,10 +5404,10 @@
       <c r="A89" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B89" s="4" t="s">
+      <c r="B89" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="C89" s="4" t="s">
+      <c r="C89" s="21" t="s">
         <v>17</v>
       </c>
       <c r="D89" s="4" t="s">
@@ -5415,7 +5438,7 @@
       <c r="A90" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B90" s="4" t="s">
+      <c r="B90" s="21" t="s">
         <v>187</v>
       </c>
       <c r="C90" s="12" t="s">
@@ -5438,10 +5461,10 @@
       <c r="J90" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L90" s="28" t="s">
+      <c r="L90" s="27" t="s">
         <v>149</v>
       </c>
-      <c r="M90" s="24" t="s">
+      <c r="M90" s="23" t="s">
         <v>216</v>
       </c>
     </row>
@@ -5449,10 +5472,10 @@
       <c r="A91" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B91" s="4" t="s">
+      <c r="B91" s="21" t="s">
         <v>201</v>
       </c>
-      <c r="C91" s="4" t="s">
+      <c r="C91" s="21" t="s">
         <v>217</v>
       </c>
       <c r="D91" s="5" t="s">
@@ -5479,10 +5502,10 @@
       <c r="A92" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B92" s="4" t="s">
+      <c r="B92" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C92" s="4" t="s">
+      <c r="C92" s="21" t="s">
         <v>219</v>
       </c>
       <c r="D92" s="5" t="s">
@@ -5509,10 +5532,10 @@
       <c r="A93" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B93" s="4" t="s">
+      <c r="B93" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C93" s="4" t="s">
+      <c r="C93" s="21" t="s">
         <v>23</v>
       </c>
       <c r="D93" s="5" t="s">
@@ -5539,10 +5562,10 @@
       <c r="A94" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B94" s="4" t="s">
+      <c r="B94" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C94" s="4" t="s">
+      <c r="C94" s="21" t="s">
         <v>17</v>
       </c>
       <c r="D94" s="4" t="s">
@@ -5569,10 +5592,10 @@
       <c r="A95" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B95" s="4" t="s">
+      <c r="B95" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C95" s="4" t="s">
+      <c r="C95" s="21" t="s">
         <v>23</v>
       </c>
       <c r="D95" s="5" t="s">
@@ -5603,10 +5626,10 @@
       <c r="A96" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B96" s="4" t="s">
+      <c r="B96" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C96" s="4" t="s">
+      <c r="C96" s="21" t="s">
         <v>23</v>
       </c>
       <c r="D96" s="5" t="s">
@@ -5633,10 +5656,10 @@
       <c r="A97" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B97" s="4" t="s">
+      <c r="B97" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C97" s="4" t="s">
+      <c r="C97" s="21" t="s">
         <v>23</v>
       </c>
       <c r="D97" s="5" t="s">
@@ -5667,10 +5690,10 @@
       <c r="A98" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B98" s="4" t="s">
+      <c r="B98" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C98" s="4" t="s">
+      <c r="C98" s="21" t="s">
         <v>23</v>
       </c>
       <c r="D98" s="5" t="s">
@@ -5697,10 +5720,10 @@
       <c r="A99" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B99" s="4" t="s">
+      <c r="B99" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C99" s="4" t="s">
+      <c r="C99" s="21" t="s">
         <v>17</v>
       </c>
       <c r="D99" s="4" t="s">
@@ -5731,10 +5754,10 @@
       <c r="A100" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B100" s="4" t="s">
+      <c r="B100" s="21" t="s">
         <v>231</v>
       </c>
-      <c r="C100" s="4" t="s">
+      <c r="C100" s="21" t="s">
         <v>232</v>
       </c>
       <c r="D100" s="5" t="s">
@@ -5761,10 +5784,10 @@
       <c r="A101" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B101" s="4" t="s">
+      <c r="B101" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="C101" s="4" t="s">
+      <c r="C101" s="21" t="s">
         <v>234</v>
       </c>
       <c r="D101" s="5" t="s">
@@ -5782,7 +5805,7 @@
       <c r="J101" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L101" s="29" t="s">
+      <c r="L101" s="28" t="s">
         <v>71</v>
       </c>
       <c r="M101"/>
@@ -5791,10 +5814,10 @@
       <c r="A102" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B102" s="4" t="s">
+      <c r="B102" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="C102" s="4" t="s">
+      <c r="C102" s="21" t="s">
         <v>23</v>
       </c>
       <c r="D102" s="5" t="s">
@@ -5825,10 +5848,10 @@
       <c r="A103" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B103" s="4" t="s">
+      <c r="B103" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="C103" s="4" t="s">
+      <c r="C103" s="21" t="s">
         <v>23</v>
       </c>
       <c r="D103" s="5" t="s">
@@ -5855,10 +5878,10 @@
       <c r="A104" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B104" s="4" t="s">
+      <c r="B104" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="C104" s="4" t="s">
+      <c r="C104" s="21" t="s">
         <v>23</v>
       </c>
       <c r="D104" s="4" t="s">
@@ -5878,10 +5901,10 @@
       <c r="J104" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L104" s="28" t="s">
+      <c r="L104" s="27" t="s">
         <v>149</v>
       </c>
-      <c r="M104" s="24" t="s">
+      <c r="M104" s="23" t="s">
         <v>241</v>
       </c>
     </row>
@@ -5889,10 +5912,10 @@
       <c r="A105" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B105" s="4" t="s">
+      <c r="B105" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="C105" s="4" t="s">
+      <c r="C105" s="21" t="s">
         <v>23</v>
       </c>
       <c r="D105" s="4" t="s">
@@ -5923,10 +5946,10 @@
       <c r="A106" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B106" s="4" t="s">
+      <c r="B106" s="21" t="s">
         <v>234</v>
       </c>
-      <c r="C106" s="4" t="s">
+      <c r="C106" s="21" t="s">
         <v>37</v>
       </c>
       <c r="D106" s="5" t="s">
@@ -5957,10 +5980,10 @@
       <c r="A107" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B107" s="4" t="s">
+      <c r="B107" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C107" s="4" t="s">
+      <c r="C107" s="21" t="s">
         <v>47</v>
       </c>
       <c r="D107" s="5" t="s">
@@ -5987,10 +6010,10 @@
       <c r="A108" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B108" s="4" t="s">
+      <c r="B108" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C108" s="4" t="s">
+      <c r="C108" s="21" t="s">
         <v>47</v>
       </c>
       <c r="D108" s="5" t="s">
@@ -6017,10 +6040,10 @@
       <c r="A109" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B109" s="4" t="s">
+      <c r="B109" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C109" s="4" t="s">
+      <c r="C109" s="21" t="s">
         <v>47</v>
       </c>
       <c r="D109" s="5" t="s">
@@ -6047,10 +6070,10 @@
       <c r="A110" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B110" s="4" t="s">
+      <c r="B110" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C110" s="4" t="s">
+      <c r="C110" s="21" t="s">
         <v>47</v>
       </c>
       <c r="D110" s="5" t="s">
@@ -6077,10 +6100,10 @@
       <c r="A111" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B111" s="4" t="s">
+      <c r="B111" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C111" s="4" t="s">
+      <c r="C111" s="21" t="s">
         <v>47</v>
       </c>
       <c r="D111" s="5" t="s">
@@ -6111,13 +6134,13 @@
       <c r="A112" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B112" s="4" t="s">
+      <c r="B112" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C112" s="4" t="s">
+      <c r="C112" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="D112" s="31" t="s">
+      <c r="D112" s="29" t="s">
         <v>252</v>
       </c>
       <c r="E112" s="4"/>
@@ -6141,10 +6164,10 @@
       <c r="A113" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B113" s="4" t="s">
+      <c r="B113" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C113" s="4" t="s">
+      <c r="C113" s="21" t="s">
         <v>47</v>
       </c>
       <c r="D113" s="5" t="s">
@@ -6175,10 +6198,10 @@
       <c r="A114" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B114" s="4" t="s">
+      <c r="B114" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C114" s="4" t="s">
+      <c r="C114" s="21" t="s">
         <v>256</v>
       </c>
       <c r="D114" s="5" t="s">
@@ -6209,10 +6232,10 @@
       <c r="A115" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B115" s="4" t="s">
+      <c r="B115" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C115" s="4" t="s">
+      <c r="C115" s="21" t="s">
         <v>43</v>
       </c>
       <c r="D115" s="4" t="s">
@@ -6232,10 +6255,10 @@
       <c r="J115" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L115" s="28" t="s">
+      <c r="L115" s="27" t="s">
         <v>149</v>
       </c>
-      <c r="M115" s="24" t="s">
+      <c r="M115" s="23" t="s">
         <v>261</v>
       </c>
     </row>
@@ -6243,10 +6266,10 @@
       <c r="A116" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B116" s="4" t="s">
+      <c r="B116" s="21" t="s">
         <v>262</v>
       </c>
-      <c r="C116" s="4" t="s">
+      <c r="C116" s="21" t="s">
         <v>263</v>
       </c>
       <c r="D116" s="5" t="s">
@@ -6273,10 +6296,10 @@
       <c r="A117" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B117" s="4" t="s">
+      <c r="B117" s="21" t="s">
         <v>265</v>
       </c>
-      <c r="C117" s="4" t="s">
+      <c r="C117" s="21" t="s">
         <v>266</v>
       </c>
       <c r="D117" s="5" t="s">
@@ -6307,10 +6330,10 @@
       <c r="A118" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B118" s="4" t="s">
+      <c r="B118" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="C118" s="4" t="s">
+      <c r="C118" s="21" t="s">
         <v>47</v>
       </c>
       <c r="D118" s="4" t="s">
@@ -6330,10 +6353,10 @@
       <c r="J118" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L118" s="28" t="s">
+      <c r="L118" s="27" t="s">
         <v>149</v>
       </c>
-      <c r="M118" s="24" t="s">
+      <c r="M118" s="23" t="s">
         <v>270</v>
       </c>
     </row>
@@ -6341,10 +6364,10 @@
       <c r="A119" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B119" s="4" t="s">
+      <c r="B119" s="21" t="s">
         <v>256</v>
       </c>
-      <c r="C119" s="4" t="s">
+      <c r="C119" s="21" t="s">
         <v>54</v>
       </c>
       <c r="D119" s="5" t="s">
@@ -6371,10 +6394,10 @@
       <c r="A120" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B120" s="4" t="s">
+      <c r="B120" s="21" t="s">
         <v>272</v>
       </c>
-      <c r="C120" s="4" t="s">
+      <c r="C120" s="21" t="s">
         <v>67</v>
       </c>
       <c r="D120" s="5" t="s">
@@ -6405,10 +6428,10 @@
       <c r="A121" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B121" s="4" t="s">
+      <c r="B121" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C121" s="17" t="s">
+      <c r="C121" s="12" t="s">
         <v>275</v>
       </c>
       <c r="D121" s="5" t="s">
@@ -6435,10 +6458,10 @@
       <c r="A122" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B122" s="4" t="s">
+      <c r="B122" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C122" s="17" t="s">
+      <c r="C122" s="12" t="s">
         <v>275</v>
       </c>
       <c r="D122" s="5" t="s">
@@ -6465,10 +6488,10 @@
       <c r="A123" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B123" s="4" t="s">
+      <c r="B123" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C123" s="17" t="s">
+      <c r="C123" s="12" t="s">
         <v>275</v>
       </c>
       <c r="D123" s="5" t="s">
@@ -6499,10 +6522,10 @@
       <c r="A124" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B124" s="4" t="s">
+      <c r="B124" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C124" s="4" t="s">
+      <c r="C124" s="21" t="s">
         <v>281</v>
       </c>
       <c r="D124" s="5" t="s">
@@ -6529,10 +6552,10 @@
       <c r="A125" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B125" s="4" t="s">
+      <c r="B125" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C125" s="4" t="s">
+      <c r="C125" s="21" t="s">
         <v>275</v>
       </c>
       <c r="D125" s="5" t="s">
@@ -6563,10 +6586,10 @@
       <c r="A126" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B126" s="4" t="s">
+      <c r="B126" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C126" s="4" t="s">
+      <c r="C126" s="21" t="s">
         <v>275</v>
       </c>
       <c r="D126" s="5" t="s">
@@ -6593,10 +6616,10 @@
       <c r="A127" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B127" s="4" t="s">
+      <c r="B127" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C127" s="4" t="s">
+      <c r="C127" s="21" t="s">
         <v>67</v>
       </c>
       <c r="D127" s="5" t="s">
@@ -6623,10 +6646,10 @@
       <c r="A128" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B128" s="4" t="s">
+      <c r="B128" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C128" s="4" t="s">
+      <c r="C128" s="21" t="s">
         <v>281</v>
       </c>
       <c r="D128" s="5" t="s">
@@ -6653,10 +6676,10 @@
       <c r="A129" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B129" s="4" t="s">
+      <c r="B129" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="C129" s="4" t="s">
+      <c r="C129" s="21" t="s">
         <v>281</v>
       </c>
       <c r="D129" s="4" t="s">
@@ -6676,10 +6699,10 @@
       <c r="J129" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L129" s="28" t="s">
+      <c r="L129" s="27" t="s">
         <v>149</v>
       </c>
-      <c r="M129" s="24" t="s">
+      <c r="M129" s="23" t="s">
         <v>290</v>
       </c>
     </row>
@@ -6687,10 +6710,10 @@
       <c r="A130" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B130" s="4" t="s">
+      <c r="B130" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="C130" s="17" t="s">
+      <c r="C130" s="12" t="s">
         <v>291</v>
       </c>
       <c r="D130" s="5" t="s">
@@ -6717,10 +6740,10 @@
       <c r="A131" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B131" s="4" t="s">
+      <c r="B131" s="21" t="s">
         <v>293</v>
       </c>
-      <c r="C131" s="17" t="s">
+      <c r="C131" s="12" t="s">
         <v>294</v>
       </c>
       <c r="D131" s="5" t="s">
@@ -6747,10 +6770,10 @@
       <c r="A132" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B132" s="4" t="s">
+      <c r="B132" s="21" t="s">
         <v>293</v>
       </c>
-      <c r="C132" s="17" t="s">
+      <c r="C132" s="12" t="s">
         <v>296</v>
       </c>
       <c r="D132" s="5" t="s">
@@ -6781,10 +6804,10 @@
       <c r="A133" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B133" s="4" t="s">
+      <c r="B133" s="21" t="s">
         <v>281</v>
       </c>
-      <c r="C133" s="17" t="s">
+      <c r="C133" s="12" t="s">
         <v>299</v>
       </c>
       <c r="D133" s="5" t="s">
@@ -6811,10 +6834,10 @@
       <c r="A134" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="B134" s="13" t="s">
+      <c r="B134" s="40" t="s">
         <v>281</v>
       </c>
-      <c r="C134" s="19" t="s">
+      <c r="C134" s="39" t="s">
         <v>299</v>
       </c>
       <c r="D134" s="5" t="s">
@@ -6845,10 +6868,10 @@
       <c r="A135" s="10" t="s">
         <v>303</v>
       </c>
-      <c r="B135" s="4" t="s">
+      <c r="B135" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="C135" s="4" t="s">
+      <c r="C135" s="21" t="s">
         <v>90</v>
       </c>
       <c r="D135" s="5" t="s">
@@ -6875,10 +6898,10 @@
       <c r="A136" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B136" s="4" t="s">
+      <c r="B136" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="C136" s="4" t="s">
+      <c r="C136" s="21" t="s">
         <v>90</v>
       </c>
       <c r="D136" s="5" t="s">
@@ -6905,10 +6928,10 @@
       <c r="A137" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B137" s="4" t="s">
+      <c r="B137" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="C137" s="4" t="s">
+      <c r="C137" s="21" t="s">
         <v>90</v>
       </c>
       <c r="D137" s="5" t="s">
@@ -6939,10 +6962,10 @@
       <c r="A138" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B138" s="4" t="s">
+      <c r="B138" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="C138" s="4" t="s">
+      <c r="C138" s="21" t="s">
         <v>90</v>
       </c>
       <c r="D138" s="5" t="s">
@@ -6969,10 +6992,10 @@
       <c r="A139" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B139" s="4" t="s">
+      <c r="B139" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="C139" s="4" t="s">
+      <c r="C139" s="21" t="s">
         <v>90</v>
       </c>
       <c r="D139" s="5" t="s">
@@ -7003,10 +7026,10 @@
       <c r="A140" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B140" s="4" t="s">
+      <c r="B140" s="21" t="s">
         <v>313</v>
       </c>
-      <c r="C140" s="4" t="s">
+      <c r="C140" s="21" t="s">
         <v>314</v>
       </c>
       <c r="D140" s="5" t="s">
@@ -7033,10 +7056,10 @@
       <c r="A141" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B141" s="4" t="s">
+      <c r="B141" s="21" t="s">
         <v>316</v>
       </c>
-      <c r="C141" s="4" t="s">
+      <c r="C141" s="21" t="s">
         <v>90</v>
       </c>
       <c r="D141" s="5" t="s">
@@ -7063,10 +7086,10 @@
       <c r="A142" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B142" s="4" t="s">
+      <c r="B142" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="C142" s="4" t="s">
+      <c r="C142" s="21" t="s">
         <v>115</v>
       </c>
       <c r="D142" s="5" t="s">
@@ -7093,10 +7116,10 @@
       <c r="A143" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B143" s="4" t="s">
+      <c r="B143" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="C143" s="4" t="s">
+      <c r="C143" s="21" t="s">
         <v>115</v>
       </c>
       <c r="D143" s="5" t="s">
@@ -7123,10 +7146,10 @@
       <c r="A144" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B144" s="4" t="s">
+      <c r="B144" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="C144" s="4" t="s">
+      <c r="C144" s="21" t="s">
         <v>115</v>
       </c>
       <c r="D144" s="4" t="s">
@@ -7140,16 +7163,16 @@
         <v>170</v>
       </c>
       <c r="H144" s="4"/>
-      <c r="I144" s="24" t="s">
+      <c r="I144" s="23" t="s">
         <v>321</v>
       </c>
       <c r="J144" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L144" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="M144" s="24" t="s">
+      <c r="L144" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="M144" s="23" t="s">
         <v>321</v>
       </c>
     </row>
@@ -7157,10 +7180,10 @@
       <c r="A145" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B145" s="4" t="s">
+      <c r="B145" s="21" t="s">
         <v>314</v>
       </c>
-      <c r="C145" s="4" t="s">
+      <c r="C145" s="21" t="s">
         <v>322</v>
       </c>
       <c r="D145" s="5" t="s">
@@ -7187,10 +7210,10 @@
       <c r="A146" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B146" s="4" t="s">
+      <c r="B146" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="C146" s="4" t="s">
+      <c r="C146" s="21" t="s">
         <v>106</v>
       </c>
       <c r="D146" s="5" t="s">
@@ -7217,10 +7240,10 @@
       <c r="A147" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B147" s="4" t="s">
+      <c r="B147" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="C147" s="4" t="s">
+      <c r="C147" s="21" t="s">
         <v>325</v>
       </c>
       <c r="D147" s="5" t="s">
@@ -7247,10 +7270,10 @@
       <c r="A148" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B148" s="4" t="s">
+      <c r="B148" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="C148" s="4" t="s">
+      <c r="C148" s="21" t="s">
         <v>106</v>
       </c>
       <c r="D148" t="s">
@@ -7277,10 +7300,10 @@
       <c r="A149" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B149" s="4" t="s">
+      <c r="B149" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="C149" s="4" t="s">
+      <c r="C149" s="21" t="s">
         <v>106</v>
       </c>
       <c r="D149" s="5" t="s">
@@ -7311,10 +7334,10 @@
       <c r="A150" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B150" s="4" t="s">
+      <c r="B150" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="C150" s="4" t="s">
+      <c r="C150" s="21" t="s">
         <v>106</v>
       </c>
       <c r="D150" s="5" t="s">
@@ -7345,10 +7368,10 @@
       <c r="A151" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B151" s="4" t="s">
+      <c r="B151" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="C151" s="4" t="s">
+      <c r="C151" s="21" t="s">
         <v>106</v>
       </c>
       <c r="D151" s="5" t="s">
@@ -7379,10 +7402,10 @@
       <c r="A152" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B152" s="4" t="s">
+      <c r="B152" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="C152" s="4" t="s">
+      <c r="C152" s="21" t="s">
         <v>106</v>
       </c>
       <c r="D152" s="5" t="s">
@@ -7409,10 +7432,10 @@
       <c r="A153" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B153" s="4" t="s">
+      <c r="B153" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="C153" s="4" t="s">
+      <c r="C153" s="21" t="s">
         <v>106</v>
       </c>
       <c r="D153" s="4" t="s">
@@ -7426,16 +7449,16 @@
         <v>170</v>
       </c>
       <c r="H153" s="4"/>
-      <c r="I153" s="24" t="s">
+      <c r="I153" s="23" t="s">
         <v>339</v>
       </c>
       <c r="J153" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L153" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="M153" s="24" t="s">
+      <c r="L153" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="M153" s="23" t="s">
         <v>339</v>
       </c>
     </row>
@@ -7443,10 +7466,10 @@
       <c r="A154" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B154" s="4" t="s">
+      <c r="B154" s="21" t="s">
         <v>322</v>
       </c>
-      <c r="C154" s="4" t="s">
+      <c r="C154" s="21" t="s">
         <v>340</v>
       </c>
       <c r="D154" s="5" t="s">
@@ -7464,7 +7487,7 @@
       <c r="J154" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L154" s="29" t="s">
+      <c r="L154" s="35" t="s">
         <v>21</v>
       </c>
       <c r="M154"/>
@@ -7473,10 +7496,10 @@
       <c r="A155" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B155" s="4" t="s">
+      <c r="B155" s="21" t="s">
         <v>325</v>
       </c>
-      <c r="C155" s="4" t="s">
+      <c r="C155" s="21" t="s">
         <v>342</v>
       </c>
       <c r="D155" s="5" t="s">
@@ -7503,10 +7526,10 @@
       <c r="A156" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B156" s="4" t="s">
+      <c r="B156" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="C156" s="4" t="s">
+      <c r="C156" s="21" t="s">
         <v>119</v>
       </c>
       <c r="D156" s="5" t="s">
@@ -7533,10 +7556,10 @@
       <c r="A157" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B157" s="4" t="s">
+      <c r="B157" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="C157" s="4" t="s">
+      <c r="C157" s="21" t="s">
         <v>119</v>
       </c>
       <c r="D157" s="5" t="s">
@@ -7563,10 +7586,10 @@
       <c r="A158" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B158" s="4" t="s">
+      <c r="B158" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="C158" s="4" t="s">
+      <c r="C158" s="21" t="s">
         <v>342</v>
       </c>
       <c r="D158" s="5" t="s">
@@ -7593,10 +7616,10 @@
       <c r="A159" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B159" s="4" t="s">
+      <c r="B159" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="C159" s="4" t="s">
+      <c r="C159" s="21" t="s">
         <v>119</v>
       </c>
       <c r="D159" s="5" t="s">
@@ -7627,10 +7650,10 @@
       <c r="A160" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B160" s="4" t="s">
+      <c r="B160" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="C160" s="4" t="s">
+      <c r="C160" s="21" t="s">
         <v>119</v>
       </c>
       <c r="D160" s="5" t="s">
@@ -7661,10 +7684,10 @@
       <c r="A161" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B161" s="4" t="s">
+      <c r="B161" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="C161" s="4" t="s">
+      <c r="C161" s="21" t="s">
         <v>119</v>
       </c>
       <c r="D161" s="5" t="s">
@@ -7691,10 +7714,10 @@
       <c r="A162" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B162" s="4" t="s">
+      <c r="B162" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="C162" s="4" t="s">
+      <c r="C162" s="21" t="s">
         <v>342</v>
       </c>
       <c r="D162" s="17" t="s">
@@ -7708,16 +7731,16 @@
         <v>170</v>
       </c>
       <c r="H162" s="4"/>
-      <c r="I162" s="24" t="s">
+      <c r="I162" s="23" t="s">
         <v>354</v>
       </c>
       <c r="J162" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L162" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="M162" s="24" t="s">
+      <c r="L162" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="M162" s="23" t="s">
         <v>354</v>
       </c>
     </row>
@@ -7725,10 +7748,10 @@
       <c r="A163" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B163" s="4" t="s">
+      <c r="B163" s="21" t="s">
         <v>342</v>
       </c>
-      <c r="C163" s="4" t="s">
+      <c r="C163" s="21" t="s">
         <v>355</v>
       </c>
       <c r="D163" s="5" t="s">
@@ -7755,10 +7778,10 @@
       <c r="A164" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B164" s="4" t="s">
+      <c r="B164" s="21" t="s">
         <v>342</v>
       </c>
-      <c r="C164" s="4" t="s">
+      <c r="C164" s="21" t="s">
         <v>355</v>
       </c>
       <c r="D164" s="5" t="s">
@@ -7785,10 +7808,10 @@
       <c r="A165" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B165" s="4" t="s">
+      <c r="B165" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="C165" s="4" t="s">
+      <c r="C165" s="21" t="s">
         <v>127</v>
       </c>
       <c r="D165" s="5" t="s">
@@ -7815,10 +7838,10 @@
       <c r="A166" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B166" s="4" t="s">
+      <c r="B166" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="C166" s="4" t="s">
+      <c r="C166" s="21" t="s">
         <v>127</v>
       </c>
       <c r="D166" s="5" t="s">
@@ -7845,10 +7868,10 @@
       <c r="A167" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B167" s="4" t="s">
+      <c r="B167" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="C167" s="4" t="s">
+      <c r="C167" s="21" t="s">
         <v>127</v>
       </c>
       <c r="D167" s="5" t="s">
@@ -7879,10 +7902,10 @@
       <c r="A168" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B168" s="4" t="s">
+      <c r="B168" s="21" t="s">
         <v>355</v>
       </c>
-      <c r="C168" s="4" t="s">
+      <c r="C168" s="21" t="s">
         <v>129</v>
       </c>
       <c r="D168" s="5" t="s">
@@ -7913,10 +7936,10 @@
       <c r="A169" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B169" s="4" t="s">
+      <c r="B169" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="C169" s="4" t="s">
+      <c r="C169" s="21" t="s">
         <v>136</v>
       </c>
       <c r="D169" s="5" t="s">
@@ -7947,10 +7970,10 @@
       <c r="A170" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B170" s="4" t="s">
+      <c r="B170" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="C170" s="4" t="s">
+      <c r="C170" s="21" t="s">
         <v>136</v>
       </c>
       <c r="D170" s="5" t="s">
@@ -7977,10 +8000,10 @@
       <c r="A171" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B171" s="4" t="s">
+      <c r="B171" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="C171" s="4" t="s">
+      <c r="C171" s="21" t="s">
         <v>140</v>
       </c>
       <c r="D171" s="5" t="s">
@@ -8011,10 +8034,10 @@
       <c r="A172" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B172" s="4" t="s">
+      <c r="B172" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="C172" s="4" t="s">
+      <c r="C172" s="21" t="s">
         <v>140</v>
       </c>
       <c r="D172" s="5" t="s">
@@ -8041,10 +8064,10 @@
       <c r="A173" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B173" s="4" t="s">
+      <c r="B173" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="C173" s="4" t="s">
+      <c r="C173" s="21" t="s">
         <v>134</v>
       </c>
       <c r="D173" s="4" t="s">
@@ -8075,10 +8098,10 @@
       <c r="A174" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B174" s="4" t="s">
+      <c r="B174" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="C174" s="4" t="s">
+      <c r="C174" s="21" t="s">
         <v>140</v>
       </c>
       <c r="D174" s="4" t="s">
@@ -8143,10 +8166,10 @@
       <c r="A176" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B176" s="4" t="s">
+      <c r="B176" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="C176" s="4" t="s">
+      <c r="C176" s="21" t="s">
         <v>144</v>
       </c>
       <c r="D176" s="5" t="s">
@@ -8173,10 +8196,10 @@
       <c r="A177" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B177" s="4" t="s">
+      <c r="B177" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="C177" s="4" t="s">
+      <c r="C177" s="21" t="s">
         <v>144</v>
       </c>
       <c r="D177" s="5" t="s">
@@ -8203,10 +8226,10 @@
       <c r="A178" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B178" s="4" t="s">
+      <c r="B178" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="C178" s="4" t="s">
+      <c r="C178" s="21" t="s">
         <v>144</v>
       </c>
       <c r="D178" s="5" t="s">
@@ -8237,10 +8260,10 @@
       <c r="A179" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B179" s="4" t="s">
+      <c r="B179" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="C179" s="4" t="s">
+      <c r="C179" s="21" t="s">
         <v>144</v>
       </c>
       <c r="D179" s="5" t="s">
@@ -8267,10 +8290,10 @@
       <c r="A180" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B180" s="4" t="s">
+      <c r="B180" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="C180" s="4" t="s">
+      <c r="C180" s="21" t="s">
         <v>16</v>
       </c>
       <c r="D180" s="5" t="s">
@@ -8297,10 +8320,10 @@
       <c r="A181" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B181" s="4" t="s">
+      <c r="B181" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="C181" s="4" t="s">
+      <c r="C181" s="21" t="s">
         <v>160</v>
       </c>
       <c r="D181" s="4" t="s">
@@ -8320,10 +8343,10 @@
       <c r="J181" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L181" s="28" t="s">
+      <c r="L181" s="27" t="s">
         <v>149</v>
       </c>
-      <c r="M181" s="24" t="s">
+      <c r="M181" s="23" t="s">
         <v>385</v>
       </c>
     </row>
@@ -8331,10 +8354,10 @@
       <c r="A182" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B182" s="4" t="s">
+      <c r="B182" s="21" t="s">
         <v>374</v>
       </c>
-      <c r="C182" s="4" t="s">
+      <c r="C182" s="21" t="s">
         <v>144</v>
       </c>
       <c r="D182" s="4" t="s">
@@ -8365,10 +8388,10 @@
       <c r="A183" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B183" s="4" t="s">
+      <c r="B183" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="C183" s="4" t="s">
+      <c r="C183" s="21" t="s">
         <v>168</v>
       </c>
       <c r="D183" s="4" t="s">
@@ -8393,10 +8416,10 @@
       <c r="A184" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B184" s="4" t="s">
+      <c r="B184" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="C184" s="4" t="s">
+      <c r="C184" s="21" t="s">
         <v>181</v>
       </c>
       <c r="D184" s="4" t="s">
@@ -8427,10 +8450,10 @@
       <c r="A185" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B185" s="4" t="s">
+      <c r="B185" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="C185" s="4" t="s">
+      <c r="C185" s="21" t="s">
         <v>144</v>
       </c>
       <c r="D185" s="4" t="s">
@@ -8461,10 +8484,10 @@
       <c r="A186" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B186" s="4" t="s">
+      <c r="B186" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="C186" s="4" t="s">
+      <c r="C186" s="21" t="s">
         <v>16</v>
       </c>
       <c r="D186" s="31" t="s">
@@ -8495,10 +8518,10 @@
       <c r="A187" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B187" s="4" t="s">
+      <c r="B187" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="C187" s="4" t="s">
+      <c r="C187" s="21" t="s">
         <v>16</v>
       </c>
       <c r="D187" s="5" t="s">
@@ -8525,10 +8548,10 @@
       <c r="A188" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B188" s="4" t="s">
+      <c r="B188" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="C188" s="4" t="s">
+      <c r="C188" s="21" t="s">
         <v>16</v>
       </c>
       <c r="D188" s="5" t="s">
@@ -8559,10 +8582,10 @@
       <c r="A189" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B189" s="4" t="s">
+      <c r="B189" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="C189" s="4" t="s">
+      <c r="C189" s="21" t="s">
         <v>16</v>
       </c>
       <c r="D189" s="5" t="s">
@@ -8589,10 +8612,10 @@
       <c r="A190" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B190" s="4" t="s">
+      <c r="B190" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="C190" s="4" t="s">
+      <c r="C190" s="21" t="s">
         <v>16</v>
       </c>
       <c r="D190" s="5" t="s">
@@ -8619,10 +8642,10 @@
       <c r="A191" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B191" s="4" t="s">
+      <c r="B191" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="C191" s="4" t="s">
+      <c r="C191" s="21" t="s">
         <v>16</v>
       </c>
       <c r="D191" s="4" t="s">
@@ -8639,7 +8662,7 @@
       <c r="J191" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L191" s="28" t="s">
+      <c r="L191" s="27" t="s">
         <v>149</v>
       </c>
       <c r="M191" s="4" t="s">
@@ -8650,10 +8673,10 @@
       <c r="A192" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B192" s="4" t="s">
+      <c r="B192" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="C192" s="4" t="s">
+      <c r="C192" s="21" t="s">
         <v>404</v>
       </c>
       <c r="D192" s="5" t="s">
@@ -8684,10 +8707,10 @@
       <c r="A193" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B193" s="4" t="s">
+      <c r="B193" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="C193" s="4" t="s">
+      <c r="C193" s="21" t="s">
         <v>16</v>
       </c>
       <c r="D193" s="4" t="s">
@@ -8718,10 +8741,10 @@
       <c r="A194" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B194" s="4" t="s">
+      <c r="B194" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="C194" s="4" t="s">
+      <c r="C194" s="21" t="s">
         <v>16</v>
       </c>
       <c r="D194" s="4" t="s">
@@ -8750,10 +8773,10 @@
       <c r="A195" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B195" s="4" t="s">
+      <c r="B195" s="21" t="s">
         <v>412</v>
       </c>
-      <c r="C195" s="4" t="s">
+      <c r="C195" s="21" t="s">
         <v>159</v>
       </c>
       <c r="D195" s="5" t="s">
@@ -8773,7 +8796,7 @@
       <c r="J195" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L195" s="29" t="s">
+      <c r="L195" s="28" t="s">
         <v>71</v>
       </c>
       <c r="M195" t="s">
@@ -8784,10 +8807,10 @@
       <c r="A196" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B196" s="4" t="s">
+      <c r="B196" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C196" s="4" t="s">
+      <c r="C196" s="21" t="s">
         <v>22</v>
       </c>
       <c r="D196" s="5" t="s">
@@ -8818,10 +8841,10 @@
       <c r="A197" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B197" s="4" t="s">
+      <c r="B197" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C197" s="4" t="s">
+      <c r="C197" s="21" t="s">
         <v>22</v>
       </c>
       <c r="D197" s="5" t="s">
@@ -8852,10 +8875,10 @@
       <c r="A198" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B198" s="4" t="s">
+      <c r="B198" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C198" s="4" t="s">
+      <c r="C198" s="21" t="s">
         <v>22</v>
       </c>
       <c r="D198" s="5" t="s">
@@ -8882,10 +8905,10 @@
       <c r="A199" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B199" s="4" t="s">
+      <c r="B199" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C199" s="4" t="s">
+      <c r="C199" s="21" t="s">
         <v>22</v>
       </c>
       <c r="D199" s="5" t="s">
@@ -8912,10 +8935,10 @@
       <c r="A200" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B200" s="4" t="s">
+      <c r="B200" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C200" s="4" t="s">
+      <c r="C200" s="21" t="s">
         <v>22</v>
       </c>
       <c r="D200" s="5" t="s">
@@ -8942,10 +8965,10 @@
       <c r="A201" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B201" s="4" t="s">
+      <c r="B201" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C201" s="4" t="s">
+      <c r="C201" s="21" t="s">
         <v>22</v>
       </c>
       <c r="D201" s="5" t="s">
@@ -8976,10 +8999,10 @@
       <c r="A202" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B202" s="4" t="s">
+      <c r="B202" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C202" s="4" t="s">
+      <c r="C202" s="21" t="s">
         <v>201</v>
       </c>
       <c r="D202" s="4" t="s">
@@ -9006,10 +9029,10 @@
       <c r="A203" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B203" s="4" t="s">
+      <c r="B203" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="C203" s="4" t="s">
+      <c r="C203" s="21" t="s">
         <v>22</v>
       </c>
       <c r="D203" s="4" t="s">
@@ -9040,10 +9063,10 @@
       <c r="A204" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B204" s="4" t="s">
+      <c r="B204" s="21" t="s">
         <v>429</v>
       </c>
-      <c r="C204" s="4" t="s">
+      <c r="C204" s="21" t="s">
         <v>201</v>
       </c>
       <c r="D204" s="5" t="s">
@@ -9074,10 +9097,10 @@
       <c r="A205" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B205" s="4" t="s">
+      <c r="B205" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="C205" s="4" t="s">
+      <c r="C205" s="21" t="s">
         <v>22</v>
       </c>
       <c r="D205" s="4" t="s">
@@ -9108,10 +9131,10 @@
       <c r="A206" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B206" s="4" t="s">
+      <c r="B206" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C206" s="4" t="s">
+      <c r="C206" s="21" t="s">
         <v>23</v>
       </c>
       <c r="D206" s="5" t="s">
@@ -9138,10 +9161,10 @@
       <c r="A207" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B207" s="4" t="s">
+      <c r="B207" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C207" s="4" t="s">
+      <c r="C207" s="21" t="s">
         <v>37</v>
       </c>
       <c r="D207" s="5" t="s">
@@ -9168,10 +9191,10 @@
       <c r="A208" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B208" s="4" t="s">
+      <c r="B208" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C208" s="4" t="s">
+      <c r="C208" s="21" t="s">
         <v>23</v>
       </c>
       <c r="D208" s="5" t="s">
@@ -9202,10 +9225,10 @@
       <c r="A209" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B209" s="4" t="s">
+      <c r="B209" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C209" s="4" t="s">
+      <c r="C209" s="21" t="s">
         <v>29</v>
       </c>
       <c r="D209" s="5" t="s">
@@ -9236,10 +9259,10 @@
       <c r="A210" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B210" s="4" t="s">
+      <c r="B210" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C210" s="4" t="s">
+      <c r="C210" s="21" t="s">
         <v>23</v>
       </c>
       <c r="D210" s="5" t="s">
@@ -9266,10 +9289,10 @@
       <c r="A211" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B211" s="4" t="s">
+      <c r="B211" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C211" s="4" t="s">
+      <c r="C211" s="21" t="s">
         <v>23</v>
       </c>
       <c r="D211" s="5" t="s">
@@ -9296,10 +9319,10 @@
       <c r="A212" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B212" s="4" t="s">
+      <c r="B212" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C212" s="4" t="s">
+      <c r="C212" s="21" t="s">
         <v>444</v>
       </c>
       <c r="D212" s="5" t="s">
@@ -9319,7 +9342,7 @@
       <c r="J212" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L212" s="29" t="s">
+      <c r="L212" s="28" t="s">
         <v>71</v>
       </c>
       <c r="M212" t="s">
@@ -9330,10 +9353,10 @@
       <c r="A213" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B213" s="4" t="s">
+      <c r="B213" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C213" s="4" t="s">
+      <c r="C213" s="21" t="s">
         <v>29</v>
       </c>
       <c r="D213" s="5" t="s">
@@ -9360,10 +9383,10 @@
       <c r="A214" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B214" s="4" t="s">
+      <c r="B214" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C214" s="4" t="s">
+      <c r="C214" s="21" t="s">
         <v>23</v>
       </c>
       <c r="D214" s="4" t="s">
@@ -9383,10 +9406,10 @@
       <c r="J214" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L214" s="28" t="s">
+      <c r="L214" s="27" t="s">
         <v>149</v>
       </c>
-      <c r="M214" s="24" t="s">
+      <c r="M214" s="23" t="s">
         <v>449</v>
       </c>
     </row>
@@ -9394,17 +9417,17 @@
       <c r="A215" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B215" s="4" t="s">
+      <c r="B215" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C215" s="4" t="s">
+      <c r="C215" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="D215" s="23" t="s">
+      <c r="D215" s="22" t="s">
         <v>450</v>
       </c>
       <c r="E215" s="4"/>
-      <c r="F215" s="23" t="s">
+      <c r="F215" s="22" t="s">
         <v>450</v>
       </c>
       <c r="G215" s="4" t="s">
@@ -9424,10 +9447,10 @@
       <c r="A216" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B216" s="4" t="s">
+      <c r="B216" s="21" t="s">
         <v>451</v>
       </c>
-      <c r="C216" s="4" t="s">
+      <c r="C216" s="21" t="s">
         <v>29</v>
       </c>
       <c r="D216" s="4" t="s">
@@ -9458,10 +9481,10 @@
       <c r="A217" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B217" s="4" t="s">
+      <c r="B217" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="C217" s="4" t="s">
+      <c r="C217" s="21" t="s">
         <v>234</v>
       </c>
       <c r="D217" s="5" t="s">
@@ -9488,10 +9511,10 @@
       <c r="A218" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B218" s="4" t="s">
+      <c r="B218" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="C218" s="4" t="s">
+      <c r="C218" s="21" t="s">
         <v>456</v>
       </c>
       <c r="D218" s="5" t="s">
@@ -9518,10 +9541,10 @@
       <c r="A219" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B219" s="4" t="s">
+      <c r="B219" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="C219" s="4" t="s">
+      <c r="C219" s="21" t="s">
         <v>263</v>
       </c>
       <c r="D219" s="5" t="s">
@@ -9552,10 +9575,10 @@
       <c r="A220" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B220" s="4" t="s">
+      <c r="B220" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="C220" s="4" t="s">
+      <c r="C220" s="21" t="s">
         <v>43</v>
       </c>
       <c r="D220" s="5" t="s">
@@ -9586,10 +9609,10 @@
       <c r="A221" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B221" s="4" t="s">
+      <c r="B221" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C221" s="4" t="s">
+      <c r="C221" s="21" t="s">
         <v>47</v>
       </c>
       <c r="D221" s="5" t="s">
@@ -9616,10 +9639,10 @@
       <c r="A222" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B222" s="4" t="s">
+      <c r="B222" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C222" s="4" t="s">
+      <c r="C222" s="21" t="s">
         <v>47</v>
       </c>
       <c r="D222" s="5" t="s">
@@ -9646,17 +9669,17 @@
       <c r="A223" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B223" s="4" t="s">
+      <c r="B223" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C223" s="4" t="s">
+      <c r="C223" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="D223" s="23" t="s">
+      <c r="D223" s="22" t="s">
         <v>670</v>
       </c>
       <c r="E223" s="4"/>
-      <c r="F223" s="23" t="s">
+      <c r="F223" s="22" t="s">
         <v>670</v>
       </c>
       <c r="G223" s="4" t="s">
@@ -9680,10 +9703,10 @@
       <c r="A224" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B224" s="4" t="s">
+      <c r="B224" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C224" s="4" t="s">
+      <c r="C224" s="21" t="s">
         <v>47</v>
       </c>
       <c r="D224" s="5" t="s">
@@ -9714,10 +9737,10 @@
       <c r="A225" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B225" s="4" t="s">
+      <c r="B225" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C225" s="4" t="s">
+      <c r="C225" s="21" t="s">
         <v>469</v>
       </c>
       <c r="D225" s="5" t="s">
@@ -9744,10 +9767,10 @@
       <c r="A226" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B226" s="4" t="s">
+      <c r="B226" s="21" t="s">
         <v>471</v>
       </c>
-      <c r="C226" s="4" t="s">
+      <c r="C226" s="21" t="s">
         <v>472</v>
       </c>
       <c r="D226" s="5" t="s">
@@ -9778,10 +9801,10 @@
       <c r="A227" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B227" s="4" t="s">
+      <c r="B227" s="21" t="s">
         <v>262</v>
       </c>
-      <c r="C227" s="4" t="s">
+      <c r="C227" s="21" t="s">
         <v>43</v>
       </c>
       <c r="D227" s="5" t="s">
@@ -9808,10 +9831,10 @@
       <c r="A228" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B228" s="4" t="s">
+      <c r="B228" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="C228" s="4" t="s">
+      <c r="C228" s="21" t="s">
         <v>61</v>
       </c>
       <c r="D228" s="5" t="s">
@@ -9838,10 +9861,10 @@
       <c r="A229" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B229" s="4" t="s">
+      <c r="B229" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="C229" s="4" t="s">
+      <c r="C229" s="21" t="s">
         <v>478</v>
       </c>
       <c r="D229" s="4" t="s">
@@ -9861,7 +9884,7 @@
       <c r="J229" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L229" s="28" t="s">
+      <c r="L229" s="27" t="s">
         <v>149</v>
       </c>
       <c r="M229" s="4" t="s">
@@ -9872,10 +9895,10 @@
       <c r="A230" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B230" s="4" t="s">
+      <c r="B230" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="C230" s="4" t="s">
+      <c r="C230" s="21" t="s">
         <v>61</v>
       </c>
       <c r="D230" s="5" t="s">
@@ -9906,10 +9929,10 @@
       <c r="A231" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B231" s="4" t="s">
+      <c r="B231" s="21" t="s">
         <v>263</v>
       </c>
-      <c r="C231" s="4" t="s">
+      <c r="C231" s="21" t="s">
         <v>54</v>
       </c>
       <c r="D231" s="5" t="s">
@@ -9936,10 +9959,10 @@
       <c r="A232" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B232" s="4" t="s">
+      <c r="B232" s="21" t="s">
         <v>263</v>
       </c>
-      <c r="C232" s="4" t="s">
+      <c r="C232" s="21" t="s">
         <v>486</v>
       </c>
       <c r="D232" s="5" t="s">
@@ -9970,10 +9993,10 @@
       <c r="A233" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B233" s="4" t="s">
+      <c r="B233" s="21" t="s">
         <v>256</v>
       </c>
-      <c r="C233" s="4" t="s">
+      <c r="C233" s="21" t="s">
         <v>61</v>
       </c>
       <c r="D233" s="5" t="s">
@@ -10000,10 +10023,10 @@
       <c r="A234" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B234" s="4" t="s">
+      <c r="B234" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C234" s="4" t="s">
+      <c r="C234" s="21" t="s">
         <v>491</v>
       </c>
       <c r="D234" s="5" t="s">
@@ -10034,10 +10057,10 @@
       <c r="A235" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B235" s="4" t="s">
+      <c r="B235" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C235" s="17" t="s">
+      <c r="C235" s="12" t="s">
         <v>491</v>
       </c>
       <c r="D235" s="5" t="s">
@@ -10064,10 +10087,10 @@
       <c r="A236" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B236" s="4" t="s">
+      <c r="B236" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C236" s="4" t="s">
+      <c r="C236" s="21" t="s">
         <v>491</v>
       </c>
       <c r="D236" s="5" t="s">
@@ -10094,10 +10117,10 @@
       <c r="A237" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B237" s="4" t="s">
+      <c r="B237" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C237" s="4" t="s">
+      <c r="C237" s="21" t="s">
         <v>491</v>
       </c>
       <c r="D237" s="5" t="s">
@@ -10124,10 +10147,10 @@
       <c r="A238" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B238" s="4" t="s">
+      <c r="B238" s="21" t="s">
         <v>497</v>
       </c>
-      <c r="C238" s="4" t="s">
+      <c r="C238" s="21" t="s">
         <v>498</v>
       </c>
       <c r="D238" s="5" t="s">
@@ -10154,10 +10177,10 @@
       <c r="A239" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B239" s="4" t="s">
+      <c r="B239" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="C239" s="17" t="s">
+      <c r="C239" s="12" t="s">
         <v>491</v>
       </c>
       <c r="D239" s="5" t="s">
@@ -10188,10 +10211,10 @@
       <c r="A240" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B240" s="4" t="s">
+      <c r="B240" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="C240" s="4" t="s">
+      <c r="C240" s="21" t="s">
         <v>491</v>
       </c>
       <c r="D240" s="5" t="s">
@@ -10218,10 +10241,10 @@
       <c r="A241" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B241" s="4" t="s">
+      <c r="B241" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="C241" s="4" t="s">
+      <c r="C241" s="21" t="s">
         <v>491</v>
       </c>
       <c r="D241" s="5" t="s">
@@ -10248,10 +10271,10 @@
       <c r="A242" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B242" s="4" t="s">
+      <c r="B242" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="C242" s="17" t="s">
+      <c r="C242" s="12" t="s">
         <v>478</v>
       </c>
       <c r="D242" s="5" t="s">
@@ -10282,10 +10305,10 @@
       <c r="A243" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="B243" s="13" t="s">
+      <c r="B243" s="40" t="s">
         <v>293</v>
       </c>
-      <c r="C243" s="19" t="s">
+      <c r="C243" s="39" t="s">
         <v>491</v>
       </c>
       <c r="D243" s="5" t="s">
@@ -10316,7 +10339,7 @@
       <c r="A244" s="10" t="s">
         <v>508</v>
       </c>
-      <c r="B244" s="4" t="s">
+      <c r="B244" s="21" t="s">
         <v>89</v>
       </c>
       <c r="C244" s="12" t="s">
@@ -10333,7 +10356,7 @@
         <v>39</v>
       </c>
       <c r="H244" s="8"/>
-      <c r="I244" s="20"/>
+      <c r="I244" s="19"/>
       <c r="J244" s="8" t="s">
         <v>20</v>
       </c>
@@ -10346,10 +10369,10 @@
       <c r="A245" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B245" s="4" t="s">
+      <c r="B245" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="C245" s="4" t="s">
+      <c r="C245" s="21" t="s">
         <v>90</v>
       </c>
       <c r="D245" s="5" t="s">
@@ -10380,10 +10403,10 @@
       <c r="A246" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B246" s="4" t="s">
+      <c r="B246" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="C246" s="4" t="s">
+      <c r="C246" s="21" t="s">
         <v>90</v>
       </c>
       <c r="D246" s="5" t="s">
@@ -10410,10 +10433,10 @@
       <c r="A247" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B247" s="4" t="s">
+      <c r="B247" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="C247" s="4" t="s">
+      <c r="C247" s="21" t="s">
         <v>98</v>
       </c>
       <c r="D247" s="5" t="s">
@@ -10440,10 +10463,10 @@
       <c r="A248" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B248" s="4" t="s">
+      <c r="B248" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="C248" s="4" t="s">
+      <c r="C248" s="21" t="s">
         <v>90</v>
       </c>
       <c r="D248" s="5" t="s">
@@ -10470,10 +10493,10 @@
       <c r="A249" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B249" s="4" t="s">
+      <c r="B249" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="C249" s="4" t="s">
+      <c r="C249" s="21" t="s">
         <v>95</v>
       </c>
       <c r="D249" s="5" t="s">
@@ -10504,10 +10527,10 @@
       <c r="A250" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B250" s="4" t="s">
+      <c r="B250" s="21" t="s">
         <v>313</v>
       </c>
-      <c r="C250" s="4" t="s">
+      <c r="C250" s="21" t="s">
         <v>95</v>
       </c>
       <c r="D250" s="5" t="s">
@@ -10525,7 +10548,7 @@
       <c r="J250" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L250" s="29" t="s">
+      <c r="L250" s="28" t="s">
         <v>21</v>
       </c>
       <c r="M250"/>
@@ -10534,10 +10557,10 @@
       <c r="A251" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B251" s="4" t="s">
+      <c r="B251" s="21" t="s">
         <v>316</v>
       </c>
-      <c r="C251" s="4" t="s">
+      <c r="C251" s="21" t="s">
         <v>90</v>
       </c>
       <c r="D251" s="5" t="s">
@@ -10564,10 +10587,10 @@
       <c r="A252" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B252" s="4" t="s">
+      <c r="B252" s="21" t="s">
         <v>316</v>
       </c>
-      <c r="C252" s="4" t="s">
+      <c r="C252" s="21" t="s">
         <v>95</v>
       </c>
       <c r="D252" s="5" t="s">
@@ -10594,10 +10617,10 @@
       <c r="A253" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B253" s="4" t="s">
+      <c r="B253" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="C253" s="4" t="s">
+      <c r="C253" s="21" t="s">
         <v>104</v>
       </c>
       <c r="D253" s="5" t="s">
@@ -10624,10 +10647,10 @@
       <c r="A254" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B254" s="4" t="s">
+      <c r="B254" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="C254" s="4" t="s">
+      <c r="C254" s="21" t="s">
         <v>115</v>
       </c>
       <c r="D254" s="4" t="s">
@@ -10641,16 +10664,16 @@
         <v>170</v>
       </c>
       <c r="H254" s="4"/>
-      <c r="I254" s="24" t="s">
+      <c r="I254" s="23" t="s">
         <v>522</v>
       </c>
       <c r="J254" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L254" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="M254" s="24" t="s">
+      <c r="L254" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="M254" s="23" t="s">
         <v>522</v>
       </c>
     </row>
@@ -10658,10 +10681,10 @@
       <c r="A255" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B255" s="4" t="s">
+      <c r="B255" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="C255" s="4" t="s">
+      <c r="C255" s="21" t="s">
         <v>104</v>
       </c>
       <c r="D255" s="5" t="s">
@@ -10688,10 +10711,10 @@
       <c r="A256" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B256" s="4" t="s">
+      <c r="B256" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="C256" s="4" t="s">
+      <c r="C256" s="21" t="s">
         <v>104</v>
       </c>
       <c r="D256" s="5" t="s">
@@ -10718,10 +10741,10 @@
       <c r="A257" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B257" s="4" t="s">
+      <c r="B257" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="C257" s="4" t="s">
+      <c r="C257" s="21" t="s">
         <v>106</v>
       </c>
       <c r="D257" s="5" t="s">
@@ -10748,10 +10771,10 @@
       <c r="A258" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B258" s="4" t="s">
+      <c r="B258" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="C258" s="4" t="s">
+      <c r="C258" s="21" t="s">
         <v>106</v>
       </c>
       <c r="D258" s="5" t="s">
@@ -10782,10 +10805,10 @@
       <c r="A259" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B259" s="4" t="s">
+      <c r="B259" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="C259" s="4" t="s">
+      <c r="C259" s="21" t="s">
         <v>106</v>
       </c>
       <c r="D259" s="5" t="s">
@@ -10812,10 +10835,10 @@
       <c r="A260" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B260" s="4" t="s">
+      <c r="B260" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="C260" s="4" t="s">
+      <c r="C260" s="21" t="s">
         <v>325</v>
       </c>
       <c r="D260" s="5" t="s">
@@ -10842,10 +10865,10 @@
       <c r="A261" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B261" s="4" t="s">
+      <c r="B261" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="C261" s="4" t="s">
+      <c r="C261" s="21" t="s">
         <v>106</v>
       </c>
       <c r="D261" s="5" t="s">
@@ -10876,10 +10899,10 @@
       <c r="A262" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B262" s="4" t="s">
+      <c r="B262" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="C262" s="4" t="s">
+      <c r="C262" s="21" t="s">
         <v>106</v>
       </c>
       <c r="D262" s="4" t="s">
@@ -10893,16 +10916,16 @@
         <v>170</v>
       </c>
       <c r="H262" s="4"/>
-      <c r="I262" s="24" t="s">
+      <c r="I262" s="23" t="s">
         <v>534</v>
       </c>
       <c r="J262" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L262" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="M262" s="24" t="s">
+      <c r="L262" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="M262" s="23" t="s">
         <v>535</v>
       </c>
     </row>
@@ -10910,10 +10933,10 @@
       <c r="A263" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B263" s="4" t="s">
+      <c r="B263" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="C263" s="4" t="s">
+      <c r="C263" s="21" t="s">
         <v>117</v>
       </c>
       <c r="D263" s="5" t="s">
@@ -10940,10 +10963,10 @@
       <c r="A264" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B264" s="4" t="s">
+      <c r="B264" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="C264" s="4" t="s">
+      <c r="C264" s="21" t="s">
         <v>110</v>
       </c>
       <c r="D264" s="5" t="s">
@@ -10974,10 +10997,10 @@
       <c r="A265" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B265" s="4" t="s">
+      <c r="B265" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="C265" s="4" t="s">
+      <c r="C265" s="21" t="s">
         <v>117</v>
       </c>
       <c r="D265" s="5" t="s">
@@ -11008,10 +11031,10 @@
       <c r="A266" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B266" s="4" t="s">
+      <c r="B266" s="21" t="s">
         <v>325</v>
       </c>
-      <c r="C266" s="4" t="s">
+      <c r="C266" s="21" t="s">
         <v>110</v>
       </c>
       <c r="D266" s="5" t="s">
@@ -11038,10 +11061,10 @@
       <c r="A267" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B267" s="4" t="s">
+      <c r="B267" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="C267" s="4" t="s">
+      <c r="C267" s="21" t="s">
         <v>119</v>
       </c>
       <c r="D267" s="5" t="s">
@@ -11068,10 +11091,10 @@
       <c r="A268" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B268" s="4" t="s">
+      <c r="B268" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="C268" s="4" t="s">
+      <c r="C268" s="21" t="s">
         <v>119</v>
       </c>
       <c r="D268" s="5" t="s">
@@ -11102,10 +11125,10 @@
       <c r="A269" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B269" s="4" t="s">
+      <c r="B269" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="C269" s="4" t="s">
+      <c r="C269" s="21" t="s">
         <v>119</v>
       </c>
       <c r="D269" s="5" t="s">
@@ -11136,10 +11159,10 @@
       <c r="A270" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B270" s="4" t="s">
+      <c r="B270" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="C270" s="4" t="s">
+      <c r="C270" s="21" t="s">
         <v>119</v>
       </c>
       <c r="D270" s="5" t="s">
@@ -11170,10 +11193,10 @@
       <c r="A271" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B271" s="4" t="s">
+      <c r="B271" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="C271" s="4" t="s">
+      <c r="C271" s="21" t="s">
         <v>342</v>
       </c>
       <c r="D271" s="4" t="s">
@@ -11191,7 +11214,7 @@
       <c r="J271" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L271" s="28" t="s">
+      <c r="L271" s="27" t="s">
         <v>21</v>
       </c>
     </row>
@@ -11199,10 +11222,10 @@
       <c r="A272" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B272" s="4" t="s">
+      <c r="B272" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="C272" s="4" t="s">
+      <c r="C272" s="21" t="s">
         <v>119</v>
       </c>
       <c r="D272" s="5" t="s">
@@ -11229,10 +11252,10 @@
       <c r="A273" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B273" s="4" t="s">
+      <c r="B273" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="C273" s="4" t="s">
+      <c r="C273" s="21" t="s">
         <v>553</v>
       </c>
       <c r="D273" s="5" t="s">
@@ -11259,10 +11282,10 @@
       <c r="A274" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B274" s="4" t="s">
+      <c r="B274" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="C274" s="4" t="s">
+      <c r="C274" s="21" t="s">
         <v>119</v>
       </c>
       <c r="D274" s="5" t="s">
@@ -11282,7 +11305,7 @@
       <c r="J274" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L274" s="29" t="s">
+      <c r="L274" s="28" t="s">
         <v>71</v>
       </c>
       <c r="M274" t="s">
@@ -11293,10 +11316,10 @@
       <c r="A275" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B275" s="4" t="s">
+      <c r="B275" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="C275" s="4" t="s">
+      <c r="C275" s="21" t="s">
         <v>129</v>
       </c>
       <c r="D275" s="5" t="s">
@@ -11323,10 +11346,10 @@
       <c r="A276" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B276" s="4" t="s">
+      <c r="B276" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="C276" s="4" t="s">
+      <c r="C276" s="21" t="s">
         <v>127</v>
       </c>
       <c r="D276" s="5" t="s">
@@ -11357,10 +11380,10 @@
       <c r="A277" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B277" s="4" t="s">
+      <c r="B277" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="C277" s="4" t="s">
+      <c r="C277" s="21" t="s">
         <v>560</v>
       </c>
       <c r="D277" s="5" t="s">
@@ -11391,10 +11414,10 @@
       <c r="A278" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B278" s="4" t="s">
+      <c r="B278" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="C278" s="4" t="s">
+      <c r="C278" s="21" t="s">
         <v>127</v>
       </c>
       <c r="D278" s="5" t="s">
@@ -11425,10 +11448,10 @@
       <c r="A279" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B279" s="4" t="s">
+      <c r="B279" s="21" t="s">
         <v>560</v>
       </c>
-      <c r="C279" s="4" t="s">
+      <c r="C279" s="21" t="s">
         <v>129</v>
       </c>
       <c r="D279" s="5" t="s">
@@ -11455,10 +11478,10 @@
       <c r="A280" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B280" s="4" t="s">
+      <c r="B280" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="C280" s="4" t="s">
+      <c r="C280" s="21" t="s">
         <v>136</v>
       </c>
       <c r="D280" s="5" t="s">
@@ -11489,10 +11512,10 @@
       <c r="A281" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B281" s="4" t="s">
+      <c r="B281" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="C281" s="4" t="s">
+      <c r="C281" s="21" t="s">
         <v>134</v>
       </c>
       <c r="D281" s="5" t="s">
@@ -11523,10 +11546,10 @@
       <c r="A282" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B282" s="4" t="s">
+      <c r="B282" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="C282" s="4" t="s">
+      <c r="C282" s="21" t="s">
         <v>140</v>
       </c>
       <c r="D282" s="5" t="s">
@@ -11553,10 +11576,10 @@
       <c r="A283" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B283" s="4" t="s">
+      <c r="B283" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="C283" s="4" t="s">
+      <c r="C283" s="21" t="s">
         <v>154</v>
       </c>
       <c r="D283" s="5" t="s">
@@ -11587,10 +11610,10 @@
       <c r="A284" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B284" s="4" t="s">
+      <c r="B284" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="C284" s="4" t="s">
+      <c r="C284" s="21" t="s">
         <v>140</v>
       </c>
       <c r="D284" s="4" t="s">
@@ -11621,10 +11644,10 @@
       <c r="A285" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B285" s="4" t="s">
+      <c r="B285" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="C285" s="4" t="s">
+      <c r="C285" s="21" t="s">
         <v>144</v>
       </c>
       <c r="D285" s="5" t="s">
@@ -11655,10 +11678,10 @@
       <c r="A286" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B286" s="4" t="s">
+      <c r="B286" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="C286" s="4" t="s">
+      <c r="C286" s="21" t="s">
         <v>159</v>
       </c>
       <c r="D286" s="5" t="s">
@@ -11685,10 +11708,10 @@
       <c r="A287" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B287" s="4" t="s">
+      <c r="B287" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="C287" s="4" t="s">
+      <c r="C287" s="21" t="s">
         <v>166</v>
       </c>
       <c r="D287" s="5" t="s">
@@ -11719,10 +11742,10 @@
       <c r="A288" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B288" s="4" t="s">
+      <c r="B288" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="C288" s="4" t="s">
+      <c r="C288" s="21" t="s">
         <v>168</v>
       </c>
       <c r="D288" s="5" t="s">
@@ -11783,10 +11806,10 @@
       <c r="A290" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B290" s="4" t="s">
+      <c r="B290" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="C290" s="4" t="s">
+      <c r="C290" s="21" t="s">
         <v>144</v>
       </c>
       <c r="D290" s="4" t="s">
@@ -11813,107 +11836,123 @@
         <v>585</v>
       </c>
     </row>
-    <row r="291" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A291" s="4"/>
-      <c r="B291" s="4"/>
-      <c r="C291" s="4"/>
-      <c r="D291" s="4"/>
+    <row r="291" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A291" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="B291" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="C291" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="D291" s="4" t="s">
+        <v>586</v>
+      </c>
       <c r="E291" s="4"/>
-      <c r="F291" s="4"/>
-      <c r="G291" s="4"/>
+      <c r="F291" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="G291" s="4" t="s">
+        <v>170</v>
+      </c>
       <c r="H291" s="4"/>
-      <c r="I291" s="4"/>
-      <c r="J291" s="4"/>
-      <c r="L291" s="6"/>
-      <c r="M291"/>
-    </row>
-    <row r="292" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I291" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="J291" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L291" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="M291" s="23" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="292" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B292" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C292" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="D292" s="4" t="s">
-        <v>586</v>
+      <c r="B292" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="C292" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D292" s="5" t="s">
+        <v>588</v>
       </c>
       <c r="E292" s="4"/>
-      <c r="F292" s="4" t="s">
-        <v>586</v>
+      <c r="F292" s="5" t="s">
+        <v>588</v>
       </c>
       <c r="G292" s="4" t="s">
-        <v>170</v>
+        <v>39</v>
       </c>
       <c r="H292" s="4"/>
-      <c r="I292" s="4" t="s">
-        <v>587</v>
+      <c r="I292" t="s">
+        <v>589</v>
       </c>
       <c r="J292" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L292" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="M292" s="24" t="s">
-        <v>587</v>
+      <c r="L292" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M292" t="s">
+        <v>589</v>
       </c>
     </row>
     <row r="293" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B293" s="4" t="s">
+      <c r="B293" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="C293" s="4" t="s">
+      <c r="C293" s="21" t="s">
         <v>16</v>
       </c>
       <c r="D293" s="5" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="E293" s="4"/>
       <c r="F293" s="5" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="G293" s="4" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="H293" s="4"/>
-      <c r="I293" t="s">
-        <v>589</v>
-      </c>
+      <c r="I293" s="4"/>
       <c r="J293" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L293" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M293" t="s">
-        <v>589</v>
-      </c>
+      <c r="M293"/>
     </row>
     <row r="294" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B294" s="4" t="s">
+      <c r="B294" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="C294" s="4" t="s">
+      <c r="C294" s="21" t="s">
         <v>16</v>
       </c>
       <c r="D294" s="5" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E294" s="4"/>
       <c r="F294" s="5" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="G294" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H294" s="4"/>
       <c r="I294" s="4"/>
@@ -11925,25 +11964,25 @@
       </c>
       <c r="M294"/>
     </row>
-    <row r="295" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B295" s="4" t="s">
+      <c r="B295" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="C295" s="4" t="s">
+      <c r="C295" s="21" t="s">
         <v>16</v>
       </c>
       <c r="D295" s="5" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E295" s="4"/>
       <c r="F295" s="5" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="G295" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H295" s="4"/>
       <c r="I295" s="4"/>
@@ -11955,89 +11994,89 @@
       </c>
       <c r="M295"/>
     </row>
-    <row r="296" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B296" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="C296" s="4" t="s">
+      <c r="B296" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="C296" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="D296" s="5" t="s">
-        <v>592</v>
+      <c r="D296" s="4" t="s">
+        <v>593</v>
       </c>
       <c r="E296" s="4"/>
-      <c r="F296" s="5" t="s">
-        <v>592</v>
+      <c r="F296" s="4" t="s">
+        <v>593</v>
       </c>
       <c r="G296" s="4" t="s">
-        <v>35</v>
+        <v>152</v>
       </c>
       <c r="H296" s="4"/>
-      <c r="I296" s="4"/>
+      <c r="I296" s="4" t="s">
+        <v>594</v>
+      </c>
       <c r="J296" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L296" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M296"/>
+        <v>149</v>
+      </c>
+      <c r="M296" t="s">
+        <v>594</v>
+      </c>
     </row>
     <row r="297" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B297" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="C297" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D297" s="4" t="s">
-        <v>593</v>
+      <c r="B297" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="C297" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="D297" s="5" t="s">
+        <v>595</v>
       </c>
       <c r="E297" s="4"/>
-      <c r="F297" s="4" t="s">
-        <v>593</v>
+      <c r="F297" s="5" t="s">
+        <v>595</v>
       </c>
       <c r="G297" s="4" t="s">
-        <v>152</v>
+        <v>56</v>
       </c>
       <c r="H297" s="4"/>
-      <c r="I297" s="4" t="s">
-        <v>594</v>
-      </c>
+      <c r="I297" s="4"/>
       <c r="J297" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L297" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="M297" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="298" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+      <c r="M297"/>
+    </row>
+    <row r="298" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A298" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B298" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="C298" s="4" t="s">
+      <c r="B298" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C298" s="21" t="s">
         <v>22</v>
       </c>
       <c r="D298" s="5" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E298" s="4"/>
       <c r="F298" s="5" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="G298" s="4" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="H298" s="4"/>
       <c r="I298" s="4"/>
@@ -12053,21 +12092,21 @@
       <c r="A299" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B299" s="4" t="s">
+      <c r="B299" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C299" s="4" t="s">
+      <c r="C299" s="21" t="s">
         <v>22</v>
       </c>
       <c r="D299" s="5" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="E299" s="4"/>
       <c r="F299" s="5" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="G299" s="4" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="H299" s="4"/>
       <c r="I299" s="4"/>
@@ -12083,21 +12122,21 @@
       <c r="A300" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B300" s="4" t="s">
+      <c r="B300" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C300" s="4" t="s">
+      <c r="C300" s="21" t="s">
         <v>22</v>
       </c>
       <c r="D300" s="5" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E300" s="4"/>
       <c r="F300" s="5" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="G300" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H300" s="4"/>
       <c r="I300" s="4"/>
@@ -12109,25 +12148,25 @@
       </c>
       <c r="M300"/>
     </row>
-    <row r="301" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B301" s="4" t="s">
+      <c r="B301" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C301" s="4" t="s">
+      <c r="C301" s="21" t="s">
         <v>22</v>
       </c>
       <c r="D301" s="5" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E301" s="4"/>
       <c r="F301" s="5" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G301" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H301" s="4"/>
       <c r="I301" s="4"/>
@@ -12143,123 +12182,127 @@
       <c r="A302" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B302" s="4" t="s">
+      <c r="B302" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C302" s="4" t="s">
+      <c r="C302" s="21" t="s">
         <v>22</v>
       </c>
       <c r="D302" s="5" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E302" s="4"/>
       <c r="F302" s="5" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="G302" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H302" s="4"/>
-      <c r="I302" s="4"/>
+      <c r="I302" t="s">
+        <v>601</v>
+      </c>
       <c r="J302" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L302" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M302"/>
+      <c r="M302" t="s">
+        <v>602</v>
+      </c>
     </row>
     <row r="303" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B303" s="4" t="s">
+      <c r="B303" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C303" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D303" s="5" t="s">
-        <v>600</v>
+      <c r="C303" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="D303" s="4" t="s">
+        <v>603</v>
       </c>
       <c r="E303" s="4"/>
-      <c r="F303" s="5" t="s">
-        <v>600</v>
+      <c r="F303" s="4" t="s">
+        <v>603</v>
       </c>
       <c r="G303" s="4" t="s">
-        <v>35</v>
+        <v>170</v>
       </c>
       <c r="H303" s="4"/>
-      <c r="I303" t="s">
-        <v>601</v>
+      <c r="I303" s="4" t="s">
+        <v>604</v>
       </c>
       <c r="J303" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L303" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M303" t="s">
-        <v>602</v>
+      <c r="L303" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="M303" s="23" t="s">
+        <v>604</v>
       </c>
     </row>
     <row r="304" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B304" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C304" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="D304" s="4" t="s">
-        <v>603</v>
+      <c r="B304" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="C304" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="D304" s="5" t="s">
+        <v>605</v>
       </c>
       <c r="E304" s="4"/>
-      <c r="F304" s="4" t="s">
-        <v>603</v>
+      <c r="F304" s="5" t="s">
+        <v>605</v>
       </c>
       <c r="G304" s="4" t="s">
-        <v>170</v>
+        <v>19</v>
       </c>
       <c r="H304" s="4"/>
-      <c r="I304" s="4" t="s">
-        <v>604</v>
+      <c r="I304" t="s">
+        <v>606</v>
       </c>
       <c r="J304" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L304" s="28" t="s">
-        <v>149</v>
-      </c>
-      <c r="M304" s="24" t="s">
-        <v>604</v>
+      <c r="L304" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M304" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="305" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A305" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B305" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="C305" s="4" t="s">
+      <c r="B305" s="21" t="s">
         <v>22</v>
       </c>
+      <c r="C305" s="21" t="s">
+        <v>23</v>
+      </c>
       <c r="D305" s="5" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="E305" s="4"/>
       <c r="F305" s="5" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="G305" s="4" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="H305" s="4"/>
       <c r="I305" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="J305" s="4" t="s">
         <v>20</v>
@@ -12268,32 +12311,32 @@
         <v>21</v>
       </c>
       <c r="M305" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="306" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B306" s="4" t="s">
+      <c r="B306" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C306" s="4" t="s">
+      <c r="C306" s="21" t="s">
         <v>23</v>
       </c>
       <c r="D306" s="5" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E306" s="4"/>
       <c r="F306" s="5" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="G306" s="4" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="H306" s="4"/>
       <c r="I306" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="J306" s="4" t="s">
         <v>20</v>
@@ -12302,62 +12345,58 @@
         <v>21</v>
       </c>
       <c r="M306" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="307" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A307" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B307" s="4" t="s">
+      <c r="B307" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C307" s="4" t="s">
+      <c r="C307" s="21" t="s">
         <v>23</v>
       </c>
       <c r="D307" s="5" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="E307" s="4"/>
       <c r="F307" s="5" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="G307" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H307" s="4"/>
-      <c r="I307" t="s">
-        <v>610</v>
-      </c>
+      <c r="I307" s="4"/>
       <c r="J307" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L307" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M307" t="s">
-        <v>610</v>
-      </c>
+      <c r="M307"/>
     </row>
     <row r="308" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A308" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B308" s="4" t="s">
+      <c r="B308" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C308" s="4" t="s">
+      <c r="C308" s="21" t="s">
         <v>23</v>
       </c>
       <c r="D308" s="5" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="E308" s="4"/>
       <c r="F308" s="5" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="G308" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H308" s="4"/>
       <c r="I308" s="4"/>
@@ -12373,21 +12412,21 @@
       <c r="A309" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B309" s="4" t="s">
+      <c r="B309" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C309" s="4" t="s">
-        <v>23</v>
+      <c r="C309" s="21" t="s">
+        <v>43</v>
       </c>
       <c r="D309" s="5" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E309" s="4"/>
       <c r="F309" s="5" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="G309" s="4" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="H309" s="4"/>
       <c r="I309" s="4"/>
@@ -12403,55 +12442,59 @@
       <c r="A310" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B310" s="4" t="s">
+      <c r="B310" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C310" s="4" t="s">
+      <c r="C310" s="21" t="s">
         <v>43</v>
       </c>
       <c r="D310" s="5" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="E310" s="4"/>
       <c r="F310" s="5" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="G310" s="4" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="H310" s="4"/>
-      <c r="I310" s="4"/>
+      <c r="I310" t="s">
+        <v>615</v>
+      </c>
       <c r="J310" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L310" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M310"/>
+      <c r="M310" t="s">
+        <v>615</v>
+      </c>
     </row>
     <row r="311" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A311" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B311" s="4" t="s">
+      <c r="B311" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C311" s="4" t="s">
-        <v>43</v>
+      <c r="C311" s="21" t="s">
+        <v>29</v>
       </c>
       <c r="D311" s="5" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="E311" s="4"/>
       <c r="F311" s="5" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="G311" s="4" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="H311" s="4"/>
       <c r="I311" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="J311" s="4" t="s">
         <v>20</v>
@@ -12460,96 +12503,92 @@
         <v>21</v>
       </c>
       <c r="M311" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="312" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A312" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B312" s="4" t="s">
+      <c r="B312" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C312" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D312" s="5" t="s">
-        <v>616</v>
+      <c r="C312" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="D312" s="4" t="s">
+        <v>618</v>
       </c>
       <c r="E312" s="4"/>
-      <c r="F312" s="5" t="s">
-        <v>616</v>
+      <c r="F312" s="4" t="s">
+        <v>618</v>
       </c>
       <c r="G312" s="4" t="s">
-        <v>19</v>
+        <v>170</v>
       </c>
       <c r="H312" s="4"/>
-      <c r="I312" t="s">
-        <v>617</v>
+      <c r="I312" s="4" t="s">
+        <v>619</v>
       </c>
       <c r="J312" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L312" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M312" t="s">
-        <v>617</v>
+      <c r="L312" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="M312" s="23" t="s">
+        <v>619</v>
       </c>
     </row>
     <row r="313" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A313" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B313" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C313" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D313" s="4" t="s">
-        <v>618</v>
+      <c r="B313" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C313" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="D313" s="5" t="s">
+        <v>620</v>
       </c>
       <c r="E313" s="4"/>
-      <c r="F313" s="4" t="s">
-        <v>618</v>
+      <c r="F313" s="5" t="s">
+        <v>620</v>
       </c>
       <c r="G313" s="4" t="s">
-        <v>170</v>
+        <v>19</v>
       </c>
       <c r="H313" s="4"/>
-      <c r="I313" s="4" t="s">
-        <v>619</v>
-      </c>
+      <c r="I313" s="4"/>
       <c r="J313" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L313" s="28" t="s">
-        <v>149</v>
-      </c>
-      <c r="M313" s="24" t="s">
-        <v>619</v>
-      </c>
+      <c r="L313" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M313"/>
     </row>
     <row r="314" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A314" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B314" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C314" s="4" t="s">
-        <v>43</v>
+      <c r="B314" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C314" s="21" t="s">
+        <v>47</v>
       </c>
       <c r="D314" s="5" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="E314" s="4"/>
       <c r="F314" s="5" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="G314" s="4" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="H314" s="4"/>
       <c r="I314" s="4"/>
@@ -12565,55 +12604,59 @@
       <c r="A315" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B315" s="4" t="s">
+      <c r="B315" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C315" s="4" t="s">
-        <v>47</v>
+      <c r="C315" s="21" t="s">
+        <v>54</v>
       </c>
       <c r="D315" s="5" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E315" s="4"/>
       <c r="F315" s="5" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="G315" s="4" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="H315" s="4"/>
-      <c r="I315" s="4"/>
+      <c r="I315" t="s">
+        <v>623</v>
+      </c>
       <c r="J315" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L315" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M315"/>
+      <c r="M315" t="s">
+        <v>623</v>
+      </c>
     </row>
     <row r="316" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A316" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B316" s="4" t="s">
+      <c r="B316" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C316" s="4" t="s">
-        <v>54</v>
+      <c r="C316" s="21" t="s">
+        <v>47</v>
       </c>
       <c r="D316" s="5" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="E316" s="4"/>
       <c r="F316" s="5" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="G316" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H316" s="4"/>
       <c r="I316" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="J316" s="4" t="s">
         <v>20</v>
@@ -12622,32 +12665,32 @@
         <v>21</v>
       </c>
       <c r="M316" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="317" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A317" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B317" s="4" t="s">
+      <c r="B317" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C317" s="4" t="s">
-        <v>47</v>
+      <c r="C317" s="21" t="s">
+        <v>256</v>
       </c>
       <c r="D317" s="5" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="E317" s="4"/>
       <c r="F317" s="5" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="G317" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H317" s="4"/>
       <c r="I317" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="J317" s="4" t="s">
         <v>20</v>
@@ -12656,62 +12699,58 @@
         <v>21</v>
       </c>
       <c r="M317" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="318" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A318" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B318" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C318" s="4" t="s">
-        <v>256</v>
+      <c r="B318" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="C318" s="21" t="s">
+        <v>628</v>
       </c>
       <c r="D318" s="5" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="E318" s="4"/>
       <c r="F318" s="5" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="G318" s="4" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="H318" s="4"/>
-      <c r="I318" t="s">
-        <v>627</v>
-      </c>
+      <c r="I318" s="4"/>
       <c r="J318" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L318" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M318" t="s">
-        <v>627</v>
-      </c>
+      <c r="M318"/>
     </row>
     <row r="319" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A319" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B319" s="4" t="s">
+      <c r="B319" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="C319" s="4" t="s">
-        <v>628</v>
-      </c>
-      <c r="D319" s="5" t="s">
-        <v>629</v>
+      <c r="C319" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D319" s="22" t="s">
+        <v>671</v>
       </c>
       <c r="E319" s="4"/>
-      <c r="F319" s="5" t="s">
-        <v>629</v>
+      <c r="F319" s="22" t="s">
+        <v>671</v>
       </c>
       <c r="G319" s="4" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="H319" s="4"/>
       <c r="I319" s="4"/>
@@ -12727,55 +12766,59 @@
       <c r="A320" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B320" s="4" t="s">
+      <c r="B320" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="C320" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D320" s="23" t="s">
-        <v>671</v>
+      <c r="C320" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="D320" s="5" t="s">
+        <v>630</v>
       </c>
       <c r="E320" s="4"/>
-      <c r="F320" s="23" t="s">
-        <v>671</v>
+      <c r="F320" s="5" t="s">
+        <v>630</v>
       </c>
       <c r="G320" s="4" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="H320" s="4"/>
-      <c r="I320" s="4"/>
+      <c r="I320" t="s">
+        <v>631</v>
+      </c>
       <c r="J320" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L320" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M320"/>
+      <c r="M320" t="s">
+        <v>632</v>
+      </c>
     </row>
     <row r="321" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A321" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B321" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C321" s="4" t="s">
-        <v>61</v>
+      <c r="B321" s="21" t="s">
+        <v>256</v>
+      </c>
+      <c r="C321" s="21" t="s">
+        <v>54</v>
       </c>
       <c r="D321" s="5" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="E321" s="4"/>
       <c r="F321" s="5" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="G321" s="4" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H321" s="4"/>
       <c r="I321" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="J321" s="4" t="s">
         <v>20</v>
@@ -12784,62 +12827,58 @@
         <v>21</v>
       </c>
       <c r="M321" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="322" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A322" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B322" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="C322" s="4" t="s">
-        <v>54</v>
+      <c r="B322" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="C322" s="21" t="s">
+        <v>628</v>
       </c>
       <c r="D322" s="5" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="E322" s="4"/>
       <c r="F322" s="5" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="G322" s="4" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H322" s="4"/>
-      <c r="I322" t="s">
-        <v>634</v>
-      </c>
+      <c r="I322" s="4"/>
       <c r="J322" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L322" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M322" t="s">
-        <v>634</v>
-      </c>
+      <c r="M322"/>
     </row>
     <row r="323" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A323" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B323" s="4" t="s">
+      <c r="B323" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C323" s="4" t="s">
+      <c r="C323" s="21" t="s">
         <v>628</v>
       </c>
       <c r="D323" s="5" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="E323" s="4"/>
       <c r="F323" s="5" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="G323" s="4" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="H323" s="4"/>
       <c r="I323" s="4"/>
@@ -12855,85 +12894,85 @@
       <c r="A324" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B324" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C324" s="4" t="s">
+      <c r="B324" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C324" s="21" t="s">
         <v>628</v>
       </c>
       <c r="D324" s="5" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E324" s="4"/>
       <c r="F324" s="5" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="G324" s="4" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="H324" s="4"/>
-      <c r="I324" s="4"/>
+      <c r="I324" t="s">
+        <v>638</v>
+      </c>
       <c r="J324" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L324" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M324"/>
+      <c r="M324" t="s">
+        <v>639</v>
+      </c>
     </row>
     <row r="325" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A325" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B325" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C325" s="4" t="s">
-        <v>628</v>
+      <c r="B325" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="C325" s="21" t="s">
+        <v>640</v>
       </c>
       <c r="D325" s="5" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="E325" s="4"/>
       <c r="F325" s="5" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="G325" s="4" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H325" s="4"/>
-      <c r="I325" t="s">
-        <v>638</v>
-      </c>
+      <c r="I325" s="4"/>
       <c r="J325" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L325" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M325" t="s">
-        <v>639</v>
-      </c>
+      <c r="M325"/>
     </row>
     <row r="326" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A326" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B326" s="4" t="s">
+      <c r="B326" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="C326" s="4" t="s">
-        <v>640</v>
+      <c r="C326" s="21" t="s">
+        <v>642</v>
       </c>
       <c r="D326" s="5" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="E326" s="4"/>
       <c r="F326" s="5" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="G326" s="4" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H326" s="4"/>
       <c r="I326" s="4"/>
@@ -12945,89 +12984,89 @@
       </c>
       <c r="M326"/>
     </row>
-    <row r="327" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A327" s="4" t="s">
+    <row r="327" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A327" s="13" t="s">
         <v>508</v>
       </c>
-      <c r="B327" s="4" t="s">
+      <c r="B327" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C327" s="4" t="s">
-        <v>642</v>
-      </c>
-      <c r="D327" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="E327" s="4"/>
-      <c r="F327" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="G327" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H327" s="4"/>
-      <c r="I327" s="4"/>
-      <c r="J327" s="4" t="s">
+      <c r="C327" s="40" t="s">
+        <v>644</v>
+      </c>
+      <c r="D327" s="36" t="s">
+        <v>645</v>
+      </c>
+      <c r="E327" s="13"/>
+      <c r="F327" s="15" t="s">
+        <v>646</v>
+      </c>
+      <c r="G327" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="H327" s="13"/>
+      <c r="I327" s="14" t="s">
+        <v>647</v>
+      </c>
+      <c r="J327" s="13" t="s">
         <v>20</v>
       </c>
       <c r="L327" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M327"/>
-    </row>
-    <row r="328" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A328" s="13" t="s">
-        <v>508</v>
-      </c>
-      <c r="B328" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="C328" s="13" t="s">
-        <v>644</v>
-      </c>
-      <c r="D328" s="32" t="s">
-        <v>645</v>
-      </c>
-      <c r="E328" s="13"/>
-      <c r="F328" s="15" t="s">
-        <v>646</v>
-      </c>
-      <c r="G328" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="H328" s="13"/>
-      <c r="I328" s="14" t="s">
+      <c r="M327" t="s">
         <v>647</v>
       </c>
-      <c r="J328" s="13" t="s">
+    </row>
+    <row r="328" spans="1:13" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A328" s="10" t="s">
+        <v>648</v>
+      </c>
+      <c r="B328" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="C328" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="D328" s="5" t="s">
+        <v>649</v>
+      </c>
+      <c r="E328" s="4"/>
+      <c r="F328" s="5" t="s">
+        <v>649</v>
+      </c>
+      <c r="G328" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H328" s="4"/>
+      <c r="I328" s="4"/>
+      <c r="J328" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L328" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M328" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="329" spans="1:13" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A329" s="10" t="s">
+      <c r="M328"/>
+    </row>
+    <row r="329" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A329" s="4" t="s">
         <v>648</v>
       </c>
-      <c r="B329" s="4" t="s">
+      <c r="B329" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="C329" s="4" t="s">
+      <c r="C329" s="21" t="s">
         <v>90</v>
       </c>
       <c r="D329" s="5" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="E329" s="4"/>
       <c r="F329" s="5" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="G329" s="4" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="H329" s="4"/>
       <c r="I329" s="4"/>
@@ -13043,85 +13082,85 @@
       <c r="A330" s="4" t="s">
         <v>648</v>
       </c>
-      <c r="B330" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C330" s="4" t="s">
+      <c r="B330" s="21" t="s">
+        <v>316</v>
+      </c>
+      <c r="C330" s="21" t="s">
         <v>90</v>
       </c>
       <c r="D330" s="5" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="E330" s="4"/>
       <c r="F330" s="5" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="G330" s="4" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="H330" s="4"/>
-      <c r="I330" s="4"/>
+      <c r="I330" t="s">
+        <v>652</v>
+      </c>
       <c r="J330" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L330" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M330"/>
+      <c r="M330" t="s">
+        <v>652</v>
+      </c>
     </row>
     <row r="331" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A331" s="4" t="s">
         <v>648</v>
       </c>
-      <c r="B331" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="C331" s="4" t="s">
-        <v>90</v>
+      <c r="B331" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="C331" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="D331" s="5" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E331" s="4"/>
       <c r="F331" s="5" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="G331" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H331" s="4"/>
-      <c r="I331" t="s">
-        <v>652</v>
-      </c>
+      <c r="I331" s="4"/>
       <c r="J331" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L331" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M331" t="s">
-        <v>652</v>
-      </c>
+      <c r="M331"/>
     </row>
     <row r="332" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A332" s="4" t="s">
         <v>648</v>
       </c>
-      <c r="B332" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C332" s="4" t="s">
-        <v>104</v>
+      <c r="B332" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C332" s="21" t="s">
+        <v>110</v>
       </c>
       <c r="D332" s="5" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E332" s="4"/>
       <c r="F332" s="5" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="G332" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H332" s="4"/>
       <c r="I332" s="4"/>
@@ -13137,21 +13176,21 @@
       <c r="A333" s="4" t="s">
         <v>648</v>
       </c>
-      <c r="B333" s="4" t="s">
+      <c r="B333" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="C333" s="4" t="s">
-        <v>110</v>
+      <c r="C333" s="21" t="s">
+        <v>106</v>
       </c>
       <c r="D333" s="5" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E333" s="4"/>
       <c r="F333" s="5" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="G333" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H333" s="4"/>
       <c r="I333" s="4"/>
@@ -13167,55 +13206,59 @@
       <c r="A334" s="4" t="s">
         <v>648</v>
       </c>
-      <c r="B334" s="4" t="s">
+      <c r="B334" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="C334" s="4" t="s">
-        <v>106</v>
+      <c r="C334" s="21" t="s">
+        <v>119</v>
       </c>
       <c r="D334" s="5" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E334" s="4"/>
       <c r="F334" s="5" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="G334" s="4" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="H334" s="4"/>
-      <c r="I334" s="4"/>
+      <c r="I334" t="s">
+        <v>657</v>
+      </c>
       <c r="J334" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L334" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M334"/>
+      <c r="M334" t="s">
+        <v>658</v>
+      </c>
     </row>
     <row r="335" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A335" s="4" t="s">
         <v>648</v>
       </c>
-      <c r="B335" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C335" s="4" t="s">
-        <v>119</v>
+      <c r="B335" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="C335" s="21" t="s">
+        <v>110</v>
       </c>
       <c r="D335" s="5" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="E335" s="4"/>
       <c r="F335" s="5" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="G335" s="4" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="H335" s="4"/>
       <c r="I335" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="J335" s="4" t="s">
         <v>20</v>
@@ -13224,62 +13267,58 @@
         <v>21</v>
       </c>
       <c r="M335" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="336" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A336" s="4" t="s">
         <v>648</v>
       </c>
-      <c r="B336" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="C336" s="4" t="s">
-        <v>110</v>
+      <c r="B336" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="C336" s="21" t="s">
+        <v>119</v>
       </c>
       <c r="D336" s="5" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="E336" s="4"/>
       <c r="F336" s="5" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="G336" s="4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H336" s="4"/>
-      <c r="I336" t="s">
-        <v>660</v>
-      </c>
+      <c r="I336" s="4"/>
       <c r="J336" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L336" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M336" t="s">
-        <v>660</v>
-      </c>
+      <c r="M336"/>
     </row>
     <row r="337" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A337" s="4" t="s">
         <v>648</v>
       </c>
-      <c r="B337" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="C337" s="4" t="s">
-        <v>119</v>
+      <c r="B337" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="C337" s="21" t="s">
+        <v>355</v>
       </c>
       <c r="D337" s="5" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E337" s="4"/>
       <c r="F337" s="5" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="G337" s="4" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H337" s="4"/>
       <c r="I337" s="4"/>
@@ -13295,21 +13334,21 @@
       <c r="A338" s="4" t="s">
         <v>648</v>
       </c>
-      <c r="B338" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C338" s="4" t="s">
-        <v>355</v>
+      <c r="B338" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C338" s="21" t="s">
+        <v>129</v>
       </c>
       <c r="D338" s="5" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E338" s="4"/>
       <c r="F338" s="5" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="G338" s="4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H338" s="4"/>
       <c r="I338" s="4"/>
@@ -13325,82 +13364,82 @@
       <c r="A339" s="4" t="s">
         <v>648</v>
       </c>
-      <c r="B339" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="C339" s="4" t="s">
+      <c r="B339" s="21" t="s">
+        <v>355</v>
+      </c>
+      <c r="C339" s="21" t="s">
         <v>129</v>
       </c>
       <c r="D339" s="5" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E339" s="4"/>
       <c r="F339" s="5" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="G339" s="4" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H339" s="4"/>
-      <c r="I339" s="4"/>
+      <c r="I339" t="s">
+        <v>665</v>
+      </c>
       <c r="J339" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L339" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M339"/>
+      <c r="M339" t="s">
+        <v>665</v>
+      </c>
     </row>
     <row r="340" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A340" s="4" t="s">
         <v>648</v>
       </c>
-      <c r="B340" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="C340" s="4" t="s">
+      <c r="B340" s="21" t="s">
         <v>129</v>
       </c>
+      <c r="C340" s="21" t="s">
+        <v>134</v>
+      </c>
       <c r="D340" s="5" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="E340" s="4"/>
       <c r="F340" s="5" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="G340" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H340" s="4"/>
-      <c r="I340" t="s">
-        <v>665</v>
-      </c>
+      <c r="I340" s="4"/>
       <c r="J340" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L340" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M340" t="s">
-        <v>665</v>
-      </c>
+      <c r="M340"/>
     </row>
     <row r="341" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A341" s="4" t="s">
         <v>648</v>
       </c>
-      <c r="B341" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="C341" s="4" t="s">
+      <c r="B341" s="21" t="s">
         <v>134</v>
       </c>
+      <c r="C341" s="21" t="s">
+        <v>154</v>
+      </c>
       <c r="D341" s="5" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E341" s="4"/>
       <c r="F341" s="5" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G341" s="4" t="s">
         <v>35</v>
@@ -13419,18 +13458,18 @@
       <c r="A342" s="4" t="s">
         <v>648</v>
       </c>
-      <c r="B342" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="C342" s="4" t="s">
+      <c r="B342" s="21" t="s">
         <v>154</v>
       </c>
+      <c r="C342" s="21" t="s">
+        <v>166</v>
+      </c>
       <c r="D342" s="5" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E342" s="4"/>
       <c r="F342" s="5" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="G342" s="4" t="s">
         <v>35</v>
@@ -13445,40 +13484,10 @@
       </c>
       <c r="M342"/>
     </row>
-    <row r="343" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A343" s="4" t="s">
-        <v>648</v>
-      </c>
-      <c r="B343" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="C343" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="D343" s="5" t="s">
-        <v>669</v>
-      </c>
-      <c r="E343" s="4"/>
-      <c r="F343" s="5" t="s">
-        <v>669</v>
-      </c>
-      <c r="G343" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="H343" s="4"/>
-      <c r="I343" s="4"/>
-      <c r="J343" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L343" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M343"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:M343" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A244:M328">
-    <sortCondition ref="B244:B328"/>
+  <autoFilter ref="A3:M342" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A244:M327">
+    <sortCondition ref="B244:B327"/>
   </sortState>
   <pageMargins left="0.390277777777778" right="0.390277777777778" top="0.390277777777778" bottom="0.390277777777778" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>

--- a/import/timetable.xlsx
+++ b/import/timetable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michaelstork/Library/CloudStorage/Box-Box/Feel Festival/Marketing/03_Website/2026_timetable/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA132741-E5EA-E748-95FF-25676D477CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09A70DBD-87DA-5A4B-B9BE-D527AC55820D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -919,9 +919,6 @@
     <t>Miss Take, jewelry and OLIV come together to shape the chill-out floor into a space of warmth, depth and quiet energy. With their distinct yet complementary approaches, the three artists create a continuous, carefully layered journey—moving between dubby textures, subtle breakbeats, shimmering 2-step rhythms and gentle downtempo grooves. The result is an effortless blend of sounds that shift and evolve without force, inviting listeners into a space that feels both grounded and expansive. Expect slow-burning basslines, delicate melodies and moments of calm woven into playful rhythmic patterns—all held together by a shared sense of balance and restraint. Nothing rushed, nothing overwhelming—just a steady, unfolding atmosphere that carries the night into the early light of morning.</t>
   </si>
   <si>
-    <t>AZULU B2B GEM</t>
-  </si>
-  <si>
     <t>CARLO KARACHO</t>
   </si>
   <si>
@@ -2186,6 +2183,9 @@
   </si>
   <si>
     <t>JÖRDIIS B2B FRESHSAX</t>
+  </si>
+  <si>
+    <t>AZULU B2B GEM:INI</t>
   </si>
 </sst>
 </file>
@@ -2301,7 +2301,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2375,24 +2375,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3441,8 +3424,7 @@
       <c r="J27" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K27" s="34"/>
-      <c r="L27" s="35" t="s">
+      <c r="L27" s="6" t="s">
         <v>71</v>
       </c>
       <c r="M27" t="s">
@@ -3474,8 +3456,7 @@
       <c r="J28" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K28" s="34"/>
-      <c r="L28" s="35" t="s">
+      <c r="L28" s="6" t="s">
         <v>21</v>
       </c>
       <c r="M28"/>
@@ -3505,8 +3486,7 @@
       <c r="J29" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K29" s="34"/>
-      <c r="L29" s="35" t="s">
+      <c r="L29" s="6" t="s">
         <v>21</v>
       </c>
       <c r="M29"/>
@@ -3538,8 +3518,7 @@
       <c r="J30" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K30" s="34"/>
-      <c r="L30" s="35" t="s">
+      <c r="L30" s="6" t="s">
         <v>21</v>
       </c>
       <c r="M30" t="s">
@@ -3571,8 +3550,7 @@
       <c r="J31" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K31" s="34"/>
-      <c r="L31" s="35" t="s">
+      <c r="L31" s="6" t="s">
         <v>21</v>
       </c>
       <c r="M31"/>
@@ -3581,10 +3559,10 @@
       <c r="A32" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="B32" s="37" t="s">
+      <c r="B32" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="C32" s="37" t="s">
+      <c r="C32" s="31" t="s">
         <v>90</v>
       </c>
       <c r="D32" s="5" t="s">
@@ -3602,8 +3580,7 @@
       <c r="J32" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="K32" s="34"/>
-      <c r="L32" s="35" t="s">
+      <c r="L32" s="6" t="s">
         <v>21</v>
       </c>
       <c r="M32"/>
@@ -3642,13 +3619,13 @@
       <c r="A34" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B34" s="38" t="s">
+      <c r="B34" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="C34" s="38" t="s">
+      <c r="C34" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="D34" s="31" t="s">
+      <c r="D34" s="5" t="s">
         <v>93</v>
       </c>
       <c r="E34" s="4"/>
@@ -3676,13 +3653,13 @@
       <c r="A35" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B35" s="38" t="s">
+      <c r="B35" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="C35" s="38" t="s">
+      <c r="C35" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="D35" s="31" t="s">
+      <c r="D35" s="5" t="s">
         <v>96</v>
       </c>
       <c r="E35" s="4"/>
@@ -3706,13 +3683,13 @@
       <c r="A36" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B36" s="38" t="s">
+      <c r="B36" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="C36" s="32" t="s">
+      <c r="C36" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="D36" s="31" t="s">
+      <c r="D36" s="5" t="s">
         <v>97</v>
       </c>
       <c r="E36" s="4"/>
@@ -3736,13 +3713,13 @@
       <c r="A37" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B37" s="33" t="s">
+      <c r="B37" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="C37" s="32" t="s">
+      <c r="C37" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="D37" s="31" t="s">
+      <c r="D37" s="5" t="s">
         <v>99</v>
       </c>
       <c r="E37" s="4"/>
@@ -6592,12 +6569,12 @@
       <c r="C126" s="21" t="s">
         <v>275</v>
       </c>
-      <c r="D126" s="5" t="s">
-        <v>285</v>
+      <c r="D126" s="22" t="s">
+        <v>671</v>
       </c>
       <c r="E126" s="4"/>
-      <c r="F126" s="5" t="s">
-        <v>285</v>
+      <c r="F126" s="22" t="s">
+        <v>671</v>
       </c>
       <c r="G126" s="4" t="s">
         <v>35</v>
@@ -6623,11 +6600,11 @@
         <v>67</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E127" s="4"/>
       <c r="F127" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G127" s="4" t="s">
         <v>194</v>
@@ -6653,11 +6630,11 @@
         <v>281</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E128" s="4"/>
       <c r="F128" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G128" s="4" t="s">
         <v>19</v>
@@ -6683,18 +6660,18 @@
         <v>281</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E129" s="4"/>
       <c r="F129" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G129" s="4" t="s">
         <v>170</v>
       </c>
       <c r="H129" s="4"/>
       <c r="I129" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J129" s="4" t="s">
         <v>20</v>
@@ -6703,7 +6680,7 @@
         <v>149</v>
       </c>
       <c r="M129" s="23" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="130" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -6714,14 +6691,14 @@
         <v>54</v>
       </c>
       <c r="C130" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="D130" s="5" t="s">
         <v>291</v>
-      </c>
-      <c r="D130" s="5" t="s">
-        <v>292</v>
       </c>
       <c r="E130" s="4"/>
       <c r="F130" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G130" s="4" t="s">
         <v>258</v>
@@ -6741,17 +6718,17 @@
         <v>88</v>
       </c>
       <c r="B131" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="C131" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="C131" s="12" t="s">
+      <c r="D131" s="5" t="s">
         <v>294</v>
-      </c>
-      <c r="D131" s="5" t="s">
-        <v>295</v>
       </c>
       <c r="E131" s="4"/>
       <c r="F131" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G131" s="4" t="s">
         <v>49</v>
@@ -6771,24 +6748,24 @@
         <v>88</v>
       </c>
       <c r="B132" s="21" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C132" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="D132" s="5" t="s">
         <v>296</v>
-      </c>
-      <c r="D132" s="5" t="s">
-        <v>297</v>
       </c>
       <c r="E132" s="4"/>
       <c r="F132" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G132" s="4" t="s">
         <v>194</v>
       </c>
       <c r="H132" s="4"/>
       <c r="I132" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J132" s="4" t="s">
         <v>20</v>
@@ -6797,7 +6774,7 @@
         <v>71</v>
       </c>
       <c r="M132" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="133" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6808,14 +6785,14 @@
         <v>281</v>
       </c>
       <c r="C133" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="D133" s="5" t="s">
         <v>299</v>
-      </c>
-      <c r="D133" s="5" t="s">
-        <v>300</v>
       </c>
       <c r="E133" s="4"/>
       <c r="F133" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G133" s="4" t="s">
         <v>31</v>
@@ -6834,25 +6811,25 @@
       <c r="A134" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="B134" s="40" t="s">
+      <c r="B134" s="33" t="s">
         <v>281</v>
       </c>
-      <c r="C134" s="39" t="s">
-        <v>299</v>
+      <c r="C134" s="32" t="s">
+        <v>298</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E134" s="4"/>
       <c r="F134" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G134" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H134" s="4"/>
       <c r="I134" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="J134" s="4" t="s">
         <v>20</v>
@@ -6861,12 +6838,12 @@
         <v>21</v>
       </c>
       <c r="M134" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="135" spans="1:13" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A135" s="10" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B135" s="21" t="s">
         <v>89</v>
@@ -6875,11 +6852,11 @@
         <v>90</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E135" s="8"/>
       <c r="F135" s="16" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G135" s="8" t="s">
         <v>39</v>
@@ -6896,7 +6873,7 @@
     </row>
     <row r="136" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B136" s="21" t="s">
         <v>89</v>
@@ -6905,11 +6882,11 @@
         <v>90</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E136" s="4"/>
       <c r="F136" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G136" s="4" t="s">
         <v>25</v>
@@ -6926,7 +6903,7 @@
     </row>
     <row r="137" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B137" s="21" t="s">
         <v>89</v>
@@ -6935,32 +6912,32 @@
         <v>90</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E137" s="4"/>
       <c r="F137" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G137" s="4" t="s">
         <v>28</v>
       </c>
       <c r="H137" s="4"/>
       <c r="I137" t="s">
+        <v>306</v>
+      </c>
+      <c r="J137" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L137" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M137" t="s">
         <v>307</v>
-      </c>
-      <c r="J137" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L137" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M137" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="138" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B138" s="21" t="s">
         <v>89</v>
@@ -6969,11 +6946,11 @@
         <v>90</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E138" s="4"/>
       <c r="F138" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G138" s="4" t="s">
         <v>56</v>
@@ -6990,7 +6967,7 @@
     </row>
     <row r="139" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B139" s="21" t="s">
         <v>89</v>
@@ -6999,45 +6976,45 @@
         <v>90</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E139" s="4"/>
       <c r="F139" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G139" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H139" s="4"/>
       <c r="I139" t="s">
+        <v>310</v>
+      </c>
+      <c r="J139" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L139" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M139" t="s">
         <v>311</v>
-      </c>
-      <c r="J139" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L139" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M139" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="140" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B140" s="21" t="s">
+        <v>312</v>
+      </c>
+      <c r="C140" s="21" t="s">
         <v>313</v>
       </c>
-      <c r="C140" s="21" t="s">
+      <c r="D140" s="5" t="s">
         <v>314</v>
-      </c>
-      <c r="D140" s="5" t="s">
-        <v>315</v>
       </c>
       <c r="E140" s="4"/>
       <c r="F140" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G140" s="4" t="s">
         <v>49</v>
@@ -7054,20 +7031,20 @@
     </row>
     <row r="141" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B141" s="21" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C141" s="21" t="s">
         <v>90</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E141" s="4"/>
       <c r="F141" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G141" s="4" t="s">
         <v>258</v>
@@ -7084,7 +7061,7 @@
     </row>
     <row r="142" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B142" s="21" t="s">
         <v>98</v>
@@ -7093,11 +7070,11 @@
         <v>115</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E142" s="4"/>
       <c r="F142" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G142" s="4" t="s">
         <v>31</v>
@@ -7114,7 +7091,7 @@
     </row>
     <row r="143" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B143" s="21" t="s">
         <v>98</v>
@@ -7123,11 +7100,11 @@
         <v>115</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E143" s="4"/>
       <c r="F143" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G143" s="4" t="s">
         <v>19</v>
@@ -7144,7 +7121,7 @@
     </row>
     <row r="144" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B144" s="21" t="s">
         <v>98</v>
@@ -7153,18 +7130,18 @@
         <v>115</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E144" s="4"/>
       <c r="F144" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G144" s="4" t="s">
         <v>170</v>
       </c>
       <c r="H144" s="4"/>
       <c r="I144" s="23" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="J144" s="4" t="s">
         <v>20</v>
@@ -7173,25 +7150,25 @@
         <v>21</v>
       </c>
       <c r="M144" s="23" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="145" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B145" s="21" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C145" s="21" t="s">
+        <v>321</v>
+      </c>
+      <c r="D145" s="5" t="s">
         <v>322</v>
-      </c>
-      <c r="D145" s="5" t="s">
-        <v>323</v>
       </c>
       <c r="E145" s="4"/>
       <c r="F145" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G145" s="4" t="s">
         <v>49</v>
@@ -7208,7 +7185,7 @@
     </row>
     <row r="146" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B146" s="21" t="s">
         <v>90</v>
@@ -7217,11 +7194,11 @@
         <v>106</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E146" s="4"/>
       <c r="F146" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G146" s="4" t="s">
         <v>39</v>
@@ -7238,20 +7215,20 @@
     </row>
     <row r="147" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B147" s="21" t="s">
         <v>90</v>
       </c>
       <c r="C147" s="21" t="s">
+        <v>324</v>
+      </c>
+      <c r="D147" s="5" t="s">
         <v>325</v>
-      </c>
-      <c r="D147" s="5" t="s">
-        <v>326</v>
       </c>
       <c r="E147" s="4"/>
       <c r="F147" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G147" s="4" t="s">
         <v>25</v>
@@ -7268,7 +7245,7 @@
     </row>
     <row r="148" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B148" s="21" t="s">
         <v>90</v>
@@ -7277,11 +7254,11 @@
         <v>106</v>
       </c>
       <c r="D148" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E148" s="4"/>
       <c r="F148" s="5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G148" s="4" t="s">
         <v>28</v>
@@ -7298,7 +7275,7 @@
     </row>
     <row r="149" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B149" s="21" t="s">
         <v>90</v>
@@ -7307,32 +7284,32 @@
         <v>106</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E149" s="4"/>
       <c r="F149" s="5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G149" s="4" t="s">
         <v>56</v>
       </c>
       <c r="H149" s="4"/>
       <c r="I149" t="s">
+        <v>329</v>
+      </c>
+      <c r="J149" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L149" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M149" t="s">
         <v>330</v>
-      </c>
-      <c r="J149" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L149" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M149" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="150" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B150" s="21" t="s">
         <v>90</v>
@@ -7341,18 +7318,18 @@
         <v>106</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E150" s="4"/>
       <c r="F150" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G150" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H150" s="4"/>
       <c r="I150" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="J150" s="4" t="s">
         <v>20</v>
@@ -7361,12 +7338,12 @@
         <v>21</v>
       </c>
       <c r="M150" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="151" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B151" s="21" t="s">
         <v>115</v>
@@ -7375,32 +7352,32 @@
         <v>106</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E151" s="4"/>
       <c r="F151" s="5" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G151" s="4" t="s">
         <v>31</v>
       </c>
       <c r="H151" s="4"/>
       <c r="I151" t="s">
+        <v>334</v>
+      </c>
+      <c r="J151" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L151" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M151" t="s">
         <v>335</v>
-      </c>
-      <c r="J151" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L151" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M151" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="152" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B152" s="21" t="s">
         <v>115</v>
@@ -7409,11 +7386,11 @@
         <v>106</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E152" s="4"/>
       <c r="F152" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G152" s="4" t="s">
         <v>19</v>
@@ -7430,7 +7407,7 @@
     </row>
     <row r="153" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B153" s="21" t="s">
         <v>115</v>
@@ -7439,18 +7416,18 @@
         <v>106</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E153" s="4"/>
       <c r="F153" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G153" s="4" t="s">
         <v>170</v>
       </c>
       <c r="H153" s="4"/>
       <c r="I153" s="23" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J153" s="4" t="s">
         <v>20</v>
@@ -7459,25 +7436,25 @@
         <v>21</v>
       </c>
       <c r="M153" s="23" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="154" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B154" s="21" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C154" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="D154" s="5" t="s">
         <v>340</v>
-      </c>
-      <c r="D154" s="5" t="s">
-        <v>341</v>
       </c>
       <c r="E154" s="4"/>
       <c r="F154" s="5" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G154" s="4" t="s">
         <v>49</v>
@@ -7487,27 +7464,27 @@
       <c r="J154" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L154" s="35" t="s">
+      <c r="L154" s="6" t="s">
         <v>21</v>
       </c>
       <c r="M154"/>
     </row>
     <row r="155" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B155" s="21" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C155" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="D155" s="5" t="s">
         <v>342</v>
-      </c>
-      <c r="D155" s="5" t="s">
-        <v>343</v>
       </c>
       <c r="E155" s="4"/>
       <c r="F155" s="5" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G155" s="4" t="s">
         <v>25</v>
@@ -7524,7 +7501,7 @@
     </row>
     <row r="156" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B156" s="21" t="s">
         <v>106</v>
@@ -7533,11 +7510,11 @@
         <v>119</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E156" s="4"/>
       <c r="F156" s="5" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G156" s="4" t="s">
         <v>39</v>
@@ -7554,7 +7531,7 @@
     </row>
     <row r="157" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B157" s="21" t="s">
         <v>106</v>
@@ -7563,11 +7540,11 @@
         <v>119</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E157" s="4"/>
       <c r="F157" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G157" s="4" t="s">
         <v>28</v>
@@ -7584,20 +7561,20 @@
     </row>
     <row r="158" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B158" s="21" t="s">
         <v>106</v>
       </c>
       <c r="C158" s="21" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E158" s="4"/>
       <c r="F158" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G158" s="4" t="s">
         <v>31</v>
@@ -7614,7 +7591,7 @@
     </row>
     <row r="159" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B159" s="21" t="s">
         <v>106</v>
@@ -7623,18 +7600,18 @@
         <v>119</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E159" s="4"/>
       <c r="F159" s="5" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G159" s="4" t="s">
         <v>56</v>
       </c>
       <c r="H159" s="4"/>
       <c r="I159" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J159" s="4" t="s">
         <v>20</v>
@@ -7643,12 +7620,12 @@
         <v>21</v>
       </c>
       <c r="M159" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="160" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B160" s="21" t="s">
         <v>106</v>
@@ -7657,18 +7634,18 @@
         <v>119</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E160" s="4"/>
       <c r="F160" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G160" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H160" s="4"/>
       <c r="I160" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="J160" s="4" t="s">
         <v>20</v>
@@ -7677,12 +7654,12 @@
         <v>21</v>
       </c>
       <c r="M160" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="161" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B161" s="21" t="s">
         <v>106</v>
@@ -7691,11 +7668,11 @@
         <v>119</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E161" s="4"/>
       <c r="F161" s="5" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G161" s="4" t="s">
         <v>19</v>
@@ -7712,27 +7689,27 @@
     </row>
     <row r="162" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B162" s="21" t="s">
         <v>106</v>
       </c>
       <c r="C162" s="21" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D162" s="17" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E162" s="4"/>
       <c r="F162" s="17" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G162" s="4" t="s">
         <v>170</v>
       </c>
       <c r="H162" s="4"/>
       <c r="I162" s="23" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="J162" s="4" t="s">
         <v>20</v>
@@ -7741,25 +7718,25 @@
         <v>21</v>
       </c>
       <c r="M162" s="23" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="163" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B163" s="21" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C163" s="21" t="s">
+        <v>354</v>
+      </c>
+      <c r="D163" s="5" t="s">
         <v>355</v>
-      </c>
-      <c r="D163" s="5" t="s">
-        <v>356</v>
       </c>
       <c r="E163" s="4"/>
       <c r="F163" s="5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G163" s="4" t="s">
         <v>25</v>
@@ -7776,20 +7753,20 @@
     </row>
     <row r="164" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B164" s="21" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C164" s="21" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E164" s="4"/>
       <c r="F164" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G164" s="4" t="s">
         <v>31</v>
@@ -7806,7 +7783,7 @@
     </row>
     <row r="165" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B165" s="21" t="s">
         <v>119</v>
@@ -7815,11 +7792,11 @@
         <v>127</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E165" s="4"/>
       <c r="F165" s="5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G165" s="4" t="s">
         <v>28</v>
@@ -7836,7 +7813,7 @@
     </row>
     <row r="166" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B166" s="21" t="s">
         <v>119</v>
@@ -7845,11 +7822,11 @@
         <v>127</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E166" s="4"/>
       <c r="F166" s="5" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G166" s="4" t="s">
         <v>56</v>
@@ -7866,7 +7843,7 @@
     </row>
     <row r="167" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B167" s="21" t="s">
         <v>119</v>
@@ -7875,18 +7852,18 @@
         <v>127</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E167" s="4"/>
       <c r="F167" s="5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G167" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H167" s="4"/>
       <c r="I167" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="J167" s="4" t="s">
         <v>20</v>
@@ -7895,32 +7872,32 @@
         <v>21</v>
       </c>
       <c r="M167" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="168" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B168" s="21" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C168" s="21" t="s">
         <v>129</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E168" s="4"/>
       <c r="F168" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G168" s="4" t="s">
         <v>25</v>
       </c>
       <c r="H168" s="4"/>
       <c r="I168" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="J168" s="4" t="s">
         <v>20</v>
@@ -7929,12 +7906,12 @@
         <v>21</v>
       </c>
       <c r="M168" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="169" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B169" s="21" t="s">
         <v>127</v>
@@ -7943,18 +7920,18 @@
         <v>136</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E169" s="4"/>
       <c r="F169" s="5" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G169" s="4" t="s">
         <v>56</v>
       </c>
       <c r="H169" s="4"/>
       <c r="I169" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="J169" s="4" t="s">
         <v>20</v>
@@ -7963,12 +7940,12 @@
         <v>21</v>
       </c>
       <c r="M169" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="170" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B170" s="21" t="s">
         <v>127</v>
@@ -7977,11 +7954,11 @@
         <v>136</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E170" s="4"/>
       <c r="F170" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G170" s="4" t="s">
         <v>35</v>
@@ -7998,7 +7975,7 @@
     </row>
     <row r="171" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B171" s="21" t="s">
         <v>136</v>
@@ -8007,18 +7984,18 @@
         <v>140</v>
       </c>
       <c r="D171" s="5" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E171" s="4"/>
       <c r="F171" s="5" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G171" s="4" t="s">
         <v>56</v>
       </c>
       <c r="H171" s="4"/>
       <c r="I171" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="J171" s="4" t="s">
         <v>20</v>
@@ -8027,12 +8004,12 @@
         <v>21</v>
       </c>
       <c r="M171" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="172" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B172" s="21" t="s">
         <v>136</v>
@@ -8041,11 +8018,11 @@
         <v>140</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E172" s="4"/>
       <c r="F172" s="5" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G172" s="4" t="s">
         <v>35</v>
@@ -8062,7 +8039,7 @@
     </row>
     <row r="173" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B173" s="21" t="s">
         <v>136</v>
@@ -8071,18 +8048,18 @@
         <v>134</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E173" s="4"/>
       <c r="F173" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G173" s="4" t="s">
         <v>152</v>
       </c>
       <c r="H173" s="4"/>
       <c r="I173" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="J173" s="4" t="s">
         <v>20</v>
@@ -8091,12 +8068,12 @@
         <v>149</v>
       </c>
       <c r="M173" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="174" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B174" s="21" t="s">
         <v>143</v>
@@ -8105,18 +8082,18 @@
         <v>140</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E174" s="4"/>
       <c r="F174" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G174" s="4" t="s">
         <v>162</v>
       </c>
       <c r="H174" s="4"/>
       <c r="I174" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="J174" s="4" t="s">
         <v>20</v>
@@ -8125,32 +8102,32 @@
         <v>149</v>
       </c>
       <c r="M174" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="175" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B175" s="12" t="s">
         <v>150</v>
       </c>
       <c r="C175" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="D175" s="4" t="s">
         <v>374</v>
-      </c>
-      <c r="D175" s="4" t="s">
-        <v>375</v>
       </c>
       <c r="E175" s="4"/>
       <c r="F175" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G175" s="4" t="s">
         <v>152</v>
       </c>
       <c r="H175" s="4"/>
       <c r="I175" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="J175" s="4" t="s">
         <v>20</v>
@@ -8159,12 +8136,12 @@
         <v>149</v>
       </c>
       <c r="M175" s="5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="176" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B176" s="21" t="s">
         <v>140</v>
@@ -8173,11 +8150,11 @@
         <v>144</v>
       </c>
       <c r="D176" s="5" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E176" s="4"/>
       <c r="F176" s="5" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G176" s="4" t="s">
         <v>28</v>
@@ -8194,7 +8171,7 @@
     </row>
     <row r="177" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B177" s="21" t="s">
         <v>140</v>
@@ -8203,11 +8180,11 @@
         <v>144</v>
       </c>
       <c r="D177" s="5" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E177" s="4"/>
       <c r="F177" s="5" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="G177" s="4" t="s">
         <v>31</v>
@@ -8224,7 +8201,7 @@
     </row>
     <row r="178" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B178" s="21" t="s">
         <v>140</v>
@@ -8233,32 +8210,32 @@
         <v>144</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E178" s="4"/>
       <c r="F178" s="5" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G178" s="4" t="s">
         <v>56</v>
       </c>
       <c r="H178" s="4"/>
       <c r="I178" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="J178" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L178" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M178" t="s">
         <v>381</v>
-      </c>
-      <c r="J178" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L178" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M178" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="179" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B179" s="21" t="s">
         <v>140</v>
@@ -8267,11 +8244,11 @@
         <v>144</v>
       </c>
       <c r="D179" s="5" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E179" s="4"/>
       <c r="F179" s="5" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="G179" s="4" t="s">
         <v>35</v>
@@ -8288,7 +8265,7 @@
     </row>
     <row r="180" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B180" s="21" t="s">
         <v>140</v>
@@ -8318,7 +8295,7 @@
     </row>
     <row r="181" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B181" s="21" t="s">
         <v>140</v>
@@ -8327,18 +8304,18 @@
         <v>160</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E181" s="4"/>
       <c r="F181" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G181" s="4" t="s">
         <v>170</v>
       </c>
       <c r="H181" s="4"/>
       <c r="I181" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="J181" s="4" t="s">
         <v>20</v>
@@ -8347,32 +8324,32 @@
         <v>149</v>
       </c>
       <c r="M181" s="23" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="182" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B182" s="21" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C182" s="21" t="s">
         <v>144</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E182" s="4"/>
       <c r="F182" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G182" s="4" t="s">
         <v>162</v>
       </c>
       <c r="H182" s="4"/>
       <c r="I182" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="J182" s="4" t="s">
         <v>20</v>
@@ -8381,12 +8358,12 @@
         <v>149</v>
       </c>
       <c r="M182" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="183" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B183" s="21" t="s">
         <v>154</v>
@@ -8395,7 +8372,7 @@
         <v>168</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E183" s="4"/>
       <c r="F183"/>
@@ -8414,7 +8391,7 @@
     </row>
     <row r="184" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B184" s="21" t="s">
         <v>154</v>
@@ -8423,18 +8400,18 @@
         <v>181</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E184" s="4"/>
       <c r="F184" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G184" s="4" t="s">
         <v>147</v>
       </c>
       <c r="H184" s="4"/>
       <c r="I184" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="J184" s="4" t="s">
         <v>20</v>
@@ -8443,12 +8420,12 @@
         <v>149</v>
       </c>
       <c r="M184" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="185" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B185" s="21" t="s">
         <v>154</v>
@@ -8457,18 +8434,18 @@
         <v>144</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E185" s="4"/>
       <c r="F185" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G185" s="4" t="s">
         <v>152</v>
       </c>
       <c r="H185" s="4"/>
       <c r="I185" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="J185" s="4" t="s">
         <v>20</v>
@@ -8477,12 +8454,12 @@
         <v>149</v>
       </c>
       <c r="M185" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="186" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B186" s="21" t="s">
         <v>144</v>
@@ -8490,33 +8467,33 @@
       <c r="C186" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="D186" s="31" t="s">
-        <v>393</v>
+      <c r="D186" s="5" t="s">
+        <v>392</v>
       </c>
       <c r="E186" s="4"/>
       <c r="F186" s="5" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G186" s="4" t="s">
         <v>39</v>
       </c>
       <c r="H186" s="4"/>
       <c r="I186" t="s">
+        <v>393</v>
+      </c>
+      <c r="J186" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L186" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M186" t="s">
         <v>394</v>
-      </c>
-      <c r="J186" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L186" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M186" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="187" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B187" s="21" t="s">
         <v>144</v>
@@ -8525,11 +8502,11 @@
         <v>16</v>
       </c>
       <c r="D187" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E187" s="4"/>
       <c r="F187" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G187" s="4" t="s">
         <v>28</v>
@@ -8546,7 +8523,7 @@
     </row>
     <row r="188" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B188" s="21" t="s">
         <v>144</v>
@@ -8555,18 +8532,18 @@
         <v>16</v>
       </c>
       <c r="D188" s="5" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E188" s="4"/>
       <c r="F188" s="5" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G188" s="4" t="s">
         <v>31</v>
       </c>
       <c r="H188" s="4"/>
       <c r="I188" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="J188" s="4" t="s">
         <v>20</v>
@@ -8575,12 +8552,12 @@
         <v>21</v>
       </c>
       <c r="M188" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="189" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B189" s="21" t="s">
         <v>144</v>
@@ -8589,11 +8566,11 @@
         <v>16</v>
       </c>
       <c r="D189" s="5" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E189" s="4"/>
       <c r="F189" s="5" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G189" s="4" t="s">
         <v>56</v>
@@ -8610,7 +8587,7 @@
     </row>
     <row r="190" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B190" s="21" t="s">
         <v>144</v>
@@ -8619,11 +8596,11 @@
         <v>16</v>
       </c>
       <c r="D190" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E190" s="4"/>
       <c r="F190" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G190" s="4" t="s">
         <v>35</v>
@@ -8640,7 +8617,7 @@
     </row>
     <row r="191" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B191" s="21" t="s">
         <v>144</v>
@@ -8649,7 +8626,7 @@
         <v>16</v>
       </c>
       <c r="D191" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E191" s="4"/>
       <c r="G191" s="4" t="s">
@@ -8657,7 +8634,7 @@
       </c>
       <c r="H191" s="4"/>
       <c r="I191" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="J191" s="4" t="s">
         <v>20</v>
@@ -8666,32 +8643,32 @@
         <v>149</v>
       </c>
       <c r="M191" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="192" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B192" s="21" t="s">
         <v>168</v>
       </c>
       <c r="C192" s="21" t="s">
+        <v>403</v>
+      </c>
+      <c r="D192" s="5" t="s">
         <v>404</v>
-      </c>
-      <c r="D192" s="5" t="s">
-        <v>405</v>
       </c>
       <c r="E192" s="4"/>
       <c r="F192" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G192" s="4" t="s">
         <v>194</v>
       </c>
       <c r="H192" s="4"/>
       <c r="I192" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="J192" s="4" t="s">
         <v>20</v>
@@ -8700,12 +8677,12 @@
         <v>71</v>
       </c>
       <c r="M192" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="193" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B193" s="21" t="s">
         <v>168</v>
@@ -8714,18 +8691,18 @@
         <v>16</v>
       </c>
       <c r="D193" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E193" s="4"/>
       <c r="F193" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="G193" s="4" t="s">
         <v>152</v>
       </c>
       <c r="H193" s="4"/>
       <c r="I193" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="J193" s="4" t="s">
         <v>20</v>
@@ -8734,12 +8711,12 @@
         <v>149</v>
       </c>
       <c r="M193" s="5" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="194" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B194" s="21" t="s">
         <v>168</v>
@@ -8748,7 +8725,7 @@
         <v>16</v>
       </c>
       <c r="D194" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E194" s="4"/>
       <c r="F194" s="4"/>
@@ -8757,7 +8734,7 @@
       </c>
       <c r="H194" s="4"/>
       <c r="I194" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="J194" s="4" t="s">
         <v>20</v>
@@ -8766,32 +8743,32 @@
         <v>149</v>
       </c>
       <c r="M194" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="195" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B195" s="21" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C195" s="21" t="s">
         <v>159</v>
       </c>
       <c r="D195" s="5" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E195" s="4"/>
       <c r="F195" s="5" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G195" s="4" t="s">
         <v>194</v>
       </c>
       <c r="H195" s="4"/>
       <c r="I195" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="J195" s="4" t="s">
         <v>20</v>
@@ -8800,12 +8777,12 @@
         <v>71</v>
       </c>
       <c r="M195" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="196" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B196" s="21" t="s">
         <v>16</v>
@@ -8814,18 +8791,18 @@
         <v>22</v>
       </c>
       <c r="D196" s="5" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E196" s="4"/>
       <c r="F196" s="5" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="G196" s="4" t="s">
         <v>39</v>
       </c>
       <c r="H196" s="4"/>
       <c r="I196" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="J196" s="4" t="s">
         <v>20</v>
@@ -8834,12 +8811,12 @@
         <v>21</v>
       </c>
       <c r="M196" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="197" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B197" s="21" t="s">
         <v>16</v>
@@ -8848,32 +8825,32 @@
         <v>22</v>
       </c>
       <c r="D197" s="5" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E197" s="4"/>
       <c r="F197" s="5" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="G197" s="4" t="s">
         <v>28</v>
       </c>
       <c r="H197" s="4"/>
       <c r="I197" t="s">
+        <v>417</v>
+      </c>
+      <c r="J197" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L197" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M197" t="s">
         <v>418</v>
-      </c>
-      <c r="J197" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L197" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M197" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="198" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B198" s="21" t="s">
         <v>16</v>
@@ -8882,11 +8859,11 @@
         <v>22</v>
       </c>
       <c r="D198" s="5" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E198" s="4"/>
       <c r="F198" s="5" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G198" s="4" t="s">
         <v>31</v>
@@ -8903,7 +8880,7 @@
     </row>
     <row r="199" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B199" s="21" t="s">
         <v>16</v>
@@ -8912,11 +8889,11 @@
         <v>22</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E199" s="4"/>
       <c r="F199" s="5" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G199" s="4" t="s">
         <v>56</v>
@@ -8933,7 +8910,7 @@
     </row>
     <row r="200" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B200" s="21" t="s">
         <v>16</v>
@@ -8942,11 +8919,11 @@
         <v>22</v>
       </c>
       <c r="D200" s="5" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E200" s="4"/>
       <c r="F200" s="5" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G200" s="4" t="s">
         <v>35</v>
@@ -8963,7 +8940,7 @@
     </row>
     <row r="201" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B201" s="21" t="s">
         <v>16</v>
@@ -8972,18 +8949,18 @@
         <v>22</v>
       </c>
       <c r="D201" s="5" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E201" s="4"/>
       <c r="F201" s="5" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="G201" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H201" s="4"/>
       <c r="I201" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="J201" s="4" t="s">
         <v>20</v>
@@ -8992,12 +8969,12 @@
         <v>21</v>
       </c>
       <c r="M201" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="202" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B202" s="21" t="s">
         <v>16</v>
@@ -9006,11 +8983,11 @@
         <v>201</v>
       </c>
       <c r="D202" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E202" s="4"/>
       <c r="F202" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G202" s="4" t="s">
         <v>147</v>
@@ -9027,7 +9004,7 @@
     </row>
     <row r="203" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B203" s="21" t="s">
         <v>159</v>
@@ -9036,18 +9013,18 @@
         <v>22</v>
       </c>
       <c r="D203" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E203" s="4"/>
       <c r="F203" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G203" s="4" t="s">
         <v>162</v>
       </c>
       <c r="H203" s="4"/>
       <c r="I203" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="J203" s="4" t="s">
         <v>20</v>
@@ -9056,32 +9033,32 @@
         <v>149</v>
       </c>
       <c r="M203" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="204" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B204" s="21" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C204" s="21" t="s">
         <v>201</v>
       </c>
       <c r="D204" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E204" s="4"/>
       <c r="F204" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G204" s="4" t="s">
         <v>194</v>
       </c>
       <c r="H204" s="4"/>
       <c r="I204" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="J204" s="4" t="s">
         <v>20</v>
@@ -9090,12 +9067,12 @@
         <v>71</v>
       </c>
       <c r="M204" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="205" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B205" s="21" t="s">
         <v>187</v>
@@ -9104,18 +9081,18 @@
         <v>22</v>
       </c>
       <c r="D205" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E205" s="4"/>
       <c r="F205" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="G205" s="4" t="s">
         <v>152</v>
       </c>
       <c r="H205" s="4"/>
       <c r="I205" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="J205" s="4" t="s">
         <v>20</v>
@@ -9124,12 +9101,12 @@
         <v>149</v>
       </c>
       <c r="M205" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="206" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B206" s="21" t="s">
         <v>22</v>
@@ -9138,11 +9115,11 @@
         <v>23</v>
       </c>
       <c r="D206" s="5" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E206" s="4"/>
       <c r="F206" s="5" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G206" s="4" t="s">
         <v>39</v>
@@ -9159,7 +9136,7 @@
     </row>
     <row r="207" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B207" s="21" t="s">
         <v>22</v>
@@ -9168,11 +9145,11 @@
         <v>37</v>
       </c>
       <c r="D207" s="5" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E207" s="4"/>
       <c r="F207" s="5" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="G207" s="4" t="s">
         <v>25</v>
@@ -9189,7 +9166,7 @@
     </row>
     <row r="208" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B208" s="21" t="s">
         <v>22</v>
@@ -9198,18 +9175,18 @@
         <v>23</v>
       </c>
       <c r="D208" s="5" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E208" s="4"/>
       <c r="F208" s="5" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G208" s="4" t="s">
         <v>28</v>
       </c>
       <c r="H208" s="4"/>
       <c r="I208" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="J208" s="4" t="s">
         <v>20</v>
@@ -9218,12 +9195,12 @@
         <v>21</v>
       </c>
       <c r="M208" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="209" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B209" s="21" t="s">
         <v>22</v>
@@ -9232,32 +9209,32 @@
         <v>29</v>
       </c>
       <c r="D209" s="5" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E209" s="4"/>
       <c r="F209" s="5" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G209" s="4" t="s">
         <v>31</v>
       </c>
       <c r="H209" s="4"/>
       <c r="I209" t="s">
+        <v>439</v>
+      </c>
+      <c r="J209" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L209" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M209" t="s">
         <v>440</v>
-      </c>
-      <c r="J209" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L209" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M209" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="210" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B210" s="21" t="s">
         <v>22</v>
@@ -9266,11 +9243,11 @@
         <v>23</v>
       </c>
       <c r="D210" s="5" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E210" s="4"/>
       <c r="F210" s="5" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="G210" s="4" t="s">
         <v>56</v>
@@ -9287,7 +9264,7 @@
     </row>
     <row r="211" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B211" s="21" t="s">
         <v>22</v>
@@ -9296,11 +9273,11 @@
         <v>23</v>
       </c>
       <c r="D211" s="5" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E211" s="4"/>
       <c r="F211" s="5" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G211" s="4" t="s">
         <v>35</v>
@@ -9317,27 +9294,27 @@
     </row>
     <row r="212" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B212" s="21" t="s">
         <v>22</v>
       </c>
       <c r="C212" s="21" t="s">
+        <v>443</v>
+      </c>
+      <c r="D212" s="5" t="s">
         <v>444</v>
-      </c>
-      <c r="D212" s="5" t="s">
-        <v>445</v>
       </c>
       <c r="E212" s="4"/>
       <c r="F212" s="5" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="G212" s="4" t="s">
         <v>194</v>
       </c>
       <c r="H212" s="4"/>
       <c r="I212" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="J212" s="4" t="s">
         <v>20</v>
@@ -9346,12 +9323,12 @@
         <v>71</v>
       </c>
       <c r="M212" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="213" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B213" s="21" t="s">
         <v>22</v>
@@ -9360,11 +9337,11 @@
         <v>29</v>
       </c>
       <c r="D213" s="5" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E213" s="4"/>
       <c r="F213" s="5" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G213" s="4" t="s">
         <v>19</v>
@@ -9381,7 +9358,7 @@
     </row>
     <row r="214" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B214" s="21" t="s">
         <v>22</v>
@@ -9390,18 +9367,18 @@
         <v>23</v>
       </c>
       <c r="D214" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E214" s="4"/>
       <c r="F214" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="G214" s="4" t="s">
         <v>170</v>
       </c>
       <c r="H214" s="4"/>
       <c r="I214" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="J214" s="4" t="s">
         <v>20</v>
@@ -9410,12 +9387,12 @@
         <v>149</v>
       </c>
       <c r="M214" s="23" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="215" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B215" s="21" t="s">
         <v>22</v>
@@ -9424,11 +9401,11 @@
         <v>29</v>
       </c>
       <c r="D215" s="22" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E215" s="4"/>
       <c r="F215" s="22" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G215" s="4" t="s">
         <v>173</v>
@@ -9445,27 +9422,27 @@
     </row>
     <row r="216" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B216" s="21" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C216" s="21" t="s">
         <v>29</v>
       </c>
       <c r="D216" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E216" s="4"/>
       <c r="F216" s="4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G216" s="4" t="s">
         <v>152</v>
       </c>
       <c r="H216" s="4"/>
       <c r="I216" s="4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="J216" s="4" t="s">
         <v>20</v>
@@ -9474,12 +9451,12 @@
         <v>149</v>
       </c>
       <c r="M216" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="217" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B217" s="21" t="s">
         <v>17</v>
@@ -9488,11 +9465,11 @@
         <v>234</v>
       </c>
       <c r="D217" s="5" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E217" s="4"/>
       <c r="F217" s="5" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G217" s="4" t="s">
         <v>49</v>
@@ -9509,20 +9486,20 @@
     </row>
     <row r="218" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B218" s="21" t="s">
         <v>17</v>
       </c>
       <c r="C218" s="21" t="s">
+        <v>455</v>
+      </c>
+      <c r="D218" s="5" t="s">
         <v>456</v>
-      </c>
-      <c r="D218" s="5" t="s">
-        <v>457</v>
       </c>
       <c r="E218" s="4"/>
       <c r="F218" s="5" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G218" s="4" t="s">
         <v>194</v>
@@ -9539,7 +9516,7 @@
     </row>
     <row r="219" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B219" s="21" t="s">
         <v>29</v>
@@ -9548,32 +9525,32 @@
         <v>263</v>
       </c>
       <c r="D219" s="5" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E219" s="4"/>
       <c r="F219" s="5" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G219" s="4" t="s">
         <v>31</v>
       </c>
       <c r="H219" s="4"/>
       <c r="I219" t="s">
+        <v>458</v>
+      </c>
+      <c r="J219" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L219" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M219" t="s">
         <v>459</v>
-      </c>
-      <c r="J219" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L219" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M219" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="220" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B220" s="21" t="s">
         <v>29</v>
@@ -9582,32 +9559,32 @@
         <v>43</v>
       </c>
       <c r="D220" s="5" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E220" s="4"/>
       <c r="F220" s="5" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G220" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H220" s="4"/>
       <c r="I220" t="s">
+        <v>461</v>
+      </c>
+      <c r="J220" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L220" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M220" t="s">
         <v>462</v>
-      </c>
-      <c r="J220" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L220" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M220" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="221" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B221" s="21" t="s">
         <v>23</v>
@@ -9616,11 +9593,11 @@
         <v>47</v>
       </c>
       <c r="D221" s="5" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E221" s="4"/>
       <c r="F221" s="5" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G221" s="4" t="s">
         <v>39</v>
@@ -9637,7 +9614,7 @@
     </row>
     <row r="222" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B222" s="21" t="s">
         <v>23</v>
@@ -9646,11 +9623,11 @@
         <v>47</v>
       </c>
       <c r="D222" s="5" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E222" s="4"/>
       <c r="F222" s="5" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="G222" s="4" t="s">
         <v>28</v>
@@ -9667,7 +9644,7 @@
     </row>
     <row r="223" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B223" s="21" t="s">
         <v>23</v>
@@ -9676,18 +9653,18 @@
         <v>47</v>
       </c>
       <c r="D223" s="22" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="E223" s="4"/>
       <c r="F223" s="22" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="G223" s="4" t="s">
         <v>56</v>
       </c>
       <c r="H223" s="4"/>
       <c r="I223" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="J223" s="4" t="s">
         <v>20</v>
@@ -9696,12 +9673,12 @@
         <v>71</v>
       </c>
       <c r="M223" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="224" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B224" s="21" t="s">
         <v>23</v>
@@ -9710,18 +9687,18 @@
         <v>47</v>
       </c>
       <c r="D224" s="5" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E224" s="4"/>
       <c r="F224" s="5" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="G224" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H224" s="4"/>
       <c r="I224" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="J224" s="4" t="s">
         <v>20</v>
@@ -9730,25 +9707,25 @@
         <v>21</v>
       </c>
       <c r="M224" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="225" spans="1:13" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B225" s="21" t="s">
         <v>23</v>
       </c>
       <c r="C225" s="21" t="s">
+        <v>468</v>
+      </c>
+      <c r="D225" s="5" t="s">
         <v>469</v>
-      </c>
-      <c r="D225" s="5" t="s">
-        <v>470</v>
       </c>
       <c r="E225" s="4"/>
       <c r="F225" s="5" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="G225" s="4" t="s">
         <v>258</v>
@@ -9765,27 +9742,27 @@
     </row>
     <row r="226" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B226" s="21" t="s">
+        <v>470</v>
+      </c>
+      <c r="C226" s="21" t="s">
         <v>471</v>
       </c>
-      <c r="C226" s="21" t="s">
+      <c r="D226" s="5" t="s">
         <v>472</v>
-      </c>
-      <c r="D226" s="5" t="s">
-        <v>473</v>
       </c>
       <c r="E226" s="4"/>
       <c r="F226" s="5" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="G226" s="4" t="s">
         <v>194</v>
       </c>
       <c r="H226" s="4"/>
       <c r="I226" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="J226" s="4" t="s">
         <v>20</v>
@@ -9794,12 +9771,12 @@
         <v>71</v>
       </c>
       <c r="M226" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="227" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B227" s="21" t="s">
         <v>262</v>
@@ -9808,11 +9785,11 @@
         <v>43</v>
       </c>
       <c r="D227" s="5" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E227" s="4"/>
       <c r="F227" s="5" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="G227" s="4" t="s">
         <v>49</v>
@@ -9829,7 +9806,7 @@
     </row>
     <row r="228" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B228" s="21" t="s">
         <v>37</v>
@@ -9838,11 +9815,11 @@
         <v>61</v>
       </c>
       <c r="D228" s="5" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E228" s="4"/>
       <c r="F228" s="5" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="G228" s="4" t="s">
         <v>25</v>
@@ -9859,27 +9836,27 @@
     </row>
     <row r="229" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B229" s="21" t="s">
         <v>37</v>
       </c>
       <c r="C229" s="21" t="s">
+        <v>477</v>
+      </c>
+      <c r="D229" s="4" t="s">
         <v>478</v>
-      </c>
-      <c r="D229" s="4" t="s">
-        <v>479</v>
       </c>
       <c r="E229" s="4"/>
       <c r="F229" s="4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="G229" s="4" t="s">
         <v>170</v>
       </c>
       <c r="H229" s="4"/>
       <c r="I229" s="4" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J229" s="4" t="s">
         <v>20</v>
@@ -9888,12 +9865,12 @@
         <v>149</v>
       </c>
       <c r="M229" s="4" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="230" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B230" s="21" t="s">
         <v>43</v>
@@ -9902,32 +9879,32 @@
         <v>61</v>
       </c>
       <c r="D230" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E230" s="4"/>
       <c r="F230" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="G230" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H230" s="4"/>
       <c r="I230" t="s">
+        <v>482</v>
+      </c>
+      <c r="J230" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L230" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M230" t="s">
         <v>483</v>
-      </c>
-      <c r="J230" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L230" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M230" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="231" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B231" s="21" t="s">
         <v>263</v>
@@ -9936,11 +9913,11 @@
         <v>54</v>
       </c>
       <c r="D231" s="5" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E231" s="4"/>
       <c r="F231" s="5" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G231" s="4" t="s">
         <v>31</v>
@@ -9957,27 +9934,27 @@
     </row>
     <row r="232" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B232" s="21" t="s">
         <v>263</v>
       </c>
       <c r="C232" s="21" t="s">
+        <v>485</v>
+      </c>
+      <c r="D232" s="5" t="s">
         <v>486</v>
-      </c>
-      <c r="D232" s="5" t="s">
-        <v>487</v>
       </c>
       <c r="E232" s="4"/>
       <c r="F232" s="5" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="G232" s="4" t="s">
         <v>194</v>
       </c>
       <c r="H232" s="4"/>
       <c r="I232" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="J232" s="4" t="s">
         <v>20</v>
@@ -9986,12 +9963,12 @@
         <v>71</v>
       </c>
       <c r="M232" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="233" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B233" s="21" t="s">
         <v>256</v>
@@ -10000,11 +9977,11 @@
         <v>61</v>
       </c>
       <c r="D233" s="5" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E233" s="4"/>
       <c r="F233" s="5" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="G233" s="4" t="s">
         <v>49</v>
@@ -10021,27 +9998,27 @@
     </row>
     <row r="234" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B234" s="21" t="s">
         <v>47</v>
       </c>
       <c r="C234" s="21" t="s">
+        <v>490</v>
+      </c>
+      <c r="D234" s="5" t="s">
         <v>491</v>
-      </c>
-      <c r="D234" s="5" t="s">
-        <v>492</v>
       </c>
       <c r="E234" s="4"/>
       <c r="F234" s="5" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="G234" s="4" t="s">
         <v>39</v>
       </c>
       <c r="H234" s="4"/>
       <c r="I234" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="J234" s="4" t="s">
         <v>20</v>
@@ -10050,25 +10027,25 @@
         <v>21</v>
       </c>
       <c r="M234" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="235" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B235" s="21" t="s">
         <v>47</v>
       </c>
       <c r="C235" s="12" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D235" s="5" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E235" s="4"/>
       <c r="F235" s="5" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="G235" s="4" t="s">
         <v>28</v>
@@ -10085,20 +10062,20 @@
     </row>
     <row r="236" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B236" s="21" t="s">
         <v>47</v>
       </c>
       <c r="C236" s="21" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D236" s="5" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E236" s="4"/>
       <c r="F236" s="5" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="G236" s="4" t="s">
         <v>56</v>
@@ -10115,20 +10092,20 @@
     </row>
     <row r="237" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B237" s="21" t="s">
         <v>47</v>
       </c>
       <c r="C237" s="21" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D237" s="5" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E237" s="4"/>
       <c r="F237" s="5" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="G237" s="4" t="s">
         <v>35</v>
@@ -10145,20 +10122,20 @@
     </row>
     <row r="238" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B238" s="21" t="s">
+        <v>496</v>
+      </c>
+      <c r="C238" s="21" t="s">
         <v>497</v>
       </c>
-      <c r="C238" s="21" t="s">
+      <c r="D238" s="5" t="s">
         <v>498</v>
-      </c>
-      <c r="D238" s="5" t="s">
-        <v>499</v>
       </c>
       <c r="E238" s="4"/>
       <c r="F238" s="5" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="G238" s="4" t="s">
         <v>194</v>
@@ -10175,27 +10152,27 @@
     </row>
     <row r="239" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B239" s="21" t="s">
         <v>61</v>
       </c>
       <c r="C239" s="12" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D239" s="5" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E239" s="4"/>
       <c r="F239" s="5" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G239" s="4" t="s">
         <v>25</v>
       </c>
       <c r="H239" s="4"/>
       <c r="I239" s="4" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="J239" s="4" t="s">
         <v>20</v>
@@ -10204,25 +10181,25 @@
         <v>71</v>
       </c>
       <c r="M239" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="240" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B240" s="21" t="s">
         <v>61</v>
       </c>
       <c r="C240" s="21" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D240" s="5" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E240" s="4"/>
       <c r="F240" s="5" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="G240" s="4" t="s">
         <v>19</v>
@@ -10239,20 +10216,20 @@
     </row>
     <row r="241" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B241" s="21" t="s">
         <v>54</v>
       </c>
       <c r="C241" s="21" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D241" s="5" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E241" s="4"/>
       <c r="F241" s="5" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="G241" s="4" t="s">
         <v>49</v>
@@ -10269,27 +10246,27 @@
     </row>
     <row r="242" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B242" s="21" t="s">
         <v>54</v>
       </c>
       <c r="C242" s="12" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D242" s="5" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E242" s="4"/>
       <c r="F242" s="5" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="G242" s="4" t="s">
         <v>31</v>
       </c>
       <c r="H242" s="4"/>
       <c r="I242" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="J242" s="4" t="s">
         <v>20</v>
@@ -10298,32 +10275,32 @@
         <v>21</v>
       </c>
       <c r="M242" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="243" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A243" s="13" t="s">
-        <v>303</v>
-      </c>
-      <c r="B243" s="40" t="s">
-        <v>293</v>
-      </c>
-      <c r="C243" s="39" t="s">
-        <v>491</v>
+        <v>302</v>
+      </c>
+      <c r="B243" s="33" t="s">
+        <v>292</v>
+      </c>
+      <c r="C243" s="32" t="s">
+        <v>490</v>
       </c>
       <c r="D243" s="5" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E243" s="13"/>
       <c r="F243" s="5" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="G243" s="4" t="s">
         <v>194</v>
       </c>
       <c r="H243" s="4"/>
       <c r="I243" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="J243" s="4" t="s">
         <v>20</v>
@@ -10332,12 +10309,12 @@
         <v>71</v>
       </c>
       <c r="M243" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="244" spans="1:13" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A244" s="10" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B244" s="21" t="s">
         <v>89</v>
@@ -10346,11 +10323,11 @@
         <v>90</v>
       </c>
       <c r="D244" s="5" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E244" s="8"/>
       <c r="F244" s="16" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G244" s="8" t="s">
         <v>39</v>
@@ -10367,7 +10344,7 @@
     </row>
     <row r="245" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B245" s="21" t="s">
         <v>89</v>
@@ -10376,18 +10353,18 @@
         <v>90</v>
       </c>
       <c r="D245" s="5" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E245" s="4"/>
       <c r="F245" s="5" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="G245" s="4" t="s">
         <v>25</v>
       </c>
       <c r="H245" s="4"/>
       <c r="I245" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="J245" s="4" t="s">
         <v>20</v>
@@ -10396,12 +10373,12 @@
         <v>21</v>
       </c>
       <c r="M245" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B246" s="21" t="s">
         <v>89</v>
@@ -10410,11 +10387,11 @@
         <v>90</v>
       </c>
       <c r="D246" s="5" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E246" s="4"/>
       <c r="F246" s="5" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="G246" s="4" t="s">
         <v>28</v>
@@ -10431,7 +10408,7 @@
     </row>
     <row r="247" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B247" s="21" t="s">
         <v>89</v>
@@ -10440,11 +10417,11 @@
         <v>98</v>
       </c>
       <c r="D247" s="5" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E247" s="4"/>
       <c r="F247" s="5" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="G247" s="4" t="s">
         <v>56</v>
@@ -10461,7 +10438,7 @@
     </row>
     <row r="248" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B248" s="21" t="s">
         <v>89</v>
@@ -10470,11 +10447,11 @@
         <v>90</v>
       </c>
       <c r="D248" s="5" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E248" s="4"/>
       <c r="F248" s="5" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="G248" s="4" t="s">
         <v>35</v>
@@ -10491,7 +10468,7 @@
     </row>
     <row r="249" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B249" s="21" t="s">
         <v>89</v>
@@ -10500,18 +10477,18 @@
         <v>95</v>
       </c>
       <c r="D249" s="5" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E249" s="4"/>
       <c r="F249" s="5" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="G249" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H249" s="4"/>
       <c r="I249" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="J249" s="4" t="s">
         <v>20</v>
@@ -10520,25 +10497,25 @@
         <v>21</v>
       </c>
       <c r="M249" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B250" s="21" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C250" s="21" t="s">
         <v>95</v>
       </c>
       <c r="D250" s="5" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E250" s="4"/>
       <c r="F250" s="5" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="G250" s="4" t="s">
         <v>49</v>
@@ -10555,20 +10532,20 @@
     </row>
     <row r="251" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B251" s="21" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C251" s="21" t="s">
         <v>90</v>
       </c>
       <c r="D251" s="5" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E251" s="4"/>
       <c r="F251" s="5" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="G251" s="4" t="s">
         <v>31</v>
@@ -10585,20 +10562,20 @@
     </row>
     <row r="252" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B252" s="21" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C252" s="21" t="s">
         <v>95</v>
       </c>
       <c r="D252" s="5" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E252" s="4"/>
       <c r="F252" s="5" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="G252" s="4" t="s">
         <v>194</v>
@@ -10615,7 +10592,7 @@
     </row>
     <row r="253" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B253" s="21" t="s">
         <v>98</v>
@@ -10624,11 +10601,11 @@
         <v>104</v>
       </c>
       <c r="D253" s="5" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E253" s="4"/>
       <c r="F253" s="5" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="G253" s="4" t="s">
         <v>56</v>
@@ -10645,7 +10622,7 @@
     </row>
     <row r="254" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B254" s="21" t="s">
         <v>98</v>
@@ -10654,18 +10631,18 @@
         <v>115</v>
       </c>
       <c r="D254" s="4" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E254" s="4"/>
       <c r="F254" s="4" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="G254" s="4" t="s">
         <v>170</v>
       </c>
       <c r="H254" s="4"/>
       <c r="I254" s="23" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J254" s="4" t="s">
         <v>20</v>
@@ -10674,12 +10651,12 @@
         <v>21</v>
       </c>
       <c r="M254" s="23" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="255" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B255" s="21" t="s">
         <v>95</v>
@@ -10688,11 +10665,11 @@
         <v>104</v>
       </c>
       <c r="D255" s="5" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E255" s="4"/>
       <c r="F255" s="5" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="G255" s="4" t="s">
         <v>49</v>
@@ -10709,7 +10686,7 @@
     </row>
     <row r="256" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B256" s="21" t="s">
         <v>95</v>
@@ -10718,11 +10695,11 @@
         <v>104</v>
       </c>
       <c r="D256" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E256" s="4"/>
       <c r="F256" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="G256" s="4" t="s">
         <v>19</v>
@@ -10739,7 +10716,7 @@
     </row>
     <row r="257" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B257" s="21" t="s">
         <v>90</v>
@@ -10748,11 +10725,11 @@
         <v>106</v>
       </c>
       <c r="D257" s="5" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E257" s="4"/>
       <c r="F257" s="5" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="G257" s="4" t="s">
         <v>39</v>
@@ -10769,7 +10746,7 @@
     </row>
     <row r="258" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B258" s="21" t="s">
         <v>90</v>
@@ -10778,18 +10755,18 @@
         <v>106</v>
       </c>
       <c r="D258" s="5" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E258" s="4"/>
       <c r="F258" s="5" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="G258" s="4" t="s">
         <v>25</v>
       </c>
       <c r="H258" s="4"/>
       <c r="I258" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="J258" s="4" t="s">
         <v>20</v>
@@ -10798,12 +10775,12 @@
         <v>21</v>
       </c>
       <c r="M258" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="259" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B259" s="21" t="s">
         <v>90</v>
@@ -10812,11 +10789,11 @@
         <v>106</v>
       </c>
       <c r="D259" s="5" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E259" s="4"/>
       <c r="F259" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="G259" s="4" t="s">
         <v>28</v>
@@ -10833,20 +10810,20 @@
     </row>
     <row r="260" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B260" s="21" t="s">
         <v>90</v>
       </c>
       <c r="C260" s="21" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D260" s="5" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E260" s="4"/>
       <c r="F260" s="5" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="G260" s="4" t="s">
         <v>31</v>
@@ -10863,7 +10840,7 @@
     </row>
     <row r="261" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B261" s="21" t="s">
         <v>90</v>
@@ -10872,18 +10849,18 @@
         <v>106</v>
       </c>
       <c r="D261" s="5" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="E261" s="4"/>
       <c r="F261" s="5" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="G261" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H261" s="4"/>
       <c r="I261" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="J261" s="4" t="s">
         <v>20</v>
@@ -10892,12 +10869,12 @@
         <v>21</v>
       </c>
       <c r="M261" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="262" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B262" s="21" t="s">
         <v>115</v>
@@ -10906,32 +10883,32 @@
         <v>106</v>
       </c>
       <c r="D262" s="4" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E262" s="4"/>
       <c r="F262" s="4" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="G262" s="4" t="s">
         <v>170</v>
       </c>
       <c r="H262" s="4"/>
       <c r="I262" s="23" t="s">
+        <v>533</v>
+      </c>
+      <c r="J262" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L262" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="M262" s="23" t="s">
         <v>534</v>
-      </c>
-      <c r="J262" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L262" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="M262" s="23" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="263" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B263" s="21" t="s">
         <v>104</v>
@@ -10940,11 +10917,11 @@
         <v>117</v>
       </c>
       <c r="D263" s="5" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="E263" s="4"/>
       <c r="F263" s="5" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="G263" s="4" t="s">
         <v>49</v>
@@ -10961,7 +10938,7 @@
     </row>
     <row r="264" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B264" s="21" t="s">
         <v>104</v>
@@ -10970,18 +10947,18 @@
         <v>110</v>
       </c>
       <c r="D264" s="5" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E264" s="4"/>
       <c r="F264" s="5" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="G264" s="4" t="s">
         <v>56</v>
       </c>
       <c r="H264" s="4"/>
       <c r="I264" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="J264" s="4" t="s">
         <v>20</v>
@@ -10990,12 +10967,12 @@
         <v>71</v>
       </c>
       <c r="M264" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="265" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B265" s="21" t="s">
         <v>104</v>
@@ -11004,45 +10981,45 @@
         <v>117</v>
       </c>
       <c r="D265" s="5" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E265" s="4"/>
       <c r="F265" s="5" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="G265" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H265" s="4"/>
       <c r="I265" t="s">
+        <v>539</v>
+      </c>
+      <c r="J265" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L265" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M265" t="s">
         <v>540</v>
-      </c>
-      <c r="J265" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L265" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M265" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="266" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B266" s="21" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C266" s="21" t="s">
         <v>110</v>
       </c>
       <c r="D266" s="5" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E266" s="4"/>
       <c r="F266" s="5" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="G266" s="4" t="s">
         <v>31</v>
@@ -11059,7 +11036,7 @@
     </row>
     <row r="267" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B267" s="21" t="s">
         <v>106</v>
@@ -11068,11 +11045,11 @@
         <v>119</v>
       </c>
       <c r="D267" s="5" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E267" s="4"/>
       <c r="F267" s="5" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="G267" s="4" t="s">
         <v>39</v>
@@ -11089,7 +11066,7 @@
     </row>
     <row r="268" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B268" s="21" t="s">
         <v>106</v>
@@ -11098,18 +11075,18 @@
         <v>119</v>
       </c>
       <c r="D268" s="5" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E268" s="4"/>
       <c r="F268" s="5" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="G268" s="4" t="s">
         <v>25</v>
       </c>
       <c r="H268" s="4"/>
       <c r="I268" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="J268" s="4" t="s">
         <v>20</v>
@@ -11118,12 +11095,12 @@
         <v>21</v>
       </c>
       <c r="M268" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="269" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B269" s="21" t="s">
         <v>106</v>
@@ -11132,32 +11109,32 @@
         <v>119</v>
       </c>
       <c r="D269" s="5" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E269" s="4"/>
       <c r="F269" s="5" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="G269" s="4" t="s">
         <v>28</v>
       </c>
       <c r="H269" s="4"/>
       <c r="I269" t="s">
+        <v>546</v>
+      </c>
+      <c r="J269" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L269" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M269" t="s">
         <v>547</v>
-      </c>
-      <c r="J269" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L269" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M269" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="270" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B270" s="21" t="s">
         <v>106</v>
@@ -11166,18 +11143,18 @@
         <v>119</v>
       </c>
       <c r="D270" s="5" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E270" s="4"/>
       <c r="F270" s="5" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="G270" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H270" s="4"/>
       <c r="I270" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="J270" s="4" t="s">
         <v>20</v>
@@ -11186,25 +11163,25 @@
         <v>21</v>
       </c>
       <c r="M270" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="271" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B271" s="21" t="s">
         <v>106</v>
       </c>
       <c r="C271" s="21" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D271" s="4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E271" s="4"/>
       <c r="F271" s="4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G271" s="4" t="s">
         <v>170</v>
@@ -11220,7 +11197,7 @@
     </row>
     <row r="272" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B272" s="21" t="s">
         <v>117</v>
@@ -11229,11 +11206,11 @@
         <v>119</v>
       </c>
       <c r="D272" s="5" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E272" s="4"/>
       <c r="F272" s="5" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G272" s="4" t="s">
         <v>19</v>
@@ -11250,20 +11227,20 @@
     </row>
     <row r="273" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B273" s="21" t="s">
         <v>110</v>
       </c>
       <c r="C273" s="21" t="s">
+        <v>552</v>
+      </c>
+      <c r="D273" s="5" t="s">
         <v>553</v>
-      </c>
-      <c r="D273" s="5" t="s">
-        <v>554</v>
       </c>
       <c r="E273" s="4"/>
       <c r="F273" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="G273" s="4" t="s">
         <v>31</v>
@@ -11280,7 +11257,7 @@
     </row>
     <row r="274" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B274" s="21" t="s">
         <v>110</v>
@@ -11289,18 +11266,18 @@
         <v>119</v>
       </c>
       <c r="D274" s="5" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="E274" s="4"/>
       <c r="F274" s="5" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G274" s="4" t="s">
         <v>56</v>
       </c>
       <c r="H274" s="4"/>
       <c r="I274" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="J274" s="4" t="s">
         <v>20</v>
@@ -11309,12 +11286,12 @@
         <v>71</v>
       </c>
       <c r="M274" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="275" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B275" s="21" t="s">
         <v>119</v>
@@ -11323,11 +11300,11 @@
         <v>129</v>
       </c>
       <c r="D275" s="5" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="E275" s="4"/>
       <c r="F275" s="5" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="G275" s="4" t="s">
         <v>25</v>
@@ -11344,7 +11321,7 @@
     </row>
     <row r="276" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B276" s="21" t="s">
         <v>119</v>
@@ -11353,18 +11330,18 @@
         <v>127</v>
       </c>
       <c r="D276" s="5" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="E276" s="4"/>
       <c r="F276" s="5" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="G276" s="4" t="s">
         <v>28</v>
       </c>
       <c r="H276" s="4"/>
       <c r="I276" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="J276" s="4" t="s">
         <v>20</v>
@@ -11373,32 +11350,32 @@
         <v>21</v>
       </c>
       <c r="M276" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="277" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B277" s="21" t="s">
         <v>119</v>
       </c>
       <c r="C277" s="21" t="s">
+        <v>559</v>
+      </c>
+      <c r="D277" s="5" t="s">
         <v>560</v>
-      </c>
-      <c r="D277" s="5" t="s">
-        <v>561</v>
       </c>
       <c r="E277" s="4"/>
       <c r="F277" s="5" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="G277" s="4" t="s">
         <v>56</v>
       </c>
       <c r="H277" s="4"/>
       <c r="I277" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="J277" s="4" t="s">
         <v>20</v>
@@ -11407,12 +11384,12 @@
         <v>21</v>
       </c>
       <c r="M277" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="278" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B278" s="21" t="s">
         <v>119</v>
@@ -11421,18 +11398,18 @@
         <v>127</v>
       </c>
       <c r="D278" s="5" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E278" s="4"/>
       <c r="F278" s="5" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G278" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H278" s="4"/>
       <c r="I278" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="J278" s="4" t="s">
         <v>20</v>
@@ -11441,25 +11418,25 @@
         <v>21</v>
       </c>
       <c r="M278" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="279" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B279" s="21" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C279" s="21" t="s">
         <v>129</v>
       </c>
       <c r="D279" s="5" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E279" s="4"/>
       <c r="F279" s="5" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="G279" s="4" t="s">
         <v>56</v>
@@ -11476,7 +11453,7 @@
     </row>
     <row r="280" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B280" s="21" t="s">
         <v>127</v>
@@ -11485,18 +11462,18 @@
         <v>136</v>
       </c>
       <c r="D280" s="5" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E280" s="4"/>
       <c r="F280" s="5" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G280" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H280" s="4"/>
       <c r="I280" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="J280" s="4" t="s">
         <v>20</v>
@@ -11505,12 +11482,12 @@
         <v>21</v>
       </c>
       <c r="M280" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="281" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B281" s="21" t="s">
         <v>129</v>
@@ -11519,18 +11496,18 @@
         <v>134</v>
       </c>
       <c r="D281" s="5" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E281" s="4"/>
       <c r="F281" s="5" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="G281" s="4" t="s">
         <v>56</v>
       </c>
       <c r="H281" s="4"/>
       <c r="I281" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="J281" s="4" t="s">
         <v>20</v>
@@ -11539,12 +11516,12 @@
         <v>21</v>
       </c>
       <c r="M281" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="282" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B282" s="21" t="s">
         <v>136</v>
@@ -11553,11 +11530,11 @@
         <v>140</v>
       </c>
       <c r="D282" s="5" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E282" s="4"/>
       <c r="F282" s="5" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G282" s="4" t="s">
         <v>35</v>
@@ -11574,7 +11551,7 @@
     </row>
     <row r="283" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B283" s="21" t="s">
         <v>134</v>
@@ -11583,18 +11560,18 @@
         <v>154</v>
       </c>
       <c r="D283" s="5" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E283" s="4"/>
       <c r="F283" s="5" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="G283" s="4" t="s">
         <v>56</v>
       </c>
       <c r="H283" s="4"/>
       <c r="I283" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="J283" s="4" t="s">
         <v>20</v>
@@ -11603,12 +11580,12 @@
         <v>21</v>
       </c>
       <c r="M283" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="284" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B284" s="21" t="s">
         <v>134</v>
@@ -11617,18 +11594,18 @@
         <v>140</v>
       </c>
       <c r="D284" s="4" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E284" s="4"/>
       <c r="F284" s="4" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="G284" s="4" t="s">
         <v>162</v>
       </c>
       <c r="H284" s="4"/>
       <c r="I284" s="4" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="J284" s="4" t="s">
         <v>20</v>
@@ -11637,12 +11614,12 @@
         <v>149</v>
       </c>
       <c r="M284" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="285" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B285" s="21" t="s">
         <v>140</v>
@@ -11651,18 +11628,18 @@
         <v>144</v>
       </c>
       <c r="D285" s="5" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E285" s="4"/>
       <c r="F285" s="5" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="G285" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H285" s="4"/>
       <c r="I285" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J285" s="4" t="s">
         <v>20</v>
@@ -11671,12 +11648,12 @@
         <v>21</v>
       </c>
       <c r="M285" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="286" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B286" s="21" t="s">
         <v>140</v>
@@ -11706,7 +11683,7 @@
     </row>
     <row r="287" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B287" s="21" t="s">
         <v>154</v>
@@ -11715,18 +11692,18 @@
         <v>166</v>
       </c>
       <c r="D287" s="5" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E287" s="4"/>
       <c r="F287" s="5" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="G287" s="4" t="s">
         <v>56</v>
       </c>
       <c r="H287" s="4"/>
       <c r="I287" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="J287" s="4" t="s">
         <v>20</v>
@@ -11735,12 +11712,12 @@
         <v>21</v>
       </c>
       <c r="M287" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="288" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B288" s="21" t="s">
         <v>154</v>
@@ -11749,11 +11726,11 @@
         <v>168</v>
       </c>
       <c r="D288" s="5" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E288" s="4"/>
       <c r="F288" s="5" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G288" s="4" t="s">
         <v>173</v>
@@ -11770,7 +11747,7 @@
     </row>
     <row r="289" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B289" s="12" t="s">
         <v>154</v>
@@ -11779,18 +11756,18 @@
         <v>168</v>
       </c>
       <c r="D289" s="4" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E289" s="4"/>
       <c r="F289" s="4" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G289" s="4" t="s">
         <v>162</v>
       </c>
       <c r="H289" s="4"/>
       <c r="I289" s="4" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="J289" s="4" t="s">
         <v>20</v>
@@ -11799,12 +11776,12 @@
         <v>149</v>
       </c>
       <c r="M289" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="290" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B290" s="21" t="s">
         <v>154</v>
@@ -11813,18 +11790,18 @@
         <v>144</v>
       </c>
       <c r="D290" s="4" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E290" s="4"/>
       <c r="F290" s="4" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="G290" s="4" t="s">
         <v>152</v>
       </c>
       <c r="H290" s="4"/>
       <c r="I290" s="4" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="J290" s="4" t="s">
         <v>20</v>
@@ -11833,12 +11810,12 @@
         <v>149</v>
       </c>
       <c r="M290" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="291" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B291" s="21" t="s">
         <v>160</v>
@@ -11847,18 +11824,18 @@
         <v>181</v>
       </c>
       <c r="D291" s="4" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E291" s="4"/>
       <c r="F291" s="4" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="G291" s="4" t="s">
         <v>170</v>
       </c>
       <c r="H291" s="4"/>
       <c r="I291" s="4" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="J291" s="4" t="s">
         <v>20</v>
@@ -11867,12 +11844,12 @@
         <v>149</v>
       </c>
       <c r="M291" s="23" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="292" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B292" s="21" t="s">
         <v>144</v>
@@ -11881,18 +11858,18 @@
         <v>16</v>
       </c>
       <c r="D292" s="5" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E292" s="4"/>
       <c r="F292" s="5" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="G292" s="4" t="s">
         <v>39</v>
       </c>
       <c r="H292" s="4"/>
       <c r="I292" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="J292" s="4" t="s">
         <v>20</v>
@@ -11901,12 +11878,12 @@
         <v>21</v>
       </c>
       <c r="M292" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="293" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B293" s="21" t="s">
         <v>144</v>
@@ -11915,11 +11892,11 @@
         <v>16</v>
       </c>
       <c r="D293" s="5" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E293" s="4"/>
       <c r="F293" s="5" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G293" s="4" t="s">
         <v>28</v>
@@ -11936,7 +11913,7 @@
     </row>
     <row r="294" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B294" s="21" t="s">
         <v>144</v>
@@ -11945,11 +11922,11 @@
         <v>16</v>
       </c>
       <c r="D294" s="5" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E294" s="4"/>
       <c r="F294" s="5" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G294" s="4" t="s">
         <v>31</v>
@@ -11966,7 +11943,7 @@
     </row>
     <row r="295" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B295" s="21" t="s">
         <v>144</v>
@@ -11975,11 +11952,11 @@
         <v>16</v>
       </c>
       <c r="D295" s="5" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E295" s="4"/>
       <c r="F295" s="5" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="G295" s="4" t="s">
         <v>35</v>
@@ -11996,7 +11973,7 @@
     </row>
     <row r="296" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B296" s="21" t="s">
         <v>168</v>
@@ -12005,18 +11982,18 @@
         <v>16</v>
       </c>
       <c r="D296" s="4" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E296" s="4"/>
       <c r="F296" s="4" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="G296" s="4" t="s">
         <v>152</v>
       </c>
       <c r="H296" s="4"/>
       <c r="I296" s="4" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="J296" s="4" t="s">
         <v>20</v>
@@ -12025,12 +12002,12 @@
         <v>149</v>
       </c>
       <c r="M296" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="297" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B297" s="21" t="s">
         <v>166</v>
@@ -12039,11 +12016,11 @@
         <v>22</v>
       </c>
       <c r="D297" s="5" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E297" s="4"/>
       <c r="F297" s="5" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="G297" s="4" t="s">
         <v>56</v>
@@ -12060,7 +12037,7 @@
     </row>
     <row r="298" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A298" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B298" s="21" t="s">
         <v>16</v>
@@ -12069,11 +12046,11 @@
         <v>22</v>
       </c>
       <c r="D298" s="5" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E298" s="4"/>
       <c r="F298" s="5" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="G298" s="4" t="s">
         <v>39</v>
@@ -12090,7 +12067,7 @@
     </row>
     <row r="299" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A299" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B299" s="21" t="s">
         <v>16</v>
@@ -12099,11 +12076,11 @@
         <v>22</v>
       </c>
       <c r="D299" s="5" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E299" s="4"/>
       <c r="F299" s="5" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G299" s="4" t="s">
         <v>25</v>
@@ -12120,7 +12097,7 @@
     </row>
     <row r="300" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A300" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B300" s="21" t="s">
         <v>16</v>
@@ -12129,11 +12106,11 @@
         <v>22</v>
       </c>
       <c r="D300" s="5" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E300" s="4"/>
       <c r="F300" s="5" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="G300" s="4" t="s">
         <v>28</v>
@@ -12150,7 +12127,7 @@
     </row>
     <row r="301" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B301" s="21" t="s">
         <v>16</v>
@@ -12159,11 +12136,11 @@
         <v>22</v>
       </c>
       <c r="D301" s="5" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E301" s="4"/>
       <c r="F301" s="5" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="G301" s="4" t="s">
         <v>31</v>
@@ -12180,7 +12157,7 @@
     </row>
     <row r="302" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A302" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B302" s="21" t="s">
         <v>16</v>
@@ -12189,32 +12166,32 @@
         <v>22</v>
       </c>
       <c r="D302" s="5" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E302" s="4"/>
       <c r="F302" s="5" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G302" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H302" s="4"/>
       <c r="I302" t="s">
+        <v>600</v>
+      </c>
+      <c r="J302" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L302" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M302" t="s">
         <v>601</v>
-      </c>
-      <c r="J302" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L302" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M302" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="303" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B303" s="21" t="s">
         <v>16</v>
@@ -12223,18 +12200,18 @@
         <v>201</v>
       </c>
       <c r="D303" s="4" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E303" s="4"/>
       <c r="F303" s="4" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G303" s="4" t="s">
         <v>170</v>
       </c>
       <c r="H303" s="4"/>
       <c r="I303" s="4" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="J303" s="4" t="s">
         <v>20</v>
@@ -12243,12 +12220,12 @@
         <v>149</v>
       </c>
       <c r="M303" s="23" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="304" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B304" s="21" t="s">
         <v>159</v>
@@ -12257,18 +12234,18 @@
         <v>22</v>
       </c>
       <c r="D304" s="5" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E304" s="4"/>
       <c r="F304" s="5" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="G304" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H304" s="4"/>
       <c r="I304" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="J304" s="4" t="s">
         <v>20</v>
@@ -12277,12 +12254,12 @@
         <v>21</v>
       </c>
       <c r="M304" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="305" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A305" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B305" s="21" t="s">
         <v>22</v>
@@ -12291,18 +12268,18 @@
         <v>23</v>
       </c>
       <c r="D305" s="5" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="E305" s="4"/>
       <c r="F305" s="5" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="G305" s="4" t="s">
         <v>39</v>
       </c>
       <c r="H305" s="4"/>
       <c r="I305" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="J305" s="4" t="s">
         <v>20</v>
@@ -12311,12 +12288,12 @@
         <v>21</v>
       </c>
       <c r="M305" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="306" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B306" s="21" t="s">
         <v>22</v>
@@ -12325,18 +12302,18 @@
         <v>23</v>
       </c>
       <c r="D306" s="5" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E306" s="4"/>
       <c r="F306" s="5" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="G306" s="4" t="s">
         <v>25</v>
       </c>
       <c r="H306" s="4"/>
       <c r="I306" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="J306" s="4" t="s">
         <v>20</v>
@@ -12345,12 +12322,12 @@
         <v>21</v>
       </c>
       <c r="M306" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="307" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A307" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B307" s="21" t="s">
         <v>22</v>
@@ -12359,11 +12336,11 @@
         <v>23</v>
       </c>
       <c r="D307" s="5" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="E307" s="4"/>
       <c r="F307" s="5" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G307" s="4" t="s">
         <v>28</v>
@@ -12380,7 +12357,7 @@
     </row>
     <row r="308" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A308" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B308" s="21" t="s">
         <v>22</v>
@@ -12389,11 +12366,11 @@
         <v>23</v>
       </c>
       <c r="D308" s="5" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="E308" s="4"/>
       <c r="F308" s="5" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="G308" s="4" t="s">
         <v>31</v>
@@ -12410,7 +12387,7 @@
     </row>
     <row r="309" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A309" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B309" s="21" t="s">
         <v>22</v>
@@ -12419,11 +12396,11 @@
         <v>43</v>
       </c>
       <c r="D309" s="5" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="E309" s="4"/>
       <c r="F309" s="5" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="G309" s="4" t="s">
         <v>56</v>
@@ -12440,7 +12417,7 @@
     </row>
     <row r="310" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A310" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B310" s="21" t="s">
         <v>22</v>
@@ -12449,18 +12426,18 @@
         <v>43</v>
       </c>
       <c r="D310" s="5" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="E310" s="4"/>
       <c r="F310" s="5" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="G310" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H310" s="4"/>
       <c r="I310" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="J310" s="4" t="s">
         <v>20</v>
@@ -12469,12 +12446,12 @@
         <v>21</v>
       </c>
       <c r="M310" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="311" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A311" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B311" s="21" t="s">
         <v>22</v>
@@ -12483,18 +12460,18 @@
         <v>29</v>
       </c>
       <c r="D311" s="5" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E311" s="4"/>
       <c r="F311" s="5" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="G311" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H311" s="4"/>
       <c r="I311" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="J311" s="4" t="s">
         <v>20</v>
@@ -12503,12 +12480,12 @@
         <v>21</v>
       </c>
       <c r="M311" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="312" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A312" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B312" s="21" t="s">
         <v>22</v>
@@ -12517,18 +12494,18 @@
         <v>47</v>
       </c>
       <c r="D312" s="4" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E312" s="4"/>
       <c r="F312" s="4" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="G312" s="4" t="s">
         <v>170</v>
       </c>
       <c r="H312" s="4"/>
       <c r="I312" s="4" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="J312" s="4" t="s">
         <v>20</v>
@@ -12537,12 +12514,12 @@
         <v>149</v>
       </c>
       <c r="M312" s="23" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="313" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A313" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B313" s="21" t="s">
         <v>29</v>
@@ -12551,11 +12528,11 @@
         <v>43</v>
       </c>
       <c r="D313" s="5" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E313" s="4"/>
       <c r="F313" s="5" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="G313" s="4" t="s">
         <v>19</v>
@@ -12572,7 +12549,7 @@
     </row>
     <row r="314" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A314" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B314" s="21" t="s">
         <v>23</v>
@@ -12581,11 +12558,11 @@
         <v>47</v>
       </c>
       <c r="D314" s="5" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="E314" s="4"/>
       <c r="F314" s="5" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="G314" s="4" t="s">
         <v>39</v>
@@ -12602,7 +12579,7 @@
     </row>
     <row r="315" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A315" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B315" s="21" t="s">
         <v>23</v>
@@ -12611,18 +12588,18 @@
         <v>54</v>
       </c>
       <c r="D315" s="5" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="E315" s="4"/>
       <c r="F315" s="5" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="G315" s="4" t="s">
         <v>25</v>
       </c>
       <c r="H315" s="4"/>
       <c r="I315" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J315" s="4" t="s">
         <v>20</v>
@@ -12631,12 +12608,12 @@
         <v>21</v>
       </c>
       <c r="M315" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="316" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A316" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B316" s="21" t="s">
         <v>23</v>
@@ -12645,18 +12622,18 @@
         <v>47</v>
       </c>
       <c r="D316" s="5" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="E316" s="4"/>
       <c r="F316" s="5" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="G316" s="4" t="s">
         <v>28</v>
       </c>
       <c r="H316" s="4"/>
       <c r="I316" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="J316" s="4" t="s">
         <v>20</v>
@@ -12665,12 +12642,12 @@
         <v>21</v>
       </c>
       <c r="M316" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="317" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A317" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B317" s="21" t="s">
         <v>23</v>
@@ -12679,18 +12656,18 @@
         <v>256</v>
       </c>
       <c r="D317" s="5" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="E317" s="4"/>
       <c r="F317" s="5" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="G317" s="4" t="s">
         <v>31</v>
       </c>
       <c r="H317" s="4"/>
       <c r="I317" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="J317" s="4" t="s">
         <v>20</v>
@@ -12699,25 +12676,25 @@
         <v>21</v>
       </c>
       <c r="M317" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="318" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A318" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B318" s="21" t="s">
         <v>43</v>
       </c>
       <c r="C318" s="21" t="s">
+        <v>627</v>
+      </c>
+      <c r="D318" s="5" t="s">
         <v>628</v>
-      </c>
-      <c r="D318" s="5" t="s">
-        <v>629</v>
       </c>
       <c r="E318" s="4"/>
       <c r="F318" s="5" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="G318" s="4" t="s">
         <v>56</v>
@@ -12734,7 +12711,7 @@
     </row>
     <row r="319" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A319" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B319" s="21" t="s">
         <v>43</v>
@@ -12743,11 +12720,11 @@
         <v>54</v>
       </c>
       <c r="D319" s="22" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E319" s="4"/>
       <c r="F319" s="22" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="G319" s="4" t="s">
         <v>35</v>
@@ -12764,7 +12741,7 @@
     </row>
     <row r="320" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A320" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B320" s="21" t="s">
         <v>43</v>
@@ -12773,32 +12750,32 @@
         <v>61</v>
       </c>
       <c r="D320" s="5" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="E320" s="4"/>
       <c r="F320" s="5" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="G320" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H320" s="4"/>
       <c r="I320" t="s">
+        <v>630</v>
+      </c>
+      <c r="J320" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L320" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M320" t="s">
         <v>631</v>
-      </c>
-      <c r="J320" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L320" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M320" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="321" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A321" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B321" s="21" t="s">
         <v>256</v>
@@ -12807,18 +12784,18 @@
         <v>54</v>
       </c>
       <c r="D321" s="5" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="E321" s="4"/>
       <c r="F321" s="5" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="G321" s="4" t="s">
         <v>31</v>
       </c>
       <c r="H321" s="4"/>
       <c r="I321" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="J321" s="4" t="s">
         <v>20</v>
@@ -12827,25 +12804,25 @@
         <v>21</v>
       </c>
       <c r="M321" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="322" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A322" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B322" s="21" t="s">
         <v>47</v>
       </c>
       <c r="C322" s="21" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D322" s="5" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E322" s="4"/>
       <c r="F322" s="5" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="G322" s="4" t="s">
         <v>39</v>
@@ -12862,20 +12839,20 @@
     </row>
     <row r="323" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A323" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B323" s="21" t="s">
         <v>47</v>
       </c>
       <c r="C323" s="21" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D323" s="5" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="E323" s="4"/>
       <c r="F323" s="5" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="G323" s="4" t="s">
         <v>28</v>
@@ -12892,54 +12869,54 @@
     </row>
     <row r="324" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A324" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B324" s="21" t="s">
         <v>61</v>
       </c>
       <c r="C324" s="21" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D324" s="5" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="E324" s="4"/>
       <c r="F324" s="5" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="G324" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H324" s="4"/>
       <c r="I324" t="s">
+        <v>637</v>
+      </c>
+      <c r="J324" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L324" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M324" t="s">
         <v>638</v>
-      </c>
-      <c r="J324" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L324" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M324" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="325" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A325" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B325" s="21" t="s">
         <v>54</v>
       </c>
       <c r="C325" s="21" t="s">
+        <v>639</v>
+      </c>
+      <c r="D325" s="5" t="s">
         <v>640</v>
-      </c>
-      <c r="D325" s="5" t="s">
-        <v>641</v>
       </c>
       <c r="E325" s="4"/>
       <c r="F325" s="5" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="G325" s="4" t="s">
         <v>25</v>
@@ -12956,20 +12933,20 @@
     </row>
     <row r="326" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A326" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B326" s="21" t="s">
         <v>54</v>
       </c>
       <c r="C326" s="21" t="s">
+        <v>641</v>
+      </c>
+      <c r="D326" s="5" t="s">
         <v>642</v>
-      </c>
-      <c r="D326" s="5" t="s">
-        <v>643</v>
       </c>
       <c r="E326" s="4"/>
       <c r="F326" s="5" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="G326" s="4" t="s">
         <v>31</v>
@@ -12986,27 +12963,27 @@
     </row>
     <row r="327" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A327" s="13" t="s">
-        <v>508</v>
-      </c>
-      <c r="B327" s="40" t="s">
+        <v>507</v>
+      </c>
+      <c r="B327" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="C327" s="40" t="s">
+      <c r="C327" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="D327" s="15" t="s">
         <v>644</v>
-      </c>
-      <c r="D327" s="36" t="s">
-        <v>645</v>
       </c>
       <c r="E327" s="13"/>
       <c r="F327" s="15" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="G327" s="13" t="s">
         <v>35</v>
       </c>
       <c r="H327" s="13"/>
       <c r="I327" s="14" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="J327" s="13" t="s">
         <v>20</v>
@@ -13015,12 +12992,12 @@
         <v>21</v>
       </c>
       <c r="M327" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="328" spans="1:13" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A328" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B328" s="21" t="s">
         <v>89</v>
@@ -13029,11 +13006,11 @@
         <v>90</v>
       </c>
       <c r="D328" s="5" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E328" s="4"/>
       <c r="F328" s="5" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="G328" s="4" t="s">
         <v>28</v>
@@ -13050,7 +13027,7 @@
     </row>
     <row r="329" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A329" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B329" s="21" t="s">
         <v>89</v>
@@ -13059,11 +13036,11 @@
         <v>90</v>
       </c>
       <c r="D329" s="5" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E329" s="4"/>
       <c r="F329" s="5" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="G329" s="4" t="s">
         <v>56</v>
@@ -13080,27 +13057,27 @@
     </row>
     <row r="330" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A330" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B330" s="21" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C330" s="21" t="s">
         <v>90</v>
       </c>
       <c r="D330" s="5" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E330" s="4"/>
       <c r="F330" s="5" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="G330" s="4" t="s">
         <v>31</v>
       </c>
       <c r="H330" s="4"/>
       <c r="I330" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="J330" s="4" t="s">
         <v>20</v>
@@ -13109,12 +13086,12 @@
         <v>21</v>
       </c>
       <c r="M330" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="331" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A331" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B331" s="21" t="s">
         <v>98</v>
@@ -13123,11 +13100,11 @@
         <v>104</v>
       </c>
       <c r="D331" s="5" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="E331" s="4"/>
       <c r="F331" s="5" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="G331" s="4" t="s">
         <v>35</v>
@@ -13144,7 +13121,7 @@
     </row>
     <row r="332" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A332" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B332" s="21" t="s">
         <v>90</v>
@@ -13153,11 +13130,11 @@
         <v>110</v>
       </c>
       <c r="D332" s="5" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="E332" s="4"/>
       <c r="F332" s="5" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="G332" s="4" t="s">
         <v>25</v>
@@ -13174,7 +13151,7 @@
     </row>
     <row r="333" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A333" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B333" s="21" t="s">
         <v>90</v>
@@ -13183,11 +13160,11 @@
         <v>106</v>
       </c>
       <c r="D333" s="5" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="E333" s="4"/>
       <c r="F333" s="5" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="G333" s="4" t="s">
         <v>28</v>
@@ -13204,7 +13181,7 @@
     </row>
     <row r="334" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A334" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B334" s="21" t="s">
         <v>90</v>
@@ -13213,32 +13190,32 @@
         <v>119</v>
       </c>
       <c r="D334" s="5" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E334" s="4"/>
       <c r="F334" s="5" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="G334" s="4" t="s">
         <v>56</v>
       </c>
       <c r="H334" s="4"/>
       <c r="I334" t="s">
+        <v>656</v>
+      </c>
+      <c r="J334" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L334" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M334" t="s">
         <v>657</v>
-      </c>
-      <c r="J334" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L334" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M334" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="335" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A335" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B335" s="21" t="s">
         <v>104</v>
@@ -13247,18 +13224,18 @@
         <v>110</v>
       </c>
       <c r="D335" s="5" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="E335" s="4"/>
       <c r="F335" s="5" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="G335" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H335" s="4"/>
       <c r="I335" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="J335" s="4" t="s">
         <v>20</v>
@@ -13267,12 +13244,12 @@
         <v>21</v>
       </c>
       <c r="M335" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="336" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A336" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B336" s="21" t="s">
         <v>106</v>
@@ -13281,11 +13258,11 @@
         <v>119</v>
       </c>
       <c r="D336" s="5" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E336" s="4"/>
       <c r="F336" s="5" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="G336" s="4" t="s">
         <v>28</v>
@@ -13302,20 +13279,20 @@
     </row>
     <row r="337" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A337" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B337" s="21" t="s">
         <v>110</v>
       </c>
       <c r="C337" s="21" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D337" s="5" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="E337" s="4"/>
       <c r="F337" s="5" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="G337" s="4" t="s">
         <v>35</v>
@@ -13332,7 +13309,7 @@
     </row>
     <row r="338" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A338" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B338" s="21" t="s">
         <v>119</v>
@@ -13341,11 +13318,11 @@
         <v>129</v>
       </c>
       <c r="D338" s="5" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="E338" s="4"/>
       <c r="F338" s="5" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="G338" s="4" t="s">
         <v>28</v>
@@ -13362,27 +13339,27 @@
     </row>
     <row r="339" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A339" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B339" s="21" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C339" s="21" t="s">
         <v>129</v>
       </c>
       <c r="D339" s="5" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E339" s="4"/>
       <c r="F339" s="5" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="G339" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H339" s="4"/>
       <c r="I339" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="J339" s="4" t="s">
         <v>20</v>
@@ -13391,12 +13368,12 @@
         <v>21</v>
       </c>
       <c r="M339" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="340" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A340" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B340" s="21" t="s">
         <v>129</v>
@@ -13405,11 +13382,11 @@
         <v>134</v>
       </c>
       <c r="D340" s="5" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="E340" s="4"/>
       <c r="F340" s="5" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G340" s="4" t="s">
         <v>35</v>
@@ -13426,7 +13403,7 @@
     </row>
     <row r="341" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A341" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B341" s="21" t="s">
         <v>134</v>
@@ -13435,11 +13412,11 @@
         <v>154</v>
       </c>
       <c r="D341" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="E341" s="4"/>
       <c r="F341" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G341" s="4" t="s">
         <v>35</v>
@@ -13456,7 +13433,7 @@
     </row>
     <row r="342" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A342" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B342" s="21" t="s">
         <v>154</v>
@@ -13465,11 +13442,11 @@
         <v>166</v>
       </c>
       <c r="D342" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="E342" s="4"/>
       <c r="F342" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="G342" s="4" t="s">
         <v>35</v>

--- a/import/timetable.xlsx
+++ b/import/timetable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michaelstork/Library/CloudStorage/Box-Box/Feel Festival/Marketing/03_Website/2026_timetable/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09A70DBD-87DA-5A4B-B9BE-D527AC55820D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADE73FDB-10EE-6548-821F-6720B97E4BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3048" uniqueCount="672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3048" uniqueCount="673">
   <si>
     <t>Timetable 2026</t>
   </si>
@@ -1770,9 +1770,6 @@
     <t>BIPOLAR SOUNDSYSTEM B2B GRIA</t>
   </si>
   <si>
-    <t>TOSH &amp; DAVIDS</t>
-  </si>
-  <si>
     <t>Davids &amp; Tosh explore the dynamic interplay between field recordings, machines, their own voices, and drums, often resulting in sounds that sit somewhere between ambient, electronica and dub techno.  For Feel Festival, they tap into live improvisation, where sounds and decisions arise spontaneously, fed by the energy of the space and audience in the moment.</t>
   </si>
   <si>
@@ -2186,6 +2183,12 @@
   </si>
   <si>
     <t>AZULU B2B GEM:INI</t>
+  </si>
+  <si>
+    <t>DAVIDS &amp; TOSH LIVE</t>
+  </si>
+  <si>
+    <t>KATTA LANA &amp; BRAUER</t>
   </si>
 </sst>
 </file>
@@ -6570,11 +6573,11 @@
         <v>275</v>
       </c>
       <c r="D126" s="22" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E126" s="4"/>
       <c r="F126" s="22" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="G126" s="4" t="s">
         <v>35</v>
@@ -9653,11 +9656,11 @@
         <v>47</v>
       </c>
       <c r="D223" s="22" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="E223" s="4"/>
       <c r="F223" s="22" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="G223" s="4" t="s">
         <v>56</v>
@@ -10540,8 +10543,8 @@
       <c r="C251" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="D251" s="5" t="s">
-        <v>517</v>
+      <c r="D251" s="22" t="s">
+        <v>672</v>
       </c>
       <c r="E251" s="4"/>
       <c r="F251" s="5" t="s">
@@ -10556,7 +10559,7 @@
         <v>20</v>
       </c>
       <c r="L251" s="6" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="M251"/>
     </row>
@@ -10946,19 +10949,19 @@
       <c r="C264" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="D264" s="5" t="s">
-        <v>536</v>
+      <c r="D264" s="22" t="s">
+        <v>671</v>
       </c>
       <c r="E264" s="4"/>
-      <c r="F264" s="5" t="s">
-        <v>536</v>
+      <c r="F264" s="22" t="s">
+        <v>671</v>
       </c>
       <c r="G264" s="4" t="s">
         <v>56</v>
       </c>
       <c r="H264" s="4"/>
       <c r="I264" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="J264" s="4" t="s">
         <v>20</v>
@@ -10967,7 +10970,7 @@
         <v>71</v>
       </c>
       <c r="M264" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="265" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -10981,27 +10984,27 @@
         <v>117</v>
       </c>
       <c r="D265" s="5" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E265" s="4"/>
       <c r="F265" s="5" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="G265" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H265" s="4"/>
       <c r="I265" t="s">
+        <v>538</v>
+      </c>
+      <c r="J265" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L265" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M265" t="s">
         <v>539</v>
-      </c>
-      <c r="J265" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L265" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M265" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="266" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -11015,11 +11018,11 @@
         <v>110</v>
       </c>
       <c r="D266" s="5" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E266" s="4"/>
       <c r="F266" s="5" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="G266" s="4" t="s">
         <v>31</v>
@@ -11045,11 +11048,11 @@
         <v>119</v>
       </c>
       <c r="D267" s="5" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E267" s="4"/>
       <c r="F267" s="5" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="G267" s="4" t="s">
         <v>39</v>
@@ -11075,18 +11078,18 @@
         <v>119</v>
       </c>
       <c r="D268" s="5" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E268" s="4"/>
       <c r="F268" s="5" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="G268" s="4" t="s">
         <v>25</v>
       </c>
       <c r="H268" s="4"/>
       <c r="I268" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="J268" s="4" t="s">
         <v>20</v>
@@ -11095,7 +11098,7 @@
         <v>21</v>
       </c>
       <c r="M268" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="269" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -11109,27 +11112,27 @@
         <v>119</v>
       </c>
       <c r="D269" s="5" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E269" s="4"/>
       <c r="F269" s="5" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="G269" s="4" t="s">
         <v>28</v>
       </c>
       <c r="H269" s="4"/>
       <c r="I269" t="s">
+        <v>545</v>
+      </c>
+      <c r="J269" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L269" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M269" t="s">
         <v>546</v>
-      </c>
-      <c r="J269" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L269" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M269" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="270" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -11143,18 +11146,18 @@
         <v>119</v>
       </c>
       <c r="D270" s="5" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="E270" s="4"/>
       <c r="F270" s="5" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="G270" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H270" s="4"/>
       <c r="I270" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="J270" s="4" t="s">
         <v>20</v>
@@ -11163,7 +11166,7 @@
         <v>21</v>
       </c>
       <c r="M270" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="271" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -11177,11 +11180,11 @@
         <v>341</v>
       </c>
       <c r="D271" s="4" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E271" s="4"/>
       <c r="F271" s="4" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="G271" s="4" t="s">
         <v>170</v>
@@ -11206,11 +11209,11 @@
         <v>119</v>
       </c>
       <c r="D272" s="5" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E272" s="4"/>
       <c r="F272" s="5" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G272" s="4" t="s">
         <v>19</v>
@@ -11233,14 +11236,14 @@
         <v>110</v>
       </c>
       <c r="C273" s="21" t="s">
+        <v>551</v>
+      </c>
+      <c r="D273" s="5" t="s">
         <v>552</v>
-      </c>
-      <c r="D273" s="5" t="s">
-        <v>553</v>
       </c>
       <c r="E273" s="4"/>
       <c r="F273" s="5" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="G273" s="4" t="s">
         <v>31</v>
@@ -11266,18 +11269,18 @@
         <v>119</v>
       </c>
       <c r="D274" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E274" s="4"/>
       <c r="F274" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="G274" s="4" t="s">
         <v>56</v>
       </c>
       <c r="H274" s="4"/>
       <c r="I274" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="J274" s="4" t="s">
         <v>20</v>
@@ -11286,7 +11289,7 @@
         <v>71</v>
       </c>
       <c r="M274" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="275" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -11300,11 +11303,11 @@
         <v>129</v>
       </c>
       <c r="D275" s="5" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E275" s="4"/>
       <c r="F275" s="5" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="G275" s="4" t="s">
         <v>25</v>
@@ -11330,18 +11333,18 @@
         <v>127</v>
       </c>
       <c r="D276" s="5" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="E276" s="4"/>
       <c r="F276" s="5" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="G276" s="4" t="s">
         <v>28</v>
       </c>
       <c r="H276" s="4"/>
       <c r="I276" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="J276" s="4" t="s">
         <v>20</v>
@@ -11350,7 +11353,7 @@
         <v>21</v>
       </c>
       <c r="M276" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="277" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -11361,21 +11364,21 @@
         <v>119</v>
       </c>
       <c r="C277" s="21" t="s">
+        <v>558</v>
+      </c>
+      <c r="D277" s="5" t="s">
         <v>559</v>
-      </c>
-      <c r="D277" s="5" t="s">
-        <v>560</v>
       </c>
       <c r="E277" s="4"/>
       <c r="F277" s="5" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G277" s="4" t="s">
         <v>56</v>
       </c>
       <c r="H277" s="4"/>
       <c r="I277" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="J277" s="4" t="s">
         <v>20</v>
@@ -11384,7 +11387,7 @@
         <v>21</v>
       </c>
       <c r="M277" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="278" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -11398,18 +11401,18 @@
         <v>127</v>
       </c>
       <c r="D278" s="5" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E278" s="4"/>
       <c r="F278" s="5" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="G278" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H278" s="4"/>
       <c r="I278" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="J278" s="4" t="s">
         <v>20</v>
@@ -11418,7 +11421,7 @@
         <v>21</v>
       </c>
       <c r="M278" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="279" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -11426,17 +11429,17 @@
         <v>507</v>
       </c>
       <c r="B279" s="21" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C279" s="21" t="s">
         <v>129</v>
       </c>
       <c r="D279" s="5" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E279" s="4"/>
       <c r="F279" s="5" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="G279" s="4" t="s">
         <v>56</v>
@@ -11462,18 +11465,18 @@
         <v>136</v>
       </c>
       <c r="D280" s="5" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E280" s="4"/>
       <c r="F280" s="5" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="G280" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H280" s="4"/>
       <c r="I280" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="J280" s="4" t="s">
         <v>20</v>
@@ -11482,7 +11485,7 @@
         <v>21</v>
       </c>
       <c r="M280" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="281" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -11496,18 +11499,18 @@
         <v>134</v>
       </c>
       <c r="D281" s="5" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E281" s="4"/>
       <c r="F281" s="5" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="G281" s="4" t="s">
         <v>56</v>
       </c>
       <c r="H281" s="4"/>
       <c r="I281" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="J281" s="4" t="s">
         <v>20</v>
@@ -11516,7 +11519,7 @@
         <v>21</v>
       </c>
       <c r="M281" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="282" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -11530,11 +11533,11 @@
         <v>140</v>
       </c>
       <c r="D282" s="5" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E282" s="4"/>
       <c r="F282" s="5" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="G282" s="4" t="s">
         <v>35</v>
@@ -11560,18 +11563,18 @@
         <v>154</v>
       </c>
       <c r="D283" s="5" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E283" s="4"/>
       <c r="F283" s="5" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G283" s="4" t="s">
         <v>56</v>
       </c>
       <c r="H283" s="4"/>
       <c r="I283" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="J283" s="4" t="s">
         <v>20</v>
@@ -11580,7 +11583,7 @@
         <v>21</v>
       </c>
       <c r="M283" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="284" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -11594,18 +11597,18 @@
         <v>140</v>
       </c>
       <c r="D284" s="4" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E284" s="4"/>
       <c r="F284" s="4" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="G284" s="4" t="s">
         <v>162</v>
       </c>
       <c r="H284" s="4"/>
       <c r="I284" s="4" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="J284" s="4" t="s">
         <v>20</v>
@@ -11614,7 +11617,7 @@
         <v>149</v>
       </c>
       <c r="M284" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="285" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -11628,18 +11631,18 @@
         <v>144</v>
       </c>
       <c r="D285" s="5" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E285" s="4"/>
       <c r="F285" s="5" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="G285" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H285" s="4"/>
       <c r="I285" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="J285" s="4" t="s">
         <v>20</v>
@@ -11648,7 +11651,7 @@
         <v>21</v>
       </c>
       <c r="M285" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="286" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -11692,18 +11695,18 @@
         <v>166</v>
       </c>
       <c r="D287" s="5" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E287" s="4"/>
       <c r="F287" s="5" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="G287" s="4" t="s">
         <v>56</v>
       </c>
       <c r="H287" s="4"/>
       <c r="I287" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="J287" s="4" t="s">
         <v>20</v>
@@ -11712,7 +11715,7 @@
         <v>21</v>
       </c>
       <c r="M287" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="288" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.2">
@@ -11726,11 +11729,11 @@
         <v>168</v>
       </c>
       <c r="D288" s="5" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E288" s="4"/>
       <c r="F288" s="5" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="G288" s="4" t="s">
         <v>173</v>
@@ -11756,18 +11759,18 @@
         <v>168</v>
       </c>
       <c r="D289" s="4" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E289" s="4"/>
       <c r="F289" s="4" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G289" s="4" t="s">
         <v>162</v>
       </c>
       <c r="H289" s="4"/>
       <c r="I289" s="4" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="J289" s="4" t="s">
         <v>20</v>
@@ -11776,7 +11779,7 @@
         <v>149</v>
       </c>
       <c r="M289" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="290" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -11790,18 +11793,18 @@
         <v>144</v>
       </c>
       <c r="D290" s="4" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E290" s="4"/>
       <c r="F290" s="4" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="G290" s="4" t="s">
         <v>152</v>
       </c>
       <c r="H290" s="4"/>
       <c r="I290" s="4" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="J290" s="4" t="s">
         <v>20</v>
@@ -11810,7 +11813,7 @@
         <v>149</v>
       </c>
       <c r="M290" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="291" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -11824,18 +11827,18 @@
         <v>181</v>
       </c>
       <c r="D291" s="4" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E291" s="4"/>
       <c r="F291" s="4" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="G291" s="4" t="s">
         <v>170</v>
       </c>
       <c r="H291" s="4"/>
       <c r="I291" s="4" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J291" s="4" t="s">
         <v>20</v>
@@ -11844,7 +11847,7 @@
         <v>149</v>
       </c>
       <c r="M291" s="23" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="292" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -11858,18 +11861,18 @@
         <v>16</v>
       </c>
       <c r="D292" s="5" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="E292" s="4"/>
       <c r="F292" s="5" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="G292" s="4" t="s">
         <v>39</v>
       </c>
       <c r="H292" s="4"/>
       <c r="I292" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="J292" s="4" t="s">
         <v>20</v>
@@ -11878,7 +11881,7 @@
         <v>21</v>
       </c>
       <c r="M292" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="293" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -11892,11 +11895,11 @@
         <v>16</v>
       </c>
       <c r="D293" s="5" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E293" s="4"/>
       <c r="F293" s="5" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="G293" s="4" t="s">
         <v>28</v>
@@ -11922,11 +11925,11 @@
         <v>16</v>
       </c>
       <c r="D294" s="5" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E294" s="4"/>
       <c r="F294" s="5" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G294" s="4" t="s">
         <v>31</v>
@@ -11952,11 +11955,11 @@
         <v>16</v>
       </c>
       <c r="D295" s="5" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E295" s="4"/>
       <c r="F295" s="5" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G295" s="4" t="s">
         <v>35</v>
@@ -11982,18 +11985,18 @@
         <v>16</v>
       </c>
       <c r="D296" s="4" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E296" s="4"/>
       <c r="F296" s="4" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="G296" s="4" t="s">
         <v>152</v>
       </c>
       <c r="H296" s="4"/>
       <c r="I296" s="4" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="J296" s="4" t="s">
         <v>20</v>
@@ -12002,7 +12005,7 @@
         <v>149</v>
       </c>
       <c r="M296" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="297" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -12016,11 +12019,11 @@
         <v>22</v>
       </c>
       <c r="D297" s="5" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E297" s="4"/>
       <c r="F297" s="5" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="G297" s="4" t="s">
         <v>56</v>
@@ -12046,11 +12049,11 @@
         <v>22</v>
       </c>
       <c r="D298" s="5" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E298" s="4"/>
       <c r="F298" s="5" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="G298" s="4" t="s">
         <v>39</v>
@@ -12076,11 +12079,11 @@
         <v>22</v>
       </c>
       <c r="D299" s="5" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E299" s="4"/>
       <c r="F299" s="5" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="G299" s="4" t="s">
         <v>25</v>
@@ -12106,11 +12109,11 @@
         <v>22</v>
       </c>
       <c r="D300" s="5" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E300" s="4"/>
       <c r="F300" s="5" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G300" s="4" t="s">
         <v>28</v>
@@ -12136,11 +12139,11 @@
         <v>22</v>
       </c>
       <c r="D301" s="5" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E301" s="4"/>
       <c r="F301" s="5" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="G301" s="4" t="s">
         <v>31</v>
@@ -12166,27 +12169,27 @@
         <v>22</v>
       </c>
       <c r="D302" s="5" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E302" s="4"/>
       <c r="F302" s="5" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="G302" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H302" s="4"/>
       <c r="I302" t="s">
+        <v>599</v>
+      </c>
+      <c r="J302" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L302" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M302" t="s">
         <v>600</v>
-      </c>
-      <c r="J302" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L302" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M302" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="303" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -12200,18 +12203,18 @@
         <v>201</v>
       </c>
       <c r="D303" s="4" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E303" s="4"/>
       <c r="F303" s="4" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G303" s="4" t="s">
         <v>170</v>
       </c>
       <c r="H303" s="4"/>
       <c r="I303" s="4" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="J303" s="4" t="s">
         <v>20</v>
@@ -12220,7 +12223,7 @@
         <v>149</v>
       </c>
       <c r="M303" s="23" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="304" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -12234,18 +12237,18 @@
         <v>22</v>
       </c>
       <c r="D304" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E304" s="4"/>
       <c r="F304" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G304" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H304" s="4"/>
       <c r="I304" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="J304" s="4" t="s">
         <v>20</v>
@@ -12254,7 +12257,7 @@
         <v>21</v>
       </c>
       <c r="M304" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="305" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -12268,18 +12271,18 @@
         <v>23</v>
       </c>
       <c r="D305" s="5" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E305" s="4"/>
       <c r="F305" s="5" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="G305" s="4" t="s">
         <v>39</v>
       </c>
       <c r="H305" s="4"/>
       <c r="I305" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="J305" s="4" t="s">
         <v>20</v>
@@ -12288,7 +12291,7 @@
         <v>21</v>
       </c>
       <c r="M305" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="306" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -12302,18 +12305,18 @@
         <v>23</v>
       </c>
       <c r="D306" s="5" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="E306" s="4"/>
       <c r="F306" s="5" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="G306" s="4" t="s">
         <v>25</v>
       </c>
       <c r="H306" s="4"/>
       <c r="I306" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="J306" s="4" t="s">
         <v>20</v>
@@ -12322,7 +12325,7 @@
         <v>21</v>
       </c>
       <c r="M306" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="307" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -12336,11 +12339,11 @@
         <v>23</v>
       </c>
       <c r="D307" s="5" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="E307" s="4"/>
       <c r="F307" s="5" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="G307" s="4" t="s">
         <v>28</v>
@@ -12366,11 +12369,11 @@
         <v>23</v>
       </c>
       <c r="D308" s="5" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="E308" s="4"/>
       <c r="F308" s="5" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G308" s="4" t="s">
         <v>31</v>
@@ -12396,11 +12399,11 @@
         <v>43</v>
       </c>
       <c r="D309" s="5" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="E309" s="4"/>
       <c r="F309" s="5" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="G309" s="4" t="s">
         <v>56</v>
@@ -12426,18 +12429,18 @@
         <v>43</v>
       </c>
       <c r="D310" s="5" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="E310" s="4"/>
       <c r="F310" s="5" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="G310" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H310" s="4"/>
       <c r="I310" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="J310" s="4" t="s">
         <v>20</v>
@@ -12446,7 +12449,7 @@
         <v>21</v>
       </c>
       <c r="M310" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="311" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -12460,18 +12463,18 @@
         <v>29</v>
       </c>
       <c r="D311" s="5" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E311" s="4"/>
       <c r="F311" s="5" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="G311" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H311" s="4"/>
       <c r="I311" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="J311" s="4" t="s">
         <v>20</v>
@@ -12480,7 +12483,7 @@
         <v>21</v>
       </c>
       <c r="M311" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="312" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -12494,18 +12497,18 @@
         <v>47</v>
       </c>
       <c r="D312" s="4" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="E312" s="4"/>
       <c r="F312" s="4" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="G312" s="4" t="s">
         <v>170</v>
       </c>
       <c r="H312" s="4"/>
       <c r="I312" s="4" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="J312" s="4" t="s">
         <v>20</v>
@@ -12514,7 +12517,7 @@
         <v>149</v>
       </c>
       <c r="M312" s="23" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="313" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -12528,11 +12531,11 @@
         <v>43</v>
       </c>
       <c r="D313" s="5" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="E313" s="4"/>
       <c r="F313" s="5" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="G313" s="4" t="s">
         <v>19</v>
@@ -12558,11 +12561,11 @@
         <v>47</v>
       </c>
       <c r="D314" s="5" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E314" s="4"/>
       <c r="F314" s="5" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="G314" s="4" t="s">
         <v>39</v>
@@ -12588,18 +12591,18 @@
         <v>54</v>
       </c>
       <c r="D315" s="5" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="E315" s="4"/>
       <c r="F315" s="5" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="G315" s="4" t="s">
         <v>25</v>
       </c>
       <c r="H315" s="4"/>
       <c r="I315" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="J315" s="4" t="s">
         <v>20</v>
@@ -12608,7 +12611,7 @@
         <v>21</v>
       </c>
       <c r="M315" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="316" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -12622,18 +12625,18 @@
         <v>47</v>
       </c>
       <c r="D316" s="5" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E316" s="4"/>
       <c r="F316" s="5" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="G316" s="4" t="s">
         <v>28</v>
       </c>
       <c r="H316" s="4"/>
       <c r="I316" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="J316" s="4" t="s">
         <v>20</v>
@@ -12642,7 +12645,7 @@
         <v>21</v>
       </c>
       <c r="M316" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="317" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -12656,18 +12659,18 @@
         <v>256</v>
       </c>
       <c r="D317" s="5" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="E317" s="4"/>
       <c r="F317" s="5" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="G317" s="4" t="s">
         <v>31</v>
       </c>
       <c r="H317" s="4"/>
       <c r="I317" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="J317" s="4" t="s">
         <v>20</v>
@@ -12676,7 +12679,7 @@
         <v>21</v>
       </c>
       <c r="M317" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="318" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -12687,14 +12690,14 @@
         <v>43</v>
       </c>
       <c r="C318" s="21" t="s">
+        <v>626</v>
+      </c>
+      <c r="D318" s="5" t="s">
         <v>627</v>
-      </c>
-      <c r="D318" s="5" t="s">
-        <v>628</v>
       </c>
       <c r="E318" s="4"/>
       <c r="F318" s="5" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G318" s="4" t="s">
         <v>56</v>
@@ -12720,11 +12723,11 @@
         <v>54</v>
       </c>
       <c r="D319" s="22" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="E319" s="4"/>
       <c r="F319" s="22" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="G319" s="4" t="s">
         <v>35</v>
@@ -12750,27 +12753,27 @@
         <v>61</v>
       </c>
       <c r="D320" s="5" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E320" s="4"/>
       <c r="F320" s="5" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="G320" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H320" s="4"/>
       <c r="I320" t="s">
+        <v>629</v>
+      </c>
+      <c r="J320" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L320" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M320" t="s">
         <v>630</v>
-      </c>
-      <c r="J320" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L320" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M320" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="321" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -12784,18 +12787,18 @@
         <v>54</v>
       </c>
       <c r="D321" s="5" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E321" s="4"/>
       <c r="F321" s="5" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="G321" s="4" t="s">
         <v>31</v>
       </c>
       <c r="H321" s="4"/>
       <c r="I321" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="J321" s="4" t="s">
         <v>20</v>
@@ -12804,7 +12807,7 @@
         <v>21</v>
       </c>
       <c r="M321" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="322" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -12815,14 +12818,14 @@
         <v>47</v>
       </c>
       <c r="C322" s="21" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D322" s="5" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="E322" s="4"/>
       <c r="F322" s="5" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="G322" s="4" t="s">
         <v>39</v>
@@ -12845,14 +12848,14 @@
         <v>47</v>
       </c>
       <c r="C323" s="21" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D323" s="5" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E323" s="4"/>
       <c r="F323" s="5" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="G323" s="4" t="s">
         <v>28</v>
@@ -12875,30 +12878,30 @@
         <v>61</v>
       </c>
       <c r="C324" s="21" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D324" s="5" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="E324" s="4"/>
       <c r="F324" s="5" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="G324" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H324" s="4"/>
       <c r="I324" t="s">
+        <v>636</v>
+      </c>
+      <c r="J324" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L324" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M324" t="s">
         <v>637</v>
-      </c>
-      <c r="J324" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L324" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M324" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="325" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -12909,14 +12912,14 @@
         <v>54</v>
       </c>
       <c r="C325" s="21" t="s">
+        <v>638</v>
+      </c>
+      <c r="D325" s="5" t="s">
         <v>639</v>
-      </c>
-      <c r="D325" s="5" t="s">
-        <v>640</v>
       </c>
       <c r="E325" s="4"/>
       <c r="F325" s="5" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="G325" s="4" t="s">
         <v>25</v>
@@ -12939,14 +12942,14 @@
         <v>54</v>
       </c>
       <c r="C326" s="21" t="s">
+        <v>640</v>
+      </c>
+      <c r="D326" s="5" t="s">
         <v>641</v>
-      </c>
-      <c r="D326" s="5" t="s">
-        <v>642</v>
       </c>
       <c r="E326" s="4"/>
       <c r="F326" s="5" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="G326" s="4" t="s">
         <v>31</v>
@@ -12969,21 +12972,21 @@
         <v>54</v>
       </c>
       <c r="C327" s="33" t="s">
+        <v>642</v>
+      </c>
+      <c r="D327" s="15" t="s">
         <v>643</v>
-      </c>
-      <c r="D327" s="15" t="s">
-        <v>644</v>
       </c>
       <c r="E327" s="13"/>
       <c r="F327" s="15" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="G327" s="13" t="s">
         <v>35</v>
       </c>
       <c r="H327" s="13"/>
       <c r="I327" s="14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J327" s="13" t="s">
         <v>20</v>
@@ -12992,12 +12995,12 @@
         <v>21</v>
       </c>
       <c r="M327" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="328" spans="1:13" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A328" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B328" s="21" t="s">
         <v>89</v>
@@ -13006,11 +13009,11 @@
         <v>90</v>
       </c>
       <c r="D328" s="5" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="E328" s="4"/>
       <c r="F328" s="5" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="G328" s="4" t="s">
         <v>28</v>
@@ -13027,7 +13030,7 @@
     </row>
     <row r="329" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A329" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B329" s="21" t="s">
         <v>89</v>
@@ -13036,11 +13039,11 @@
         <v>90</v>
       </c>
       <c r="D329" s="5" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E329" s="4"/>
       <c r="F329" s="5" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="G329" s="4" t="s">
         <v>56</v>
@@ -13057,7 +13060,7 @@
     </row>
     <row r="330" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A330" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B330" s="21" t="s">
         <v>315</v>
@@ -13066,18 +13069,18 @@
         <v>90</v>
       </c>
       <c r="D330" s="5" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E330" s="4"/>
       <c r="F330" s="5" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="G330" s="4" t="s">
         <v>31</v>
       </c>
       <c r="H330" s="4"/>
       <c r="I330" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="J330" s="4" t="s">
         <v>20</v>
@@ -13086,12 +13089,12 @@
         <v>21</v>
       </c>
       <c r="M330" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="331" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A331" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B331" s="21" t="s">
         <v>98</v>
@@ -13100,11 +13103,11 @@
         <v>104</v>
       </c>
       <c r="D331" s="5" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E331" s="4"/>
       <c r="F331" s="5" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="G331" s="4" t="s">
         <v>35</v>
@@ -13121,7 +13124,7 @@
     </row>
     <row r="332" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A332" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B332" s="21" t="s">
         <v>90</v>
@@ -13130,11 +13133,11 @@
         <v>110</v>
       </c>
       <c r="D332" s="5" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="E332" s="4"/>
       <c r="F332" s="5" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="G332" s="4" t="s">
         <v>25</v>
@@ -13151,7 +13154,7 @@
     </row>
     <row r="333" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A333" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B333" s="21" t="s">
         <v>90</v>
@@ -13160,11 +13163,11 @@
         <v>106</v>
       </c>
       <c r="D333" s="5" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="E333" s="4"/>
       <c r="F333" s="5" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="G333" s="4" t="s">
         <v>28</v>
@@ -13181,7 +13184,7 @@
     </row>
     <row r="334" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A334" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B334" s="21" t="s">
         <v>90</v>
@@ -13190,32 +13193,32 @@
         <v>119</v>
       </c>
       <c r="D334" s="5" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="E334" s="4"/>
       <c r="F334" s="5" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="G334" s="4" t="s">
         <v>56</v>
       </c>
       <c r="H334" s="4"/>
       <c r="I334" t="s">
+        <v>655</v>
+      </c>
+      <c r="J334" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L334" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M334" t="s">
         <v>656</v>
-      </c>
-      <c r="J334" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L334" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M334" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="335" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A335" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B335" s="21" t="s">
         <v>104</v>
@@ -13224,18 +13227,18 @@
         <v>110</v>
       </c>
       <c r="D335" s="5" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E335" s="4"/>
       <c r="F335" s="5" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="G335" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H335" s="4"/>
       <c r="I335" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="J335" s="4" t="s">
         <v>20</v>
@@ -13244,12 +13247,12 @@
         <v>21</v>
       </c>
       <c r="M335" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="336" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A336" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B336" s="21" t="s">
         <v>106</v>
@@ -13258,11 +13261,11 @@
         <v>119</v>
       </c>
       <c r="D336" s="5" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="E336" s="4"/>
       <c r="F336" s="5" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="G336" s="4" t="s">
         <v>28</v>
@@ -13279,7 +13282,7 @@
     </row>
     <row r="337" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A337" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B337" s="21" t="s">
         <v>110</v>
@@ -13288,11 +13291,11 @@
         <v>354</v>
       </c>
       <c r="D337" s="5" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E337" s="4"/>
       <c r="F337" s="5" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="G337" s="4" t="s">
         <v>35</v>
@@ -13309,7 +13312,7 @@
     </row>
     <row r="338" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A338" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B338" s="21" t="s">
         <v>119</v>
@@ -13318,11 +13321,11 @@
         <v>129</v>
       </c>
       <c r="D338" s="5" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="E338" s="4"/>
       <c r="F338" s="5" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="G338" s="4" t="s">
         <v>28</v>
@@ -13339,7 +13342,7 @@
     </row>
     <row r="339" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A339" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B339" s="21" t="s">
         <v>354</v>
@@ -13348,18 +13351,18 @@
         <v>129</v>
       </c>
       <c r="D339" s="5" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="E339" s="4"/>
       <c r="F339" s="5" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="G339" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H339" s="4"/>
       <c r="I339" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="J339" s="4" t="s">
         <v>20</v>
@@ -13368,12 +13371,12 @@
         <v>21</v>
       </c>
       <c r="M339" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="340" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A340" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B340" s="21" t="s">
         <v>129</v>
@@ -13382,11 +13385,11 @@
         <v>134</v>
       </c>
       <c r="D340" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="E340" s="4"/>
       <c r="F340" s="5" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G340" s="4" t="s">
         <v>35</v>
@@ -13403,7 +13406,7 @@
     </row>
     <row r="341" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A341" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B341" s="21" t="s">
         <v>134</v>
@@ -13412,11 +13415,11 @@
         <v>154</v>
       </c>
       <c r="D341" s="5" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E341" s="4"/>
       <c r="F341" s="5" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G341" s="4" t="s">
         <v>35</v>
@@ -13433,7 +13436,7 @@
     </row>
     <row r="342" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A342" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B342" s="21" t="s">
         <v>154</v>
@@ -13442,11 +13445,11 @@
         <v>166</v>
       </c>
       <c r="D342" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="E342" s="4"/>
       <c r="F342" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G342" s="4" t="s">
         <v>35</v>

--- a/import/timetable.xlsx
+++ b/import/timetable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michaelstork/Library/CloudStorage/Box-Box/Feel Festival/Marketing/03_Website/2026_timetable/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADE73FDB-10EE-6548-821F-6720B97E4BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B379722A-D28D-A444-865B-92811D12EF0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Worksheet!$A$3:$M$342</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Worksheet!$A$3:$M$344</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3048" uniqueCount="673">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3064" uniqueCount="675">
   <si>
     <t>Timetable 2026</t>
   </si>
@@ -2189,6 +2189,12 @@
   </si>
   <si>
     <t>KATTA LANA &amp; BRAUER</t>
+  </si>
+  <si>
+    <t>SAILOR RAVE B2B MAX MASTER</t>
+  </si>
+  <si>
+    <t>SAX</t>
   </si>
 </sst>
 </file>
@@ -2304,7 +2310,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2386,6 +2392,9 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2583,10 +2592,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M342"/>
+  <dimension ref="A1:M344"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -2654,7 +2663,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" ht="30" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>15</v>
       </c>
@@ -2684,7 +2693,7 @@
       </c>
       <c r="M4"/>
     </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>15</v>
       </c>
@@ -2718,7 +2727,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
@@ -2748,7 +2757,7 @@
       </c>
       <c r="M6"/>
     </row>
-    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>15</v>
       </c>
@@ -2782,7 +2791,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>15</v>
       </c>
@@ -2816,7 +2825,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>15</v>
       </c>
@@ -2850,7 +2859,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>15</v>
       </c>
@@ -2884,7 +2893,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>15</v>
       </c>
@@ -2914,7 +2923,7 @@
       </c>
       <c r="M11"/>
     </row>
-    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>15</v>
       </c>
@@ -2948,7 +2957,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>15</v>
       </c>
@@ -2978,7 +2987,7 @@
       </c>
       <c r="M13"/>
     </row>
-    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>15</v>
       </c>
@@ -3012,7 +3021,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>15</v>
       </c>
@@ -3046,7 +3055,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
@@ -3080,7 +3089,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>15</v>
       </c>
@@ -3110,7 +3119,7 @@
       </c>
       <c r="M17"/>
     </row>
-    <row r="18" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>15</v>
       </c>
@@ -3144,7 +3153,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>15</v>
       </c>
@@ -3178,7 +3187,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>15</v>
       </c>
@@ -3212,7 +3221,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>15</v>
       </c>
@@ -3242,7 +3251,7 @@
       </c>
       <c r="M21"/>
     </row>
-    <row r="22" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>15</v>
       </c>
@@ -3276,7 +3285,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>15</v>
       </c>
@@ -3306,7 +3315,7 @@
       </c>
       <c r="M23"/>
     </row>
-    <row r="24" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>15</v>
       </c>
@@ -3336,7 +3345,7 @@
       </c>
       <c r="M24"/>
     </row>
-    <row r="25" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>15</v>
       </c>
@@ -3370,7 +3379,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>15</v>
       </c>
@@ -3400,7 +3409,7 @@
       </c>
       <c r="M26"/>
     </row>
-    <row r="27" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>15</v>
       </c>
@@ -3434,7 +3443,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>15</v>
       </c>
@@ -3464,7 +3473,7 @@
       </c>
       <c r="M28"/>
     </row>
-    <row r="29" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>15</v>
       </c>
@@ -3494,7 +3503,7 @@
       </c>
       <c r="M29"/>
     </row>
-    <row r="30" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>15</v>
       </c>
@@ -3528,7 +3537,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" ht="30" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>15</v>
       </c>
@@ -3558,7 +3567,7 @@
       </c>
       <c r="M31"/>
     </row>
-    <row r="32" spans="1:13" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:13" ht="15" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A32" s="7" t="s">
         <v>88</v>
       </c>
@@ -3588,7 +3597,7 @@
       </c>
       <c r="M32"/>
     </row>
-    <row r="33" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>88</v>
       </c>
@@ -3618,7 +3627,7 @@
       </c>
       <c r="M33"/>
     </row>
-    <row r="34" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>88</v>
       </c>
@@ -3652,7 +3661,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>88</v>
       </c>
@@ -3682,7 +3691,7 @@
       </c>
       <c r="M35"/>
     </row>
-    <row r="36" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>88</v>
       </c>
@@ -3712,7 +3721,7 @@
       </c>
       <c r="M36"/>
     </row>
-    <row r="37" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>88</v>
       </c>
@@ -3746,7 +3755,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>88</v>
       </c>
@@ -3780,7 +3789,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
         <v>88</v>
       </c>
@@ -3810,7 +3819,7 @@
       </c>
       <c r="M39"/>
     </row>
-    <row r="40" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>88</v>
       </c>
@@ -3840,7 +3849,7 @@
       </c>
       <c r="M40"/>
     </row>
-    <row r="41" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
         <v>88</v>
       </c>
@@ -3870,7 +3879,7 @@
       </c>
       <c r="M41"/>
     </row>
-    <row r="42" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>88</v>
       </c>
@@ -3900,7 +3909,7 @@
       </c>
       <c r="M42"/>
     </row>
-    <row r="43" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
         <v>88</v>
       </c>
@@ -3934,7 +3943,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
         <v>88</v>
       </c>
@@ -3964,7 +3973,7 @@
       </c>
       <c r="M44"/>
     </row>
-    <row r="45" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
         <v>88</v>
       </c>
@@ -3994,7 +4003,7 @@
       </c>
       <c r="M45"/>
     </row>
-    <row r="46" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:13" ht="26" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="17" t="s">
         <v>88</v>
       </c>
@@ -4024,7 +4033,7 @@
       </c>
       <c r="M46"/>
     </row>
-    <row r="47" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
         <v>88</v>
       </c>
@@ -4054,7 +4063,7 @@
       </c>
       <c r="M47"/>
     </row>
-    <row r="48" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
         <v>88</v>
       </c>
@@ -4084,7 +4093,7 @@
       </c>
       <c r="M48"/>
     </row>
-    <row r="49" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
         <v>88</v>
       </c>
@@ -4114,7 +4123,7 @@
       </c>
       <c r="M49"/>
     </row>
-    <row r="50" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
         <v>88</v>
       </c>
@@ -4148,7 +4157,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
         <v>88</v>
       </c>
@@ -4182,7 +4191,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
         <v>88</v>
       </c>
@@ -4212,7 +4221,7 @@
       </c>
       <c r="M52"/>
     </row>
-    <row r="53" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
         <v>88</v>
       </c>
@@ -4242,7 +4251,7 @@
       </c>
       <c r="M53"/>
     </row>
-    <row r="54" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
         <v>88</v>
       </c>
@@ -4272,7 +4281,7 @@
       </c>
       <c r="M54"/>
     </row>
-    <row r="55" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
         <v>88</v>
       </c>
@@ -4302,7 +4311,7 @@
       </c>
       <c r="M55"/>
     </row>
-    <row r="56" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
         <v>88</v>
       </c>
@@ -4336,7 +4345,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="57" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
         <v>88</v>
       </c>
@@ -4366,7 +4375,7 @@
       </c>
       <c r="M57"/>
     </row>
-    <row r="58" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
         <v>88</v>
       </c>
@@ -4400,7 +4409,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
         <v>88</v>
       </c>
@@ -4434,7 +4443,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="10" t="s">
         <v>88</v>
       </c>
@@ -4468,7 +4477,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="61" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
         <v>88</v>
       </c>
@@ -4502,7 +4511,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
         <v>88</v>
       </c>
@@ -4536,7 +4545,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="63" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
         <v>88</v>
       </c>
@@ -4570,7 +4579,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
         <v>88</v>
       </c>
@@ -4600,7 +4609,7 @@
       </c>
       <c r="M64"/>
     </row>
-    <row r="65" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
         <v>88</v>
       </c>
@@ -4634,7 +4643,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
         <v>88</v>
       </c>
@@ -4668,7 +4677,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
         <v>88</v>
       </c>
@@ -4698,7 +4707,7 @@
       </c>
       <c r="M67"/>
     </row>
-    <row r="68" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
         <v>88</v>
       </c>
@@ -4732,7 +4741,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="4" t="s">
         <v>88</v>
       </c>
@@ -4762,7 +4771,7 @@
       </c>
       <c r="M69"/>
     </row>
-    <row r="70" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
         <v>88</v>
       </c>
@@ -4792,7 +4801,7 @@
       </c>
       <c r="M70"/>
     </row>
-    <row r="71" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:13" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
         <v>88</v>
       </c>
@@ -4822,7 +4831,7 @@
       </c>
       <c r="M71"/>
     </row>
-    <row r="72" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="4" t="s">
         <v>88</v>
       </c>
@@ -4852,7 +4861,7 @@
       </c>
       <c r="M72"/>
     </row>
-    <row r="73" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="4" t="s">
         <v>88</v>
       </c>
@@ -4886,7 +4895,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="74" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="4" t="s">
         <v>88</v>
       </c>
@@ -4920,7 +4929,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="75" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
         <v>88</v>
       </c>
@@ -4954,7 +4963,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="76" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="4" t="s">
         <v>88</v>
       </c>
@@ -4988,7 +4997,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="77" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
         <v>88</v>
       </c>
@@ -5018,7 +5027,7 @@
       </c>
       <c r="M77"/>
     </row>
-    <row r="78" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
         <v>88</v>
       </c>
@@ -5052,7 +5061,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="79" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
         <v>88</v>
       </c>
@@ -5086,7 +5095,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="80" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
         <v>88</v>
       </c>
@@ -5116,7 +5125,7 @@
       </c>
       <c r="M80"/>
     </row>
-    <row r="81" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
         <v>88</v>
       </c>
@@ -5146,7 +5155,7 @@
       </c>
       <c r="M81"/>
     </row>
-    <row r="82" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="4" t="s">
         <v>88</v>
       </c>
@@ -5180,7 +5189,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="83" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="4" t="s">
         <v>88</v>
       </c>
@@ -5210,7 +5219,7 @@
       </c>
       <c r="M83"/>
     </row>
-    <row r="84" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
         <v>88</v>
       </c>
@@ -5244,7 +5253,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="85" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
         <v>88</v>
       </c>
@@ -5278,7 +5287,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="86" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
         <v>88</v>
       </c>
@@ -5312,7 +5321,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="87" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="4" t="s">
         <v>88</v>
       </c>
@@ -5346,7 +5355,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="88" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="4" t="s">
         <v>88</v>
       </c>
@@ -5380,7 +5389,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="89" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="4" t="s">
         <v>88</v>
       </c>
@@ -5414,7 +5423,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="90" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="4" t="s">
         <v>88</v>
       </c>
@@ -5448,7 +5457,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="91" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="4" t="s">
         <v>88</v>
       </c>
@@ -5478,7 +5487,7 @@
       </c>
       <c r="M91"/>
     </row>
-    <row r="92" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="4" t="s">
         <v>88</v>
       </c>
@@ -5508,7 +5517,7 @@
       </c>
       <c r="M92"/>
     </row>
-    <row r="93" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="4" t="s">
         <v>88</v>
       </c>
@@ -5538,7 +5547,7 @@
       </c>
       <c r="M93"/>
     </row>
-    <row r="94" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="4" t="s">
         <v>88</v>
       </c>
@@ -5568,7 +5577,7 @@
       </c>
       <c r="M94"/>
     </row>
-    <row r="95" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="4" t="s">
         <v>88</v>
       </c>
@@ -5602,7 +5611,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="96" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
         <v>88</v>
       </c>
@@ -5632,7 +5641,7 @@
       </c>
       <c r="M96"/>
     </row>
-    <row r="97" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
         <v>88</v>
       </c>
@@ -5666,7 +5675,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="98" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
         <v>88</v>
       </c>
@@ -5696,7 +5705,7 @@
       </c>
       <c r="M98"/>
     </row>
-    <row r="99" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="4" t="s">
         <v>88</v>
       </c>
@@ -5730,7 +5739,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="100" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
         <v>88</v>
       </c>
@@ -5760,7 +5769,7 @@
       </c>
       <c r="M100"/>
     </row>
-    <row r="101" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
         <v>88</v>
       </c>
@@ -5790,7 +5799,7 @@
       </c>
       <c r="M101"/>
     </row>
-    <row r="102" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="4" t="s">
         <v>88</v>
       </c>
@@ -5824,7 +5833,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="103" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="4" t="s">
         <v>88</v>
       </c>
@@ -5854,7 +5863,7 @@
       </c>
       <c r="M103"/>
     </row>
-    <row r="104" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
         <v>88</v>
       </c>
@@ -5888,7 +5897,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="105" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="4" t="s">
         <v>88</v>
       </c>
@@ -5922,7 +5931,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="106" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="4" t="s">
         <v>88</v>
       </c>
@@ -5956,7 +5965,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="107" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="4" t="s">
         <v>88</v>
       </c>
@@ -5986,7 +5995,7 @@
       </c>
       <c r="M107"/>
     </row>
-    <row r="108" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="4" t="s">
         <v>88</v>
       </c>
@@ -6016,7 +6025,7 @@
       </c>
       <c r="M108"/>
     </row>
-    <row r="109" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="4" t="s">
         <v>88</v>
       </c>
@@ -6046,7 +6055,7 @@
       </c>
       <c r="M109"/>
     </row>
-    <row r="110" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="4" t="s">
         <v>88</v>
       </c>
@@ -6076,7 +6085,7 @@
       </c>
       <c r="M110"/>
     </row>
-    <row r="111" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="4" t="s">
         <v>88</v>
       </c>
@@ -6110,7 +6119,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="112" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="4" t="s">
         <v>88</v>
       </c>
@@ -6140,7 +6149,7 @@
       </c>
       <c r="M112"/>
     </row>
-    <row r="113" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="4" t="s">
         <v>88</v>
       </c>
@@ -6174,7 +6183,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="114" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:13" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A114" s="4" t="s">
         <v>88</v>
       </c>
@@ -6208,7 +6217,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="115" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="4" t="s">
         <v>88</v>
       </c>
@@ -6242,7 +6251,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="116" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="4" t="s">
         <v>88</v>
       </c>
@@ -6272,7 +6281,7 @@
       </c>
       <c r="M116"/>
     </row>
-    <row r="117" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="4" t="s">
         <v>88</v>
       </c>
@@ -6306,7 +6315,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="118" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="4" t="s">
         <v>88</v>
       </c>
@@ -6370,7 +6379,7 @@
       </c>
       <c r="M119"/>
     </row>
-    <row r="120" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="4" t="s">
         <v>88</v>
       </c>
@@ -6404,7 +6413,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="121" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="4" t="s">
         <v>88</v>
       </c>
@@ -6434,7 +6443,7 @@
       </c>
       <c r="M121"/>
     </row>
-    <row r="122" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="4" t="s">
         <v>88</v>
       </c>
@@ -6464,7 +6473,7 @@
       </c>
       <c r="M122"/>
     </row>
-    <row r="123" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="4" t="s">
         <v>88</v>
       </c>
@@ -6498,7 +6507,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="124" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:13" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="4" t="s">
         <v>88</v>
       </c>
@@ -6528,7 +6537,7 @@
       </c>
       <c r="M124"/>
     </row>
-    <row r="125" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="4" t="s">
         <v>88</v>
       </c>
@@ -6562,7 +6571,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="126" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="4" t="s">
         <v>88</v>
       </c>
@@ -6592,7 +6601,7 @@
       </c>
       <c r="M126"/>
     </row>
-    <row r="127" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="4" t="s">
         <v>88</v>
       </c>
@@ -6622,7 +6631,7 @@
       </c>
       <c r="M127"/>
     </row>
-    <row r="128" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="4" t="s">
         <v>88</v>
       </c>
@@ -6652,7 +6661,7 @@
       </c>
       <c r="M128"/>
     </row>
-    <row r="129" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="4" t="s">
         <v>88</v>
       </c>
@@ -6716,7 +6725,7 @@
       </c>
       <c r="M130"/>
     </row>
-    <row r="131" spans="1:13" ht="31" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:13" ht="31" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="4" t="s">
         <v>88</v>
       </c>
@@ -6746,7 +6755,7 @@
       </c>
       <c r="M131"/>
     </row>
-    <row r="132" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="4" t="s">
         <v>88</v>
       </c>
@@ -6780,7 +6789,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="133" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="4" t="s">
         <v>88</v>
       </c>
@@ -6810,7 +6819,7 @@
       </c>
       <c r="M133"/>
     </row>
-    <row r="134" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A134" s="13" t="s">
         <v>88</v>
       </c>
@@ -6844,7 +6853,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="135" spans="1:13" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:13" ht="30" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A135" s="10" t="s">
         <v>302</v>
       </c>
@@ -6874,7 +6883,7 @@
       </c>
       <c r="M135"/>
     </row>
-    <row r="136" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="4" t="s">
         <v>302</v>
       </c>
@@ -6904,7 +6913,7 @@
       </c>
       <c r="M136"/>
     </row>
-    <row r="137" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="4" t="s">
         <v>302</v>
       </c>
@@ -6938,7 +6947,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="138" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="4" t="s">
         <v>302</v>
       </c>
@@ -6968,7 +6977,7 @@
       </c>
       <c r="M138"/>
     </row>
-    <row r="139" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="4" t="s">
         <v>302</v>
       </c>
@@ -7002,7 +7011,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="140" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="4" t="s">
         <v>302</v>
       </c>
@@ -7066,21 +7075,21 @@
       <c r="A142" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="B142" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="C142" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="D142" s="5" t="s">
-        <v>317</v>
+      <c r="B142" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C142" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="D142" s="22" t="s">
+        <v>673</v>
       </c>
       <c r="E142" s="4"/>
-      <c r="F142" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="G142" s="4" t="s">
-        <v>31</v>
+      <c r="F142" s="22" t="s">
+        <v>673</v>
+      </c>
+      <c r="G142" s="17" t="s">
+        <v>258</v>
       </c>
       <c r="H142" s="4"/>
       <c r="I142" s="4"/>
@@ -7096,33 +7105,29 @@
       <c r="A143" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="B143" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="C143" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="D143" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="E143" s="4"/>
-      <c r="F143" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="G143" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H143" s="4"/>
-      <c r="I143" s="4"/>
+      <c r="B143" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="C143" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D143" s="11" t="s">
+        <v>674</v>
+      </c>
+      <c r="F143" s="34" t="s">
+        <v>674</v>
+      </c>
+      <c r="G143" s="17" t="s">
+        <v>258</v>
+      </c>
       <c r="J143" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L143" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M143"/>
-    </row>
-    <row r="144" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L143" s="34" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="4" t="s">
         <v>302</v>
       </c>
@@ -7132,49 +7137,45 @@
       <c r="C144" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="D144" s="4" t="s">
-        <v>319</v>
+      <c r="D144" s="5" t="s">
+        <v>317</v>
       </c>
       <c r="E144" s="4"/>
-      <c r="F144" s="4" t="s">
-        <v>319</v>
+      <c r="F144" s="5" t="s">
+        <v>317</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>170</v>
+        <v>31</v>
       </c>
       <c r="H144" s="4"/>
-      <c r="I144" s="23" t="s">
-        <v>320</v>
-      </c>
+      <c r="I144" s="4"/>
       <c r="J144" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L144" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="M144" s="23" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="145" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L144" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M144"/>
+    </row>
+    <row r="145" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B145" s="21" t="s">
-        <v>313</v>
+        <v>98</v>
       </c>
       <c r="C145" s="21" t="s">
-        <v>321</v>
+        <v>115</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E145" s="4"/>
       <c r="F145" s="5" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="H145" s="4"/>
       <c r="I145" s="4"/>
@@ -7186,55 +7187,59 @@
       </c>
       <c r="M145"/>
     </row>
-    <row r="146" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B146" s="21" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C146" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="D146" s="5" t="s">
-        <v>323</v>
+        <v>115</v>
+      </c>
+      <c r="D146" s="4" t="s">
+        <v>319</v>
       </c>
       <c r="E146" s="4"/>
-      <c r="F146" s="5" t="s">
-        <v>323</v>
+      <c r="F146" s="4" t="s">
+        <v>319</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>39</v>
+        <v>170</v>
       </c>
       <c r="H146" s="4"/>
-      <c r="I146" s="4"/>
+      <c r="I146" s="23" t="s">
+        <v>320</v>
+      </c>
       <c r="J146" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L146" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M146"/>
-    </row>
-    <row r="147" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L146" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="M146" s="23" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B147" s="21" t="s">
-        <v>90</v>
+        <v>313</v>
       </c>
       <c r="C147" s="21" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E147" s="4"/>
       <c r="F147" s="5" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="H147" s="4"/>
       <c r="I147" s="4"/>
@@ -7246,7 +7251,7 @@
       </c>
       <c r="M147"/>
     </row>
-    <row r="148" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="4" t="s">
         <v>302</v>
       </c>
@@ -7256,15 +7261,15 @@
       <c r="C148" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="D148" t="s">
-        <v>326</v>
+      <c r="D148" s="5" t="s">
+        <v>323</v>
       </c>
       <c r="E148" s="4"/>
       <c r="F148" s="5" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="H148" s="4"/>
       <c r="I148" s="4"/>
@@ -7276,7 +7281,7 @@
       </c>
       <c r="M148"/>
     </row>
-    <row r="149" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="4" t="s">
         <v>302</v>
       </c>
@@ -7284,33 +7289,29 @@
         <v>90</v>
       </c>
       <c r="C149" s="21" t="s">
-        <v>106</v>
+        <v>324</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="E149" s="4"/>
       <c r="F149" s="5" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="H149" s="4"/>
-      <c r="I149" t="s">
-        <v>329</v>
-      </c>
+      <c r="I149" s="4"/>
       <c r="J149" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L149" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M149" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="150" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M149"/>
+    </row>
+    <row r="150" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="4" t="s">
         <v>302</v>
       </c>
@@ -7320,53 +7321,49 @@
       <c r="C150" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="D150" s="5" t="s">
-        <v>331</v>
+      <c r="D150" t="s">
+        <v>326</v>
       </c>
       <c r="E150" s="4"/>
       <c r="F150" s="5" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H150" s="4"/>
-      <c r="I150" t="s">
-        <v>332</v>
-      </c>
+      <c r="I150" s="4"/>
       <c r="J150" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L150" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M150" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="151" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M150"/>
+    </row>
+    <row r="151" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B151" s="21" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="C151" s="21" t="s">
         <v>106</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="E151" s="4"/>
       <c r="F151" s="5" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="H151" s="4"/>
       <c r="I151" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="J151" s="4" t="s">
         <v>20</v>
@@ -7375,40 +7372,44 @@
         <v>21</v>
       </c>
       <c r="M151" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="152" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B152" s="21" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="C152" s="21" t="s">
         <v>106</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="E152" s="4"/>
       <c r="F152" s="5" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="H152" s="4"/>
-      <c r="I152" s="4"/>
+      <c r="I152" t="s">
+        <v>332</v>
+      </c>
       <c r="J152" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L152" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M152"/>
-    </row>
-    <row r="153" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M152" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="4" t="s">
         <v>302</v>
       </c>
@@ -7418,49 +7419,49 @@
       <c r="C153" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="D153" s="4" t="s">
-        <v>337</v>
+      <c r="D153" s="5" t="s">
+        <v>333</v>
       </c>
       <c r="E153" s="4"/>
-      <c r="F153" s="4" t="s">
-        <v>337</v>
+      <c r="F153" s="5" t="s">
+        <v>333</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>170</v>
+        <v>31</v>
       </c>
       <c r="H153" s="4"/>
-      <c r="I153" s="23" t="s">
-        <v>338</v>
+      <c r="I153" t="s">
+        <v>334</v>
       </c>
       <c r="J153" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L153" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="M153" s="23" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="154" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L153" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M153" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B154" s="21" t="s">
-        <v>321</v>
+        <v>115</v>
       </c>
       <c r="C154" s="21" t="s">
-        <v>339</v>
+        <v>106</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E154" s="4"/>
       <c r="F154" s="5" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="H154" s="4"/>
       <c r="I154" s="4"/>
@@ -7472,55 +7473,59 @@
       </c>
       <c r="M154"/>
     </row>
-    <row r="155" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B155" s="21" t="s">
-        <v>324</v>
+        <v>115</v>
       </c>
       <c r="C155" s="21" t="s">
-        <v>341</v>
-      </c>
-      <c r="D155" s="5" t="s">
-        <v>342</v>
+        <v>106</v>
+      </c>
+      <c r="D155" s="4" t="s">
+        <v>337</v>
       </c>
       <c r="E155" s="4"/>
-      <c r="F155" s="5" t="s">
-        <v>342</v>
+      <c r="F155" s="4" t="s">
+        <v>337</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>25</v>
+        <v>170</v>
       </c>
       <c r="H155" s="4"/>
-      <c r="I155" s="4"/>
+      <c r="I155" s="23" t="s">
+        <v>338</v>
+      </c>
       <c r="J155" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L155" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M155"/>
-    </row>
-    <row r="156" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L155" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="M155" s="23" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B156" s="21" t="s">
-        <v>106</v>
+        <v>321</v>
       </c>
       <c r="C156" s="21" t="s">
-        <v>119</v>
+        <v>339</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="E156" s="4"/>
       <c r="F156" s="5" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H156" s="4"/>
       <c r="I156" s="4"/>
@@ -7532,25 +7537,25 @@
       </c>
       <c r="M156"/>
     </row>
-    <row r="157" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B157" s="21" t="s">
-        <v>106</v>
+        <v>324</v>
       </c>
       <c r="C157" s="21" t="s">
-        <v>119</v>
+        <v>341</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E157" s="4"/>
       <c r="F157" s="5" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H157" s="4"/>
       <c r="I157" s="4"/>
@@ -7562,7 +7567,7 @@
       </c>
       <c r="M157"/>
     </row>
-    <row r="158" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="4" t="s">
         <v>302</v>
       </c>
@@ -7570,17 +7575,17 @@
         <v>106</v>
       </c>
       <c r="C158" s="21" t="s">
-        <v>341</v>
+        <v>119</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E158" s="4"/>
       <c r="F158" s="5" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H158" s="4"/>
       <c r="I158" s="4"/>
@@ -7592,7 +7597,7 @@
       </c>
       <c r="M158"/>
     </row>
-    <row r="159" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:13" ht="60" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="4" t="s">
         <v>302</v>
       </c>
@@ -7603,30 +7608,26 @@
         <v>119</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E159" s="4"/>
       <c r="F159" s="5" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="H159" s="4"/>
-      <c r="I159" t="s">
-        <v>347</v>
-      </c>
+      <c r="I159" s="4"/>
       <c r="J159" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L159" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M159" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="160" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M159"/>
+    </row>
+    <row r="160" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="4" t="s">
         <v>302</v>
       </c>
@@ -7634,33 +7635,29 @@
         <v>106</v>
       </c>
       <c r="C160" s="21" t="s">
-        <v>119</v>
+        <v>341</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="E160" s="4"/>
       <c r="F160" s="5" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H160" s="4"/>
-      <c r="I160" t="s">
-        <v>349</v>
-      </c>
+      <c r="I160" s="4"/>
       <c r="J160" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L160" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M160" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="161" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M160"/>
+    </row>
+    <row r="161" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="4" t="s">
         <v>302</v>
       </c>
@@ -7671,26 +7668,30 @@
         <v>119</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="E161" s="4"/>
       <c r="F161" s="5" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="H161" s="4"/>
-      <c r="I161" s="4"/>
+      <c r="I161" t="s">
+        <v>347</v>
+      </c>
       <c r="J161" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L161" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M161"/>
-    </row>
-    <row r="162" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M161" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="4" t="s">
         <v>302</v>
       </c>
@@ -7698,51 +7699,51 @@
         <v>106</v>
       </c>
       <c r="C162" s="21" t="s">
-        <v>341</v>
-      </c>
-      <c r="D162" s="17" t="s">
-        <v>351</v>
+        <v>119</v>
+      </c>
+      <c r="D162" s="5" t="s">
+        <v>348</v>
       </c>
       <c r="E162" s="4"/>
-      <c r="F162" s="17" t="s">
-        <v>352</v>
+      <c r="F162" s="5" t="s">
+        <v>348</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="H162" s="4"/>
-      <c r="I162" s="23" t="s">
-        <v>353</v>
+      <c r="I162" t="s">
+        <v>349</v>
       </c>
       <c r="J162" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L162" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="M162" s="23" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="163" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L162" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M162" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B163" s="21" t="s">
-        <v>341</v>
+        <v>106</v>
       </c>
       <c r="C163" s="21" t="s">
-        <v>354</v>
+        <v>119</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="E163" s="4"/>
       <c r="F163" s="5" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H163" s="4"/>
       <c r="I163" s="4"/>
@@ -7754,55 +7755,59 @@
       </c>
       <c r="M163"/>
     </row>
-    <row r="164" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:13" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B164" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="C164" s="21" t="s">
         <v>341</v>
       </c>
-      <c r="C164" s="21" t="s">
-        <v>354</v>
-      </c>
-      <c r="D164" s="5" t="s">
-        <v>356</v>
+      <c r="D164" s="17" t="s">
+        <v>351</v>
       </c>
       <c r="E164" s="4"/>
-      <c r="F164" s="5" t="s">
-        <v>356</v>
+      <c r="F164" s="17" t="s">
+        <v>352</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>31</v>
+        <v>170</v>
       </c>
       <c r="H164" s="4"/>
-      <c r="I164" s="4"/>
+      <c r="I164" s="23" t="s">
+        <v>353</v>
+      </c>
       <c r="J164" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L164" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M164"/>
-    </row>
-    <row r="165" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L164" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="M164" s="23" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B165" s="21" t="s">
-        <v>119</v>
+        <v>341</v>
       </c>
       <c r="C165" s="21" t="s">
-        <v>127</v>
+        <v>354</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E165" s="4"/>
       <c r="F165" s="5" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H165" s="4"/>
       <c r="I165" s="4"/>
@@ -7814,25 +7819,25 @@
       </c>
       <c r="M165"/>
     </row>
-    <row r="166" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:13" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B166" s="21" t="s">
-        <v>119</v>
+        <v>341</v>
       </c>
       <c r="C166" s="21" t="s">
-        <v>127</v>
+        <v>354</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E166" s="4"/>
       <c r="F166" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="H166" s="4"/>
       <c r="I166" s="4"/>
@@ -7844,7 +7849,7 @@
       </c>
       <c r="M166"/>
     </row>
-    <row r="167" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="4" t="s">
         <v>302</v>
       </c>
@@ -7855,86 +7860,78 @@
         <v>127</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E167" s="4"/>
       <c r="F167" s="5" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H167" s="4"/>
-      <c r="I167" t="s">
-        <v>360</v>
-      </c>
+      <c r="I167" s="4"/>
       <c r="J167" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L167" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M167" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="168" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M167"/>
+    </row>
+    <row r="168" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B168" s="21" t="s">
-        <v>354</v>
+        <v>119</v>
       </c>
       <c r="C168" s="21" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="E168" s="4"/>
       <c r="F168" s="5" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="G168" s="4" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="H168" s="4"/>
-      <c r="I168" t="s">
-        <v>362</v>
-      </c>
+      <c r="I168" s="4"/>
       <c r="J168" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L168" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M168" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="169" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M168"/>
+    </row>
+    <row r="169" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B169" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C169" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="C169" s="21" t="s">
-        <v>136</v>
-      </c>
       <c r="D169" s="5" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E169" s="4"/>
       <c r="F169" s="5" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="H169" s="4"/>
       <c r="I169" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="J169" s="4" t="s">
         <v>20</v>
@@ -7943,62 +7940,66 @@
         <v>21</v>
       </c>
       <c r="M169" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="170" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="170" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B170" s="21" t="s">
-        <v>127</v>
+        <v>354</v>
       </c>
       <c r="C170" s="21" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="E170" s="4"/>
       <c r="F170" s="5" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H170" s="4"/>
-      <c r="I170" s="4"/>
+      <c r="I170" t="s">
+        <v>362</v>
+      </c>
       <c r="J170" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L170" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M170"/>
-    </row>
-    <row r="171" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M170" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B171" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="C171" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="C171" s="21" t="s">
-        <v>140</v>
-      </c>
       <c r="D171" s="5" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="E171" s="4"/>
       <c r="F171" s="5" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="G171" s="4" t="s">
         <v>56</v>
       </c>
       <c r="H171" s="4"/>
       <c r="I171" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="J171" s="4" t="s">
         <v>20</v>
@@ -8007,25 +8008,25 @@
         <v>21</v>
       </c>
       <c r="M171" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="172" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="172" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B172" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="C172" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="C172" s="21" t="s">
-        <v>140</v>
-      </c>
       <c r="D172" s="5" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="E172" s="4"/>
       <c r="F172" s="5" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="G172" s="4" t="s">
         <v>35</v>
@@ -8040,7 +8041,7 @@
       </c>
       <c r="M172"/>
     </row>
-    <row r="173" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="4" t="s">
         <v>302</v>
       </c>
@@ -8048,89 +8049,85 @@
         <v>136</v>
       </c>
       <c r="C173" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="D173" s="4" t="s">
-        <v>369</v>
+        <v>140</v>
+      </c>
+      <c r="D173" s="5" t="s">
+        <v>366</v>
       </c>
       <c r="E173" s="4"/>
-      <c r="F173" s="4" t="s">
-        <v>369</v>
+      <c r="F173" s="5" t="s">
+        <v>366</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>152</v>
+        <v>56</v>
       </c>
       <c r="H173" s="4"/>
-      <c r="I173" s="4" t="s">
-        <v>370</v>
+      <c r="I173" t="s">
+        <v>367</v>
       </c>
       <c r="J173" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L173" s="6" t="s">
-        <v>149</v>
+        <v>21</v>
       </c>
       <c r="M173" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="174" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="174" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B174" s="21" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="C174" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="D174" s="4" t="s">
-        <v>371</v>
+      <c r="D174" s="5" t="s">
+        <v>368</v>
       </c>
       <c r="E174" s="4"/>
-      <c r="F174" s="4" t="s">
-        <v>371</v>
+      <c r="F174" s="5" t="s">
+        <v>368</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>162</v>
+        <v>35</v>
       </c>
       <c r="H174" s="4"/>
-      <c r="I174" s="4" t="s">
-        <v>372</v>
-      </c>
+      <c r="I174" s="4"/>
       <c r="J174" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L174" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="M174" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="175" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+      <c r="M174"/>
+    </row>
+    <row r="175" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="B175" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="C175" s="12" t="s">
-        <v>373</v>
+      <c r="B175" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="C175" s="21" t="s">
+        <v>134</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="E175" s="4"/>
       <c r="F175" s="4" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="G175" s="4" t="s">
         <v>152</v>
       </c>
       <c r="H175" s="4"/>
       <c r="I175" s="4" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="J175" s="4" t="s">
         <v>20</v>
@@ -8138,71 +8135,79 @@
       <c r="L175" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="M175" s="5" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="176" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M175" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="176" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B176" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="C176" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="C176" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="D176" s="5" t="s">
-        <v>377</v>
+      <c r="D176" s="4" t="s">
+        <v>371</v>
       </c>
       <c r="E176" s="4"/>
-      <c r="F176" s="5" t="s">
-        <v>377</v>
+      <c r="F176" s="4" t="s">
+        <v>371</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>28</v>
+        <v>162</v>
       </c>
       <c r="H176" s="4"/>
-      <c r="I176" s="4"/>
+      <c r="I176" s="4" t="s">
+        <v>372</v>
+      </c>
       <c r="J176" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L176" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M176"/>
-    </row>
-    <row r="177" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>149</v>
+      </c>
+      <c r="M176" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="177" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="B177" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="C177" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="D177" s="5" t="s">
-        <v>378</v>
+      <c r="B177" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="C177" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="D177" s="4" t="s">
+        <v>374</v>
       </c>
       <c r="E177" s="4"/>
-      <c r="F177" s="5" t="s">
-        <v>378</v>
+      <c r="F177" s="4" t="s">
+        <v>374</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>31</v>
+        <v>152</v>
       </c>
       <c r="H177" s="4"/>
-      <c r="I177" s="4"/>
+      <c r="I177" s="4" t="s">
+        <v>375</v>
+      </c>
       <c r="J177" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L177" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M177"/>
-    </row>
-    <row r="178" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+        <v>149</v>
+      </c>
+      <c r="M177" s="5" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="178" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="4" t="s">
         <v>302</v>
       </c>
@@ -8213,30 +8218,26 @@
         <v>144</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E178" s="4"/>
       <c r="F178" s="5" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="H178" s="4"/>
-      <c r="I178" s="4" t="s">
-        <v>380</v>
-      </c>
+      <c r="I178" s="4"/>
       <c r="J178" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L178" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M178" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="179" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M178"/>
+    </row>
+    <row r="179" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="4" t="s">
         <v>302</v>
       </c>
@@ -8247,14 +8248,14 @@
         <v>144</v>
       </c>
       <c r="D179" s="5" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E179" s="4"/>
       <c r="F179" s="5" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H179" s="4"/>
       <c r="I179" s="4"/>
@@ -8266,7 +8267,7 @@
       </c>
       <c r="M179"/>
     </row>
-    <row r="180" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="4" t="s">
         <v>302</v>
       </c>
@@ -8274,29 +8275,33 @@
         <v>140</v>
       </c>
       <c r="C180" s="21" t="s">
-        <v>16</v>
+        <v>144</v>
       </c>
       <c r="D180" s="5" t="s">
-        <v>18</v>
+        <v>379</v>
       </c>
       <c r="E180" s="4"/>
       <c r="F180" s="5" t="s">
-        <v>18</v>
+        <v>379</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="H180" s="4"/>
-      <c r="I180" s="4"/>
+      <c r="I180" s="4" t="s">
+        <v>380</v>
+      </c>
       <c r="J180" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L180" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M180"/>
-    </row>
-    <row r="181" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M180" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="181" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="4" t="s">
         <v>302</v>
       </c>
@@ -8304,117 +8309,115 @@
         <v>140</v>
       </c>
       <c r="C181" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="D181" s="4" t="s">
-        <v>383</v>
+        <v>144</v>
+      </c>
+      <c r="D181" s="5" t="s">
+        <v>382</v>
       </c>
       <c r="E181" s="4"/>
-      <c r="F181" s="4" t="s">
-        <v>383</v>
+      <c r="F181" s="5" t="s">
+        <v>382</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="H181" s="4"/>
-      <c r="I181" s="4" t="s">
-        <v>384</v>
-      </c>
+      <c r="I181" s="4"/>
       <c r="J181" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L181" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="M181" s="23" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="182" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L181" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M181"/>
+    </row>
+    <row r="182" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B182" s="21" t="s">
-        <v>373</v>
+        <v>140</v>
       </c>
       <c r="C182" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="D182" s="4" t="s">
-        <v>385</v>
+        <v>16</v>
+      </c>
+      <c r="D182" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="E182" s="4"/>
-      <c r="F182" s="4" t="s">
-        <v>385</v>
+      <c r="F182" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>162</v>
+        <v>19</v>
       </c>
       <c r="H182" s="4"/>
-      <c r="I182" s="4" t="s">
-        <v>386</v>
-      </c>
+      <c r="I182" s="4"/>
       <c r="J182" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L182" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="M182" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="183" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+      <c r="M182"/>
+    </row>
+    <row r="183" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B183" s="21" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="C183" s="21" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="E183" s="4"/>
-      <c r="F183"/>
+      <c r="F183" s="4" t="s">
+        <v>383</v>
+      </c>
       <c r="G183" s="4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H183" s="4"/>
-      <c r="I183" s="4"/>
+      <c r="I183" s="4" t="s">
+        <v>384</v>
+      </c>
       <c r="J183" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L183" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M183"/>
-    </row>
-    <row r="184" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L183" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="M183" s="23" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="184" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B184" s="21" t="s">
-        <v>154</v>
+        <v>373</v>
       </c>
       <c r="C184" s="21" t="s">
-        <v>181</v>
+        <v>144</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="E184" s="4"/>
       <c r="F184" s="4" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="G184" s="4" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="H184" s="4"/>
       <c r="I184" s="4" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="J184" s="4" t="s">
         <v>20</v>
@@ -8423,10 +8426,10 @@
         <v>149</v>
       </c>
       <c r="M184" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="185" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="185" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="4" t="s">
         <v>302</v>
       </c>
@@ -8434,97 +8437,95 @@
         <v>154</v>
       </c>
       <c r="C185" s="21" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="E185" s="4"/>
-      <c r="F185" s="4" t="s">
-        <v>390</v>
-      </c>
+      <c r="F185"/>
       <c r="G185" s="4" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="H185" s="4"/>
-      <c r="I185" s="4" t="s">
-        <v>391</v>
-      </c>
+      <c r="I185" s="4"/>
       <c r="J185" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L185" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="M185" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="186" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+      <c r="M185"/>
+    </row>
+    <row r="186" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B186" s="21" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="C186" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D186" s="5" t="s">
-        <v>392</v>
+        <v>181</v>
+      </c>
+      <c r="D186" s="4" t="s">
+        <v>388</v>
       </c>
       <c r="E186" s="4"/>
-      <c r="F186" s="5" t="s">
-        <v>392</v>
+      <c r="F186" s="4" t="s">
+        <v>388</v>
       </c>
       <c r="G186" s="4" t="s">
-        <v>39</v>
+        <v>147</v>
       </c>
       <c r="H186" s="4"/>
-      <c r="I186" t="s">
-        <v>393</v>
+      <c r="I186" s="4" t="s">
+        <v>389</v>
       </c>
       <c r="J186" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L186" s="6" t="s">
-        <v>21</v>
+        <v>149</v>
       </c>
       <c r="M186" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="187" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="187" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B187" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="C187" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="C187" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D187" s="5" t="s">
-        <v>395</v>
+      <c r="D187" s="4" t="s">
+        <v>390</v>
       </c>
       <c r="E187" s="4"/>
-      <c r="F187" s="5" t="s">
-        <v>395</v>
+      <c r="F187" s="4" t="s">
+        <v>390</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>28</v>
+        <v>152</v>
       </c>
       <c r="H187" s="4"/>
-      <c r="I187" s="4"/>
+      <c r="I187" s="4" t="s">
+        <v>391</v>
+      </c>
       <c r="J187" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L187" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M187"/>
-    </row>
-    <row r="188" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>149</v>
+      </c>
+      <c r="M187" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="188" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="4" t="s">
         <v>302</v>
       </c>
@@ -8535,18 +8536,18 @@
         <v>16</v>
       </c>
       <c r="D188" s="5" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="E188" s="4"/>
       <c r="F188" s="5" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="G188" s="4" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H188" s="4"/>
       <c r="I188" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="J188" s="4" t="s">
         <v>20</v>
@@ -8555,10 +8556,10 @@
         <v>21</v>
       </c>
       <c r="M188" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="189" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="189" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="4" t="s">
         <v>302</v>
       </c>
@@ -8569,14 +8570,14 @@
         <v>16</v>
       </c>
       <c r="D189" s="5" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="E189" s="4"/>
       <c r="F189" s="5" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="G189" s="4" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="H189" s="4"/>
       <c r="I189" s="4"/>
@@ -8588,7 +8589,7 @@
       </c>
       <c r="M189"/>
     </row>
-    <row r="190" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="4" t="s">
         <v>302</v>
       </c>
@@ -8599,26 +8600,30 @@
         <v>16</v>
       </c>
       <c r="D190" s="5" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E190" s="4"/>
       <c r="F190" s="5" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="G190" s="4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H190" s="4"/>
-      <c r="I190" s="4"/>
+      <c r="I190" t="s">
+        <v>397</v>
+      </c>
       <c r="J190" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L190" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M190"/>
-    </row>
-    <row r="191" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M190" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="191" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="4" t="s">
         <v>302</v>
       </c>
@@ -8628,96 +8633,88 @@
       <c r="C191" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="D191" s="4" t="s">
-        <v>400</v>
+      <c r="D191" s="5" t="s">
+        <v>398</v>
       </c>
       <c r="E191" s="4"/>
+      <c r="F191" s="5" t="s">
+        <v>398</v>
+      </c>
       <c r="G191" s="4" t="s">
-        <v>170</v>
+        <v>56</v>
       </c>
       <c r="H191" s="4"/>
-      <c r="I191" s="4" t="s">
-        <v>401</v>
-      </c>
+      <c r="I191" s="4"/>
       <c r="J191" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L191" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="M191" s="4" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="192" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L191" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M191"/>
+    </row>
+    <row r="192" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B192" s="21" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="C192" s="21" t="s">
-        <v>403</v>
+        <v>16</v>
       </c>
       <c r="D192" s="5" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="E192" s="4"/>
       <c r="F192" s="5" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="G192" s="4" t="s">
-        <v>194</v>
+        <v>35</v>
       </c>
       <c r="H192" s="4"/>
-      <c r="I192" t="s">
-        <v>405</v>
-      </c>
+      <c r="I192" s="4"/>
       <c r="J192" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L192" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="M192" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="193" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+      <c r="M192"/>
+    </row>
+    <row r="193" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B193" s="21" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="C193" s="21" t="s">
         <v>16</v>
       </c>
       <c r="D193" s="4" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="E193" s="4"/>
-      <c r="F193" s="4" t="s">
-        <v>406</v>
-      </c>
       <c r="G193" s="4" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="H193" s="4"/>
       <c r="I193" s="4" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="J193" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L193" s="6" t="s">
+      <c r="L193" s="27" t="s">
         <v>149</v>
       </c>
-      <c r="M193" s="5" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="194" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M193" s="4" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="194" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="4" t="s">
         <v>302</v>
       </c>
@@ -8725,133 +8722,133 @@
         <v>168</v>
       </c>
       <c r="C194" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D194" s="4" t="s">
-        <v>409</v>
+        <v>403</v>
+      </c>
+      <c r="D194" s="5" t="s">
+        <v>404</v>
       </c>
       <c r="E194" s="4"/>
-      <c r="F194" s="4"/>
+      <c r="F194" s="5" t="s">
+        <v>404</v>
+      </c>
       <c r="G194" s="4" t="s">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c r="H194" s="4"/>
-      <c r="I194" s="4" t="s">
-        <v>410</v>
+      <c r="I194" t="s">
+        <v>405</v>
       </c>
       <c r="J194" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L194" s="6" t="s">
-        <v>149</v>
+        <v>71</v>
       </c>
       <c r="M194" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="195" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="195" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B195" s="21" t="s">
-        <v>411</v>
+        <v>168</v>
       </c>
       <c r="C195" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="D195" s="5" t="s">
-        <v>412</v>
+        <v>16</v>
+      </c>
+      <c r="D195" s="4" t="s">
+        <v>406</v>
       </c>
       <c r="E195" s="4"/>
-      <c r="F195" s="5" t="s">
-        <v>412</v>
+      <c r="F195" s="4" t="s">
+        <v>406</v>
       </c>
       <c r="G195" s="4" t="s">
-        <v>194</v>
+        <v>152</v>
       </c>
       <c r="H195" s="4"/>
-      <c r="I195" t="s">
-        <v>413</v>
+      <c r="I195" s="4" t="s">
+        <v>407</v>
       </c>
       <c r="J195" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L195" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="M195" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="196" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L195" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="M195" s="5" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="196" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B196" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="C196" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C196" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="D196" s="5" t="s">
-        <v>414</v>
+      <c r="D196" s="4" t="s">
+        <v>409</v>
       </c>
       <c r="E196" s="4"/>
-      <c r="F196" s="5" t="s">
-        <v>414</v>
-      </c>
+      <c r="F196" s="4"/>
       <c r="G196" s="4" t="s">
-        <v>39</v>
+        <v>162</v>
       </c>
       <c r="H196" s="4"/>
-      <c r="I196" t="s">
-        <v>415</v>
+      <c r="I196" s="4" t="s">
+        <v>410</v>
       </c>
       <c r="J196" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L196" s="6" t="s">
-        <v>21</v>
+        <v>149</v>
       </c>
       <c r="M196" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="197" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="197" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B197" s="21" t="s">
-        <v>16</v>
+        <v>411</v>
       </c>
       <c r="C197" s="21" t="s">
-        <v>22</v>
+        <v>159</v>
       </c>
       <c r="D197" s="5" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="E197" s="4"/>
       <c r="F197" s="5" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="G197" s="4" t="s">
-        <v>28</v>
+        <v>194</v>
       </c>
       <c r="H197" s="4"/>
       <c r="I197" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="J197" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L197" s="6" t="s">
-        <v>21</v>
+      <c r="L197" s="28" t="s">
+        <v>71</v>
       </c>
       <c r="M197" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="198" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="198" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="4" t="s">
         <v>302</v>
       </c>
@@ -8862,26 +8859,30 @@
         <v>22</v>
       </c>
       <c r="D198" s="5" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="E198" s="4"/>
       <c r="F198" s="5" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="G198" s="4" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H198" s="4"/>
-      <c r="I198" s="4"/>
+      <c r="I198" t="s">
+        <v>415</v>
+      </c>
       <c r="J198" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L198" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M198"/>
-    </row>
-    <row r="199" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M198" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="199" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="4" t="s">
         <v>302</v>
       </c>
@@ -8892,26 +8893,30 @@
         <v>22</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="E199" s="4"/>
       <c r="F199" s="5" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="G199" s="4" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="H199" s="4"/>
-      <c r="I199" s="4"/>
+      <c r="I199" t="s">
+        <v>417</v>
+      </c>
       <c r="J199" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L199" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M199"/>
-    </row>
-    <row r="200" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M199" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="200" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="4" t="s">
         <v>302</v>
       </c>
@@ -8922,14 +8927,14 @@
         <v>22</v>
       </c>
       <c r="D200" s="5" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="E200" s="4"/>
       <c r="F200" s="5" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="G200" s="4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H200" s="4"/>
       <c r="I200" s="4"/>
@@ -8941,7 +8946,7 @@
       </c>
       <c r="M200"/>
     </row>
-    <row r="201" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="4" t="s">
         <v>302</v>
       </c>
@@ -8952,30 +8957,26 @@
         <v>22</v>
       </c>
       <c r="D201" s="5" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E201" s="4"/>
       <c r="F201" s="5" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G201" s="4" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="H201" s="4"/>
-      <c r="I201" t="s">
-        <v>423</v>
-      </c>
+      <c r="I201" s="4"/>
       <c r="J201" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L201" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M201" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="202" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M201"/>
+    </row>
+    <row r="202" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="4" t="s">
         <v>302</v>
       </c>
@@ -8983,17 +8984,17 @@
         <v>16</v>
       </c>
       <c r="C202" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="D202" s="4" t="s">
-        <v>424</v>
+        <v>22</v>
+      </c>
+      <c r="D202" s="5" t="s">
+        <v>421</v>
       </c>
       <c r="E202" s="4"/>
-      <c r="F202" s="4" t="s">
-        <v>425</v>
+      <c r="F202" s="5" t="s">
+        <v>421</v>
       </c>
       <c r="G202" s="4" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="H202" s="4"/>
       <c r="I202" s="4"/>
@@ -9001,101 +9002,97 @@
         <v>20</v>
       </c>
       <c r="L202" s="6" t="s">
-        <v>149</v>
+        <v>21</v>
       </c>
       <c r="M202"/>
     </row>
-    <row r="203" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B203" s="21" t="s">
-        <v>159</v>
+        <v>16</v>
       </c>
       <c r="C203" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="D203" s="4" t="s">
-        <v>426</v>
+      <c r="D203" s="5" t="s">
+        <v>422</v>
       </c>
       <c r="E203" s="4"/>
-      <c r="F203" s="4" t="s">
-        <v>426</v>
+      <c r="F203" s="5" t="s">
+        <v>422</v>
       </c>
       <c r="G203" s="4" t="s">
-        <v>162</v>
+        <v>19</v>
       </c>
       <c r="H203" s="4"/>
-      <c r="I203" s="4" t="s">
-        <v>427</v>
+      <c r="I203" t="s">
+        <v>423</v>
       </c>
       <c r="J203" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L203" s="6" t="s">
-        <v>149</v>
+        <v>21</v>
       </c>
       <c r="M203" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="204" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="204" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B204" s="21" t="s">
-        <v>428</v>
+        <v>16</v>
       </c>
       <c r="C204" s="21" t="s">
         <v>201</v>
       </c>
-      <c r="D204" s="5" t="s">
-        <v>429</v>
+      <c r="D204" s="4" t="s">
+        <v>424</v>
       </c>
       <c r="E204" s="4"/>
-      <c r="F204" s="5" t="s">
-        <v>429</v>
+      <c r="F204" s="4" t="s">
+        <v>425</v>
       </c>
       <c r="G204" s="4" t="s">
-        <v>194</v>
+        <v>147</v>
       </c>
       <c r="H204" s="4"/>
-      <c r="I204" t="s">
-        <v>430</v>
-      </c>
+      <c r="I204" s="4"/>
       <c r="J204" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L204" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="M204" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="205" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+        <v>149</v>
+      </c>
+      <c r="M204"/>
+    </row>
+    <row r="205" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B205" s="21" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="C205" s="21" t="s">
         <v>22</v>
       </c>
       <c r="D205" s="4" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="E205" s="4"/>
       <c r="F205" s="4" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="G205" s="4" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="H205" s="4"/>
       <c r="I205" s="4" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="J205" s="4" t="s">
         <v>20</v>
@@ -9104,70 +9101,78 @@
         <v>149</v>
       </c>
       <c r="M205" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="206" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="206" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B206" s="21" t="s">
-        <v>22</v>
+        <v>428</v>
       </c>
       <c r="C206" s="21" t="s">
-        <v>23</v>
+        <v>201</v>
       </c>
       <c r="D206" s="5" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="E206" s="4"/>
       <c r="F206" s="5" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="G206" s="4" t="s">
-        <v>39</v>
+        <v>194</v>
       </c>
       <c r="H206" s="4"/>
-      <c r="I206" s="4"/>
+      <c r="I206" t="s">
+        <v>430</v>
+      </c>
       <c r="J206" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L206" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M206"/>
-    </row>
-    <row r="207" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+      <c r="M206" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="207" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B207" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="C207" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C207" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="D207" s="5" t="s">
-        <v>435</v>
+      <c r="D207" s="4" t="s">
+        <v>431</v>
       </c>
       <c r="E207" s="4"/>
-      <c r="F207" s="5" t="s">
-        <v>435</v>
+      <c r="F207" s="4" t="s">
+        <v>432</v>
       </c>
       <c r="G207" s="4" t="s">
-        <v>25</v>
+        <v>152</v>
       </c>
       <c r="H207" s="4"/>
-      <c r="I207" s="4"/>
+      <c r="I207" s="4" t="s">
+        <v>433</v>
+      </c>
       <c r="J207" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L207" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M207"/>
-    </row>
-    <row r="208" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>149</v>
+      </c>
+      <c r="M207" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="208" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="4" t="s">
         <v>302</v>
       </c>
@@ -9178,30 +9183,26 @@
         <v>23</v>
       </c>
       <c r="D208" s="5" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E208" s="4"/>
       <c r="F208" s="5" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="G208" s="4" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="H208" s="4"/>
-      <c r="I208" t="s">
-        <v>437</v>
-      </c>
+      <c r="I208" s="4"/>
       <c r="J208" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L208" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M208" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="209" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M208"/>
+    </row>
+    <row r="209" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="4" t="s">
         <v>302</v>
       </c>
@@ -9209,33 +9210,29 @@
         <v>22</v>
       </c>
       <c r="C209" s="21" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D209" s="5" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E209" s="4"/>
       <c r="F209" s="5" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="G209" s="4" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H209" s="4"/>
-      <c r="I209" t="s">
-        <v>439</v>
-      </c>
+      <c r="I209" s="4"/>
       <c r="J209" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L209" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M209" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="210" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M209"/>
+    </row>
+    <row r="210" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="4" t="s">
         <v>302</v>
       </c>
@@ -9246,26 +9243,30 @@
         <v>23</v>
       </c>
       <c r="D210" s="5" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="E210" s="4"/>
       <c r="F210" s="5" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="G210" s="4" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="H210" s="4"/>
-      <c r="I210" s="4"/>
+      <c r="I210" t="s">
+        <v>437</v>
+      </c>
       <c r="J210" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L210" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M210"/>
-    </row>
-    <row r="211" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M210" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="211" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="4" t="s">
         <v>302</v>
       </c>
@@ -9273,29 +9274,33 @@
         <v>22</v>
       </c>
       <c r="C211" s="21" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D211" s="5" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="E211" s="4"/>
       <c r="F211" s="5" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="G211" s="4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H211" s="4"/>
-      <c r="I211" s="4"/>
+      <c r="I211" t="s">
+        <v>439</v>
+      </c>
       <c r="J211" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L211" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M211"/>
-    </row>
-    <row r="212" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M211" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="212" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="4" t="s">
         <v>302</v>
       </c>
@@ -9303,33 +9308,29 @@
         <v>22</v>
       </c>
       <c r="C212" s="21" t="s">
-        <v>443</v>
+        <v>23</v>
       </c>
       <c r="D212" s="5" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E212" s="4"/>
       <c r="F212" s="5" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="G212" s="4" t="s">
-        <v>194</v>
+        <v>56</v>
       </c>
       <c r="H212" s="4"/>
-      <c r="I212" t="s">
-        <v>445</v>
-      </c>
+      <c r="I212" s="4"/>
       <c r="J212" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L212" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="M212" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="213" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L212" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M212"/>
+    </row>
+    <row r="213" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="4" t="s">
         <v>302</v>
       </c>
@@ -9337,17 +9338,17 @@
         <v>22</v>
       </c>
       <c r="C213" s="21" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D213" s="5" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="E213" s="4"/>
       <c r="F213" s="5" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="G213" s="4" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="H213" s="4"/>
       <c r="I213" s="4"/>
@@ -9359,7 +9360,7 @@
       </c>
       <c r="M213"/>
     </row>
-    <row r="214" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="4" t="s">
         <v>302</v>
       </c>
@@ -9367,33 +9368,33 @@
         <v>22</v>
       </c>
       <c r="C214" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="D214" s="4" t="s">
-        <v>447</v>
+        <v>443</v>
+      </c>
+      <c r="D214" s="5" t="s">
+        <v>444</v>
       </c>
       <c r="E214" s="4"/>
-      <c r="F214" s="4" t="s">
-        <v>447</v>
+      <c r="F214" s="5" t="s">
+        <v>444</v>
       </c>
       <c r="G214" s="4" t="s">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="H214" s="4"/>
-      <c r="I214" s="4" t="s">
-        <v>448</v>
+      <c r="I214" t="s">
+        <v>445</v>
       </c>
       <c r="J214" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L214" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="M214" s="23" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="215" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L214" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="M214" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="215" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="4" t="s">
         <v>302</v>
       </c>
@@ -9403,15 +9404,15 @@
       <c r="C215" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="D215" s="22" t="s">
-        <v>449</v>
+      <c r="D215" s="5" t="s">
+        <v>446</v>
       </c>
       <c r="E215" s="4"/>
-      <c r="F215" s="22" t="s">
-        <v>449</v>
+      <c r="F215" s="5" t="s">
+        <v>446</v>
       </c>
       <c r="G215" s="4" t="s">
-        <v>173</v>
+        <v>19</v>
       </c>
       <c r="H215" s="4"/>
       <c r="I215" s="4"/>
@@ -9423,59 +9424,59 @@
       </c>
       <c r="M215"/>
     </row>
-    <row r="216" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B216" s="21" t="s">
-        <v>450</v>
+        <v>22</v>
       </c>
       <c r="C216" s="21" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D216" s="4" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="E216" s="4"/>
       <c r="F216" s="4" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="G216" s="4" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="H216" s="4"/>
       <c r="I216" s="4" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="J216" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L216" s="6" t="s">
+      <c r="L216" s="27" t="s">
         <v>149</v>
       </c>
-      <c r="M216" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="217" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M216" s="23" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="217" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B217" s="21" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C217" s="21" t="s">
-        <v>234</v>
-      </c>
-      <c r="D217" s="5" t="s">
-        <v>454</v>
+        <v>29</v>
+      </c>
+      <c r="D217" s="22" t="s">
+        <v>449</v>
       </c>
       <c r="E217" s="4"/>
-      <c r="F217" s="5" t="s">
-        <v>454</v>
+      <c r="F217" s="22" t="s">
+        <v>449</v>
       </c>
       <c r="G217" s="4" t="s">
-        <v>49</v>
+        <v>173</v>
       </c>
       <c r="H217" s="4"/>
       <c r="I217" s="4"/>
@@ -9483,169 +9484,173 @@
         <v>20</v>
       </c>
       <c r="L217" s="6" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="M217"/>
     </row>
-    <row r="218" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B218" s="21" t="s">
-        <v>17</v>
+        <v>450</v>
       </c>
       <c r="C218" s="21" t="s">
-        <v>455</v>
-      </c>
-      <c r="D218" s="5" t="s">
-        <v>456</v>
+        <v>29</v>
+      </c>
+      <c r="D218" s="4" t="s">
+        <v>451</v>
       </c>
       <c r="E218" s="4"/>
-      <c r="F218" s="5" t="s">
-        <v>456</v>
+      <c r="F218" s="4" t="s">
+        <v>452</v>
       </c>
       <c r="G218" s="4" t="s">
-        <v>194</v>
+        <v>152</v>
       </c>
       <c r="H218" s="4"/>
-      <c r="I218" s="4"/>
+      <c r="I218" s="4" t="s">
+        <v>453</v>
+      </c>
       <c r="J218" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L218" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="M218"/>
-    </row>
-    <row r="219" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>149</v>
+      </c>
+      <c r="M218" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="219" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B219" s="21" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C219" s="21" t="s">
-        <v>263</v>
+        <v>234</v>
       </c>
       <c r="D219" s="5" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="E219" s="4"/>
       <c r="F219" s="5" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="G219" s="4" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="H219" s="4"/>
-      <c r="I219" t="s">
-        <v>458</v>
-      </c>
+      <c r="I219" s="4"/>
       <c r="J219" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L219" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M219" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="220" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+      <c r="M219"/>
+    </row>
+    <row r="220" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B220" s="21" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C220" s="21" t="s">
-        <v>43</v>
+        <v>455</v>
       </c>
       <c r="D220" s="5" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="E220" s="4"/>
       <c r="F220" s="5" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="G220" s="4" t="s">
-        <v>19</v>
+        <v>194</v>
       </c>
       <c r="H220" s="4"/>
-      <c r="I220" t="s">
-        <v>461</v>
-      </c>
+      <c r="I220" s="4"/>
       <c r="J220" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L220" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M220" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="221" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+      <c r="M220"/>
+    </row>
+    <row r="221" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B221" s="21" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C221" s="21" t="s">
-        <v>47</v>
+        <v>263</v>
       </c>
       <c r="D221" s="5" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="E221" s="4"/>
       <c r="F221" s="5" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="G221" s="4" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="H221" s="4"/>
-      <c r="I221" s="4"/>
+      <c r="I221" t="s">
+        <v>458</v>
+      </c>
       <c r="J221" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L221" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M221"/>
-    </row>
-    <row r="222" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M221" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="222" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B222" s="21" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C222" s="21" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D222" s="5" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="E222" s="4"/>
       <c r="F222" s="5" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="G222" s="4" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="H222" s="4"/>
-      <c r="I222" s="4"/>
+      <c r="I222" t="s">
+        <v>461</v>
+      </c>
       <c r="J222" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L222" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M222"/>
-    </row>
-    <row r="223" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M222" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="223" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="4" t="s">
         <v>302</v>
       </c>
@@ -9655,31 +9660,27 @@
       <c r="C223" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="D223" s="22" t="s">
-        <v>668</v>
+      <c r="D223" s="5" t="s">
+        <v>463</v>
       </c>
       <c r="E223" s="4"/>
-      <c r="F223" s="22" t="s">
-        <v>668</v>
+      <c r="F223" s="5" t="s">
+        <v>463</v>
       </c>
       <c r="G223" s="4" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="H223" s="4"/>
-      <c r="I223" t="s">
-        <v>465</v>
-      </c>
+      <c r="I223" s="4"/>
       <c r="J223" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L223" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="M223" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="224" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+      <c r="M223"/>
+    </row>
+    <row r="224" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="4" t="s">
         <v>302</v>
       </c>
@@ -9690,30 +9691,26 @@
         <v>47</v>
       </c>
       <c r="D224" s="5" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E224" s="4"/>
       <c r="F224" s="5" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="G224" s="4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H224" s="4"/>
-      <c r="I224" t="s">
-        <v>467</v>
-      </c>
+      <c r="I224" s="4"/>
       <c r="J224" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L224" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M224" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="225" spans="1:13" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M224"/>
+    </row>
+    <row r="225" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="4" t="s">
         <v>302</v>
       </c>
@@ -9721,81 +9718,85 @@
         <v>23</v>
       </c>
       <c r="C225" s="21" t="s">
-        <v>468</v>
-      </c>
-      <c r="D225" s="5" t="s">
-        <v>469</v>
+        <v>47</v>
+      </c>
+      <c r="D225" s="22" t="s">
+        <v>668</v>
       </c>
       <c r="E225" s="4"/>
-      <c r="F225" s="5" t="s">
-        <v>469</v>
+      <c r="F225" s="22" t="s">
+        <v>668</v>
       </c>
       <c r="G225" s="4" t="s">
-        <v>258</v>
+        <v>56</v>
       </c>
       <c r="H225" s="4"/>
-      <c r="I225" s="4"/>
+      <c r="I225" t="s">
+        <v>465</v>
+      </c>
       <c r="J225" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L225" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M225"/>
-    </row>
-    <row r="226" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+      <c r="M225" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="226" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B226" s="21" t="s">
-        <v>470</v>
+        <v>23</v>
       </c>
       <c r="C226" s="21" t="s">
-        <v>471</v>
+        <v>47</v>
       </c>
       <c r="D226" s="5" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="E226" s="4"/>
       <c r="F226" s="5" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="G226" s="4" t="s">
-        <v>194</v>
+        <v>35</v>
       </c>
       <c r="H226" s="4"/>
       <c r="I226" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="J226" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L226" s="6" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="M226" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="227" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="227" spans="1:13" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B227" s="21" t="s">
-        <v>262</v>
+        <v>23</v>
       </c>
       <c r="C227" s="21" t="s">
-        <v>43</v>
+        <v>468</v>
       </c>
       <c r="D227" s="5" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="E227" s="4"/>
       <c r="F227" s="5" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="G227" s="4" t="s">
-        <v>49</v>
+        <v>258</v>
       </c>
       <c r="H227" s="4"/>
       <c r="I227" s="4"/>
@@ -9803,191 +9804,191 @@
         <v>20</v>
       </c>
       <c r="L227" s="6" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="M227"/>
     </row>
-    <row r="228" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B228" s="21" t="s">
-        <v>37</v>
+        <v>470</v>
       </c>
       <c r="C228" s="21" t="s">
-        <v>61</v>
+        <v>471</v>
       </c>
       <c r="D228" s="5" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="E228" s="4"/>
       <c r="F228" s="5" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="G228" s="4" t="s">
-        <v>25</v>
+        <v>194</v>
       </c>
       <c r="H228" s="4"/>
-      <c r="I228" s="4"/>
+      <c r="I228" t="s">
+        <v>473</v>
+      </c>
       <c r="J228" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L228" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M228"/>
-    </row>
-    <row r="229" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+      <c r="M228" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="229" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B229" s="21" t="s">
-        <v>37</v>
+        <v>262</v>
       </c>
       <c r="C229" s="21" t="s">
-        <v>477</v>
-      </c>
-      <c r="D229" s="4" t="s">
-        <v>478</v>
+        <v>43</v>
+      </c>
+      <c r="D229" s="5" t="s">
+        <v>475</v>
       </c>
       <c r="E229" s="4"/>
-      <c r="F229" s="4" t="s">
-        <v>478</v>
+      <c r="F229" s="5" t="s">
+        <v>475</v>
       </c>
       <c r="G229" s="4" t="s">
-        <v>170</v>
+        <v>49</v>
       </c>
       <c r="H229" s="4"/>
-      <c r="I229" s="4" t="s">
-        <v>479</v>
-      </c>
+      <c r="I229" s="4"/>
       <c r="J229" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L229" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="M229" s="4" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="230" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L229" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="M229"/>
+    </row>
+    <row r="230" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B230" s="21" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C230" s="21" t="s">
         <v>61</v>
       </c>
       <c r="D230" s="5" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="E230" s="4"/>
       <c r="F230" s="5" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="G230" s="4" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H230" s="4"/>
-      <c r="I230" t="s">
-        <v>482</v>
-      </c>
+      <c r="I230" s="4"/>
       <c r="J230" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L230" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M230" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="231" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M230"/>
+    </row>
+    <row r="231" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B231" s="21" t="s">
-        <v>263</v>
+        <v>37</v>
       </c>
       <c r="C231" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="D231" s="5" t="s">
-        <v>484</v>
+        <v>477</v>
+      </c>
+      <c r="D231" s="4" t="s">
+        <v>478</v>
       </c>
       <c r="E231" s="4"/>
-      <c r="F231" s="5" t="s">
-        <v>484</v>
+      <c r="F231" s="4" t="s">
+        <v>478</v>
       </c>
       <c r="G231" s="4" t="s">
-        <v>31</v>
+        <v>170</v>
       </c>
       <c r="H231" s="4"/>
-      <c r="I231" s="4"/>
+      <c r="I231" s="4" t="s">
+        <v>479</v>
+      </c>
       <c r="J231" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L231" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M231"/>
-    </row>
-    <row r="232" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L231" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="M231" s="4" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="232" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B232" s="21" t="s">
-        <v>263</v>
+        <v>43</v>
       </c>
       <c r="C232" s="21" t="s">
-        <v>485</v>
+        <v>61</v>
       </c>
       <c r="D232" s="5" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="E232" s="4"/>
       <c r="F232" s="5" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="G232" s="4" t="s">
-        <v>194</v>
+        <v>19</v>
       </c>
       <c r="H232" s="4"/>
       <c r="I232" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="J232" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L232" s="6" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="M232" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="233" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="233" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B233" s="21" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="C233" s="21" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D233" s="5" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="E233" s="4"/>
       <c r="F233" s="5" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="G233" s="4" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="H233" s="4"/>
       <c r="I233" s="4"/>
@@ -9995,63 +9996,63 @@
         <v>20</v>
       </c>
       <c r="L233" s="6" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="M233"/>
     </row>
-    <row r="234" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B234" s="21" t="s">
-        <v>47</v>
+        <v>263</v>
       </c>
       <c r="C234" s="21" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="D234" s="5" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="E234" s="4"/>
       <c r="F234" s="5" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="G234" s="4" t="s">
-        <v>39</v>
+        <v>194</v>
       </c>
       <c r="H234" s="4"/>
       <c r="I234" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="J234" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L234" s="6" t="s">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="M234" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="235" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="235" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B235" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="C235" s="12" t="s">
-        <v>490</v>
+        <v>256</v>
+      </c>
+      <c r="C235" s="21" t="s">
+        <v>61</v>
       </c>
       <c r="D235" s="5" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="E235" s="4"/>
       <c r="F235" s="5" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="G235" s="4" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="H235" s="4"/>
       <c r="I235" s="4"/>
@@ -10059,11 +10060,11 @@
         <v>20</v>
       </c>
       <c r="L235" s="6" t="s">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="M235"/>
     </row>
-    <row r="236" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:13" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="4" t="s">
         <v>302</v>
       </c>
@@ -10074,44 +10075,48 @@
         <v>490</v>
       </c>
       <c r="D236" s="5" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="E236" s="4"/>
       <c r="F236" s="5" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="G236" s="4" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="H236" s="4"/>
-      <c r="I236"/>
+      <c r="I236" t="s">
+        <v>492</v>
+      </c>
       <c r="J236" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L236" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M236"/>
-    </row>
-    <row r="237" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M236" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="237" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B237" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C237" s="21" t="s">
+      <c r="C237" s="12" t="s">
         <v>490</v>
       </c>
       <c r="D237" s="5" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E237" s="4"/>
       <c r="F237" s="5" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="G237" s="4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H237" s="4"/>
       <c r="I237" s="4"/>
@@ -10123,89 +10128,85 @@
       </c>
       <c r="M237"/>
     </row>
-    <row r="238" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:13" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B238" s="21" t="s">
-        <v>496</v>
+        <v>47</v>
       </c>
       <c r="C238" s="21" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="D238" s="5" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="E238" s="4"/>
       <c r="F238" s="5" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="G238" s="4" t="s">
-        <v>194</v>
+        <v>56</v>
       </c>
       <c r="H238" s="4"/>
-      <c r="I238" s="4"/>
+      <c r="I238"/>
       <c r="J238" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L238" s="6" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="M238"/>
     </row>
-    <row r="239" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B239" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="C239" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C239" s="21" t="s">
         <v>490</v>
       </c>
       <c r="D239" s="5" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="E239" s="4"/>
       <c r="F239" s="5" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="G239" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H239" s="4"/>
-      <c r="I239" s="4" t="s">
-        <v>500</v>
-      </c>
+      <c r="I239" s="4"/>
       <c r="J239" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L239" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="M239" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="240" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+      <c r="M239"/>
+    </row>
+    <row r="240" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B240" s="21" t="s">
-        <v>61</v>
+        <v>496</v>
       </c>
       <c r="C240" s="21" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="D240" s="5" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="E240" s="4"/>
       <c r="F240" s="5" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="G240" s="4" t="s">
-        <v>19</v>
+        <v>194</v>
       </c>
       <c r="H240" s="4"/>
       <c r="I240" s="4"/>
@@ -10213,195 +10214,195 @@
         <v>20</v>
       </c>
       <c r="L240" s="6" t="s">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="M240"/>
     </row>
-    <row r="241" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B241" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="C241" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C241" s="12" t="s">
         <v>490</v>
       </c>
       <c r="D241" s="5" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="E241" s="4"/>
       <c r="F241" s="5" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="G241" s="4" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="H241" s="4"/>
-      <c r="I241" s="4"/>
+      <c r="I241" s="4" t="s">
+        <v>500</v>
+      </c>
       <c r="J241" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L241" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="M241"/>
-    </row>
-    <row r="242" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M241" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="242" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B242" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="C242" s="12" t="s">
-        <v>477</v>
+        <v>61</v>
+      </c>
+      <c r="C242" s="21" t="s">
+        <v>490</v>
       </c>
       <c r="D242" s="5" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="E242" s="4"/>
       <c r="F242" s="5" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="G242" s="4" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="H242" s="4"/>
-      <c r="I242" s="4" t="s">
-        <v>504</v>
-      </c>
+      <c r="I242" s="4"/>
       <c r="J242" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L242" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M242" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="243" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A243" s="13" t="s">
+      <c r="M242"/>
+    </row>
+    <row r="243" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A243" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="B243" s="33" t="s">
-        <v>292</v>
-      </c>
-      <c r="C243" s="32" t="s">
+      <c r="B243" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="C243" s="21" t="s">
         <v>490</v>
       </c>
       <c r="D243" s="5" t="s">
-        <v>505</v>
-      </c>
-      <c r="E243" s="13"/>
+        <v>502</v>
+      </c>
+      <c r="E243" s="4"/>
       <c r="F243" s="5" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="G243" s="4" t="s">
-        <v>194</v>
+        <v>49</v>
       </c>
       <c r="H243" s="4"/>
-      <c r="I243" t="s">
-        <v>506</v>
-      </c>
+      <c r="I243" s="4"/>
       <c r="J243" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L243" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="M243" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="244" spans="1:13" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A244" s="10" t="s">
-        <v>507</v>
+      <c r="M243"/>
+    </row>
+    <row r="244" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A244" s="4" t="s">
+        <v>302</v>
       </c>
       <c r="B244" s="21" t="s">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="C244" s="12" t="s">
-        <v>90</v>
+        <v>477</v>
       </c>
       <c r="D244" s="5" t="s">
-        <v>508</v>
-      </c>
-      <c r="E244" s="8"/>
-      <c r="F244" s="16" t="s">
-        <v>508</v>
-      </c>
-      <c r="G244" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="H244" s="8"/>
-      <c r="I244" s="19"/>
-      <c r="J244" s="8" t="s">
+        <v>503</v>
+      </c>
+      <c r="E244" s="4"/>
+      <c r="F244" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="G244" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H244" s="4"/>
+      <c r="I244" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="J244" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L244" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M244"/>
-    </row>
-    <row r="245" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A245" s="4" t="s">
-        <v>507</v>
-      </c>
-      <c r="B245" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="C245" s="21" t="s">
-        <v>90</v>
+      <c r="M244" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="245" spans="1:13" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A245" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="B245" s="33" t="s">
+        <v>292</v>
+      </c>
+      <c r="C245" s="32" t="s">
+        <v>490</v>
       </c>
       <c r="D245" s="5" t="s">
-        <v>509</v>
-      </c>
-      <c r="E245" s="4"/>
+        <v>505</v>
+      </c>
+      <c r="E245" s="13"/>
       <c r="F245" s="5" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="G245" s="4" t="s">
-        <v>25</v>
+        <v>194</v>
       </c>
       <c r="H245" s="4"/>
       <c r="I245" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="J245" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L245" s="6" t="s">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="M245" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="246" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A246" s="4" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="246" spans="1:13" ht="30" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A246" s="10" t="s">
         <v>507</v>
       </c>
       <c r="B246" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="C246" s="21" t="s">
+      <c r="C246" s="12" t="s">
         <v>90</v>
       </c>
       <c r="D246" s="5" t="s">
-        <v>511</v>
-      </c>
-      <c r="E246" s="4"/>
-      <c r="F246" s="5" t="s">
-        <v>511</v>
-      </c>
-      <c r="G246" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H246" s="4"/>
-      <c r="I246" s="4"/>
-      <c r="J246" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="E246" s="8"/>
+      <c r="F246" s="16" t="s">
+        <v>508</v>
+      </c>
+      <c r="G246" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H246" s="8"/>
+      <c r="I246" s="19"/>
+      <c r="J246" s="8" t="s">
         <v>20</v>
       </c>
       <c r="L246" s="6" t="s">
@@ -10409,7 +10410,7 @@
       </c>
       <c r="M246"/>
     </row>
-    <row r="247" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="4" t="s">
         <v>507</v>
       </c>
@@ -10417,29 +10418,33 @@
         <v>89</v>
       </c>
       <c r="C247" s="21" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D247" s="5" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="E247" s="4"/>
       <c r="F247" s="5" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="G247" s="4" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="H247" s="4"/>
-      <c r="I247" s="4"/>
+      <c r="I247" t="s">
+        <v>510</v>
+      </c>
       <c r="J247" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L247" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M247"/>
-    </row>
-    <row r="248" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M247" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="248" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="4" t="s">
         <v>507</v>
       </c>
@@ -10450,14 +10455,14 @@
         <v>90</v>
       </c>
       <c r="D248" s="5" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E248" s="4"/>
       <c r="F248" s="5" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="G248" s="4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H248" s="4"/>
       <c r="I248" s="4"/>
@@ -10469,7 +10474,7 @@
       </c>
       <c r="M248"/>
     </row>
-    <row r="249" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="4" t="s">
         <v>507</v>
       </c>
@@ -10477,141 +10482,141 @@
         <v>89</v>
       </c>
       <c r="C249" s="21" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D249" s="5" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E249" s="4"/>
       <c r="F249" s="5" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="G249" s="4" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="H249" s="4"/>
-      <c r="I249" t="s">
-        <v>515</v>
-      </c>
+      <c r="I249" s="4"/>
       <c r="J249" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L249" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M249" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="250" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M249"/>
+    </row>
+    <row r="250" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B250" s="21" t="s">
-        <v>312</v>
+        <v>89</v>
       </c>
       <c r="C250" s="21" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D250" s="5" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="E250" s="4"/>
       <c r="F250" s="5" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="G250" s="4" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="H250" s="4"/>
       <c r="I250" s="4"/>
       <c r="J250" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L250" s="28" t="s">
+      <c r="L250" s="6" t="s">
         <v>21</v>
       </c>
       <c r="M250"/>
     </row>
-    <row r="251" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B251" s="21" t="s">
-        <v>315</v>
+        <v>89</v>
       </c>
       <c r="C251" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="D251" s="22" t="s">
-        <v>672</v>
+        <v>95</v>
+      </c>
+      <c r="D251" s="5" t="s">
+        <v>514</v>
       </c>
       <c r="E251" s="4"/>
       <c r="F251" s="5" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="G251" s="4" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="H251" s="4"/>
-      <c r="I251" s="4"/>
+      <c r="I251" t="s">
+        <v>515</v>
+      </c>
       <c r="J251" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L251" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M251"/>
-    </row>
-    <row r="252" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M251" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="252" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B252" s="21" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C252" s="21" t="s">
         <v>95</v>
       </c>
       <c r="D252" s="5" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E252" s="4"/>
       <c r="F252" s="5" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="G252" s="4" t="s">
-        <v>194</v>
+        <v>49</v>
       </c>
       <c r="H252" s="4"/>
       <c r="I252" s="4"/>
       <c r="J252" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L252" s="6" t="s">
-        <v>71</v>
+      <c r="L252" s="28" t="s">
+        <v>21</v>
       </c>
       <c r="M252"/>
     </row>
-    <row r="253" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B253" s="21" t="s">
-        <v>98</v>
+        <v>315</v>
       </c>
       <c r="C253" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="D253" s="5" t="s">
-        <v>519</v>
+        <v>90</v>
+      </c>
+      <c r="D253" s="22" t="s">
+        <v>672</v>
       </c>
       <c r="E253" s="4"/>
       <c r="F253" s="5" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="G253" s="4" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="H253" s="4"/>
       <c r="I253" s="4"/>
@@ -10623,59 +10628,55 @@
       </c>
       <c r="M253"/>
     </row>
-    <row r="254" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B254" s="21" t="s">
-        <v>98</v>
+        <v>315</v>
       </c>
       <c r="C254" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="D254" s="4" t="s">
-        <v>520</v>
+        <v>95</v>
+      </c>
+      <c r="D254" s="5" t="s">
+        <v>518</v>
       </c>
       <c r="E254" s="4"/>
-      <c r="F254" s="4" t="s">
-        <v>520</v>
+      <c r="F254" s="5" t="s">
+        <v>518</v>
       </c>
       <c r="G254" s="4" t="s">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="H254" s="4"/>
-      <c r="I254" s="23" t="s">
-        <v>521</v>
-      </c>
+      <c r="I254" s="4"/>
       <c r="J254" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L254" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="M254" s="23" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="255" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L254" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="M254"/>
+    </row>
+    <row r="255" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B255" s="21" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C255" s="21" t="s">
         <v>104</v>
       </c>
       <c r="D255" s="5" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="E255" s="4"/>
       <c r="F255" s="5" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="G255" s="4" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H255" s="4"/>
       <c r="I255" s="4"/>
@@ -10687,55 +10688,59 @@
       </c>
       <c r="M255"/>
     </row>
-    <row r="256" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B256" s="21" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C256" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="D256" s="5" t="s">
-        <v>523</v>
+        <v>115</v>
+      </c>
+      <c r="D256" s="4" t="s">
+        <v>520</v>
       </c>
       <c r="E256" s="4"/>
-      <c r="F256" s="5" t="s">
-        <v>523</v>
+      <c r="F256" s="4" t="s">
+        <v>520</v>
       </c>
       <c r="G256" s="4" t="s">
-        <v>19</v>
+        <v>170</v>
       </c>
       <c r="H256" s="4"/>
-      <c r="I256" s="4"/>
+      <c r="I256" s="23" t="s">
+        <v>521</v>
+      </c>
       <c r="J256" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L256" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M256"/>
-    </row>
-    <row r="257" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L256" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="M256" s="23" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="257" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B257" s="21" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C257" s="21" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D257" s="5" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="E257" s="4"/>
       <c r="F257" s="5" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="G257" s="4" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H257" s="4"/>
       <c r="I257" s="4"/>
@@ -10747,41 +10752,37 @@
       </c>
       <c r="M257"/>
     </row>
-    <row r="258" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B258" s="21" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C258" s="21" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D258" s="5" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="E258" s="4"/>
       <c r="F258" s="5" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="G258" s="4" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H258" s="4"/>
-      <c r="I258" t="s">
-        <v>526</v>
-      </c>
+      <c r="I258" s="4"/>
       <c r="J258" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L258" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M258" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="259" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M258"/>
+    </row>
+    <row r="259" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="4" t="s">
         <v>507</v>
       </c>
@@ -10792,14 +10793,14 @@
         <v>106</v>
       </c>
       <c r="D259" s="5" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="E259" s="4"/>
       <c r="F259" s="5" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="G259" s="4" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="H259" s="4"/>
       <c r="I259" s="4"/>
@@ -10811,7 +10812,7 @@
       </c>
       <c r="M259"/>
     </row>
-    <row r="260" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="4" t="s">
         <v>507</v>
       </c>
@@ -10819,29 +10820,33 @@
         <v>90</v>
       </c>
       <c r="C260" s="21" t="s">
-        <v>324</v>
+        <v>106</v>
       </c>
       <c r="D260" s="5" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="E260" s="4"/>
       <c r="F260" s="5" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="G260" s="4" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H260" s="4"/>
-      <c r="I260" s="4"/>
+      <c r="I260" t="s">
+        <v>526</v>
+      </c>
       <c r="J260" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L260" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M260"/>
-    </row>
-    <row r="261" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M260" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="261" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="4" t="s">
         <v>507</v>
       </c>
@@ -10852,128 +10857,124 @@
         <v>106</v>
       </c>
       <c r="D261" s="5" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="E261" s="4"/>
       <c r="F261" s="5" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="G261" s="4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H261" s="4"/>
-      <c r="I261" t="s">
-        <v>531</v>
-      </c>
+      <c r="I261" s="4"/>
       <c r="J261" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L261" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M261" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="262" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M261"/>
+    </row>
+    <row r="262" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B262" s="21" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="C262" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="D262" s="4" t="s">
-        <v>532</v>
+        <v>324</v>
+      </c>
+      <c r="D262" s="5" t="s">
+        <v>529</v>
       </c>
       <c r="E262" s="4"/>
-      <c r="F262" s="4" t="s">
-        <v>532</v>
+      <c r="F262" s="5" t="s">
+        <v>529</v>
       </c>
       <c r="G262" s="4" t="s">
-        <v>170</v>
+        <v>31</v>
       </c>
       <c r="H262" s="4"/>
-      <c r="I262" s="23" t="s">
-        <v>533</v>
-      </c>
+      <c r="I262" s="4"/>
       <c r="J262" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L262" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="M262" s="23" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="263" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L262" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M262"/>
+    </row>
+    <row r="263" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B263" s="21" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="C263" s="21" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="D263" s="5" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="E263" s="4"/>
       <c r="F263" s="5" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="G263" s="4" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="H263" s="4"/>
-      <c r="I263" s="4"/>
+      <c r="I263" t="s">
+        <v>531</v>
+      </c>
       <c r="J263" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L263" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M263"/>
-    </row>
-    <row r="264" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M263" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="264" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B264" s="21" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="C264" s="21" t="s">
-        <v>110</v>
-      </c>
-      <c r="D264" s="22" t="s">
-        <v>671</v>
+        <v>106</v>
+      </c>
+      <c r="D264" s="4" t="s">
+        <v>532</v>
       </c>
       <c r="E264" s="4"/>
-      <c r="F264" s="22" t="s">
-        <v>671</v>
+      <c r="F264" s="4" t="s">
+        <v>532</v>
       </c>
       <c r="G264" s="4" t="s">
-        <v>56</v>
+        <v>170</v>
       </c>
       <c r="H264" s="4"/>
-      <c r="I264" t="s">
-        <v>536</v>
+      <c r="I264" s="23" t="s">
+        <v>533</v>
       </c>
       <c r="J264" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L264" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="M264" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="265" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L264" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="M264" s="23" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="265" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="4" t="s">
         <v>507</v>
       </c>
@@ -10984,124 +10985,124 @@
         <v>117</v>
       </c>
       <c r="D265" s="5" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="E265" s="4"/>
       <c r="F265" s="5" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="G265" s="4" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="H265" s="4"/>
-      <c r="I265" t="s">
-        <v>538</v>
-      </c>
+      <c r="I265" s="4"/>
       <c r="J265" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L265" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M265" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="266" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M265"/>
+    </row>
+    <row r="266" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B266" s="21" t="s">
-        <v>324</v>
+        <v>104</v>
       </c>
       <c r="C266" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="D266" s="5" t="s">
-        <v>540</v>
+      <c r="D266" s="22" t="s">
+        <v>671</v>
       </c>
       <c r="E266" s="4"/>
-      <c r="F266" s="5" t="s">
-        <v>540</v>
+      <c r="F266" s="22" t="s">
+        <v>671</v>
       </c>
       <c r="G266" s="4" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="H266" s="4"/>
-      <c r="I266" s="4"/>
+      <c r="I266" t="s">
+        <v>536</v>
+      </c>
       <c r="J266" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L266" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M266"/>
-    </row>
-    <row r="267" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+      <c r="M266" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="267" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B267" s="21" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C267" s="21" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D267" s="5" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="E267" s="4"/>
       <c r="F267" s="5" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="G267" s="4" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="H267" s="4"/>
-      <c r="I267" s="4"/>
+      <c r="I267" t="s">
+        <v>538</v>
+      </c>
       <c r="J267" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L267" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M267"/>
-    </row>
-    <row r="268" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M267" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="268" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B268" s="21" t="s">
-        <v>106</v>
+        <v>324</v>
       </c>
       <c r="C268" s="21" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="D268" s="5" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="E268" s="4"/>
       <c r="F268" s="5" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="G268" s="4" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H268" s="4"/>
-      <c r="I268" t="s">
-        <v>543</v>
-      </c>
+      <c r="I268" s="4"/>
       <c r="J268" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L268" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M268" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="269" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M268"/>
+    </row>
+    <row r="269" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="4" t="s">
         <v>507</v>
       </c>
@@ -11112,30 +11113,26 @@
         <v>119</v>
       </c>
       <c r="D269" s="5" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="E269" s="4"/>
       <c r="F269" s="5" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="G269" s="4" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="H269" s="4"/>
-      <c r="I269" t="s">
-        <v>545</v>
-      </c>
+      <c r="I269" s="4"/>
       <c r="J269" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L269" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M269" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="270" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M269"/>
+    </row>
+    <row r="270" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="4" t="s">
         <v>507</v>
       </c>
@@ -11146,18 +11143,18 @@
         <v>119</v>
       </c>
       <c r="D270" s="5" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="E270" s="4"/>
       <c r="F270" s="5" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="G270" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H270" s="4"/>
       <c r="I270" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="J270" s="4" t="s">
         <v>20</v>
@@ -11166,10 +11163,10 @@
         <v>21</v>
       </c>
       <c r="M270" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="271" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="271" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="4" t="s">
         <v>507</v>
       </c>
@@ -11177,140 +11174,144 @@
         <v>106</v>
       </c>
       <c r="C271" s="21" t="s">
-        <v>341</v>
-      </c>
-      <c r="D271" s="4" t="s">
-        <v>549</v>
+        <v>119</v>
+      </c>
+      <c r="D271" s="5" t="s">
+        <v>544</v>
       </c>
       <c r="E271" s="4"/>
-      <c r="F271" s="4" t="s">
-        <v>549</v>
+      <c r="F271" s="5" t="s">
+        <v>544</v>
       </c>
       <c r="G271" s="4" t="s">
-        <v>170</v>
+        <v>28</v>
       </c>
       <c r="H271" s="4"/>
-      <c r="I271" s="4"/>
+      <c r="I271" t="s">
+        <v>545</v>
+      </c>
       <c r="J271" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L271" s="27" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="272" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L271" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M271" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="272" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B272" s="21" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="C272" s="21" t="s">
         <v>119</v>
       </c>
       <c r="D272" s="5" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="E272" s="4"/>
       <c r="F272" s="5" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="G272" s="4" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="H272" s="4"/>
-      <c r="I272" s="4"/>
+      <c r="I272" t="s">
+        <v>548</v>
+      </c>
       <c r="J272" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L272" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M272"/>
-    </row>
-    <row r="273" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M272" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="273" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B273" s="21" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C273" s="21" t="s">
-        <v>551</v>
-      </c>
-      <c r="D273" s="5" t="s">
-        <v>552</v>
+        <v>341</v>
+      </c>
+      <c r="D273" s="4" t="s">
+        <v>549</v>
       </c>
       <c r="E273" s="4"/>
-      <c r="F273" s="5" t="s">
-        <v>552</v>
+      <c r="F273" s="4" t="s">
+        <v>549</v>
       </c>
       <c r="G273" s="4" t="s">
-        <v>31</v>
+        <v>170</v>
       </c>
       <c r="H273" s="4"/>
       <c r="I273" s="4"/>
       <c r="J273" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L273" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M273"/>
-    </row>
-    <row r="274" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L273" s="27" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="274" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B274" s="21" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C274" s="21" t="s">
         <v>119</v>
       </c>
       <c r="D274" s="5" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="E274" s="4"/>
       <c r="F274" s="5" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="G274" s="4" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="H274" s="4"/>
-      <c r="I274" t="s">
-        <v>554</v>
-      </c>
+      <c r="I274" s="4"/>
       <c r="J274" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L274" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="M274" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="275" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L274" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M274"/>
+    </row>
+    <row r="275" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B275" s="21" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="C275" s="21" t="s">
-        <v>129</v>
+        <v>551</v>
       </c>
       <c r="D275" s="5" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="E275" s="4"/>
       <c r="F275" s="5" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="G275" s="4" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H275" s="4"/>
       <c r="I275" s="4"/>
@@ -11322,41 +11323,41 @@
       </c>
       <c r="M275"/>
     </row>
-    <row r="276" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B276" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="C276" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="C276" s="21" t="s">
-        <v>127</v>
-      </c>
       <c r="D276" s="5" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="E276" s="4"/>
       <c r="F276" s="5" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="G276" s="4" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="H276" s="4"/>
       <c r="I276" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="J276" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L276" s="6" t="s">
-        <v>21</v>
+      <c r="L276" s="28" t="s">
+        <v>71</v>
       </c>
       <c r="M276" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="277" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="277" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="4" t="s">
         <v>507</v>
       </c>
@@ -11364,33 +11365,29 @@
         <v>119</v>
       </c>
       <c r="C277" s="21" t="s">
-        <v>558</v>
+        <v>129</v>
       </c>
       <c r="D277" s="5" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="E277" s="4"/>
       <c r="F277" s="5" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="G277" s="4" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="H277" s="4"/>
-      <c r="I277" t="s">
-        <v>560</v>
-      </c>
+      <c r="I277" s="4"/>
       <c r="J277" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L277" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M277" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="278" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M277"/>
+    </row>
+    <row r="278" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="4" t="s">
         <v>507</v>
       </c>
@@ -11401,18 +11398,18 @@
         <v>127</v>
       </c>
       <c r="D278" s="5" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="E278" s="4"/>
       <c r="F278" s="5" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="G278" s="4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H278" s="4"/>
       <c r="I278" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="J278" s="4" t="s">
         <v>20</v>
@@ -11421,62 +11418,66 @@
         <v>21</v>
       </c>
       <c r="M278" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="279" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="279" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B279" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C279" s="21" t="s">
         <v>558</v>
       </c>
-      <c r="C279" s="21" t="s">
-        <v>129</v>
-      </c>
       <c r="D279" s="5" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="E279" s="4"/>
       <c r="F279" s="5" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="G279" s="4" t="s">
         <v>56</v>
       </c>
       <c r="H279" s="4"/>
-      <c r="I279" s="4"/>
+      <c r="I279" t="s">
+        <v>560</v>
+      </c>
       <c r="J279" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L279" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M279"/>
-    </row>
-    <row r="280" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M279" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="280" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B280" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C280" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="C280" s="21" t="s">
-        <v>136</v>
-      </c>
       <c r="D280" s="5" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="E280" s="4"/>
       <c r="F280" s="5" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="G280" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H280" s="4"/>
       <c r="I280" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="J280" s="4" t="s">
         <v>20</v>
@@ -11485,96 +11486,96 @@
         <v>21</v>
       </c>
       <c r="M280" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="281" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="281" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B281" s="21" t="s">
+        <v>558</v>
+      </c>
+      <c r="C281" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="C281" s="21" t="s">
-        <v>134</v>
-      </c>
       <c r="D281" s="5" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="E281" s="4"/>
       <c r="F281" s="5" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="G281" s="4" t="s">
         <v>56</v>
       </c>
       <c r="H281" s="4"/>
-      <c r="I281" t="s">
-        <v>568</v>
-      </c>
+      <c r="I281" s="4"/>
       <c r="J281" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L281" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M281" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="282" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M281"/>
+    </row>
+    <row r="282" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B282" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="C282" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="C282" s="21" t="s">
-        <v>140</v>
-      </c>
       <c r="D282" s="5" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="E282" s="4"/>
       <c r="F282" s="5" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="G282" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H282" s="4"/>
-      <c r="I282" s="4"/>
+      <c r="I282" t="s">
+        <v>565</v>
+      </c>
       <c r="J282" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L282" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M282"/>
-    </row>
-    <row r="283" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M282" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="283" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B283" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="C283" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="C283" s="21" t="s">
-        <v>154</v>
-      </c>
       <c r="D283" s="5" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="E283" s="4"/>
       <c r="F283" s="5" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="G283" s="4" t="s">
         <v>56</v>
       </c>
       <c r="H283" s="4"/>
       <c r="I283" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="J283" s="4" t="s">
         <v>20</v>
@@ -11583,66 +11584,62 @@
         <v>21</v>
       </c>
       <c r="M283" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="284" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="284" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B284" s="21" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C284" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="D284" s="4" t="s">
-        <v>572</v>
+      <c r="D284" s="5" t="s">
+        <v>569</v>
       </c>
       <c r="E284" s="4"/>
-      <c r="F284" s="4" t="s">
-        <v>573</v>
+      <c r="F284" s="5" t="s">
+        <v>569</v>
       </c>
       <c r="G284" s="4" t="s">
-        <v>162</v>
+        <v>35</v>
       </c>
       <c r="H284" s="4"/>
-      <c r="I284" s="4" t="s">
-        <v>574</v>
-      </c>
+      <c r="I284" s="4"/>
       <c r="J284" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L284" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="M284" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="285" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+      <c r="M284"/>
+    </row>
+    <row r="285" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B285" s="21" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C285" s="21" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="D285" s="5" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="E285" s="4"/>
       <c r="F285" s="5" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="G285" s="4" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="H285" s="4"/>
       <c r="I285" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="J285" s="4" t="s">
         <v>20</v>
@@ -11651,62 +11648,66 @@
         <v>21</v>
       </c>
       <c r="M285" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="286" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="286" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B286" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="C286" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="C286" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="D286" s="5" t="s">
-        <v>18</v>
+      <c r="D286" s="4" t="s">
+        <v>572</v>
       </c>
       <c r="E286" s="4"/>
-      <c r="F286" s="5" t="s">
-        <v>18</v>
+      <c r="F286" s="4" t="s">
+        <v>573</v>
       </c>
       <c r="G286" s="4" t="s">
-        <v>19</v>
+        <v>162</v>
       </c>
       <c r="H286" s="4"/>
-      <c r="I286" s="4"/>
+      <c r="I286" s="4" t="s">
+        <v>574</v>
+      </c>
       <c r="J286" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L286" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M286"/>
-    </row>
-    <row r="287" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>149</v>
+      </c>
+      <c r="M286" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="287" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B287" s="21" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="C287" s="21" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="D287" s="5" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E287" s="4"/>
       <c r="F287" s="5" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="G287" s="4" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="H287" s="4"/>
       <c r="I287" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="J287" s="4" t="s">
         <v>20</v>
@@ -11715,28 +11716,28 @@
         <v>21</v>
       </c>
       <c r="M287" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="288" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="288" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B288" s="21" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="C288" s="21" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="D288" s="5" t="s">
-        <v>579</v>
+        <v>18</v>
       </c>
       <c r="E288" s="4"/>
       <c r="F288" s="5" t="s">
-        <v>579</v>
+        <v>18</v>
       </c>
       <c r="G288" s="4" t="s">
-        <v>173</v>
+        <v>19</v>
       </c>
       <c r="H288" s="4"/>
       <c r="I288" s="4"/>
@@ -11748,41 +11749,41 @@
       </c>
       <c r="M288"/>
     </row>
-    <row r="289" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="4" t="s">
         <v>507</v>
       </c>
-      <c r="B289" s="12" t="s">
+      <c r="B289" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="C289" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="D289" s="4" t="s">
-        <v>580</v>
+      <c r="C289" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="D289" s="5" t="s">
+        <v>577</v>
       </c>
       <c r="E289" s="4"/>
-      <c r="F289" s="4" t="s">
-        <v>580</v>
+      <c r="F289" s="5" t="s">
+        <v>577</v>
       </c>
       <c r="G289" s="4" t="s">
-        <v>162</v>
+        <v>56</v>
       </c>
       <c r="H289" s="4"/>
-      <c r="I289" s="4" t="s">
-        <v>581</v>
+      <c r="I289" t="s">
+        <v>578</v>
       </c>
       <c r="J289" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L289" s="6" t="s">
-        <v>149</v>
+        <v>21</v>
       </c>
       <c r="M289" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="290" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="290" spans="1:13" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="4" t="s">
         <v>507</v>
       </c>
@@ -11790,131 +11791,131 @@
         <v>154</v>
       </c>
       <c r="C290" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="D290" s="4" t="s">
-        <v>582</v>
+        <v>168</v>
+      </c>
+      <c r="D290" s="5" t="s">
+        <v>579</v>
       </c>
       <c r="E290" s="4"/>
-      <c r="F290" s="4" t="s">
-        <v>582</v>
+      <c r="F290" s="5" t="s">
+        <v>579</v>
       </c>
       <c r="G290" s="4" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="H290" s="4"/>
-      <c r="I290" s="4" t="s">
-        <v>583</v>
-      </c>
+      <c r="I290" s="4"/>
       <c r="J290" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L290" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="M290" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="291" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+      <c r="M290"/>
+    </row>
+    <row r="291" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="4" t="s">
         <v>507</v>
       </c>
-      <c r="B291" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="C291" s="21" t="s">
-        <v>181</v>
+      <c r="B291" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="C291" s="12" t="s">
+        <v>168</v>
       </c>
       <c r="D291" s="4" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="E291" s="4"/>
       <c r="F291" s="4" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="G291" s="4" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="H291" s="4"/>
       <c r="I291" s="4" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="J291" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L291" s="30" t="s">
+      <c r="L291" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="M291" s="23" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="292" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M291" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="292" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B292" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="C292" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="C292" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D292" s="5" t="s">
-        <v>586</v>
+      <c r="D292" s="4" t="s">
+        <v>582</v>
       </c>
       <c r="E292" s="4"/>
-      <c r="F292" s="5" t="s">
-        <v>586</v>
+      <c r="F292" s="4" t="s">
+        <v>582</v>
       </c>
       <c r="G292" s="4" t="s">
-        <v>39</v>
+        <v>152</v>
       </c>
       <c r="H292" s="4"/>
-      <c r="I292" t="s">
-        <v>587</v>
+      <c r="I292" s="4" t="s">
+        <v>583</v>
       </c>
       <c r="J292" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L292" s="6" t="s">
-        <v>21</v>
+        <v>149</v>
       </c>
       <c r="M292" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="293" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="293" spans="1:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B293" s="21" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="C293" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D293" s="5" t="s">
-        <v>588</v>
+        <v>181</v>
+      </c>
+      <c r="D293" s="4" t="s">
+        <v>584</v>
       </c>
       <c r="E293" s="4"/>
-      <c r="F293" s="5" t="s">
-        <v>588</v>
+      <c r="F293" s="4" t="s">
+        <v>584</v>
       </c>
       <c r="G293" s="4" t="s">
-        <v>28</v>
+        <v>170</v>
       </c>
       <c r="H293" s="4"/>
-      <c r="I293" s="4"/>
+      <c r="I293" s="4" t="s">
+        <v>585</v>
+      </c>
       <c r="J293" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L293" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M293"/>
-    </row>
-    <row r="294" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L293" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="M293" s="23" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="294" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="4" t="s">
         <v>507</v>
       </c>
@@ -11925,26 +11926,30 @@
         <v>16</v>
       </c>
       <c r="D294" s="5" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="E294" s="4"/>
       <c r="F294" s="5" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="G294" s="4" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H294" s="4"/>
-      <c r="I294" s="4"/>
+      <c r="I294" t="s">
+        <v>587</v>
+      </c>
       <c r="J294" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L294" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M294"/>
-    </row>
-    <row r="295" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M294" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="295" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="4" t="s">
         <v>507</v>
       </c>
@@ -11955,14 +11960,14 @@
         <v>16</v>
       </c>
       <c r="D295" s="5" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E295" s="4"/>
       <c r="F295" s="5" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="G295" s="4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H295" s="4"/>
       <c r="I295" s="4"/>
@@ -11974,59 +11979,55 @@
       </c>
       <c r="M295"/>
     </row>
-    <row r="296" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B296" s="21" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="C296" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="D296" s="4" t="s">
-        <v>591</v>
+      <c r="D296" s="5" t="s">
+        <v>589</v>
       </c>
       <c r="E296" s="4"/>
-      <c r="F296" s="4" t="s">
-        <v>591</v>
+      <c r="F296" s="5" t="s">
+        <v>589</v>
       </c>
       <c r="G296" s="4" t="s">
-        <v>152</v>
+        <v>31</v>
       </c>
       <c r="H296" s="4"/>
-      <c r="I296" s="4" t="s">
-        <v>592</v>
-      </c>
+      <c r="I296" s="4"/>
       <c r="J296" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L296" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="M296" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="297" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+      <c r="M296"/>
+    </row>
+    <row r="297" spans="1:13" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B297" s="21" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="C297" s="21" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D297" s="5" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="E297" s="4"/>
       <c r="F297" s="5" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="G297" s="4" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="H297" s="4"/>
       <c r="I297" s="4"/>
@@ -12038,55 +12039,59 @@
       </c>
       <c r="M297"/>
     </row>
-    <row r="298" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B298" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="C298" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C298" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="D298" s="5" t="s">
-        <v>594</v>
+      <c r="D298" s="4" t="s">
+        <v>591</v>
       </c>
       <c r="E298" s="4"/>
-      <c r="F298" s="5" t="s">
-        <v>594</v>
+      <c r="F298" s="4" t="s">
+        <v>591</v>
       </c>
       <c r="G298" s="4" t="s">
-        <v>39</v>
+        <v>152</v>
       </c>
       <c r="H298" s="4"/>
-      <c r="I298" s="4"/>
+      <c r="I298" s="4" t="s">
+        <v>592</v>
+      </c>
       <c r="J298" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L298" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M298"/>
-    </row>
-    <row r="299" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+        <v>149</v>
+      </c>
+      <c r="M298" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="299" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B299" s="21" t="s">
-        <v>16</v>
+        <v>166</v>
       </c>
       <c r="C299" s="21" t="s">
         <v>22</v>
       </c>
       <c r="D299" s="5" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="E299" s="4"/>
       <c r="F299" s="5" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="G299" s="4" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="H299" s="4"/>
       <c r="I299" s="4"/>
@@ -12098,7 +12103,7 @@
       </c>
       <c r="M299"/>
     </row>
-    <row r="300" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A300" s="4" t="s">
         <v>507</v>
       </c>
@@ -12109,14 +12114,14 @@
         <v>22</v>
       </c>
       <c r="D300" s="5" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="E300" s="4"/>
       <c r="F300" s="5" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="G300" s="4" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="H300" s="4"/>
       <c r="I300" s="4"/>
@@ -12128,7 +12133,7 @@
       </c>
       <c r="M300"/>
     </row>
-    <row r="301" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A301" s="4" t="s">
         <v>507</v>
       </c>
@@ -12139,14 +12144,14 @@
         <v>22</v>
       </c>
       <c r="D301" s="5" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E301" s="4"/>
       <c r="F301" s="5" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="G301" s="4" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H301" s="4"/>
       <c r="I301" s="4"/>
@@ -12158,7 +12163,7 @@
       </c>
       <c r="M301"/>
     </row>
-    <row r="302" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A302" s="4" t="s">
         <v>507</v>
       </c>
@@ -12169,30 +12174,26 @@
         <v>22</v>
       </c>
       <c r="D302" s="5" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="E302" s="4"/>
       <c r="F302" s="5" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="G302" s="4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H302" s="4"/>
-      <c r="I302" t="s">
-        <v>599</v>
-      </c>
+      <c r="I302" s="4"/>
       <c r="J302" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L302" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M302" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="303" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M302"/>
+    </row>
+    <row r="303" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="4" t="s">
         <v>507</v>
       </c>
@@ -12200,55 +12201,51 @@
         <v>16</v>
       </c>
       <c r="C303" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="D303" s="4" t="s">
-        <v>601</v>
+        <v>22</v>
+      </c>
+      <c r="D303" s="5" t="s">
+        <v>597</v>
       </c>
       <c r="E303" s="4"/>
-      <c r="F303" s="4" t="s">
-        <v>601</v>
+      <c r="F303" s="5" t="s">
+        <v>597</v>
       </c>
       <c r="G303" s="4" t="s">
-        <v>170</v>
+        <v>31</v>
       </c>
       <c r="H303" s="4"/>
-      <c r="I303" s="4" t="s">
-        <v>602</v>
-      </c>
+      <c r="I303" s="4"/>
       <c r="J303" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L303" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="M303" s="23" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="304" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L303" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M303"/>
+    </row>
+    <row r="304" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B304" s="21" t="s">
-        <v>159</v>
+        <v>16</v>
       </c>
       <c r="C304" s="21" t="s">
         <v>22</v>
       </c>
       <c r="D304" s="5" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="E304" s="4"/>
       <c r="F304" s="5" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="G304" s="4" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="H304" s="4"/>
       <c r="I304" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="J304" s="4" t="s">
         <v>20</v>
@@ -12257,66 +12254,66 @@
         <v>21</v>
       </c>
       <c r="M304" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="305" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="305" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A305" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B305" s="21" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C305" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="D305" s="5" t="s">
-        <v>605</v>
+        <v>201</v>
+      </c>
+      <c r="D305" s="4" t="s">
+        <v>601</v>
       </c>
       <c r="E305" s="4"/>
-      <c r="F305" s="5" t="s">
-        <v>605</v>
+      <c r="F305" s="4" t="s">
+        <v>601</v>
       </c>
       <c r="G305" s="4" t="s">
-        <v>39</v>
+        <v>170</v>
       </c>
       <c r="H305" s="4"/>
-      <c r="I305" t="s">
-        <v>606</v>
+      <c r="I305" s="4" t="s">
+        <v>602</v>
       </c>
       <c r="J305" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L305" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M305" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="306" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L305" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="M305" s="23" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="306" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B306" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="C306" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C306" s="21" t="s">
-        <v>23</v>
-      </c>
       <c r="D306" s="5" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="E306" s="4"/>
       <c r="F306" s="5" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="G306" s="4" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H306" s="4"/>
       <c r="I306" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="J306" s="4" t="s">
         <v>20</v>
@@ -12325,10 +12322,10 @@
         <v>21</v>
       </c>
       <c r="M306" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="307" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="307" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A307" s="4" t="s">
         <v>507</v>
       </c>
@@ -12339,26 +12336,30 @@
         <v>23</v>
       </c>
       <c r="D307" s="5" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="E307" s="4"/>
       <c r="F307" s="5" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="G307" s="4" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="H307" s="4"/>
-      <c r="I307" s="4"/>
+      <c r="I307" t="s">
+        <v>606</v>
+      </c>
       <c r="J307" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L307" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M307"/>
-    </row>
-    <row r="308" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M307" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="308" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A308" s="4" t="s">
         <v>507</v>
       </c>
@@ -12369,26 +12370,30 @@
         <v>23</v>
       </c>
       <c r="D308" s="5" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="E308" s="4"/>
       <c r="F308" s="5" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="G308" s="4" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H308" s="4"/>
-      <c r="I308" s="4"/>
+      <c r="I308" t="s">
+        <v>608</v>
+      </c>
       <c r="J308" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L308" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M308"/>
-    </row>
-    <row r="309" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M308" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="309" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A309" s="4" t="s">
         <v>507</v>
       </c>
@@ -12396,17 +12401,17 @@
         <v>22</v>
       </c>
       <c r="C309" s="21" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D309" s="5" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="E309" s="4"/>
       <c r="F309" s="5" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="G309" s="4" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="H309" s="4"/>
       <c r="I309" s="4"/>
@@ -12418,7 +12423,7 @@
       </c>
       <c r="M309"/>
     </row>
-    <row r="310" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A310" s="4" t="s">
         <v>507</v>
       </c>
@@ -12426,33 +12431,29 @@
         <v>22</v>
       </c>
       <c r="C310" s="21" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D310" s="5" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="E310" s="4"/>
       <c r="F310" s="5" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="G310" s="4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H310" s="4"/>
-      <c r="I310" t="s">
-        <v>613</v>
-      </c>
+      <c r="I310" s="4"/>
       <c r="J310" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L310" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M310" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="311" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M310"/>
+    </row>
+    <row r="311" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A311" s="4" t="s">
         <v>507</v>
       </c>
@@ -12460,33 +12461,29 @@
         <v>22</v>
       </c>
       <c r="C311" s="21" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="D311" s="5" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="E311" s="4"/>
       <c r="F311" s="5" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="G311" s="4" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="H311" s="4"/>
-      <c r="I311" t="s">
-        <v>615</v>
-      </c>
+      <c r="I311" s="4"/>
       <c r="J311" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L311" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M311" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="312" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M311"/>
+    </row>
+    <row r="312" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A312" s="4" t="s">
         <v>507</v>
       </c>
@@ -12494,127 +12491,131 @@
         <v>22</v>
       </c>
       <c r="C312" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="D312" s="4" t="s">
-        <v>616</v>
+        <v>43</v>
+      </c>
+      <c r="D312" s="5" t="s">
+        <v>612</v>
       </c>
       <c r="E312" s="4"/>
-      <c r="F312" s="4" t="s">
-        <v>616</v>
+      <c r="F312" s="5" t="s">
+        <v>612</v>
       </c>
       <c r="G312" s="4" t="s">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="H312" s="4"/>
-      <c r="I312" s="4" t="s">
-        <v>617</v>
+      <c r="I312" t="s">
+        <v>613</v>
       </c>
       <c r="J312" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L312" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="M312" s="23" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="313" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L312" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M312" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="313" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A313" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B313" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="C313" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="C313" s="21" t="s">
-        <v>43</v>
-      </c>
       <c r="D313" s="5" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="E313" s="4"/>
       <c r="F313" s="5" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="G313" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H313" s="4"/>
-      <c r="I313" s="4"/>
+      <c r="I313" t="s">
+        <v>615</v>
+      </c>
       <c r="J313" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L313" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M313"/>
-    </row>
-    <row r="314" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M313" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="314" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A314" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B314" s="21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C314" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="D314" s="5" t="s">
-        <v>619</v>
+      <c r="D314" s="4" t="s">
+        <v>616</v>
       </c>
       <c r="E314" s="4"/>
-      <c r="F314" s="5" t="s">
-        <v>619</v>
+      <c r="F314" s="4" t="s">
+        <v>616</v>
       </c>
       <c r="G314" s="4" t="s">
-        <v>39</v>
+        <v>170</v>
       </c>
       <c r="H314" s="4"/>
-      <c r="I314" s="4"/>
+      <c r="I314" s="4" t="s">
+        <v>617</v>
+      </c>
       <c r="J314" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L314" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M314"/>
-    </row>
-    <row r="315" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L314" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="M314" s="23" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="315" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A315" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B315" s="21" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C315" s="21" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D315" s="5" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="E315" s="4"/>
       <c r="F315" s="5" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="G315" s="4" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H315" s="4"/>
-      <c r="I315" t="s">
-        <v>621</v>
-      </c>
+      <c r="I315" s="4"/>
       <c r="J315" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L315" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M315" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="316" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M315"/>
+    </row>
+    <row r="316" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A316" s="4" t="s">
         <v>507</v>
       </c>
@@ -12625,30 +12626,26 @@
         <v>47</v>
       </c>
       <c r="D316" s="5" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="E316" s="4"/>
       <c r="F316" s="5" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="G316" s="4" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="H316" s="4"/>
-      <c r="I316" t="s">
-        <v>623</v>
-      </c>
+      <c r="I316" s="4"/>
       <c r="J316" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L316" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M316" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="317" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M316"/>
+    </row>
+    <row r="317" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A317" s="4" t="s">
         <v>507</v>
       </c>
@@ -12656,21 +12653,21 @@
         <v>23</v>
       </c>
       <c r="C317" s="21" t="s">
-        <v>256</v>
+        <v>54</v>
       </c>
       <c r="D317" s="5" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="E317" s="4"/>
       <c r="F317" s="5" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="G317" s="4" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H317" s="4"/>
       <c r="I317" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="J317" s="4" t="s">
         <v>20</v>
@@ -12679,70 +12676,78 @@
         <v>21</v>
       </c>
       <c r="M317" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="318" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="318" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A318" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B318" s="21" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="C318" s="21" t="s">
-        <v>626</v>
+        <v>47</v>
       </c>
       <c r="D318" s="5" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="E318" s="4"/>
       <c r="F318" s="5" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="G318" s="4" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="H318" s="4"/>
-      <c r="I318" s="4"/>
+      <c r="I318" t="s">
+        <v>623</v>
+      </c>
       <c r="J318" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L318" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M318"/>
-    </row>
-    <row r="319" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M318" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="319" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A319" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B319" s="21" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="C319" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="D319" s="22" t="s">
-        <v>669</v>
+        <v>256</v>
+      </c>
+      <c r="D319" s="5" t="s">
+        <v>624</v>
       </c>
       <c r="E319" s="4"/>
-      <c r="F319" s="22" t="s">
-        <v>669</v>
+      <c r="F319" s="5" t="s">
+        <v>624</v>
       </c>
       <c r="G319" s="4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H319" s="4"/>
-      <c r="I319" s="4"/>
+      <c r="I319" t="s">
+        <v>625</v>
+      </c>
       <c r="J319" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L319" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M319"/>
-    </row>
-    <row r="320" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M319" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="320" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A320" s="4" t="s">
         <v>507</v>
       </c>
@@ -12750,179 +12755,175 @@
         <v>43</v>
       </c>
       <c r="C320" s="21" t="s">
-        <v>61</v>
+        <v>626</v>
       </c>
       <c r="D320" s="5" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="E320" s="4"/>
       <c r="F320" s="5" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G320" s="4" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="H320" s="4"/>
-      <c r="I320" t="s">
-        <v>629</v>
-      </c>
+      <c r="I320" s="4"/>
       <c r="J320" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L320" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M320" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="321" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M320"/>
+    </row>
+    <row r="321" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A321" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B321" s="21" t="s">
-        <v>256</v>
+        <v>43</v>
       </c>
       <c r="C321" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="D321" s="5" t="s">
-        <v>631</v>
+      <c r="D321" s="22" t="s">
+        <v>669</v>
       </c>
       <c r="E321" s="4"/>
-      <c r="F321" s="5" t="s">
-        <v>631</v>
+      <c r="F321" s="22" t="s">
+        <v>669</v>
       </c>
       <c r="G321" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H321" s="4"/>
-      <c r="I321" t="s">
-        <v>632</v>
-      </c>
+      <c r="I321" s="4"/>
       <c r="J321" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L321" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M321" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="322" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M321"/>
+    </row>
+    <row r="322" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A322" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B322" s="21" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C322" s="21" t="s">
-        <v>626</v>
+        <v>61</v>
       </c>
       <c r="D322" s="5" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="E322" s="4"/>
       <c r="F322" s="5" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="G322" s="4" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="H322" s="4"/>
-      <c r="I322" s="4"/>
+      <c r="I322" t="s">
+        <v>629</v>
+      </c>
       <c r="J322" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L322" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M322"/>
-    </row>
-    <row r="323" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M322" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="323" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A323" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B323" s="21" t="s">
-        <v>47</v>
+        <v>256</v>
       </c>
       <c r="C323" s="21" t="s">
-        <v>626</v>
+        <v>54</v>
       </c>
       <c r="D323" s="5" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="E323" s="4"/>
       <c r="F323" s="5" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="G323" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H323" s="4"/>
-      <c r="I323" s="4"/>
+      <c r="I323" t="s">
+        <v>632</v>
+      </c>
       <c r="J323" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L323" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M323"/>
-    </row>
-    <row r="324" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M323" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="324" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A324" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B324" s="21" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="C324" s="21" t="s">
         <v>626</v>
       </c>
       <c r="D324" s="5" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="E324" s="4"/>
       <c r="F324" s="5" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="G324" s="4" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="H324" s="4"/>
-      <c r="I324" t="s">
-        <v>636</v>
-      </c>
+      <c r="I324" s="4"/>
       <c r="J324" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L324" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M324" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="325" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M324"/>
+    </row>
+    <row r="325" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A325" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B325" s="21" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C325" s="21" t="s">
-        <v>638</v>
+        <v>626</v>
       </c>
       <c r="D325" s="5" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="E325" s="4"/>
       <c r="F325" s="5" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="G325" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H325" s="4"/>
       <c r="I325" s="4"/>
@@ -12934,89 +12935,89 @@
       </c>
       <c r="M325"/>
     </row>
-    <row r="326" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A326" s="4" t="s">
         <v>507</v>
       </c>
       <c r="B326" s="21" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C326" s="21" t="s">
-        <v>640</v>
+        <v>626</v>
       </c>
       <c r="D326" s="5" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="E326" s="4"/>
       <c r="F326" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="G326" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H326" s="4"/>
+      <c r="I326" t="s">
+        <v>636</v>
+      </c>
+      <c r="J326" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L326" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M326" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="327" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A327" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="B327" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="C327" s="21" t="s">
+        <v>638</v>
+      </c>
+      <c r="D327" s="5" t="s">
+        <v>639</v>
+      </c>
+      <c r="E327" s="4"/>
+      <c r="F327" s="5" t="s">
+        <v>639</v>
+      </c>
+      <c r="G327" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H327" s="4"/>
+      <c r="I327" s="4"/>
+      <c r="J327" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L327" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M327"/>
+    </row>
+    <row r="328" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A328" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="B328" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="C328" s="21" t="s">
+        <v>640</v>
+      </c>
+      <c r="D328" s="5" t="s">
         <v>641</v>
-      </c>
-      <c r="G326" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H326" s="4"/>
-      <c r="I326" s="4"/>
-      <c r="J326" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L326" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M326"/>
-    </row>
-    <row r="327" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A327" s="13" t="s">
-        <v>507</v>
-      </c>
-      <c r="B327" s="33" t="s">
-        <v>54</v>
-      </c>
-      <c r="C327" s="33" t="s">
-        <v>642</v>
-      </c>
-      <c r="D327" s="15" t="s">
-        <v>643</v>
-      </c>
-      <c r="E327" s="13"/>
-      <c r="F327" s="15" t="s">
-        <v>644</v>
-      </c>
-      <c r="G327" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="H327" s="13"/>
-      <c r="I327" s="14" t="s">
-        <v>645</v>
-      </c>
-      <c r="J327" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="L327" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M327" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="328" spans="1:13" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A328" s="10" t="s">
-        <v>646</v>
-      </c>
-      <c r="B328" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="C328" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="D328" s="5" t="s">
-        <v>647</v>
       </c>
       <c r="E328" s="4"/>
       <c r="F328" s="5" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="G328" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H328" s="4"/>
       <c r="I328" s="4"/>
@@ -13028,89 +13029,89 @@
       </c>
       <c r="M328"/>
     </row>
-    <row r="329" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A329" s="4" t="s">
+    <row r="329" spans="1:13" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A329" s="13" t="s">
+        <v>507</v>
+      </c>
+      <c r="B329" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="C329" s="33" t="s">
+        <v>642</v>
+      </c>
+      <c r="D329" s="15" t="s">
+        <v>643</v>
+      </c>
+      <c r="E329" s="13"/>
+      <c r="F329" s="15" t="s">
+        <v>644</v>
+      </c>
+      <c r="G329" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="H329" s="13"/>
+      <c r="I329" s="14" t="s">
+        <v>645</v>
+      </c>
+      <c r="J329" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="L329" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M329" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="330" spans="1:13" ht="15" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A330" s="10" t="s">
         <v>646</v>
       </c>
-      <c r="B329" s="21" t="s">
+      <c r="B330" s="21" t="s">
         <v>89</v>
-      </c>
-      <c r="C329" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="D329" s="5" t="s">
-        <v>648</v>
-      </c>
-      <c r="E329" s="4"/>
-      <c r="F329" s="5" t="s">
-        <v>648</v>
-      </c>
-      <c r="G329" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="H329" s="4"/>
-      <c r="I329" s="4"/>
-      <c r="J329" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L329" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M329"/>
-    </row>
-    <row r="330" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A330" s="4" t="s">
-        <v>646</v>
-      </c>
-      <c r="B330" s="21" t="s">
-        <v>315</v>
       </c>
       <c r="C330" s="21" t="s">
         <v>90</v>
       </c>
       <c r="D330" s="5" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="E330" s="4"/>
       <c r="F330" s="5" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="G330" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H330" s="4"/>
-      <c r="I330" t="s">
-        <v>650</v>
-      </c>
+      <c r="I330" s="4"/>
       <c r="J330" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L330" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M330" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="331" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M330"/>
+    </row>
+    <row r="331" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A331" s="4" t="s">
         <v>646</v>
       </c>
       <c r="B331" s="21" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C331" s="21" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="D331" s="5" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="E331" s="4"/>
       <c r="F331" s="5" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="G331" s="4" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="H331" s="4"/>
       <c r="I331" s="4"/>
@@ -13122,55 +13123,59 @@
       </c>
       <c r="M331"/>
     </row>
-    <row r="332" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A332" s="4" t="s">
         <v>646</v>
       </c>
       <c r="B332" s="21" t="s">
+        <v>315</v>
+      </c>
+      <c r="C332" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="C332" s="21" t="s">
-        <v>110</v>
-      </c>
       <c r="D332" s="5" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="E332" s="4"/>
       <c r="F332" s="5" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="G332" s="4" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H332" s="4"/>
-      <c r="I332" s="4"/>
+      <c r="I332" t="s">
+        <v>650</v>
+      </c>
       <c r="J332" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L332" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M332"/>
-    </row>
-    <row r="333" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M332" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="333" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A333" s="4" t="s">
         <v>646</v>
       </c>
       <c r="B333" s="21" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C333" s="21" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D333" s="5" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E333" s="4"/>
       <c r="F333" s="5" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="G333" s="4" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H333" s="4"/>
       <c r="I333" s="4"/>
@@ -13182,7 +13187,7 @@
       </c>
       <c r="M333"/>
     </row>
-    <row r="334" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A334" s="4" t="s">
         <v>646</v>
       </c>
@@ -13190,142 +13195,142 @@
         <v>90</v>
       </c>
       <c r="C334" s="21" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="D334" s="5" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="E334" s="4"/>
       <c r="F334" s="5" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G334" s="4" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="H334" s="4"/>
-      <c r="I334" t="s">
-        <v>655</v>
-      </c>
+      <c r="I334" s="4"/>
       <c r="J334" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L334" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M334" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="335" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M334"/>
+    </row>
+    <row r="335" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A335" s="4" t="s">
         <v>646</v>
       </c>
       <c r="B335" s="21" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="C335" s="21" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D335" s="5" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="E335" s="4"/>
       <c r="F335" s="5" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="G335" s="4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H335" s="4"/>
-      <c r="I335" t="s">
-        <v>658</v>
-      </c>
+      <c r="I335" s="4"/>
       <c r="J335" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L335" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M335" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="336" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M335"/>
+    </row>
+    <row r="336" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A336" s="4" t="s">
         <v>646</v>
       </c>
       <c r="B336" s="21" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="C336" s="21" t="s">
         <v>119</v>
       </c>
       <c r="D336" s="5" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="E336" s="4"/>
       <c r="F336" s="5" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="G336" s="4" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="H336" s="4"/>
-      <c r="I336" s="4"/>
+      <c r="I336" t="s">
+        <v>655</v>
+      </c>
       <c r="J336" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L336" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M336"/>
-    </row>
-    <row r="337" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M336" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="337" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A337" s="4" t="s">
         <v>646</v>
       </c>
       <c r="B337" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="C337" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="C337" s="21" t="s">
-        <v>354</v>
-      </c>
       <c r="D337" s="5" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="E337" s="4"/>
       <c r="F337" s="5" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="G337" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H337" s="4"/>
-      <c r="I337" s="4"/>
+      <c r="I337" t="s">
+        <v>658</v>
+      </c>
       <c r="J337" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L337" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M337"/>
-    </row>
-    <row r="338" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M337" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="338" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A338" s="4" t="s">
         <v>646</v>
       </c>
       <c r="B338" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="C338" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="C338" s="21" t="s">
-        <v>129</v>
-      </c>
       <c r="D338" s="5" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E338" s="4"/>
       <c r="F338" s="5" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="G338" s="4" t="s">
         <v>28</v>
@@ -13340,59 +13345,55 @@
       </c>
       <c r="M338"/>
     </row>
-    <row r="339" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A339" s="4" t="s">
         <v>646</v>
       </c>
       <c r="B339" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="C339" s="21" t="s">
         <v>354</v>
       </c>
-      <c r="C339" s="21" t="s">
-        <v>129</v>
-      </c>
       <c r="D339" s="5" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="E339" s="4"/>
       <c r="F339" s="5" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="G339" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H339" s="4"/>
-      <c r="I339" t="s">
-        <v>663</v>
-      </c>
+      <c r="I339" s="4"/>
       <c r="J339" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L339" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M339" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="340" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M339"/>
+    </row>
+    <row r="340" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A340" s="4" t="s">
         <v>646</v>
       </c>
       <c r="B340" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C340" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="C340" s="21" t="s">
-        <v>134</v>
-      </c>
       <c r="D340" s="5" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="E340" s="4"/>
       <c r="F340" s="5" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="G340" s="4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H340" s="4"/>
       <c r="I340" s="4"/>
@@ -13404,52 +13405,56 @@
       </c>
       <c r="M340"/>
     </row>
-    <row r="341" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A341" s="4" t="s">
         <v>646</v>
       </c>
       <c r="B341" s="21" t="s">
-        <v>134</v>
+        <v>354</v>
       </c>
       <c r="C341" s="21" t="s">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D341" s="5" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="E341" s="4"/>
       <c r="F341" s="5" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="G341" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H341" s="4"/>
-      <c r="I341" s="4"/>
+      <c r="I341" t="s">
+        <v>663</v>
+      </c>
       <c r="J341" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L341" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M341"/>
-    </row>
-    <row r="342" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M341" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="342" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A342" s="4" t="s">
         <v>646</v>
       </c>
       <c r="B342" s="21" t="s">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="C342" s="21" t="s">
-        <v>166</v>
+        <v>134</v>
       </c>
       <c r="D342" s="5" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="E342" s="4"/>
       <c r="F342" s="5" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="G342" s="4" t="s">
         <v>35</v>
@@ -13464,10 +13469,76 @@
       </c>
       <c r="M342"/>
     </row>
+    <row r="343" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A343" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="B343" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="C343" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="D343" s="5" t="s">
+        <v>666</v>
+      </c>
+      <c r="E343" s="4"/>
+      <c r="F343" s="5" t="s">
+        <v>666</v>
+      </c>
+      <c r="G343" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H343" s="4"/>
+      <c r="I343" s="4"/>
+      <c r="J343" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L343" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M343"/>
+    </row>
+    <row r="344" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A344" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="B344" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="C344" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="D344" s="5" t="s">
+        <v>667</v>
+      </c>
+      <c r="E344" s="4"/>
+      <c r="F344" s="5" t="s">
+        <v>667</v>
+      </c>
+      <c r="G344" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H344" s="4"/>
+      <c r="I344" s="4"/>
+      <c r="J344" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L344" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M344"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:M342" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A244:M327">
-    <sortCondition ref="B244:B327"/>
+  <autoFilter ref="A3:M344" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="6">
+      <filters>
+        <filter val="Rakete"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A246:M329">
+    <sortCondition ref="B246:B329"/>
   </sortState>
   <pageMargins left="0.390277777777778" right="0.390277777777778" top="0.390277777777778" bottom="0.390277777777778" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
